--- a/servers/maze_main_server/conf.d/data/maze_equip_pos_lv_v8【迷宫-装备-部位强化等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_equip_pos_lv_v8【迷宫-装备-部位强化等级】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54FC6266-A460-4EE5-8F3D-1E0EF451DF8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD327C64-3907-4706-867A-5B2CC47490B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -127,6 +127,9 @@
     <t>展示属性排序</t>
   </si>
   <si>
+    <t>0:0</t>
+  </si>
+  <si>
     <t>升到下一级需要探险等级</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -135,6 +138,159 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>46200001:10_46700001:2</t>
+  </si>
+  <si>
+    <t>46200001:50_46700001:4</t>
+  </si>
+  <si>
+    <t>46200001:100_46700001:6</t>
+  </si>
+  <si>
+    <t>46200001:150_46700001:8</t>
+  </si>
+  <si>
+    <t>46200001:200_46700001:10</t>
+  </si>
+  <si>
+    <t>46200001:250_46700001:12</t>
+  </si>
+  <si>
+    <t>46200001:300_46700001:14</t>
+  </si>
+  <si>
+    <t>46200001:350_46700001:16</t>
+  </si>
+  <si>
+    <t>46200001:400_46700001:18</t>
+  </si>
+  <si>
+    <t>46200001:450_46700001:20</t>
+  </si>
+  <si>
+    <t>46200001:500_46700001:22</t>
+  </si>
+  <si>
+    <t>46200001:550_46700001:24</t>
+  </si>
+  <si>
+    <t>46200001:600_46700001:26</t>
+  </si>
+  <si>
+    <t>46200001:650_46700001:28</t>
+  </si>
+  <si>
+    <t>46200001:700_46700001:30</t>
+  </si>
+  <si>
+    <t>46200001:750_46700001:32</t>
+  </si>
+  <si>
+    <t>46200001:800_46700001:34</t>
+  </si>
+  <si>
+    <t>46200001:850_46700001:36</t>
+  </si>
+  <si>
+    <t>46200001:900_46700001:38</t>
+  </si>
+  <si>
+    <t>46200001:950_46700001:40</t>
+  </si>
+  <si>
+    <t>46200001:1000_46700001:42</t>
+  </si>
+  <si>
+    <t>46200001:1050_46700001:44</t>
+  </si>
+  <si>
+    <t>46200001:1100_46700001:46</t>
+  </si>
+  <si>
+    <t>46200001:1150_46700001:48</t>
+  </si>
+  <si>
+    <t>46200001:1200_46700001:50</t>
+  </si>
+  <si>
+    <t>46200001:1250_46700001:52</t>
+  </si>
+  <si>
+    <t>46200001:1300_46700001:54</t>
+  </si>
+  <si>
+    <t>46200001:1350_46700001:56</t>
+  </si>
+  <si>
+    <t>46200001:1400_46700001:58</t>
+  </si>
+  <si>
+    <t>46200001:1450_46700001:60</t>
+  </si>
+  <si>
+    <t>46200001:1500_46700001:62</t>
+  </si>
+  <si>
+    <t>46200001:1550_46700001:64</t>
+  </si>
+  <si>
+    <t>46200001:1600_46700001:66</t>
+  </si>
+  <si>
+    <t>46200001:1650_46700001:68</t>
+  </si>
+  <si>
+    <t>46200001:1700_46700001:70</t>
+  </si>
+  <si>
+    <t>46200001:1750_46700001:72</t>
+  </si>
+  <si>
+    <t>46200001:1800_46700001:74</t>
+  </si>
+  <si>
+    <t>46200001:1850_46700001:76</t>
+  </si>
+  <si>
+    <t>46200001:1900_46700001:78</t>
+  </si>
+  <si>
+    <t>46200001:1950_46700001:80</t>
+  </si>
+  <si>
+    <t>46200001:2000_46700001:82</t>
+  </si>
+  <si>
+    <t>46200001:2050_46700001:84</t>
+  </si>
+  <si>
+    <t>46200001:2100_46700001:86</t>
+  </si>
+  <si>
+    <t>46200001:2150_46700001:88</t>
+  </si>
+  <si>
+    <t>46200001:2200_46700001:90</t>
+  </si>
+  <si>
+    <t>46200001:2250_46700001:92</t>
+  </si>
+  <si>
+    <t>46200001:2300_46700001:94</t>
+  </si>
+  <si>
+    <t>46200001:2350_46700001:96</t>
+  </si>
+  <si>
+    <t>46200001:2400_46700001:98</t>
+  </si>
+  <si>
+    <t>46200001:2450_46700001:100</t>
+  </si>
+  <si>
+    <t>46200001:2500_46700001:102</t>
+  </si>
+  <si>
     <t>3010101:2</t>
   </si>
   <si>
@@ -439,162 +595,6 @@
   </si>
   <si>
     <t>3030101:0</t>
-  </si>
-  <si>
-    <t>46200001:20_46700001:2</t>
-  </si>
-  <si>
-    <t>46200001:50_46700001:6</t>
-  </si>
-  <si>
-    <t>46200001:80_46700001:10</t>
-  </si>
-  <si>
-    <t>46200001:120_46700001:15</t>
-  </si>
-  <si>
-    <t>46200001:160_46700001:20</t>
-  </si>
-  <si>
-    <t>46200001:200_46700001:25</t>
-  </si>
-  <si>
-    <t>46200001:250_46700001:30</t>
-  </si>
-  <si>
-    <t>46200001:300_46700001:35</t>
-  </si>
-  <si>
-    <t>46200001:350_46700001:40</t>
-  </si>
-  <si>
-    <t>46200001:400_46700001:45</t>
-  </si>
-  <si>
-    <t>46200001:450_46700001:50</t>
-  </si>
-  <si>
-    <t>46200001:500_46700001:55</t>
-  </si>
-  <si>
-    <t>46200001:550_46700001:60</t>
-  </si>
-  <si>
-    <t>46200001:600_46700001:65</t>
-  </si>
-  <si>
-    <t>46200001:650_46700001:70</t>
-  </si>
-  <si>
-    <t>46200001:700_46700001:75</t>
-  </si>
-  <si>
-    <t>46200001:750_46700001:80</t>
-  </si>
-  <si>
-    <t>46200001:800_46700001:85</t>
-  </si>
-  <si>
-    <t>46200001:850_46700001:90</t>
-  </si>
-  <si>
-    <t>46200001:900_46700001:95</t>
-  </si>
-  <si>
-    <t>46200001:950_46700001:100</t>
-  </si>
-  <si>
-    <t>46200001:1000_46700001:105</t>
-  </si>
-  <si>
-    <t>46200001:1050_46700001:110</t>
-  </si>
-  <si>
-    <t>46200001:1100_46700001:115</t>
-  </si>
-  <si>
-    <t>46200001:1150_46700001:120</t>
-  </si>
-  <si>
-    <t>46200001:1200_46700001:125</t>
-  </si>
-  <si>
-    <t>46200001:1250_46700001:130</t>
-  </si>
-  <si>
-    <t>46200001:1300_46700001:135</t>
-  </si>
-  <si>
-    <t>46200001:1350_46700001:140</t>
-  </si>
-  <si>
-    <t>46200001:1400_46700001:145</t>
-  </si>
-  <si>
-    <t>46200001:1450_46700001:150</t>
-  </si>
-  <si>
-    <t>46200001:1500_46700001:155</t>
-  </si>
-  <si>
-    <t>46200001:1550_46700001:160</t>
-  </si>
-  <si>
-    <t>46200001:1600_46700001:165</t>
-  </si>
-  <si>
-    <t>46200001:1650_46700001:170</t>
-  </si>
-  <si>
-    <t>46200001:1700_46700001:175</t>
-  </si>
-  <si>
-    <t>46200001:1750_46700001:180</t>
-  </si>
-  <si>
-    <t>46200001:1800_46700001:185</t>
-  </si>
-  <si>
-    <t>46200001:1850_46700001:190</t>
-  </si>
-  <si>
-    <t>46200001:1900_46700001:195</t>
-  </si>
-  <si>
-    <t>46200001:1950_46700001:200</t>
-  </si>
-  <si>
-    <t>46200001:2000_46700001:205</t>
-  </si>
-  <si>
-    <t>46200001:2050_46700001:210</t>
-  </si>
-  <si>
-    <t>46200001:2100_46700001:215</t>
-  </si>
-  <si>
-    <t>46200001:2150_46700001:220</t>
-  </si>
-  <si>
-    <t>46200001:2200_46700001:225</t>
-  </si>
-  <si>
-    <t>46200001:2250_46700001:230</t>
-  </si>
-  <si>
-    <t>46200001:2300_46700001:235</t>
-  </si>
-  <si>
-    <t>46200001:2350_46700001:240</t>
-  </si>
-  <si>
-    <t>46200001:2400_46700001:245</t>
-  </si>
-  <si>
-    <t>46200001:2450_46700001:250</t>
-  </si>
-  <si>
-    <t>8101:0</t>
   </si>
 </sst>
 </file>
@@ -996,7 +996,7 @@
         <v>10</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H3" t="s">
         <v>18</v>
@@ -1028,7 +1028,7 @@
         <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H4" t="s">
         <v>21</v>
@@ -1057,16 +1057,16 @@
         <v>0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>128</v>
+        <v>27</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>179</v>
+        <v>24</v>
       </c>
       <c r="I5" t="s">
-        <v>126</v>
+        <v>178</v>
       </c>
       <c r="J5">
         <v>3010101</v>
@@ -1089,16 +1089,16 @@
         <v>0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>128</v>
+        <v>27</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" t="s">
         <v>179</v>
-      </c>
-      <c r="I6" t="s">
-        <v>127</v>
       </c>
       <c r="J6">
         <v>3030101</v>
@@ -1121,16 +1121,16 @@
         <v>0</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>128</v>
+        <v>27</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" t="s">
         <v>179</v>
-      </c>
-      <c r="I7" t="s">
-        <v>127</v>
       </c>
       <c r="J7">
         <v>3030101</v>
@@ -1153,16 +1153,16 @@
         <v>0</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>128</v>
+        <v>27</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" t="s">
         <v>179</v>
-      </c>
-      <c r="I8" t="s">
-        <v>127</v>
       </c>
       <c r="J8">
         <v>3030101</v>
@@ -1185,16 +1185,16 @@
         <v>0</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>128</v>
+        <v>27</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>179</v>
+        <v>24</v>
       </c>
       <c r="I9" t="s">
-        <v>126</v>
+        <v>178</v>
       </c>
       <c r="J9">
         <v>3010101</v>
@@ -1217,16 +1217,16 @@
         <v>0</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>128</v>
+        <v>27</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10" t="s">
         <v>179</v>
-      </c>
-      <c r="I10" t="s">
-        <v>127</v>
       </c>
       <c r="J10">
         <v>3030101</v>
@@ -1249,16 +1249,16 @@
         <v>0</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>128</v>
+        <v>27</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>179</v>
+        <v>24</v>
       </c>
       <c r="I11" t="s">
-        <v>126</v>
+        <v>178</v>
       </c>
       <c r="J11">
         <v>3010101</v>
@@ -1281,16 +1281,16 @@
         <v>0</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>128</v>
+        <v>27</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>179</v>
+        <v>24</v>
       </c>
       <c r="I12" t="s">
-        <v>126</v>
+        <v>178</v>
       </c>
       <c r="J12">
         <v>3010101</v>
@@ -1313,16 +1313,16 @@
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>129</v>
+        <v>28</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>179</v>
+        <v>78</v>
       </c>
       <c r="I13" t="s">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="J13" s="1">
         <v>3010101</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>129</v>
+        <v>28</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>179</v>
+        <v>79</v>
       </c>
       <c r="I14" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="J14" s="1">
         <v>3030101</v>
@@ -1377,16 +1377,16 @@
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>129</v>
+        <v>28</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>179</v>
+        <v>79</v>
       </c>
       <c r="I15" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="J15" s="1">
         <v>3030101</v>
@@ -1409,16 +1409,16 @@
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>129</v>
+        <v>28</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>179</v>
+        <v>79</v>
       </c>
       <c r="I16" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="J16" s="1">
         <v>3030101</v>
@@ -1441,16 +1441,16 @@
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>129</v>
+        <v>28</v>
       </c>
       <c r="G17">
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>179</v>
+        <v>78</v>
       </c>
       <c r="I17" t="s">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="J17" s="1">
         <v>3010101</v>
@@ -1473,16 +1473,16 @@
         <v>1</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>129</v>
+        <v>28</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>179</v>
+        <v>79</v>
       </c>
       <c r="I18" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="J18" s="1">
         <v>3030101</v>
@@ -1505,16 +1505,16 @@
         <v>1</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>129</v>
+        <v>28</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>179</v>
+        <v>78</v>
       </c>
       <c r="I19" t="s">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="J19" s="1">
         <v>3010101</v>
@@ -1537,16 +1537,16 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>129</v>
+        <v>28</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>179</v>
+        <v>78</v>
       </c>
       <c r="I20" t="s">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="J20" s="1">
         <v>3010101</v>
@@ -1569,16 +1569,16 @@
         <v>2</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>130</v>
+        <v>29</v>
       </c>
       <c r="G21">
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>179</v>
+        <v>80</v>
       </c>
       <c r="I21" t="s">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="J21" s="1">
         <v>3010101</v>
@@ -1601,16 +1601,16 @@
         <v>2</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>130</v>
+        <v>29</v>
       </c>
       <c r="G22">
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>179</v>
+        <v>81</v>
       </c>
       <c r="I22" t="s">
-        <v>29</v>
+        <v>81</v>
       </c>
       <c r="J22" s="1">
         <v>3030101</v>
@@ -1633,16 +1633,16 @@
         <v>2</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>130</v>
+        <v>29</v>
       </c>
       <c r="G23">
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>179</v>
+        <v>81</v>
       </c>
       <c r="I23" t="s">
-        <v>29</v>
+        <v>81</v>
       </c>
       <c r="J23" s="1">
         <v>3030101</v>
@@ -1665,16 +1665,16 @@
         <v>2</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>130</v>
+        <v>29</v>
       </c>
       <c r="G24">
         <v>0</v>
       </c>
       <c r="H24" t="s">
-        <v>179</v>
+        <v>81</v>
       </c>
       <c r="I24" t="s">
-        <v>29</v>
+        <v>81</v>
       </c>
       <c r="J24" s="1">
         <v>3030101</v>
@@ -1697,16 +1697,16 @@
         <v>2</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>130</v>
+        <v>29</v>
       </c>
       <c r="G25">
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>179</v>
+        <v>80</v>
       </c>
       <c r="I25" t="s">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="J25" s="1">
         <v>3010101</v>
@@ -1729,16 +1729,16 @@
         <v>2</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>130</v>
+        <v>29</v>
       </c>
       <c r="G26">
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>179</v>
+        <v>81</v>
       </c>
       <c r="I26" t="s">
-        <v>29</v>
+        <v>81</v>
       </c>
       <c r="J26" s="1">
         <v>3030101</v>
@@ -1761,16 +1761,16 @@
         <v>2</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>130</v>
+        <v>29</v>
       </c>
       <c r="G27">
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>179</v>
+        <v>80</v>
       </c>
       <c r="I27" t="s">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="J27" s="1">
         <v>3010101</v>
@@ -1793,16 +1793,16 @@
         <v>2</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>130</v>
+        <v>29</v>
       </c>
       <c r="G28">
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>179</v>
+        <v>80</v>
       </c>
       <c r="I28" t="s">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="J28" s="1">
         <v>3010101</v>
@@ -1825,16 +1825,16 @@
         <v>3</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>131</v>
+        <v>30</v>
       </c>
       <c r="G29">
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="I29" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="J29" s="1">
         <v>3010101</v>
@@ -1857,16 +1857,16 @@
         <v>3</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>131</v>
+        <v>30</v>
       </c>
       <c r="G30">
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>179</v>
+        <v>83</v>
       </c>
       <c r="I30" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="J30" s="1">
         <v>3030101</v>
@@ -1889,16 +1889,16 @@
         <v>3</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>131</v>
+        <v>30</v>
       </c>
       <c r="G31">
         <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>179</v>
+        <v>83</v>
       </c>
       <c r="I31" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="J31" s="1">
         <v>3030101</v>
@@ -1921,16 +1921,16 @@
         <v>3</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>131</v>
+        <v>30</v>
       </c>
       <c r="G32">
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>179</v>
+        <v>83</v>
       </c>
       <c r="I32" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="J32" s="1">
         <v>3030101</v>
@@ -1953,16 +1953,16 @@
         <v>3</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>131</v>
+        <v>30</v>
       </c>
       <c r="G33">
         <v>0</v>
       </c>
       <c r="H33" t="s">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="I33" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="J33" s="1">
         <v>3010101</v>
@@ -1985,16 +1985,16 @@
         <v>3</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>131</v>
+        <v>30</v>
       </c>
       <c r="G34">
         <v>0</v>
       </c>
       <c r="H34" t="s">
-        <v>179</v>
+        <v>83</v>
       </c>
       <c r="I34" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="J34" s="1">
         <v>3030101</v>
@@ -2017,16 +2017,16 @@
         <v>3</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>131</v>
+        <v>30</v>
       </c>
       <c r="G35">
         <v>0</v>
       </c>
       <c r="H35" t="s">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="I35" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="J35" s="1">
         <v>3010101</v>
@@ -2049,16 +2049,16 @@
         <v>3</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>131</v>
+        <v>30</v>
       </c>
       <c r="G36">
         <v>0</v>
       </c>
       <c r="H36" t="s">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="I36" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="J36" s="1">
         <v>3010101</v>
@@ -2081,16 +2081,16 @@
         <v>4</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>132</v>
+        <v>31</v>
       </c>
       <c r="G37">
         <v>0</v>
       </c>
       <c r="H37" t="s">
-        <v>179</v>
+        <v>84</v>
       </c>
       <c r="I37" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="J37" s="1">
         <v>3010101</v>
@@ -2113,16 +2113,16 @@
         <v>4</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>132</v>
+        <v>31</v>
       </c>
       <c r="G38">
         <v>0</v>
       </c>
       <c r="H38" t="s">
-        <v>179</v>
+        <v>85</v>
       </c>
       <c r="I38" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="J38" s="1">
         <v>3030101</v>
@@ -2145,16 +2145,16 @@
         <v>4</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>132</v>
+        <v>31</v>
       </c>
       <c r="G39">
         <v>0</v>
       </c>
       <c r="H39" t="s">
-        <v>179</v>
+        <v>85</v>
       </c>
       <c r="I39" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="J39" s="1">
         <v>3030101</v>
@@ -2177,16 +2177,16 @@
         <v>4</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>132</v>
+        <v>31</v>
       </c>
       <c r="G40">
         <v>0</v>
       </c>
       <c r="H40" t="s">
-        <v>179</v>
+        <v>85</v>
       </c>
       <c r="I40" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="J40" s="1">
         <v>3030101</v>
@@ -2209,16 +2209,16 @@
         <v>4</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>132</v>
+        <v>31</v>
       </c>
       <c r="G41">
         <v>0</v>
       </c>
       <c r="H41" t="s">
-        <v>179</v>
+        <v>84</v>
       </c>
       <c r="I41" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="J41" s="1">
         <v>3010101</v>
@@ -2241,16 +2241,16 @@
         <v>4</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>132</v>
+        <v>31</v>
       </c>
       <c r="G42">
         <v>0</v>
       </c>
       <c r="H42" t="s">
-        <v>179</v>
+        <v>85</v>
       </c>
       <c r="I42" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="J42" s="1">
         <v>3030101</v>
@@ -2273,16 +2273,16 @@
         <v>4</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>132</v>
+        <v>31</v>
       </c>
       <c r="G43">
         <v>0</v>
       </c>
       <c r="H43" t="s">
-        <v>179</v>
+        <v>84</v>
       </c>
       <c r="I43" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="J43" s="1">
         <v>3010101</v>
@@ -2305,16 +2305,16 @@
         <v>4</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>132</v>
+        <v>31</v>
       </c>
       <c r="G44">
         <v>0</v>
       </c>
       <c r="H44" t="s">
-        <v>179</v>
+        <v>84</v>
       </c>
       <c r="I44" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="J44" s="1">
         <v>3010101</v>
@@ -2337,16 +2337,16 @@
         <v>5</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>133</v>
+        <v>32</v>
       </c>
       <c r="G45">
         <v>0</v>
       </c>
       <c r="H45" t="s">
-        <v>179</v>
+        <v>86</v>
       </c>
       <c r="I45" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="J45" s="1">
         <v>3010101</v>
@@ -2369,16 +2369,16 @@
         <v>5</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>133</v>
+        <v>32</v>
       </c>
       <c r="G46">
         <v>0</v>
       </c>
       <c r="H46" t="s">
-        <v>179</v>
+        <v>87</v>
       </c>
       <c r="I46" t="s">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="J46" s="1">
         <v>3030101</v>
@@ -2401,16 +2401,16 @@
         <v>5</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>133</v>
+        <v>32</v>
       </c>
       <c r="G47">
         <v>0</v>
       </c>
       <c r="H47" t="s">
-        <v>179</v>
+        <v>87</v>
       </c>
       <c r="I47" t="s">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="J47" s="1">
         <v>3030101</v>
@@ -2433,16 +2433,16 @@
         <v>5</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>133</v>
+        <v>32</v>
       </c>
       <c r="G48">
         <v>0</v>
       </c>
       <c r="H48" t="s">
-        <v>179</v>
+        <v>87</v>
       </c>
       <c r="I48" t="s">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="J48" s="1">
         <v>3030101</v>
@@ -2465,16 +2465,16 @@
         <v>5</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>133</v>
+        <v>32</v>
       </c>
       <c r="G49">
         <v>0</v>
       </c>
       <c r="H49" t="s">
-        <v>179</v>
+        <v>86</v>
       </c>
       <c r="I49" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="J49" s="1">
         <v>3010101</v>
@@ -2497,16 +2497,16 @@
         <v>5</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>133</v>
+        <v>32</v>
       </c>
       <c r="G50">
         <v>0</v>
       </c>
       <c r="H50" t="s">
-        <v>179</v>
+        <v>87</v>
       </c>
       <c r="I50" t="s">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="J50" s="1">
         <v>3030101</v>
@@ -2529,16 +2529,16 @@
         <v>5</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>133</v>
+        <v>32</v>
       </c>
       <c r="G51">
         <v>0</v>
       </c>
       <c r="H51" t="s">
-        <v>179</v>
+        <v>86</v>
       </c>
       <c r="I51" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="J51" s="1">
         <v>3010101</v>
@@ -2561,16 +2561,16 @@
         <v>5</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>133</v>
+        <v>32</v>
       </c>
       <c r="G52">
         <v>0</v>
       </c>
       <c r="H52" t="s">
-        <v>179</v>
+        <v>86</v>
       </c>
       <c r="I52" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="J52" s="1">
         <v>3010101</v>
@@ -2593,16 +2593,16 @@
         <v>6</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>134</v>
+        <v>33</v>
       </c>
       <c r="G53">
         <v>0</v>
       </c>
       <c r="H53" t="s">
-        <v>179</v>
+        <v>88</v>
       </c>
       <c r="I53" t="s">
-        <v>36</v>
+        <v>88</v>
       </c>
       <c r="J53" s="1">
         <v>3010101</v>
@@ -2625,16 +2625,16 @@
         <v>6</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>134</v>
+        <v>33</v>
       </c>
       <c r="G54">
         <v>0</v>
       </c>
       <c r="H54" t="s">
-        <v>179</v>
+        <v>89</v>
       </c>
       <c r="I54" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="J54" s="1">
         <v>3030101</v>
@@ -2657,16 +2657,16 @@
         <v>6</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>134</v>
+        <v>33</v>
       </c>
       <c r="G55">
         <v>0</v>
       </c>
       <c r="H55" t="s">
-        <v>179</v>
+        <v>89</v>
       </c>
       <c r="I55" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="J55" s="1">
         <v>3030101</v>
@@ -2689,16 +2689,16 @@
         <v>6</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>134</v>
+        <v>33</v>
       </c>
       <c r="G56">
         <v>0</v>
       </c>
       <c r="H56" t="s">
-        <v>179</v>
+        <v>89</v>
       </c>
       <c r="I56" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="J56" s="1">
         <v>3030101</v>
@@ -2721,16 +2721,16 @@
         <v>6</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>134</v>
+        <v>33</v>
       </c>
       <c r="G57">
         <v>0</v>
       </c>
       <c r="H57" t="s">
-        <v>179</v>
+        <v>88</v>
       </c>
       <c r="I57" t="s">
-        <v>36</v>
+        <v>88</v>
       </c>
       <c r="J57" s="1">
         <v>3010101</v>
@@ -2753,16 +2753,16 @@
         <v>6</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>134</v>
+        <v>33</v>
       </c>
       <c r="G58">
         <v>0</v>
       </c>
       <c r="H58" t="s">
-        <v>179</v>
+        <v>89</v>
       </c>
       <c r="I58" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="J58" s="1">
         <v>3030101</v>
@@ -2785,16 +2785,16 @@
         <v>6</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>134</v>
+        <v>33</v>
       </c>
       <c r="G59">
         <v>0</v>
       </c>
       <c r="H59" t="s">
-        <v>179</v>
+        <v>88</v>
       </c>
       <c r="I59" t="s">
-        <v>36</v>
+        <v>88</v>
       </c>
       <c r="J59" s="1">
         <v>3010101</v>
@@ -2817,16 +2817,16 @@
         <v>6</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>134</v>
+        <v>33</v>
       </c>
       <c r="G60">
         <v>0</v>
       </c>
       <c r="H60" t="s">
-        <v>179</v>
+        <v>88</v>
       </c>
       <c r="I60" t="s">
-        <v>36</v>
+        <v>88</v>
       </c>
       <c r="J60" s="1">
         <v>3010101</v>
@@ -2849,16 +2849,16 @@
         <v>7</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>135</v>
+        <v>34</v>
       </c>
       <c r="G61">
         <v>0</v>
       </c>
       <c r="H61" t="s">
-        <v>179</v>
+        <v>90</v>
       </c>
       <c r="I61" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="J61" s="1">
         <v>3010101</v>
@@ -2881,16 +2881,16 @@
         <v>7</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>135</v>
+        <v>34</v>
       </c>
       <c r="G62">
         <v>0</v>
       </c>
       <c r="H62" t="s">
-        <v>179</v>
+        <v>91</v>
       </c>
       <c r="I62" t="s">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="J62" s="1">
         <v>3030101</v>
@@ -2913,16 +2913,16 @@
         <v>7</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>135</v>
+        <v>34</v>
       </c>
       <c r="G63">
         <v>0</v>
       </c>
       <c r="H63" t="s">
-        <v>179</v>
+        <v>91</v>
       </c>
       <c r="I63" t="s">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="J63" s="1">
         <v>3030101</v>
@@ -2945,16 +2945,16 @@
         <v>7</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>135</v>
+        <v>34</v>
       </c>
       <c r="G64">
         <v>0</v>
       </c>
       <c r="H64" t="s">
-        <v>179</v>
+        <v>91</v>
       </c>
       <c r="I64" t="s">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="J64" s="1">
         <v>3030101</v>
@@ -2977,16 +2977,16 @@
         <v>7</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>135</v>
+        <v>34</v>
       </c>
       <c r="G65">
         <v>0</v>
       </c>
       <c r="H65" t="s">
-        <v>179</v>
+        <v>90</v>
       </c>
       <c r="I65" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="J65" s="1">
         <v>3010101</v>
@@ -3009,16 +3009,16 @@
         <v>7</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>135</v>
+        <v>34</v>
       </c>
       <c r="G66">
         <v>0</v>
       </c>
       <c r="H66" t="s">
-        <v>179</v>
+        <v>91</v>
       </c>
       <c r="I66" t="s">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="J66" s="1">
         <v>3030101</v>
@@ -3041,16 +3041,16 @@
         <v>7</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>135</v>
+        <v>34</v>
       </c>
       <c r="G67">
         <v>0</v>
       </c>
       <c r="H67" t="s">
-        <v>179</v>
+        <v>90</v>
       </c>
       <c r="I67" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="J67" s="1">
         <v>3010101</v>
@@ -3073,16 +3073,16 @@
         <v>7</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>135</v>
+        <v>34</v>
       </c>
       <c r="G68">
         <v>0</v>
       </c>
       <c r="H68" t="s">
-        <v>179</v>
+        <v>90</v>
       </c>
       <c r="I68" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="J68" s="1">
         <v>3010101</v>
@@ -3105,16 +3105,16 @@
         <v>8</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>136</v>
+        <v>35</v>
       </c>
       <c r="G69">
         <v>0</v>
       </c>
       <c r="H69" t="s">
-        <v>179</v>
+        <v>92</v>
       </c>
       <c r="I69" t="s">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="J69" s="1">
         <v>3010101</v>
@@ -3137,16 +3137,16 @@
         <v>8</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>136</v>
+        <v>35</v>
       </c>
       <c r="G70">
         <v>0</v>
       </c>
       <c r="H70" t="s">
-        <v>179</v>
+        <v>93</v>
       </c>
       <c r="I70" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="J70" s="1">
         <v>3030101</v>
@@ -3169,16 +3169,16 @@
         <v>8</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>136</v>
+        <v>35</v>
       </c>
       <c r="G71">
         <v>0</v>
       </c>
       <c r="H71" t="s">
-        <v>179</v>
+        <v>93</v>
       </c>
       <c r="I71" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="J71" s="1">
         <v>3030101</v>
@@ -3201,16 +3201,16 @@
         <v>8</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>136</v>
+        <v>35</v>
       </c>
       <c r="G72">
         <v>0</v>
       </c>
       <c r="H72" t="s">
-        <v>179</v>
+        <v>93</v>
       </c>
       <c r="I72" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="J72" s="1">
         <v>3030101</v>
@@ -3233,16 +3233,16 @@
         <v>8</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>136</v>
+        <v>35</v>
       </c>
       <c r="G73">
         <v>0</v>
       </c>
       <c r="H73" t="s">
-        <v>179</v>
+        <v>92</v>
       </c>
       <c r="I73" t="s">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="J73" s="1">
         <v>3010101</v>
@@ -3265,16 +3265,16 @@
         <v>8</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>136</v>
+        <v>35</v>
       </c>
       <c r="G74">
         <v>0</v>
       </c>
       <c r="H74" t="s">
-        <v>179</v>
+        <v>93</v>
       </c>
       <c r="I74" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="J74" s="1">
         <v>3030101</v>
@@ -3297,16 +3297,16 @@
         <v>8</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>136</v>
+        <v>35</v>
       </c>
       <c r="G75">
         <v>0</v>
       </c>
       <c r="H75" t="s">
-        <v>179</v>
+        <v>92</v>
       </c>
       <c r="I75" t="s">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="J75" s="1">
         <v>3010101</v>
@@ -3329,16 +3329,16 @@
         <v>8</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>136</v>
+        <v>35</v>
       </c>
       <c r="G76">
         <v>0</v>
       </c>
       <c r="H76" t="s">
-        <v>179</v>
+        <v>92</v>
       </c>
       <c r="I76" t="s">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="J76" s="1">
         <v>3010101</v>
@@ -3361,16 +3361,16 @@
         <v>9</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>137</v>
+        <v>36</v>
       </c>
       <c r="G77">
         <v>0</v>
       </c>
       <c r="H77" t="s">
-        <v>179</v>
+        <v>94</v>
       </c>
       <c r="I77" t="s">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="J77" s="1">
         <v>3010101</v>
@@ -3393,16 +3393,16 @@
         <v>9</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>137</v>
+        <v>36</v>
       </c>
       <c r="G78">
         <v>0</v>
       </c>
       <c r="H78" t="s">
-        <v>179</v>
+        <v>95</v>
       </c>
       <c r="I78" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="J78" s="1">
         <v>3030101</v>
@@ -3425,16 +3425,16 @@
         <v>9</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>137</v>
+        <v>36</v>
       </c>
       <c r="G79">
         <v>0</v>
       </c>
       <c r="H79" t="s">
-        <v>179</v>
+        <v>95</v>
       </c>
       <c r="I79" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="J79" s="1">
         <v>3030101</v>
@@ -3457,16 +3457,16 @@
         <v>9</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>137</v>
+        <v>36</v>
       </c>
       <c r="G80">
         <v>0</v>
       </c>
       <c r="H80" t="s">
-        <v>179</v>
+        <v>95</v>
       </c>
       <c r="I80" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="J80" s="1">
         <v>3030101</v>
@@ -3489,16 +3489,16 @@
         <v>9</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>137</v>
+        <v>36</v>
       </c>
       <c r="G81">
         <v>0</v>
       </c>
       <c r="H81" t="s">
-        <v>179</v>
+        <v>94</v>
       </c>
       <c r="I81" t="s">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="J81" s="1">
         <v>3010101</v>
@@ -3521,16 +3521,16 @@
         <v>9</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>137</v>
+        <v>36</v>
       </c>
       <c r="G82">
         <v>0</v>
       </c>
       <c r="H82" t="s">
-        <v>179</v>
+        <v>95</v>
       </c>
       <c r="I82" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="J82" s="1">
         <v>3030101</v>
@@ -3553,16 +3553,16 @@
         <v>9</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>137</v>
+        <v>36</v>
       </c>
       <c r="G83">
         <v>0</v>
       </c>
       <c r="H83" t="s">
-        <v>179</v>
+        <v>94</v>
       </c>
       <c r="I83" t="s">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="J83" s="1">
         <v>3010101</v>
@@ -3585,16 +3585,16 @@
         <v>9</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>137</v>
+        <v>36</v>
       </c>
       <c r="G84">
         <v>0</v>
       </c>
       <c r="H84" t="s">
-        <v>179</v>
+        <v>94</v>
       </c>
       <c r="I84" t="s">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="J84" s="1">
         <v>3010101</v>
@@ -3617,16 +3617,16 @@
         <v>10</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>138</v>
+        <v>37</v>
       </c>
       <c r="G85">
         <v>10</v>
       </c>
       <c r="H85" t="s">
-        <v>179</v>
+        <v>96</v>
       </c>
       <c r="I85" t="s">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="J85" s="1">
         <v>3010101</v>
@@ -3649,16 +3649,16 @@
         <v>10</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>138</v>
+        <v>37</v>
       </c>
       <c r="G86">
         <v>10</v>
       </c>
       <c r="H86" t="s">
-        <v>179</v>
+        <v>97</v>
       </c>
       <c r="I86" t="s">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="J86" s="1">
         <v>3030101</v>
@@ -3681,16 +3681,16 @@
         <v>10</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>138</v>
+        <v>37</v>
       </c>
       <c r="G87">
         <v>10</v>
       </c>
       <c r="H87" t="s">
-        <v>179</v>
+        <v>97</v>
       </c>
       <c r="I87" t="s">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="J87" s="1">
         <v>3030101</v>
@@ -3713,16 +3713,16 @@
         <v>10</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>138</v>
+        <v>37</v>
       </c>
       <c r="G88">
         <v>10</v>
       </c>
       <c r="H88" t="s">
-        <v>179</v>
+        <v>97</v>
       </c>
       <c r="I88" t="s">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="J88" s="1">
         <v>3030101</v>
@@ -3745,16 +3745,16 @@
         <v>10</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>138</v>
+        <v>37</v>
       </c>
       <c r="G89">
         <v>10</v>
       </c>
       <c r="H89" t="s">
-        <v>179</v>
+        <v>96</v>
       </c>
       <c r="I89" t="s">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="J89" s="1">
         <v>3010101</v>
@@ -3777,16 +3777,16 @@
         <v>10</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>138</v>
+        <v>37</v>
       </c>
       <c r="G90">
         <v>10</v>
       </c>
       <c r="H90" t="s">
-        <v>179</v>
+        <v>97</v>
       </c>
       <c r="I90" t="s">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="J90" s="1">
         <v>3030101</v>
@@ -3809,16 +3809,16 @@
         <v>10</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>138</v>
+        <v>37</v>
       </c>
       <c r="G91">
         <v>10</v>
       </c>
       <c r="H91" t="s">
-        <v>179</v>
+        <v>96</v>
       </c>
       <c r="I91" t="s">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="J91" s="1">
         <v>3010101</v>
@@ -3841,16 +3841,16 @@
         <v>10</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>138</v>
+        <v>37</v>
       </c>
       <c r="G92">
         <v>10</v>
       </c>
       <c r="H92" t="s">
-        <v>179</v>
+        <v>96</v>
       </c>
       <c r="I92" t="s">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="J92" s="1">
         <v>3010101</v>
@@ -3873,16 +3873,16 @@
         <v>11</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="G93">
         <v>10</v>
       </c>
       <c r="H93" t="s">
-        <v>179</v>
+        <v>98</v>
       </c>
       <c r="I93" t="s">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="J93" s="1">
         <v>3010101</v>
@@ -3905,16 +3905,16 @@
         <v>11</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="G94">
         <v>10</v>
       </c>
       <c r="H94" t="s">
-        <v>179</v>
+        <v>99</v>
       </c>
       <c r="I94" t="s">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="J94" s="1">
         <v>3030101</v>
@@ -3937,16 +3937,16 @@
         <v>11</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="G95">
         <v>10</v>
       </c>
       <c r="H95" t="s">
-        <v>179</v>
+        <v>99</v>
       </c>
       <c r="I95" t="s">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="J95" s="1">
         <v>3030101</v>
@@ -3969,16 +3969,16 @@
         <v>11</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="G96">
         <v>10</v>
       </c>
       <c r="H96" t="s">
-        <v>179</v>
+        <v>99</v>
       </c>
       <c r="I96" t="s">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="J96" s="1">
         <v>3030101</v>
@@ -4001,16 +4001,16 @@
         <v>11</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="G97">
         <v>10</v>
       </c>
       <c r="H97" t="s">
-        <v>179</v>
+        <v>98</v>
       </c>
       <c r="I97" t="s">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="J97" s="1">
         <v>3010101</v>
@@ -4033,16 +4033,16 @@
         <v>11</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="G98">
         <v>10</v>
       </c>
       <c r="H98" t="s">
-        <v>179</v>
+        <v>99</v>
       </c>
       <c r="I98" t="s">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="J98" s="1">
         <v>3030101</v>
@@ -4065,16 +4065,16 @@
         <v>11</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="G99">
         <v>10</v>
       </c>
       <c r="H99" t="s">
-        <v>179</v>
+        <v>98</v>
       </c>
       <c r="I99" t="s">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="J99" s="1">
         <v>3010101</v>
@@ -4097,16 +4097,16 @@
         <v>11</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="G100">
         <v>10</v>
       </c>
       <c r="H100" t="s">
-        <v>179</v>
+        <v>98</v>
       </c>
       <c r="I100" t="s">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="J100" s="1">
         <v>3010101</v>
@@ -4129,16 +4129,16 @@
         <v>12</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
       <c r="G101">
         <v>10</v>
       </c>
       <c r="H101" t="s">
-        <v>179</v>
+        <v>100</v>
       </c>
       <c r="I101" t="s">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="J101" s="1">
         <v>3010101</v>
@@ -4161,16 +4161,16 @@
         <v>12</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
       <c r="G102">
         <v>10</v>
       </c>
       <c r="H102" t="s">
-        <v>179</v>
+        <v>101</v>
       </c>
       <c r="I102" t="s">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="J102" s="1">
         <v>3030101</v>
@@ -4193,16 +4193,16 @@
         <v>12</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
       <c r="G103">
         <v>10</v>
       </c>
       <c r="H103" t="s">
-        <v>179</v>
+        <v>101</v>
       </c>
       <c r="I103" t="s">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="J103" s="1">
         <v>3030101</v>
@@ -4225,16 +4225,16 @@
         <v>12</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
       <c r="G104">
         <v>10</v>
       </c>
       <c r="H104" t="s">
-        <v>179</v>
+        <v>101</v>
       </c>
       <c r="I104" t="s">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="J104" s="1">
         <v>3030101</v>
@@ -4257,16 +4257,16 @@
         <v>12</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
       <c r="G105">
         <v>10</v>
       </c>
       <c r="H105" t="s">
-        <v>179</v>
+        <v>100</v>
       </c>
       <c r="I105" t="s">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="J105" s="1">
         <v>3010101</v>
@@ -4289,16 +4289,16 @@
         <v>12</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
       <c r="G106">
         <v>10</v>
       </c>
       <c r="H106" t="s">
-        <v>179</v>
+        <v>101</v>
       </c>
       <c r="I106" t="s">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="J106" s="1">
         <v>3030101</v>
@@ -4321,16 +4321,16 @@
         <v>12</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
       <c r="G107">
         <v>10</v>
       </c>
       <c r="H107" t="s">
-        <v>179</v>
+        <v>100</v>
       </c>
       <c r="I107" t="s">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="J107" s="1">
         <v>3010101</v>
@@ -4353,16 +4353,16 @@
         <v>12</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
       <c r="G108">
         <v>10</v>
       </c>
       <c r="H108" t="s">
-        <v>179</v>
+        <v>100</v>
       </c>
       <c r="I108" t="s">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="J108" s="1">
         <v>3010101</v>
@@ -4385,16 +4385,16 @@
         <v>13</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>141</v>
+        <v>40</v>
       </c>
       <c r="G109">
         <v>10</v>
       </c>
       <c r="H109" t="s">
-        <v>179</v>
+        <v>102</v>
       </c>
       <c r="I109" t="s">
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="J109" s="1">
         <v>3010101</v>
@@ -4417,16 +4417,16 @@
         <v>13</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>141</v>
+        <v>40</v>
       </c>
       <c r="G110">
         <v>10</v>
       </c>
       <c r="H110" t="s">
-        <v>179</v>
+        <v>103</v>
       </c>
       <c r="I110" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="J110" s="1">
         <v>3030101</v>
@@ -4449,16 +4449,16 @@
         <v>13</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>141</v>
+        <v>40</v>
       </c>
       <c r="G111">
         <v>10</v>
       </c>
       <c r="H111" t="s">
-        <v>179</v>
+        <v>103</v>
       </c>
       <c r="I111" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="J111" s="1">
         <v>3030101</v>
@@ -4481,16 +4481,16 @@
         <v>13</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>141</v>
+        <v>40</v>
       </c>
       <c r="G112">
         <v>10</v>
       </c>
       <c r="H112" t="s">
-        <v>179</v>
+        <v>103</v>
       </c>
       <c r="I112" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="J112" s="1">
         <v>3030101</v>
@@ -4513,16 +4513,16 @@
         <v>13</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>141</v>
+        <v>40</v>
       </c>
       <c r="G113">
         <v>10</v>
       </c>
       <c r="H113" t="s">
-        <v>179</v>
+        <v>102</v>
       </c>
       <c r="I113" t="s">
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="J113" s="1">
         <v>3010101</v>
@@ -4545,16 +4545,16 @@
         <v>13</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>141</v>
+        <v>40</v>
       </c>
       <c r="G114">
         <v>10</v>
       </c>
       <c r="H114" t="s">
-        <v>179</v>
+        <v>103</v>
       </c>
       <c r="I114" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="J114" s="1">
         <v>3030101</v>
@@ -4577,16 +4577,16 @@
         <v>13</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>141</v>
+        <v>40</v>
       </c>
       <c r="G115">
         <v>10</v>
       </c>
       <c r="H115" t="s">
-        <v>179</v>
+        <v>102</v>
       </c>
       <c r="I115" t="s">
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="J115" s="1">
         <v>3010101</v>
@@ -4609,16 +4609,16 @@
         <v>13</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>141</v>
+        <v>40</v>
       </c>
       <c r="G116">
         <v>10</v>
       </c>
       <c r="H116" t="s">
-        <v>179</v>
+        <v>102</v>
       </c>
       <c r="I116" t="s">
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="J116" s="1">
         <v>3010101</v>
@@ -4641,16 +4641,16 @@
         <v>14</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="G117">
         <v>10</v>
       </c>
       <c r="H117" t="s">
-        <v>179</v>
+        <v>104</v>
       </c>
       <c r="I117" t="s">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="J117" s="1">
         <v>3010101</v>
@@ -4673,16 +4673,16 @@
         <v>14</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="G118">
         <v>10</v>
       </c>
       <c r="H118" t="s">
-        <v>179</v>
+        <v>105</v>
       </c>
       <c r="I118" t="s">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="J118" s="1">
         <v>3030101</v>
@@ -4705,16 +4705,16 @@
         <v>14</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="G119">
         <v>10</v>
       </c>
       <c r="H119" t="s">
-        <v>179</v>
+        <v>105</v>
       </c>
       <c r="I119" t="s">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="J119" s="1">
         <v>3030101</v>
@@ -4737,16 +4737,16 @@
         <v>14</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="G120">
         <v>10</v>
       </c>
       <c r="H120" t="s">
-        <v>179</v>
+        <v>105</v>
       </c>
       <c r="I120" t="s">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="J120" s="1">
         <v>3030101</v>
@@ -4769,16 +4769,16 @@
         <v>14</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="G121">
         <v>10</v>
       </c>
       <c r="H121" t="s">
-        <v>179</v>
+        <v>104</v>
       </c>
       <c r="I121" t="s">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="J121" s="1">
         <v>3010101</v>
@@ -4801,16 +4801,16 @@
         <v>14</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="G122">
         <v>10</v>
       </c>
       <c r="H122" t="s">
-        <v>179</v>
+        <v>105</v>
       </c>
       <c r="I122" t="s">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="J122" s="1">
         <v>3030101</v>
@@ -4833,16 +4833,16 @@
         <v>14</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="G123">
         <v>10</v>
       </c>
       <c r="H123" t="s">
-        <v>179</v>
+        <v>104</v>
       </c>
       <c r="I123" t="s">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="J123" s="1">
         <v>3010101</v>
@@ -4865,16 +4865,16 @@
         <v>14</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="G124">
         <v>10</v>
       </c>
       <c r="H124" t="s">
-        <v>179</v>
+        <v>104</v>
       </c>
       <c r="I124" t="s">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="J124" s="1">
         <v>3010101</v>
@@ -4897,16 +4897,16 @@
         <v>15</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>143</v>
+        <v>42</v>
       </c>
       <c r="G125">
         <v>10</v>
       </c>
       <c r="H125" t="s">
-        <v>179</v>
+        <v>106</v>
       </c>
       <c r="I125" t="s">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="J125" s="1">
         <v>3010101</v>
@@ -4929,16 +4929,16 @@
         <v>15</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>143</v>
+        <v>42</v>
       </c>
       <c r="G126">
         <v>10</v>
       </c>
       <c r="H126" t="s">
-        <v>179</v>
+        <v>107</v>
       </c>
       <c r="I126" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
       <c r="J126" s="1">
         <v>3030101</v>
@@ -4961,16 +4961,16 @@
         <v>15</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>143</v>
+        <v>42</v>
       </c>
       <c r="G127">
         <v>10</v>
       </c>
       <c r="H127" t="s">
-        <v>179</v>
+        <v>107</v>
       </c>
       <c r="I127" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
       <c r="J127" s="1">
         <v>3030101</v>
@@ -4993,16 +4993,16 @@
         <v>15</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>143</v>
+        <v>42</v>
       </c>
       <c r="G128">
         <v>10</v>
       </c>
       <c r="H128" t="s">
-        <v>179</v>
+        <v>107</v>
       </c>
       <c r="I128" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
       <c r="J128" s="1">
         <v>3030101</v>
@@ -5025,16 +5025,16 @@
         <v>15</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>143</v>
+        <v>42</v>
       </c>
       <c r="G129">
         <v>10</v>
       </c>
       <c r="H129" t="s">
-        <v>179</v>
+        <v>106</v>
       </c>
       <c r="I129" t="s">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="J129" s="1">
         <v>3010101</v>
@@ -5057,16 +5057,16 @@
         <v>15</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>143</v>
+        <v>42</v>
       </c>
       <c r="G130">
         <v>10</v>
       </c>
       <c r="H130" t="s">
-        <v>179</v>
+        <v>107</v>
       </c>
       <c r="I130" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
       <c r="J130" s="1">
         <v>3030101</v>
@@ -5089,16 +5089,16 @@
         <v>15</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>143</v>
+        <v>42</v>
       </c>
       <c r="G131">
         <v>10</v>
       </c>
       <c r="H131" t="s">
-        <v>179</v>
+        <v>106</v>
       </c>
       <c r="I131" t="s">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="J131" s="1">
         <v>3010101</v>
@@ -5121,16 +5121,16 @@
         <v>15</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>143</v>
+        <v>42</v>
       </c>
       <c r="G132">
         <v>10</v>
       </c>
       <c r="H132" t="s">
-        <v>179</v>
+        <v>106</v>
       </c>
       <c r="I132" t="s">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="J132" s="1">
         <v>3010101</v>
@@ -5153,16 +5153,16 @@
         <v>16</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
       <c r="G133">
         <v>10</v>
       </c>
       <c r="H133" t="s">
-        <v>179</v>
+        <v>108</v>
       </c>
       <c r="I133" t="s">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="J133" s="1">
         <v>3010101</v>
@@ -5185,16 +5185,16 @@
         <v>16</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
       <c r="G134">
         <v>10</v>
       </c>
       <c r="H134" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="I134" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="J134" s="1">
         <v>3030101</v>
@@ -5217,16 +5217,16 @@
         <v>16</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
       <c r="G135">
         <v>10</v>
       </c>
       <c r="H135" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="I135" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="J135" s="1">
         <v>3030101</v>
@@ -5249,16 +5249,16 @@
         <v>16</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
       <c r="G136">
         <v>10</v>
       </c>
       <c r="H136" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="I136" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="J136" s="1">
         <v>3030101</v>
@@ -5281,16 +5281,16 @@
         <v>16</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
       <c r="G137">
         <v>10</v>
       </c>
       <c r="H137" t="s">
-        <v>179</v>
+        <v>108</v>
       </c>
       <c r="I137" t="s">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="J137" s="1">
         <v>3010101</v>
@@ -5313,16 +5313,16 @@
         <v>16</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
       <c r="G138">
         <v>10</v>
       </c>
       <c r="H138" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="I138" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="J138" s="1">
         <v>3030101</v>
@@ -5345,16 +5345,16 @@
         <v>16</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
       <c r="G139">
         <v>10</v>
       </c>
       <c r="H139" t="s">
-        <v>179</v>
+        <v>108</v>
       </c>
       <c r="I139" t="s">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="J139" s="1">
         <v>3010101</v>
@@ -5377,16 +5377,16 @@
         <v>16</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
       <c r="G140">
         <v>10</v>
       </c>
       <c r="H140" t="s">
-        <v>179</v>
+        <v>108</v>
       </c>
       <c r="I140" t="s">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="J140" s="1">
         <v>3010101</v>
@@ -5409,16 +5409,16 @@
         <v>17</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>145</v>
+        <v>44</v>
       </c>
       <c r="G141">
         <v>10</v>
       </c>
       <c r="H141" t="s">
-        <v>179</v>
+        <v>110</v>
       </c>
       <c r="I141" t="s">
-        <v>58</v>
+        <v>110</v>
       </c>
       <c r="J141" s="1">
         <v>3010101</v>
@@ -5441,16 +5441,16 @@
         <v>17</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>145</v>
+        <v>44</v>
       </c>
       <c r="G142">
         <v>10</v>
       </c>
       <c r="H142" t="s">
-        <v>179</v>
+        <v>111</v>
       </c>
       <c r="I142" t="s">
-        <v>59</v>
+        <v>111</v>
       </c>
       <c r="J142" s="1">
         <v>3030101</v>
@@ -5473,16 +5473,16 @@
         <v>17</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>145</v>
+        <v>44</v>
       </c>
       <c r="G143">
         <v>10</v>
       </c>
       <c r="H143" t="s">
-        <v>179</v>
+        <v>111</v>
       </c>
       <c r="I143" t="s">
-        <v>59</v>
+        <v>111</v>
       </c>
       <c r="J143" s="1">
         <v>3030101</v>
@@ -5505,16 +5505,16 @@
         <v>17</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>145</v>
+        <v>44</v>
       </c>
       <c r="G144">
         <v>10</v>
       </c>
       <c r="H144" t="s">
-        <v>179</v>
+        <v>111</v>
       </c>
       <c r="I144" t="s">
-        <v>59</v>
+        <v>111</v>
       </c>
       <c r="J144" s="1">
         <v>3030101</v>
@@ -5537,16 +5537,16 @@
         <v>17</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>145</v>
+        <v>44</v>
       </c>
       <c r="G145">
         <v>10</v>
       </c>
       <c r="H145" t="s">
-        <v>179</v>
+        <v>110</v>
       </c>
       <c r="I145" t="s">
-        <v>58</v>
+        <v>110</v>
       </c>
       <c r="J145" s="1">
         <v>3010101</v>
@@ -5569,16 +5569,16 @@
         <v>17</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>145</v>
+        <v>44</v>
       </c>
       <c r="G146">
         <v>10</v>
       </c>
       <c r="H146" t="s">
-        <v>179</v>
+        <v>111</v>
       </c>
       <c r="I146" t="s">
-        <v>59</v>
+        <v>111</v>
       </c>
       <c r="J146" s="1">
         <v>3030101</v>
@@ -5601,16 +5601,16 @@
         <v>17</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>145</v>
+        <v>44</v>
       </c>
       <c r="G147">
         <v>10</v>
       </c>
       <c r="H147" t="s">
-        <v>179</v>
+        <v>110</v>
       </c>
       <c r="I147" t="s">
-        <v>58</v>
+        <v>110</v>
       </c>
       <c r="J147" s="1">
         <v>3010101</v>
@@ -5633,16 +5633,16 @@
         <v>17</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>145</v>
+        <v>44</v>
       </c>
       <c r="G148">
         <v>10</v>
       </c>
       <c r="H148" t="s">
-        <v>179</v>
+        <v>110</v>
       </c>
       <c r="I148" t="s">
-        <v>58</v>
+        <v>110</v>
       </c>
       <c r="J148" s="1">
         <v>3010101</v>
@@ -5665,16 +5665,16 @@
         <v>18</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>146</v>
+        <v>45</v>
       </c>
       <c r="G149">
         <v>10</v>
       </c>
       <c r="H149" t="s">
-        <v>179</v>
+        <v>112</v>
       </c>
       <c r="I149" t="s">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="J149" s="1">
         <v>3010101</v>
@@ -5697,16 +5697,16 @@
         <v>18</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>146</v>
+        <v>45</v>
       </c>
       <c r="G150">
         <v>10</v>
       </c>
       <c r="H150" t="s">
-        <v>179</v>
+        <v>113</v>
       </c>
       <c r="I150" t="s">
-        <v>61</v>
+        <v>113</v>
       </c>
       <c r="J150" s="1">
         <v>3030101</v>
@@ -5729,16 +5729,16 @@
         <v>18</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>146</v>
+        <v>45</v>
       </c>
       <c r="G151">
         <v>10</v>
       </c>
       <c r="H151" t="s">
-        <v>179</v>
+        <v>113</v>
       </c>
       <c r="I151" t="s">
-        <v>61</v>
+        <v>113</v>
       </c>
       <c r="J151" s="1">
         <v>3030101</v>
@@ -5761,16 +5761,16 @@
         <v>18</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>146</v>
+        <v>45</v>
       </c>
       <c r="G152">
         <v>10</v>
       </c>
       <c r="H152" t="s">
-        <v>179</v>
+        <v>113</v>
       </c>
       <c r="I152" t="s">
-        <v>61</v>
+        <v>113</v>
       </c>
       <c r="J152" s="1">
         <v>3030101</v>
@@ -5793,16 +5793,16 @@
         <v>18</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>146</v>
+        <v>45</v>
       </c>
       <c r="G153">
         <v>10</v>
       </c>
       <c r="H153" t="s">
-        <v>179</v>
+        <v>112</v>
       </c>
       <c r="I153" t="s">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="J153" s="1">
         <v>3010101</v>
@@ -5825,16 +5825,16 @@
         <v>18</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>146</v>
+        <v>45</v>
       </c>
       <c r="G154">
         <v>10</v>
       </c>
       <c r="H154" t="s">
-        <v>179</v>
+        <v>113</v>
       </c>
       <c r="I154" t="s">
-        <v>61</v>
+        <v>113</v>
       </c>
       <c r="J154" s="1">
         <v>3030101</v>
@@ -5857,16 +5857,16 @@
         <v>18</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>146</v>
+        <v>45</v>
       </c>
       <c r="G155">
         <v>10</v>
       </c>
       <c r="H155" t="s">
-        <v>179</v>
+        <v>112</v>
       </c>
       <c r="I155" t="s">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="J155" s="1">
         <v>3010101</v>
@@ -5889,16 +5889,16 @@
         <v>18</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>146</v>
+        <v>45</v>
       </c>
       <c r="G156">
         <v>10</v>
       </c>
       <c r="H156" t="s">
-        <v>179</v>
+        <v>112</v>
       </c>
       <c r="I156" t="s">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="J156" s="1">
         <v>3010101</v>
@@ -5921,16 +5921,16 @@
         <v>19</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>147</v>
+        <v>46</v>
       </c>
       <c r="G157">
         <v>10</v>
       </c>
       <c r="H157" t="s">
-        <v>179</v>
+        <v>114</v>
       </c>
       <c r="I157" t="s">
-        <v>62</v>
+        <v>114</v>
       </c>
       <c r="J157" s="1">
         <v>3010101</v>
@@ -5953,16 +5953,16 @@
         <v>19</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>147</v>
+        <v>46</v>
       </c>
       <c r="G158">
         <v>10</v>
       </c>
       <c r="H158" t="s">
-        <v>179</v>
+        <v>115</v>
       </c>
       <c r="I158" t="s">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="J158" s="1">
         <v>3030101</v>
@@ -5985,16 +5985,16 @@
         <v>19</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>147</v>
+        <v>46</v>
       </c>
       <c r="G159">
         <v>10</v>
       </c>
       <c r="H159" t="s">
-        <v>179</v>
+        <v>115</v>
       </c>
       <c r="I159" t="s">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="J159" s="1">
         <v>3030101</v>
@@ -6017,16 +6017,16 @@
         <v>19</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>147</v>
+        <v>46</v>
       </c>
       <c r="G160">
         <v>10</v>
       </c>
       <c r="H160" t="s">
-        <v>179</v>
+        <v>115</v>
       </c>
       <c r="I160" t="s">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="J160" s="1">
         <v>3030101</v>
@@ -6049,16 +6049,16 @@
         <v>19</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>147</v>
+        <v>46</v>
       </c>
       <c r="G161">
         <v>10</v>
       </c>
       <c r="H161" t="s">
-        <v>179</v>
+        <v>114</v>
       </c>
       <c r="I161" t="s">
-        <v>62</v>
+        <v>114</v>
       </c>
       <c r="J161" s="1">
         <v>3010101</v>
@@ -6081,16 +6081,16 @@
         <v>19</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>147</v>
+        <v>46</v>
       </c>
       <c r="G162">
         <v>10</v>
       </c>
       <c r="H162" t="s">
-        <v>179</v>
+        <v>115</v>
       </c>
       <c r="I162" t="s">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="J162" s="1">
         <v>3030101</v>
@@ -6113,16 +6113,16 @@
         <v>19</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>147</v>
+        <v>46</v>
       </c>
       <c r="G163">
         <v>10</v>
       </c>
       <c r="H163" t="s">
-        <v>179</v>
+        <v>114</v>
       </c>
       <c r="I163" t="s">
-        <v>62</v>
+        <v>114</v>
       </c>
       <c r="J163" s="1">
         <v>3010101</v>
@@ -6145,16 +6145,16 @@
         <v>19</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>147</v>
+        <v>46</v>
       </c>
       <c r="G164">
         <v>10</v>
       </c>
       <c r="H164" t="s">
-        <v>179</v>
+        <v>114</v>
       </c>
       <c r="I164" t="s">
-        <v>62</v>
+        <v>114</v>
       </c>
       <c r="J164" s="1">
         <v>3010101</v>
@@ -6177,16 +6177,16 @@
         <v>20</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>148</v>
+        <v>47</v>
       </c>
       <c r="G165">
         <v>20</v>
       </c>
       <c r="H165" t="s">
-        <v>179</v>
+        <v>116</v>
       </c>
       <c r="I165" t="s">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="J165" s="1">
         <v>3010101</v>
@@ -6209,16 +6209,16 @@
         <v>20</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>148</v>
+        <v>47</v>
       </c>
       <c r="G166">
         <v>20</v>
       </c>
       <c r="H166" t="s">
-        <v>179</v>
+        <v>117</v>
       </c>
       <c r="I166" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="J166" s="1">
         <v>3030101</v>
@@ -6241,16 +6241,16 @@
         <v>20</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>148</v>
+        <v>47</v>
       </c>
       <c r="G167">
         <v>20</v>
       </c>
       <c r="H167" t="s">
-        <v>179</v>
+        <v>117</v>
       </c>
       <c r="I167" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="J167" s="1">
         <v>3030101</v>
@@ -6273,16 +6273,16 @@
         <v>20</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>148</v>
+        <v>47</v>
       </c>
       <c r="G168">
         <v>20</v>
       </c>
       <c r="H168" t="s">
-        <v>179</v>
+        <v>117</v>
       </c>
       <c r="I168" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="J168" s="1">
         <v>3030101</v>
@@ -6305,16 +6305,16 @@
         <v>20</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>148</v>
+        <v>47</v>
       </c>
       <c r="G169">
         <v>20</v>
       </c>
       <c r="H169" t="s">
-        <v>179</v>
+        <v>116</v>
       </c>
       <c r="I169" t="s">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="J169" s="1">
         <v>3010101</v>
@@ -6337,16 +6337,16 @@
         <v>20</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>148</v>
+        <v>47</v>
       </c>
       <c r="G170">
         <v>20</v>
       </c>
       <c r="H170" t="s">
-        <v>179</v>
+        <v>117</v>
       </c>
       <c r="I170" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="J170" s="1">
         <v>3030101</v>
@@ -6369,16 +6369,16 @@
         <v>20</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>148</v>
+        <v>47</v>
       </c>
       <c r="G171">
         <v>20</v>
       </c>
       <c r="H171" t="s">
-        <v>179</v>
+        <v>116</v>
       </c>
       <c r="I171" t="s">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="J171" s="1">
         <v>3010101</v>
@@ -6401,16 +6401,16 @@
         <v>20</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>148</v>
+        <v>47</v>
       </c>
       <c r="G172">
         <v>20</v>
       </c>
       <c r="H172" t="s">
-        <v>179</v>
+        <v>116</v>
       </c>
       <c r="I172" t="s">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="J172" s="1">
         <v>3010101</v>
@@ -6433,16 +6433,16 @@
         <v>21</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>149</v>
+        <v>48</v>
       </c>
       <c r="G173">
         <v>20</v>
       </c>
       <c r="H173" t="s">
-        <v>179</v>
+        <v>118</v>
       </c>
       <c r="I173" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="J173" s="1">
         <v>3010101</v>
@@ -6465,16 +6465,16 @@
         <v>21</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>149</v>
+        <v>48</v>
       </c>
       <c r="G174">
         <v>20</v>
       </c>
       <c r="H174" t="s">
-        <v>179</v>
+        <v>119</v>
       </c>
       <c r="I174" t="s">
-        <v>67</v>
+        <v>119</v>
       </c>
       <c r="J174" s="1">
         <v>3030101</v>
@@ -6497,16 +6497,16 @@
         <v>21</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>149</v>
+        <v>48</v>
       </c>
       <c r="G175">
         <v>20</v>
       </c>
       <c r="H175" t="s">
-        <v>179</v>
+        <v>119</v>
       </c>
       <c r="I175" t="s">
-        <v>67</v>
+        <v>119</v>
       </c>
       <c r="J175" s="1">
         <v>3030101</v>
@@ -6529,16 +6529,16 @@
         <v>21</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>149</v>
+        <v>48</v>
       </c>
       <c r="G176">
         <v>20</v>
       </c>
       <c r="H176" t="s">
-        <v>179</v>
+        <v>119</v>
       </c>
       <c r="I176" t="s">
-        <v>67</v>
+        <v>119</v>
       </c>
       <c r="J176" s="1">
         <v>3030101</v>
@@ -6561,16 +6561,16 @@
         <v>21</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>149</v>
+        <v>48</v>
       </c>
       <c r="G177">
         <v>20</v>
       </c>
       <c r="H177" t="s">
-        <v>179</v>
+        <v>118</v>
       </c>
       <c r="I177" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="J177" s="1">
         <v>3010101</v>
@@ -6593,16 +6593,16 @@
         <v>21</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>149</v>
+        <v>48</v>
       </c>
       <c r="G178">
         <v>20</v>
       </c>
       <c r="H178" t="s">
-        <v>179</v>
+        <v>119</v>
       </c>
       <c r="I178" t="s">
-        <v>67</v>
+        <v>119</v>
       </c>
       <c r="J178" s="1">
         <v>3030101</v>
@@ -6625,16 +6625,16 @@
         <v>21</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>149</v>
+        <v>48</v>
       </c>
       <c r="G179">
         <v>20</v>
       </c>
       <c r="H179" t="s">
-        <v>179</v>
+        <v>118</v>
       </c>
       <c r="I179" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="J179" s="1">
         <v>3010101</v>
@@ -6657,16 +6657,16 @@
         <v>21</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>149</v>
+        <v>48</v>
       </c>
       <c r="G180">
         <v>20</v>
       </c>
       <c r="H180" t="s">
-        <v>179</v>
+        <v>118</v>
       </c>
       <c r="I180" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="J180" s="1">
         <v>3010101</v>
@@ -6689,16 +6689,16 @@
         <v>22</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>150</v>
+        <v>49</v>
       </c>
       <c r="G181">
         <v>20</v>
       </c>
       <c r="H181" t="s">
-        <v>179</v>
+        <v>120</v>
       </c>
       <c r="I181" t="s">
-        <v>68</v>
+        <v>120</v>
       </c>
       <c r="J181" s="1">
         <v>3010101</v>
@@ -6721,16 +6721,16 @@
         <v>22</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>150</v>
+        <v>49</v>
       </c>
       <c r="G182">
         <v>20</v>
       </c>
       <c r="H182" t="s">
-        <v>179</v>
+        <v>121</v>
       </c>
       <c r="I182" t="s">
-        <v>69</v>
+        <v>121</v>
       </c>
       <c r="J182" s="1">
         <v>3030101</v>
@@ -6753,16 +6753,16 @@
         <v>22</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>150</v>
+        <v>49</v>
       </c>
       <c r="G183">
         <v>20</v>
       </c>
       <c r="H183" t="s">
-        <v>179</v>
+        <v>121</v>
       </c>
       <c r="I183" t="s">
-        <v>69</v>
+        <v>121</v>
       </c>
       <c r="J183" s="1">
         <v>3030101</v>
@@ -6785,16 +6785,16 @@
         <v>22</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>150</v>
+        <v>49</v>
       </c>
       <c r="G184">
         <v>20</v>
       </c>
       <c r="H184" t="s">
-        <v>179</v>
+        <v>121</v>
       </c>
       <c r="I184" t="s">
-        <v>69</v>
+        <v>121</v>
       </c>
       <c r="J184" s="1">
         <v>3030101</v>
@@ -6817,16 +6817,16 @@
         <v>22</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>150</v>
+        <v>49</v>
       </c>
       <c r="G185">
         <v>20</v>
       </c>
       <c r="H185" t="s">
-        <v>179</v>
+        <v>120</v>
       </c>
       <c r="I185" t="s">
-        <v>68</v>
+        <v>120</v>
       </c>
       <c r="J185" s="1">
         <v>3010101</v>
@@ -6849,16 +6849,16 @@
         <v>22</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>150</v>
+        <v>49</v>
       </c>
       <c r="G186">
         <v>20</v>
       </c>
       <c r="H186" t="s">
-        <v>179</v>
+        <v>121</v>
       </c>
       <c r="I186" t="s">
-        <v>69</v>
+        <v>121</v>
       </c>
       <c r="J186" s="1">
         <v>3030101</v>
@@ -6881,16 +6881,16 @@
         <v>22</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>150</v>
+        <v>49</v>
       </c>
       <c r="G187">
         <v>20</v>
       </c>
       <c r="H187" t="s">
-        <v>179</v>
+        <v>120</v>
       </c>
       <c r="I187" t="s">
-        <v>68</v>
+        <v>120</v>
       </c>
       <c r="J187" s="1">
         <v>3010101</v>
@@ -6913,16 +6913,16 @@
         <v>22</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>150</v>
+        <v>49</v>
       </c>
       <c r="G188">
         <v>20</v>
       </c>
       <c r="H188" t="s">
-        <v>179</v>
+        <v>120</v>
       </c>
       <c r="I188" t="s">
-        <v>68</v>
+        <v>120</v>
       </c>
       <c r="J188" s="1">
         <v>3010101</v>
@@ -6945,16 +6945,16 @@
         <v>23</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>151</v>
+        <v>50</v>
       </c>
       <c r="G189">
         <v>20</v>
       </c>
       <c r="H189" t="s">
-        <v>179</v>
+        <v>122</v>
       </c>
       <c r="I189" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="J189" s="1">
         <v>3010101</v>
@@ -6977,16 +6977,16 @@
         <v>23</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>151</v>
+        <v>50</v>
       </c>
       <c r="G190">
         <v>20</v>
       </c>
       <c r="H190" t="s">
-        <v>179</v>
+        <v>123</v>
       </c>
       <c r="I190" t="s">
-        <v>71</v>
+        <v>123</v>
       </c>
       <c r="J190" s="1">
         <v>3030101</v>
@@ -7009,16 +7009,16 @@
         <v>23</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>151</v>
+        <v>50</v>
       </c>
       <c r="G191">
         <v>20</v>
       </c>
       <c r="H191" t="s">
-        <v>179</v>
+        <v>123</v>
       </c>
       <c r="I191" t="s">
-        <v>71</v>
+        <v>123</v>
       </c>
       <c r="J191" s="1">
         <v>3030101</v>
@@ -7041,16 +7041,16 @@
         <v>23</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>151</v>
+        <v>50</v>
       </c>
       <c r="G192">
         <v>20</v>
       </c>
       <c r="H192" t="s">
-        <v>179</v>
+        <v>123</v>
       </c>
       <c r="I192" t="s">
-        <v>71</v>
+        <v>123</v>
       </c>
       <c r="J192" s="1">
         <v>3030101</v>
@@ -7073,16 +7073,16 @@
         <v>23</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>151</v>
+        <v>50</v>
       </c>
       <c r="G193">
         <v>20</v>
       </c>
       <c r="H193" t="s">
-        <v>179</v>
+        <v>122</v>
       </c>
       <c r="I193" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="J193" s="1">
         <v>3010101</v>
@@ -7105,16 +7105,16 @@
         <v>23</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>151</v>
+        <v>50</v>
       </c>
       <c r="G194">
         <v>20</v>
       </c>
       <c r="H194" t="s">
-        <v>179</v>
+        <v>123</v>
       </c>
       <c r="I194" t="s">
-        <v>71</v>
+        <v>123</v>
       </c>
       <c r="J194" s="1">
         <v>3030101</v>
@@ -7137,16 +7137,16 @@
         <v>23</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>151</v>
+        <v>50</v>
       </c>
       <c r="G195">
         <v>20</v>
       </c>
       <c r="H195" t="s">
-        <v>179</v>
+        <v>122</v>
       </c>
       <c r="I195" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="J195" s="1">
         <v>3010101</v>
@@ -7169,16 +7169,16 @@
         <v>23</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>151</v>
+        <v>50</v>
       </c>
       <c r="G196">
         <v>20</v>
       </c>
       <c r="H196" t="s">
-        <v>179</v>
+        <v>122</v>
       </c>
       <c r="I196" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="J196" s="1">
         <v>3010101</v>
@@ -7201,16 +7201,16 @@
         <v>24</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>152</v>
+        <v>51</v>
       </c>
       <c r="G197">
         <v>20</v>
       </c>
       <c r="H197" t="s">
-        <v>179</v>
+        <v>124</v>
       </c>
       <c r="I197" t="s">
-        <v>72</v>
+        <v>124</v>
       </c>
       <c r="J197" s="1">
         <v>3010101</v>
@@ -7233,16 +7233,16 @@
         <v>24</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>152</v>
+        <v>51</v>
       </c>
       <c r="G198">
         <v>20</v>
       </c>
       <c r="H198" t="s">
-        <v>179</v>
+        <v>125</v>
       </c>
       <c r="I198" t="s">
-        <v>73</v>
+        <v>125</v>
       </c>
       <c r="J198" s="1">
         <v>3030101</v>
@@ -7265,16 +7265,16 @@
         <v>24</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>152</v>
+        <v>51</v>
       </c>
       <c r="G199">
         <v>20</v>
       </c>
       <c r="H199" t="s">
-        <v>179</v>
+        <v>125</v>
       </c>
       <c r="I199" t="s">
-        <v>73</v>
+        <v>125</v>
       </c>
       <c r="J199" s="1">
         <v>3030101</v>
@@ -7297,16 +7297,16 @@
         <v>24</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>152</v>
+        <v>51</v>
       </c>
       <c r="G200">
         <v>20</v>
       </c>
       <c r="H200" t="s">
-        <v>179</v>
+        <v>125</v>
       </c>
       <c r="I200" t="s">
-        <v>73</v>
+        <v>125</v>
       </c>
       <c r="J200" s="1">
         <v>3030101</v>
@@ -7329,16 +7329,16 @@
         <v>24</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>152</v>
+        <v>51</v>
       </c>
       <c r="G201">
         <v>20</v>
       </c>
       <c r="H201" t="s">
-        <v>179</v>
+        <v>124</v>
       </c>
       <c r="I201" t="s">
-        <v>72</v>
+        <v>124</v>
       </c>
       <c r="J201" s="1">
         <v>3010101</v>
@@ -7361,16 +7361,16 @@
         <v>24</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>152</v>
+        <v>51</v>
       </c>
       <c r="G202">
         <v>20</v>
       </c>
       <c r="H202" t="s">
-        <v>179</v>
+        <v>125</v>
       </c>
       <c r="I202" t="s">
-        <v>73</v>
+        <v>125</v>
       </c>
       <c r="J202" s="1">
         <v>3030101</v>
@@ -7393,16 +7393,16 @@
         <v>24</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>152</v>
+        <v>51</v>
       </c>
       <c r="G203">
         <v>20</v>
       </c>
       <c r="H203" t="s">
-        <v>179</v>
+        <v>124</v>
       </c>
       <c r="I203" t="s">
-        <v>72</v>
+        <v>124</v>
       </c>
       <c r="J203" s="1">
         <v>3010101</v>
@@ -7425,16 +7425,16 @@
         <v>24</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>152</v>
+        <v>51</v>
       </c>
       <c r="G204">
         <v>20</v>
       </c>
       <c r="H204" t="s">
-        <v>179</v>
+        <v>124</v>
       </c>
       <c r="I204" t="s">
-        <v>72</v>
+        <v>124</v>
       </c>
       <c r="J204" s="1">
         <v>3010101</v>
@@ -7457,16 +7457,16 @@
         <v>25</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>153</v>
+        <v>52</v>
       </c>
       <c r="G205">
         <v>20</v>
       </c>
       <c r="H205" t="s">
-        <v>179</v>
+        <v>126</v>
       </c>
       <c r="I205" t="s">
-        <v>74</v>
+        <v>126</v>
       </c>
       <c r="J205" s="1">
         <v>3010101</v>
@@ -7489,16 +7489,16 @@
         <v>25</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>153</v>
+        <v>52</v>
       </c>
       <c r="G206">
         <v>20</v>
       </c>
       <c r="H206" t="s">
-        <v>179</v>
+        <v>127</v>
       </c>
       <c r="I206" t="s">
-        <v>75</v>
+        <v>127</v>
       </c>
       <c r="J206" s="1">
         <v>3030101</v>
@@ -7521,16 +7521,16 @@
         <v>25</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>153</v>
+        <v>52</v>
       </c>
       <c r="G207">
         <v>20</v>
       </c>
       <c r="H207" t="s">
-        <v>179</v>
+        <v>127</v>
       </c>
       <c r="I207" t="s">
-        <v>75</v>
+        <v>127</v>
       </c>
       <c r="J207" s="1">
         <v>3030101</v>
@@ -7553,16 +7553,16 @@
         <v>25</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>153</v>
+        <v>52</v>
       </c>
       <c r="G208">
         <v>20</v>
       </c>
       <c r="H208" t="s">
-        <v>179</v>
+        <v>127</v>
       </c>
       <c r="I208" t="s">
-        <v>75</v>
+        <v>127</v>
       </c>
       <c r="J208" s="1">
         <v>3030101</v>
@@ -7585,16 +7585,16 @@
         <v>25</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>153</v>
+        <v>52</v>
       </c>
       <c r="G209">
         <v>20</v>
       </c>
       <c r="H209" t="s">
-        <v>179</v>
+        <v>126</v>
       </c>
       <c r="I209" t="s">
-        <v>74</v>
+        <v>126</v>
       </c>
       <c r="J209" s="1">
         <v>3010101</v>
@@ -7617,16 +7617,16 @@
         <v>25</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>153</v>
+        <v>52</v>
       </c>
       <c r="G210">
         <v>20</v>
       </c>
       <c r="H210" t="s">
-        <v>179</v>
+        <v>127</v>
       </c>
       <c r="I210" t="s">
-        <v>75</v>
+        <v>127</v>
       </c>
       <c r="J210" s="1">
         <v>3030101</v>
@@ -7649,16 +7649,16 @@
         <v>25</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>153</v>
+        <v>52</v>
       </c>
       <c r="G211">
         <v>20</v>
       </c>
       <c r="H211" t="s">
-        <v>179</v>
+        <v>126</v>
       </c>
       <c r="I211" t="s">
-        <v>74</v>
+        <v>126</v>
       </c>
       <c r="J211" s="1">
         <v>3010101</v>
@@ -7681,16 +7681,16 @@
         <v>25</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>153</v>
+        <v>52</v>
       </c>
       <c r="G212">
         <v>20</v>
       </c>
       <c r="H212" t="s">
-        <v>179</v>
+        <v>126</v>
       </c>
       <c r="I212" t="s">
-        <v>74</v>
+        <v>126</v>
       </c>
       <c r="J212" s="1">
         <v>3010101</v>
@@ -7713,16 +7713,16 @@
         <v>26</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>154</v>
+        <v>53</v>
       </c>
       <c r="G213">
         <v>20</v>
       </c>
       <c r="H213" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="I213" t="s">
-        <v>76</v>
+        <v>128</v>
       </c>
       <c r="J213" s="1">
         <v>3010101</v>
@@ -7745,16 +7745,16 @@
         <v>26</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>154</v>
+        <v>53</v>
       </c>
       <c r="G214">
         <v>20</v>
       </c>
       <c r="H214" t="s">
-        <v>179</v>
+        <v>129</v>
       </c>
       <c r="I214" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="J214" s="1">
         <v>3030101</v>
@@ -7777,16 +7777,16 @@
         <v>26</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>154</v>
+        <v>53</v>
       </c>
       <c r="G215">
         <v>20</v>
       </c>
       <c r="H215" t="s">
-        <v>179</v>
+        <v>129</v>
       </c>
       <c r="I215" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="J215" s="1">
         <v>3030101</v>
@@ -7809,16 +7809,16 @@
         <v>26</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>154</v>
+        <v>53</v>
       </c>
       <c r="G216">
         <v>20</v>
       </c>
       <c r="H216" t="s">
-        <v>179</v>
+        <v>129</v>
       </c>
       <c r="I216" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="J216" s="1">
         <v>3030101</v>
@@ -7841,16 +7841,16 @@
         <v>26</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>154</v>
+        <v>53</v>
       </c>
       <c r="G217">
         <v>20</v>
       </c>
       <c r="H217" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="I217" t="s">
-        <v>76</v>
+        <v>128</v>
       </c>
       <c r="J217" s="1">
         <v>3010101</v>
@@ -7873,16 +7873,16 @@
         <v>26</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>154</v>
+        <v>53</v>
       </c>
       <c r="G218">
         <v>20</v>
       </c>
       <c r="H218" t="s">
-        <v>179</v>
+        <v>129</v>
       </c>
       <c r="I218" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="J218" s="1">
         <v>3030101</v>
@@ -7905,16 +7905,16 @@
         <v>26</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>154</v>
+        <v>53</v>
       </c>
       <c r="G219">
         <v>20</v>
       </c>
       <c r="H219" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="I219" t="s">
-        <v>76</v>
+        <v>128</v>
       </c>
       <c r="J219" s="1">
         <v>3010101</v>
@@ -7937,16 +7937,16 @@
         <v>26</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>154</v>
+        <v>53</v>
       </c>
       <c r="G220">
         <v>20</v>
       </c>
       <c r="H220" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="I220" t="s">
-        <v>76</v>
+        <v>128</v>
       </c>
       <c r="J220" s="1">
         <v>3010101</v>
@@ -7969,16 +7969,16 @@
         <v>27</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>155</v>
+        <v>54</v>
       </c>
       <c r="G221">
         <v>20</v>
       </c>
       <c r="H221" t="s">
-        <v>179</v>
+        <v>130</v>
       </c>
       <c r="I221" t="s">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="J221" s="1">
         <v>3010101</v>
@@ -8001,16 +8001,16 @@
         <v>27</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>155</v>
+        <v>54</v>
       </c>
       <c r="G222">
         <v>20</v>
       </c>
       <c r="H222" t="s">
-        <v>179</v>
+        <v>131</v>
       </c>
       <c r="I222" t="s">
-        <v>79</v>
+        <v>131</v>
       </c>
       <c r="J222" s="1">
         <v>3030101</v>
@@ -8033,16 +8033,16 @@
         <v>27</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>155</v>
+        <v>54</v>
       </c>
       <c r="G223">
         <v>20</v>
       </c>
       <c r="H223" t="s">
-        <v>179</v>
+        <v>131</v>
       </c>
       <c r="I223" t="s">
-        <v>79</v>
+        <v>131</v>
       </c>
       <c r="J223" s="1">
         <v>3030101</v>
@@ -8065,16 +8065,16 @@
         <v>27</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>155</v>
+        <v>54</v>
       </c>
       <c r="G224">
         <v>20</v>
       </c>
       <c r="H224" t="s">
-        <v>179</v>
+        <v>131</v>
       </c>
       <c r="I224" t="s">
-        <v>79</v>
+        <v>131</v>
       </c>
       <c r="J224" s="1">
         <v>3030101</v>
@@ -8097,16 +8097,16 @@
         <v>27</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>155</v>
+        <v>54</v>
       </c>
       <c r="G225">
         <v>20</v>
       </c>
       <c r="H225" t="s">
-        <v>179</v>
+        <v>130</v>
       </c>
       <c r="I225" t="s">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="J225" s="1">
         <v>3010101</v>
@@ -8129,16 +8129,16 @@
         <v>27</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>155</v>
+        <v>54</v>
       </c>
       <c r="G226">
         <v>20</v>
       </c>
       <c r="H226" t="s">
-        <v>179</v>
+        <v>131</v>
       </c>
       <c r="I226" t="s">
-        <v>79</v>
+        <v>131</v>
       </c>
       <c r="J226" s="1">
         <v>3030101</v>
@@ -8161,16 +8161,16 @@
         <v>27</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>155</v>
+        <v>54</v>
       </c>
       <c r="G227">
         <v>20</v>
       </c>
       <c r="H227" t="s">
-        <v>179</v>
+        <v>130</v>
       </c>
       <c r="I227" t="s">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="J227" s="1">
         <v>3010101</v>
@@ -8193,16 +8193,16 @@
         <v>27</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>155</v>
+        <v>54</v>
       </c>
       <c r="G228">
         <v>20</v>
       </c>
       <c r="H228" t="s">
-        <v>179</v>
+        <v>130</v>
       </c>
       <c r="I228" t="s">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="J228" s="1">
         <v>3010101</v>
@@ -8225,16 +8225,16 @@
         <v>28</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>156</v>
+        <v>55</v>
       </c>
       <c r="G229">
         <v>20</v>
       </c>
       <c r="H229" t="s">
-        <v>179</v>
+        <v>132</v>
       </c>
       <c r="I229" t="s">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="J229" s="1">
         <v>3010101</v>
@@ -8257,16 +8257,16 @@
         <v>28</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>156</v>
+        <v>55</v>
       </c>
       <c r="G230">
         <v>20</v>
       </c>
       <c r="H230" t="s">
-        <v>179</v>
+        <v>133</v>
       </c>
       <c r="I230" t="s">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="J230" s="1">
         <v>3030101</v>
@@ -8289,16 +8289,16 @@
         <v>28</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>156</v>
+        <v>55</v>
       </c>
       <c r="G231">
         <v>20</v>
       </c>
       <c r="H231" t="s">
-        <v>179</v>
+        <v>133</v>
       </c>
       <c r="I231" t="s">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="J231" s="1">
         <v>3030101</v>
@@ -8321,16 +8321,16 @@
         <v>28</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>156</v>
+        <v>55</v>
       </c>
       <c r="G232">
         <v>20</v>
       </c>
       <c r="H232" t="s">
-        <v>179</v>
+        <v>133</v>
       </c>
       <c r="I232" t="s">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="J232" s="1">
         <v>3030101</v>
@@ -8353,16 +8353,16 @@
         <v>28</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>156</v>
+        <v>55</v>
       </c>
       <c r="G233">
         <v>20</v>
       </c>
       <c r="H233" t="s">
-        <v>179</v>
+        <v>132</v>
       </c>
       <c r="I233" t="s">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="J233" s="1">
         <v>3010101</v>
@@ -8385,16 +8385,16 @@
         <v>28</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>156</v>
+        <v>55</v>
       </c>
       <c r="G234">
         <v>20</v>
       </c>
       <c r="H234" t="s">
-        <v>179</v>
+        <v>133</v>
       </c>
       <c r="I234" t="s">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="J234" s="1">
         <v>3030101</v>
@@ -8417,16 +8417,16 @@
         <v>28</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>156</v>
+        <v>55</v>
       </c>
       <c r="G235">
         <v>20</v>
       </c>
       <c r="H235" t="s">
-        <v>179</v>
+        <v>132</v>
       </c>
       <c r="I235" t="s">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="J235" s="1">
         <v>3010101</v>
@@ -8449,16 +8449,16 @@
         <v>28</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>156</v>
+        <v>55</v>
       </c>
       <c r="G236">
         <v>20</v>
       </c>
       <c r="H236" t="s">
-        <v>179</v>
+        <v>132</v>
       </c>
       <c r="I236" t="s">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="J236" s="1">
         <v>3010101</v>
@@ -8481,16 +8481,16 @@
         <v>29</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>157</v>
+        <v>56</v>
       </c>
       <c r="G237">
         <v>20</v>
       </c>
       <c r="H237" t="s">
-        <v>179</v>
+        <v>134</v>
       </c>
       <c r="I237" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="J237" s="1">
         <v>3010101</v>
@@ -8513,16 +8513,16 @@
         <v>29</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>157</v>
+        <v>56</v>
       </c>
       <c r="G238">
         <v>20</v>
       </c>
       <c r="H238" t="s">
-        <v>179</v>
+        <v>135</v>
       </c>
       <c r="I238" t="s">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="J238" s="1">
         <v>3030101</v>
@@ -8545,16 +8545,16 @@
         <v>29</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>157</v>
+        <v>56</v>
       </c>
       <c r="G239">
         <v>20</v>
       </c>
       <c r="H239" t="s">
-        <v>179</v>
+        <v>135</v>
       </c>
       <c r="I239" t="s">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="J239" s="1">
         <v>3030101</v>
@@ -8577,16 +8577,16 @@
         <v>29</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>157</v>
+        <v>56</v>
       </c>
       <c r="G240">
         <v>20</v>
       </c>
       <c r="H240" t="s">
-        <v>179</v>
+        <v>135</v>
       </c>
       <c r="I240" t="s">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="J240" s="1">
         <v>3030101</v>
@@ -8609,16 +8609,16 @@
         <v>29</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>157</v>
+        <v>56</v>
       </c>
       <c r="G241">
         <v>20</v>
       </c>
       <c r="H241" t="s">
-        <v>179</v>
+        <v>134</v>
       </c>
       <c r="I241" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="J241" s="1">
         <v>3010101</v>
@@ -8641,16 +8641,16 @@
         <v>29</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>157</v>
+        <v>56</v>
       </c>
       <c r="G242">
         <v>20</v>
       </c>
       <c r="H242" t="s">
-        <v>179</v>
+        <v>135</v>
       </c>
       <c r="I242" t="s">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="J242" s="1">
         <v>3030101</v>
@@ -8673,16 +8673,16 @@
         <v>29</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>157</v>
+        <v>56</v>
       </c>
       <c r="G243">
         <v>20</v>
       </c>
       <c r="H243" t="s">
-        <v>179</v>
+        <v>134</v>
       </c>
       <c r="I243" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="J243" s="1">
         <v>3010101</v>
@@ -8705,16 +8705,16 @@
         <v>29</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>157</v>
+        <v>56</v>
       </c>
       <c r="G244">
         <v>20</v>
       </c>
       <c r="H244" t="s">
-        <v>179</v>
+        <v>134</v>
       </c>
       <c r="I244" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="J244" s="1">
         <v>3010101</v>
@@ -8737,16 +8737,16 @@
         <v>30</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>158</v>
+        <v>57</v>
       </c>
       <c r="G245">
         <v>30</v>
       </c>
       <c r="H245" t="s">
-        <v>179</v>
+        <v>136</v>
       </c>
       <c r="I245" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="J245" s="1">
         <v>3010101</v>
@@ -8769,16 +8769,16 @@
         <v>30</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>158</v>
+        <v>57</v>
       </c>
       <c r="G246">
         <v>30</v>
       </c>
       <c r="H246" t="s">
-        <v>179</v>
+        <v>137</v>
       </c>
       <c r="I246" t="s">
-        <v>85</v>
+        <v>137</v>
       </c>
       <c r="J246" s="1">
         <v>3030101</v>
@@ -8801,16 +8801,16 @@
         <v>30</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>158</v>
+        <v>57</v>
       </c>
       <c r="G247">
         <v>30</v>
       </c>
       <c r="H247" t="s">
-        <v>179</v>
+        <v>137</v>
       </c>
       <c r="I247" t="s">
-        <v>85</v>
+        <v>137</v>
       </c>
       <c r="J247" s="1">
         <v>3030101</v>
@@ -8833,16 +8833,16 @@
         <v>30</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>158</v>
+        <v>57</v>
       </c>
       <c r="G248">
         <v>30</v>
       </c>
       <c r="H248" t="s">
-        <v>179</v>
+        <v>137</v>
       </c>
       <c r="I248" t="s">
-        <v>85</v>
+        <v>137</v>
       </c>
       <c r="J248" s="1">
         <v>3030101</v>
@@ -8865,16 +8865,16 @@
         <v>30</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>158</v>
+        <v>57</v>
       </c>
       <c r="G249">
         <v>30</v>
       </c>
       <c r="H249" t="s">
-        <v>179</v>
+        <v>136</v>
       </c>
       <c r="I249" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="J249" s="1">
         <v>3010101</v>
@@ -8897,16 +8897,16 @@
         <v>30</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>158</v>
+        <v>57</v>
       </c>
       <c r="G250">
         <v>30</v>
       </c>
       <c r="H250" t="s">
-        <v>179</v>
+        <v>137</v>
       </c>
       <c r="I250" t="s">
-        <v>85</v>
+        <v>137</v>
       </c>
       <c r="J250" s="1">
         <v>3030101</v>
@@ -8929,16 +8929,16 @@
         <v>30</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>158</v>
+        <v>57</v>
       </c>
       <c r="G251">
         <v>30</v>
       </c>
       <c r="H251" t="s">
-        <v>179</v>
+        <v>136</v>
       </c>
       <c r="I251" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="J251" s="1">
         <v>3010101</v>
@@ -8961,16 +8961,16 @@
         <v>30</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>158</v>
+        <v>57</v>
       </c>
       <c r="G252">
         <v>30</v>
       </c>
       <c r="H252" t="s">
-        <v>179</v>
+        <v>136</v>
       </c>
       <c r="I252" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="J252" s="1">
         <v>3010101</v>
@@ -8993,16 +8993,16 @@
         <v>31</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>159</v>
+        <v>58</v>
       </c>
       <c r="G253">
         <v>30</v>
       </c>
       <c r="H253" t="s">
-        <v>179</v>
+        <v>138</v>
       </c>
       <c r="I253" t="s">
-        <v>86</v>
+        <v>138</v>
       </c>
       <c r="J253" s="1">
         <v>3010101</v>
@@ -9025,16 +9025,16 @@
         <v>31</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>159</v>
+        <v>58</v>
       </c>
       <c r="G254">
         <v>30</v>
       </c>
       <c r="H254" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="I254" t="s">
-        <v>87</v>
+        <v>139</v>
       </c>
       <c r="J254" s="1">
         <v>3030101</v>
@@ -9057,16 +9057,16 @@
         <v>31</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>159</v>
+        <v>58</v>
       </c>
       <c r="G255">
         <v>30</v>
       </c>
       <c r="H255" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="I255" t="s">
-        <v>87</v>
+        <v>139</v>
       </c>
       <c r="J255" s="1">
         <v>3030101</v>
@@ -9089,16 +9089,16 @@
         <v>31</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>159</v>
+        <v>58</v>
       </c>
       <c r="G256">
         <v>30</v>
       </c>
       <c r="H256" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="I256" t="s">
-        <v>87</v>
+        <v>139</v>
       </c>
       <c r="J256" s="1">
         <v>3030101</v>
@@ -9121,16 +9121,16 @@
         <v>31</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>159</v>
+        <v>58</v>
       </c>
       <c r="G257">
         <v>30</v>
       </c>
       <c r="H257" t="s">
-        <v>179</v>
+        <v>138</v>
       </c>
       <c r="I257" t="s">
-        <v>86</v>
+        <v>138</v>
       </c>
       <c r="J257" s="1">
         <v>3010101</v>
@@ -9153,16 +9153,16 @@
         <v>31</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>159</v>
+        <v>58</v>
       </c>
       <c r="G258">
         <v>30</v>
       </c>
       <c r="H258" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="I258" t="s">
-        <v>87</v>
+        <v>139</v>
       </c>
       <c r="J258" s="1">
         <v>3030101</v>
@@ -9185,16 +9185,16 @@
         <v>31</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>159</v>
+        <v>58</v>
       </c>
       <c r="G259">
         <v>30</v>
       </c>
       <c r="H259" t="s">
-        <v>179</v>
+        <v>138</v>
       </c>
       <c r="I259" t="s">
-        <v>86</v>
+        <v>138</v>
       </c>
       <c r="J259" s="1">
         <v>3010101</v>
@@ -9217,16 +9217,16 @@
         <v>31</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>159</v>
+        <v>58</v>
       </c>
       <c r="G260">
         <v>30</v>
       </c>
       <c r="H260" t="s">
-        <v>179</v>
+        <v>138</v>
       </c>
       <c r="I260" t="s">
-        <v>86</v>
+        <v>138</v>
       </c>
       <c r="J260" s="1">
         <v>3010101</v>
@@ -9249,16 +9249,16 @@
         <v>32</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>160</v>
+        <v>59</v>
       </c>
       <c r="G261">
         <v>30</v>
       </c>
       <c r="H261" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
       <c r="I261" t="s">
-        <v>88</v>
+        <v>140</v>
       </c>
       <c r="J261" s="1">
         <v>3010101</v>
@@ -9281,16 +9281,16 @@
         <v>32</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>160</v>
+        <v>59</v>
       </c>
       <c r="G262">
         <v>30</v>
       </c>
       <c r="H262" t="s">
-        <v>179</v>
+        <v>141</v>
       </c>
       <c r="I262" t="s">
-        <v>89</v>
+        <v>141</v>
       </c>
       <c r="J262" s="1">
         <v>3030101</v>
@@ -9313,16 +9313,16 @@
         <v>32</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>160</v>
+        <v>59</v>
       </c>
       <c r="G263">
         <v>30</v>
       </c>
       <c r="H263" t="s">
-        <v>179</v>
+        <v>141</v>
       </c>
       <c r="I263" t="s">
-        <v>89</v>
+        <v>141</v>
       </c>
       <c r="J263" s="1">
         <v>3030101</v>
@@ -9345,16 +9345,16 @@
         <v>32</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>160</v>
+        <v>59</v>
       </c>
       <c r="G264">
         <v>30</v>
       </c>
       <c r="H264" t="s">
-        <v>179</v>
+        <v>141</v>
       </c>
       <c r="I264" t="s">
-        <v>89</v>
+        <v>141</v>
       </c>
       <c r="J264" s="1">
         <v>3030101</v>
@@ -9377,16 +9377,16 @@
         <v>32</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>160</v>
+        <v>59</v>
       </c>
       <c r="G265">
         <v>30</v>
       </c>
       <c r="H265" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
       <c r="I265" t="s">
-        <v>88</v>
+        <v>140</v>
       </c>
       <c r="J265" s="1">
         <v>3010101</v>
@@ -9409,16 +9409,16 @@
         <v>32</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>160</v>
+        <v>59</v>
       </c>
       <c r="G266">
         <v>30</v>
       </c>
       <c r="H266" t="s">
-        <v>179</v>
+        <v>141</v>
       </c>
       <c r="I266" t="s">
-        <v>89</v>
+        <v>141</v>
       </c>
       <c r="J266" s="1">
         <v>3030101</v>
@@ -9441,16 +9441,16 @@
         <v>32</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>160</v>
+        <v>59</v>
       </c>
       <c r="G267">
         <v>30</v>
       </c>
       <c r="H267" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
       <c r="I267" t="s">
-        <v>88</v>
+        <v>140</v>
       </c>
       <c r="J267" s="1">
         <v>3010101</v>
@@ -9473,16 +9473,16 @@
         <v>32</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>160</v>
+        <v>59</v>
       </c>
       <c r="G268">
         <v>30</v>
       </c>
       <c r="H268" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
       <c r="I268" t="s">
-        <v>88</v>
+        <v>140</v>
       </c>
       <c r="J268" s="1">
         <v>3010101</v>
@@ -9505,16 +9505,16 @@
         <v>33</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>161</v>
+        <v>60</v>
       </c>
       <c r="G269">
         <v>30</v>
       </c>
       <c r="H269" t="s">
-        <v>179</v>
+        <v>142</v>
       </c>
       <c r="I269" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="J269" s="1">
         <v>3010101</v>
@@ -9537,16 +9537,16 @@
         <v>33</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>161</v>
+        <v>60</v>
       </c>
       <c r="G270">
         <v>30</v>
       </c>
       <c r="H270" t="s">
-        <v>179</v>
+        <v>143</v>
       </c>
       <c r="I270" t="s">
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="J270" s="1">
         <v>3030101</v>
@@ -9569,16 +9569,16 @@
         <v>33</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>161</v>
+        <v>60</v>
       </c>
       <c r="G271">
         <v>30</v>
       </c>
       <c r="H271" t="s">
-        <v>179</v>
+        <v>143</v>
       </c>
       <c r="I271" t="s">
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="J271" s="1">
         <v>3030101</v>
@@ -9601,16 +9601,16 @@
         <v>33</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>161</v>
+        <v>60</v>
       </c>
       <c r="G272">
         <v>30</v>
       </c>
       <c r="H272" t="s">
-        <v>179</v>
+        <v>143</v>
       </c>
       <c r="I272" t="s">
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="J272" s="1">
         <v>3030101</v>
@@ -9633,16 +9633,16 @@
         <v>33</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>161</v>
+        <v>60</v>
       </c>
       <c r="G273">
         <v>30</v>
       </c>
       <c r="H273" t="s">
-        <v>179</v>
+        <v>142</v>
       </c>
       <c r="I273" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="J273" s="1">
         <v>3010101</v>
@@ -9665,16 +9665,16 @@
         <v>33</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>161</v>
+        <v>60</v>
       </c>
       <c r="G274">
         <v>30</v>
       </c>
       <c r="H274" t="s">
-        <v>179</v>
+        <v>143</v>
       </c>
       <c r="I274" t="s">
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="J274" s="1">
         <v>3030101</v>
@@ -9697,16 +9697,16 @@
         <v>33</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>161</v>
+        <v>60</v>
       </c>
       <c r="G275">
         <v>30</v>
       </c>
       <c r="H275" t="s">
-        <v>179</v>
+        <v>142</v>
       </c>
       <c r="I275" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="J275" s="1">
         <v>3010101</v>
@@ -9729,16 +9729,16 @@
         <v>33</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>161</v>
+        <v>60</v>
       </c>
       <c r="G276">
         <v>30</v>
       </c>
       <c r="H276" t="s">
-        <v>179</v>
+        <v>142</v>
       </c>
       <c r="I276" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="J276" s="1">
         <v>3010101</v>
@@ -9761,16 +9761,16 @@
         <v>34</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>162</v>
+        <v>61</v>
       </c>
       <c r="G277">
         <v>30</v>
       </c>
       <c r="H277" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="I277" t="s">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="J277" s="1">
         <v>3010101</v>
@@ -9793,16 +9793,16 @@
         <v>34</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>162</v>
+        <v>61</v>
       </c>
       <c r="G278">
         <v>30</v>
       </c>
       <c r="H278" t="s">
-        <v>179</v>
+        <v>145</v>
       </c>
       <c r="I278" t="s">
-        <v>93</v>
+        <v>145</v>
       </c>
       <c r="J278" s="1">
         <v>3030101</v>
@@ -9825,16 +9825,16 @@
         <v>34</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>162</v>
+        <v>61</v>
       </c>
       <c r="G279">
         <v>30</v>
       </c>
       <c r="H279" t="s">
-        <v>179</v>
+        <v>145</v>
       </c>
       <c r="I279" t="s">
-        <v>93</v>
+        <v>145</v>
       </c>
       <c r="J279" s="1">
         <v>3030101</v>
@@ -9857,16 +9857,16 @@
         <v>34</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>162</v>
+        <v>61</v>
       </c>
       <c r="G280">
         <v>30</v>
       </c>
       <c r="H280" t="s">
-        <v>179</v>
+        <v>145</v>
       </c>
       <c r="I280" t="s">
-        <v>93</v>
+        <v>145</v>
       </c>
       <c r="J280" s="1">
         <v>3030101</v>
@@ -9889,16 +9889,16 @@
         <v>34</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>162</v>
+        <v>61</v>
       </c>
       <c r="G281">
         <v>30</v>
       </c>
       <c r="H281" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="I281" t="s">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="J281" s="1">
         <v>3010101</v>
@@ -9921,16 +9921,16 @@
         <v>34</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>162</v>
+        <v>61</v>
       </c>
       <c r="G282">
         <v>30</v>
       </c>
       <c r="H282" t="s">
-        <v>179</v>
+        <v>145</v>
       </c>
       <c r="I282" t="s">
-        <v>93</v>
+        <v>145</v>
       </c>
       <c r="J282" s="1">
         <v>3030101</v>
@@ -9953,16 +9953,16 @@
         <v>34</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>162</v>
+        <v>61</v>
       </c>
       <c r="G283">
         <v>30</v>
       </c>
       <c r="H283" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="I283" t="s">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="J283" s="1">
         <v>3010101</v>
@@ -9985,16 +9985,16 @@
         <v>34</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>162</v>
+        <v>61</v>
       </c>
       <c r="G284">
         <v>30</v>
       </c>
       <c r="H284" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="I284" t="s">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="J284" s="1">
         <v>3010101</v>
@@ -10017,16 +10017,16 @@
         <v>35</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>163</v>
+        <v>62</v>
       </c>
       <c r="G285">
         <v>30</v>
       </c>
       <c r="H285" t="s">
-        <v>179</v>
+        <v>146</v>
       </c>
       <c r="I285" t="s">
-        <v>94</v>
+        <v>146</v>
       </c>
       <c r="J285" s="1">
         <v>3010101</v>
@@ -10049,16 +10049,16 @@
         <v>35</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>163</v>
+        <v>62</v>
       </c>
       <c r="G286">
         <v>30</v>
       </c>
       <c r="H286" t="s">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="I286" t="s">
-        <v>95</v>
+        <v>147</v>
       </c>
       <c r="J286" s="1">
         <v>3030101</v>
@@ -10081,16 +10081,16 @@
         <v>35</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>163</v>
+        <v>62</v>
       </c>
       <c r="G287">
         <v>30</v>
       </c>
       <c r="H287" t="s">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="I287" t="s">
-        <v>95</v>
+        <v>147</v>
       </c>
       <c r="J287" s="1">
         <v>3030101</v>
@@ -10113,16 +10113,16 @@
         <v>35</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>163</v>
+        <v>62</v>
       </c>
       <c r="G288">
         <v>30</v>
       </c>
       <c r="H288" t="s">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="I288" t="s">
-        <v>95</v>
+        <v>147</v>
       </c>
       <c r="J288" s="1">
         <v>3030101</v>
@@ -10145,16 +10145,16 @@
         <v>35</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>163</v>
+        <v>62</v>
       </c>
       <c r="G289">
         <v>30</v>
       </c>
       <c r="H289" t="s">
-        <v>179</v>
+        <v>146</v>
       </c>
       <c r="I289" t="s">
-        <v>94</v>
+        <v>146</v>
       </c>
       <c r="J289" s="1">
         <v>3010101</v>
@@ -10177,16 +10177,16 @@
         <v>35</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>163</v>
+        <v>62</v>
       </c>
       <c r="G290">
         <v>30</v>
       </c>
       <c r="H290" t="s">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="I290" t="s">
-        <v>95</v>
+        <v>147</v>
       </c>
       <c r="J290" s="1">
         <v>3030101</v>
@@ -10209,16 +10209,16 @@
         <v>35</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>163</v>
+        <v>62</v>
       </c>
       <c r="G291">
         <v>30</v>
       </c>
       <c r="H291" t="s">
-        <v>179</v>
+        <v>146</v>
       </c>
       <c r="I291" t="s">
-        <v>94</v>
+        <v>146</v>
       </c>
       <c r="J291" s="1">
         <v>3010101</v>
@@ -10241,16 +10241,16 @@
         <v>35</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>163</v>
+        <v>62</v>
       </c>
       <c r="G292">
         <v>30</v>
       </c>
       <c r="H292" t="s">
-        <v>179</v>
+        <v>146</v>
       </c>
       <c r="I292" t="s">
-        <v>94</v>
+        <v>146</v>
       </c>
       <c r="J292" s="1">
         <v>3010101</v>
@@ -10273,16 +10273,16 @@
         <v>36</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>164</v>
+        <v>63</v>
       </c>
       <c r="G293">
         <v>30</v>
       </c>
       <c r="H293" t="s">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="I293" t="s">
-        <v>96</v>
+        <v>148</v>
       </c>
       <c r="J293" s="1">
         <v>3010101</v>
@@ -10305,16 +10305,16 @@
         <v>36</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>164</v>
+        <v>63</v>
       </c>
       <c r="G294">
         <v>30</v>
       </c>
       <c r="H294" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="I294" t="s">
-        <v>97</v>
+        <v>149</v>
       </c>
       <c r="J294" s="1">
         <v>3030101</v>
@@ -10337,16 +10337,16 @@
         <v>36</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>164</v>
+        <v>63</v>
       </c>
       <c r="G295">
         <v>30</v>
       </c>
       <c r="H295" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="I295" t="s">
-        <v>97</v>
+        <v>149</v>
       </c>
       <c r="J295" s="1">
         <v>3030101</v>
@@ -10369,16 +10369,16 @@
         <v>36</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>164</v>
+        <v>63</v>
       </c>
       <c r="G296">
         <v>30</v>
       </c>
       <c r="H296" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="I296" t="s">
-        <v>97</v>
+        <v>149</v>
       </c>
       <c r="J296" s="1">
         <v>3030101</v>
@@ -10401,16 +10401,16 @@
         <v>36</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>164</v>
+        <v>63</v>
       </c>
       <c r="G297">
         <v>30</v>
       </c>
       <c r="H297" t="s">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="I297" t="s">
-        <v>96</v>
+        <v>148</v>
       </c>
       <c r="J297" s="1">
         <v>3010101</v>
@@ -10433,16 +10433,16 @@
         <v>36</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>164</v>
+        <v>63</v>
       </c>
       <c r="G298">
         <v>30</v>
       </c>
       <c r="H298" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="I298" t="s">
-        <v>97</v>
+        <v>149</v>
       </c>
       <c r="J298" s="1">
         <v>3030101</v>
@@ -10465,16 +10465,16 @@
         <v>36</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>164</v>
+        <v>63</v>
       </c>
       <c r="G299">
         <v>30</v>
       </c>
       <c r="H299" t="s">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="I299" t="s">
-        <v>96</v>
+        <v>148</v>
       </c>
       <c r="J299" s="1">
         <v>3010101</v>
@@ -10497,16 +10497,16 @@
         <v>36</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>164</v>
+        <v>63</v>
       </c>
       <c r="G300">
         <v>30</v>
       </c>
       <c r="H300" t="s">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="I300" t="s">
-        <v>96</v>
+        <v>148</v>
       </c>
       <c r="J300" s="1">
         <v>3010101</v>
@@ -10529,16 +10529,16 @@
         <v>37</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>165</v>
+        <v>64</v>
       </c>
       <c r="G301">
         <v>30</v>
       </c>
       <c r="H301" t="s">
-        <v>179</v>
+        <v>150</v>
       </c>
       <c r="I301" t="s">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="J301" s="1">
         <v>3010101</v>
@@ -10561,16 +10561,16 @@
         <v>37</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>165</v>
+        <v>64</v>
       </c>
       <c r="G302">
         <v>30</v>
       </c>
       <c r="H302" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="I302" t="s">
-        <v>99</v>
+        <v>151</v>
       </c>
       <c r="J302" s="1">
         <v>3030101</v>
@@ -10593,16 +10593,16 @@
         <v>37</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>165</v>
+        <v>64</v>
       </c>
       <c r="G303">
         <v>30</v>
       </c>
       <c r="H303" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="I303" t="s">
-        <v>99</v>
+        <v>151</v>
       </c>
       <c r="J303" s="1">
         <v>3030101</v>
@@ -10625,16 +10625,16 @@
         <v>37</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>165</v>
+        <v>64</v>
       </c>
       <c r="G304">
         <v>30</v>
       </c>
       <c r="H304" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="I304" t="s">
-        <v>99</v>
+        <v>151</v>
       </c>
       <c r="J304" s="1">
         <v>3030101</v>
@@ -10657,16 +10657,16 @@
         <v>37</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>165</v>
+        <v>64</v>
       </c>
       <c r="G305">
         <v>30</v>
       </c>
       <c r="H305" t="s">
-        <v>179</v>
+        <v>150</v>
       </c>
       <c r="I305" t="s">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="J305" s="1">
         <v>3010101</v>
@@ -10689,16 +10689,16 @@
         <v>37</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>165</v>
+        <v>64</v>
       </c>
       <c r="G306">
         <v>30</v>
       </c>
       <c r="H306" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="I306" t="s">
-        <v>99</v>
+        <v>151</v>
       </c>
       <c r="J306" s="1">
         <v>3030101</v>
@@ -10721,16 +10721,16 @@
         <v>37</v>
       </c>
       <c r="F307" s="1" t="s">
-        <v>165</v>
+        <v>64</v>
       </c>
       <c r="G307">
         <v>30</v>
       </c>
       <c r="H307" t="s">
-        <v>179</v>
+        <v>150</v>
       </c>
       <c r="I307" t="s">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="J307" s="1">
         <v>3010101</v>
@@ -10753,16 +10753,16 @@
         <v>37</v>
       </c>
       <c r="F308" s="1" t="s">
-        <v>165</v>
+        <v>64</v>
       </c>
       <c r="G308">
         <v>30</v>
       </c>
       <c r="H308" t="s">
-        <v>179</v>
+        <v>150</v>
       </c>
       <c r="I308" t="s">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="J308" s="1">
         <v>3010101</v>
@@ -10785,16 +10785,16 @@
         <v>38</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>166</v>
+        <v>65</v>
       </c>
       <c r="G309">
         <v>30</v>
       </c>
       <c r="H309" t="s">
-        <v>179</v>
+        <v>152</v>
       </c>
       <c r="I309" t="s">
-        <v>100</v>
+        <v>152</v>
       </c>
       <c r="J309" s="1">
         <v>3010101</v>
@@ -10817,16 +10817,16 @@
         <v>38</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>166</v>
+        <v>65</v>
       </c>
       <c r="G310">
         <v>30</v>
       </c>
       <c r="H310" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="I310" t="s">
-        <v>101</v>
+        <v>153</v>
       </c>
       <c r="J310" s="1">
         <v>3030101</v>
@@ -10849,16 +10849,16 @@
         <v>38</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>166</v>
+        <v>65</v>
       </c>
       <c r="G311">
         <v>30</v>
       </c>
       <c r="H311" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="I311" t="s">
-        <v>101</v>
+        <v>153</v>
       </c>
       <c r="J311" s="1">
         <v>3030101</v>
@@ -10881,16 +10881,16 @@
         <v>38</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>166</v>
+        <v>65</v>
       </c>
       <c r="G312">
         <v>30</v>
       </c>
       <c r="H312" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="I312" t="s">
-        <v>101</v>
+        <v>153</v>
       </c>
       <c r="J312" s="1">
         <v>3030101</v>
@@ -10913,16 +10913,16 @@
         <v>38</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>166</v>
+        <v>65</v>
       </c>
       <c r="G313">
         <v>30</v>
       </c>
       <c r="H313" t="s">
-        <v>179</v>
+        <v>152</v>
       </c>
       <c r="I313" t="s">
-        <v>100</v>
+        <v>152</v>
       </c>
       <c r="J313" s="1">
         <v>3010101</v>
@@ -10945,16 +10945,16 @@
         <v>38</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>166</v>
+        <v>65</v>
       </c>
       <c r="G314">
         <v>30</v>
       </c>
       <c r="H314" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="I314" t="s">
-        <v>101</v>
+        <v>153</v>
       </c>
       <c r="J314" s="1">
         <v>3030101</v>
@@ -10977,16 +10977,16 @@
         <v>38</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>166</v>
+        <v>65</v>
       </c>
       <c r="G315">
         <v>30</v>
       </c>
       <c r="H315" t="s">
-        <v>179</v>
+        <v>152</v>
       </c>
       <c r="I315" t="s">
-        <v>100</v>
+        <v>152</v>
       </c>
       <c r="J315" s="1">
         <v>3010101</v>
@@ -11009,16 +11009,16 @@
         <v>38</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>166</v>
+        <v>65</v>
       </c>
       <c r="G316">
         <v>30</v>
       </c>
       <c r="H316" t="s">
-        <v>179</v>
+        <v>152</v>
       </c>
       <c r="I316" t="s">
-        <v>100</v>
+        <v>152</v>
       </c>
       <c r="J316" s="1">
         <v>3010101</v>
@@ -11041,16 +11041,16 @@
         <v>39</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>167</v>
+        <v>66</v>
       </c>
       <c r="G317">
         <v>30</v>
       </c>
       <c r="H317" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="I317" t="s">
-        <v>102</v>
+        <v>154</v>
       </c>
       <c r="J317" s="1">
         <v>3010101</v>
@@ -11073,16 +11073,16 @@
         <v>39</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>167</v>
+        <v>66</v>
       </c>
       <c r="G318">
         <v>30</v>
       </c>
       <c r="H318" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="I318" t="s">
-        <v>103</v>
+        <v>155</v>
       </c>
       <c r="J318" s="1">
         <v>3030101</v>
@@ -11105,16 +11105,16 @@
         <v>39</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>167</v>
+        <v>66</v>
       </c>
       <c r="G319">
         <v>30</v>
       </c>
       <c r="H319" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="I319" t="s">
-        <v>103</v>
+        <v>155</v>
       </c>
       <c r="J319" s="1">
         <v>3030101</v>
@@ -11137,16 +11137,16 @@
         <v>39</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>167</v>
+        <v>66</v>
       </c>
       <c r="G320">
         <v>30</v>
       </c>
       <c r="H320" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="I320" t="s">
-        <v>103</v>
+        <v>155</v>
       </c>
       <c r="J320" s="1">
         <v>3030101</v>
@@ -11169,16 +11169,16 @@
         <v>39</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>167</v>
+        <v>66</v>
       </c>
       <c r="G321">
         <v>30</v>
       </c>
       <c r="H321" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="I321" t="s">
-        <v>102</v>
+        <v>154</v>
       </c>
       <c r="J321" s="1">
         <v>3010101</v>
@@ -11201,16 +11201,16 @@
         <v>39</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>167</v>
+        <v>66</v>
       </c>
       <c r="G322">
         <v>30</v>
       </c>
       <c r="H322" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="I322" t="s">
-        <v>103</v>
+        <v>155</v>
       </c>
       <c r="J322" s="1">
         <v>3030101</v>
@@ -11233,16 +11233,16 @@
         <v>39</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>167</v>
+        <v>66</v>
       </c>
       <c r="G323">
         <v>30</v>
       </c>
       <c r="H323" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="I323" t="s">
-        <v>102</v>
+        <v>154</v>
       </c>
       <c r="J323" s="1">
         <v>3010101</v>
@@ -11265,16 +11265,16 @@
         <v>39</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>167</v>
+        <v>66</v>
       </c>
       <c r="G324">
         <v>30</v>
       </c>
       <c r="H324" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="I324" t="s">
-        <v>102</v>
+        <v>154</v>
       </c>
       <c r="J324" s="1">
         <v>3010101</v>
@@ -11297,16 +11297,16 @@
         <v>40</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>168</v>
+        <v>67</v>
       </c>
       <c r="G325">
         <v>40</v>
       </c>
       <c r="H325" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="I325" t="s">
-        <v>104</v>
+        <v>156</v>
       </c>
       <c r="J325" s="1">
         <v>3010101</v>
@@ -11329,16 +11329,16 @@
         <v>40</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>168</v>
+        <v>67</v>
       </c>
       <c r="G326">
         <v>40</v>
       </c>
       <c r="H326" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="I326" t="s">
-        <v>105</v>
+        <v>157</v>
       </c>
       <c r="J326" s="1">
         <v>3030101</v>
@@ -11361,16 +11361,16 @@
         <v>40</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>168</v>
+        <v>67</v>
       </c>
       <c r="G327">
         <v>40</v>
       </c>
       <c r="H327" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="I327" t="s">
-        <v>105</v>
+        <v>157</v>
       </c>
       <c r="J327" s="1">
         <v>3030101</v>
@@ -11393,16 +11393,16 @@
         <v>40</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>168</v>
+        <v>67</v>
       </c>
       <c r="G328">
         <v>40</v>
       </c>
       <c r="H328" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="I328" t="s">
-        <v>105</v>
+        <v>157</v>
       </c>
       <c r="J328" s="1">
         <v>3030101</v>
@@ -11425,16 +11425,16 @@
         <v>40</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>168</v>
+        <v>67</v>
       </c>
       <c r="G329">
         <v>40</v>
       </c>
       <c r="H329" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="I329" t="s">
-        <v>104</v>
+        <v>156</v>
       </c>
       <c r="J329" s="1">
         <v>3010101</v>
@@ -11457,16 +11457,16 @@
         <v>40</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>168</v>
+        <v>67</v>
       </c>
       <c r="G330">
         <v>40</v>
       </c>
       <c r="H330" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="I330" t="s">
-        <v>105</v>
+        <v>157</v>
       </c>
       <c r="J330" s="1">
         <v>3030101</v>
@@ -11489,16 +11489,16 @@
         <v>40</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>168</v>
+        <v>67</v>
       </c>
       <c r="G331">
         <v>40</v>
       </c>
       <c r="H331" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="I331" t="s">
-        <v>104</v>
+        <v>156</v>
       </c>
       <c r="J331" s="1">
         <v>3010101</v>
@@ -11521,16 +11521,16 @@
         <v>40</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>168</v>
+        <v>67</v>
       </c>
       <c r="G332">
         <v>40</v>
       </c>
       <c r="H332" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="I332" t="s">
-        <v>104</v>
+        <v>156</v>
       </c>
       <c r="J332" s="1">
         <v>3010101</v>
@@ -11553,16 +11553,16 @@
         <v>41</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>169</v>
+        <v>68</v>
       </c>
       <c r="G333">
         <v>40</v>
       </c>
       <c r="H333" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="I333" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
       <c r="J333" s="1">
         <v>3010101</v>
@@ -11585,16 +11585,16 @@
         <v>41</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>169</v>
+        <v>68</v>
       </c>
       <c r="G334">
         <v>40</v>
       </c>
       <c r="H334" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="I334" t="s">
-        <v>107</v>
+        <v>159</v>
       </c>
       <c r="J334" s="1">
         <v>3030101</v>
@@ -11617,16 +11617,16 @@
         <v>41</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>169</v>
+        <v>68</v>
       </c>
       <c r="G335">
         <v>40</v>
       </c>
       <c r="H335" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="I335" t="s">
-        <v>107</v>
+        <v>159</v>
       </c>
       <c r="J335" s="1">
         <v>3030101</v>
@@ -11649,16 +11649,16 @@
         <v>41</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>169</v>
+        <v>68</v>
       </c>
       <c r="G336">
         <v>40</v>
       </c>
       <c r="H336" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="I336" t="s">
-        <v>107</v>
+        <v>159</v>
       </c>
       <c r="J336" s="1">
         <v>3030101</v>
@@ -11681,16 +11681,16 @@
         <v>41</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>169</v>
+        <v>68</v>
       </c>
       <c r="G337">
         <v>40</v>
       </c>
       <c r="H337" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="I337" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
       <c r="J337" s="1">
         <v>3010101</v>
@@ -11713,16 +11713,16 @@
         <v>41</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>169</v>
+        <v>68</v>
       </c>
       <c r="G338">
         <v>40</v>
       </c>
       <c r="H338" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="I338" t="s">
-        <v>107</v>
+        <v>159</v>
       </c>
       <c r="J338" s="1">
         <v>3030101</v>
@@ -11745,16 +11745,16 @@
         <v>41</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>169</v>
+        <v>68</v>
       </c>
       <c r="G339">
         <v>40</v>
       </c>
       <c r="H339" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="I339" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
       <c r="J339" s="1">
         <v>3010101</v>
@@ -11777,16 +11777,16 @@
         <v>41</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>169</v>
+        <v>68</v>
       </c>
       <c r="G340">
         <v>40</v>
       </c>
       <c r="H340" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="I340" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
       <c r="J340" s="1">
         <v>3010101</v>
@@ -11809,16 +11809,16 @@
         <v>42</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>170</v>
+        <v>69</v>
       </c>
       <c r="G341">
         <v>40</v>
       </c>
       <c r="H341" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="I341" t="s">
-        <v>108</v>
+        <v>160</v>
       </c>
       <c r="J341" s="1">
         <v>3010101</v>
@@ -11841,16 +11841,16 @@
         <v>42</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>170</v>
+        <v>69</v>
       </c>
       <c r="G342">
         <v>40</v>
       </c>
       <c r="H342" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="I342" t="s">
-        <v>109</v>
+        <v>161</v>
       </c>
       <c r="J342" s="1">
         <v>3030101</v>
@@ -11873,16 +11873,16 @@
         <v>42</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>170</v>
+        <v>69</v>
       </c>
       <c r="G343">
         <v>40</v>
       </c>
       <c r="H343" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="I343" t="s">
-        <v>109</v>
+        <v>161</v>
       </c>
       <c r="J343" s="1">
         <v>3030101</v>
@@ -11905,16 +11905,16 @@
         <v>42</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>170</v>
+        <v>69</v>
       </c>
       <c r="G344">
         <v>40</v>
       </c>
       <c r="H344" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="I344" t="s">
-        <v>109</v>
+        <v>161</v>
       </c>
       <c r="J344" s="1">
         <v>3030101</v>
@@ -11937,16 +11937,16 @@
         <v>42</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>170</v>
+        <v>69</v>
       </c>
       <c r="G345">
         <v>40</v>
       </c>
       <c r="H345" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="I345" t="s">
-        <v>108</v>
+        <v>160</v>
       </c>
       <c r="J345" s="1">
         <v>3010101</v>
@@ -11969,16 +11969,16 @@
         <v>42</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>170</v>
+        <v>69</v>
       </c>
       <c r="G346">
         <v>40</v>
       </c>
       <c r="H346" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="I346" t="s">
-        <v>109</v>
+        <v>161</v>
       </c>
       <c r="J346" s="1">
         <v>3030101</v>
@@ -12001,16 +12001,16 @@
         <v>42</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>170</v>
+        <v>69</v>
       </c>
       <c r="G347">
         <v>40</v>
       </c>
       <c r="H347" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="I347" t="s">
-        <v>108</v>
+        <v>160</v>
       </c>
       <c r="J347" s="1">
         <v>3010101</v>
@@ -12033,16 +12033,16 @@
         <v>42</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>170</v>
+        <v>69</v>
       </c>
       <c r="G348">
         <v>40</v>
       </c>
       <c r="H348" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="I348" t="s">
-        <v>108</v>
+        <v>160</v>
       </c>
       <c r="J348" s="1">
         <v>3010101</v>
@@ -12065,16 +12065,16 @@
         <v>43</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>171</v>
+        <v>70</v>
       </c>
       <c r="G349">
         <v>40</v>
       </c>
       <c r="H349" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="I349" t="s">
-        <v>110</v>
+        <v>162</v>
       </c>
       <c r="J349" s="1">
         <v>3010101</v>
@@ -12097,16 +12097,16 @@
         <v>43</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>171</v>
+        <v>70</v>
       </c>
       <c r="G350">
         <v>40</v>
       </c>
       <c r="H350" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="I350" t="s">
-        <v>111</v>
+        <v>163</v>
       </c>
       <c r="J350" s="1">
         <v>3030101</v>
@@ -12129,16 +12129,16 @@
         <v>43</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>171</v>
+        <v>70</v>
       </c>
       <c r="G351">
         <v>40</v>
       </c>
       <c r="H351" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="I351" t="s">
-        <v>111</v>
+        <v>163</v>
       </c>
       <c r="J351" s="1">
         <v>3030101</v>
@@ -12161,16 +12161,16 @@
         <v>43</v>
       </c>
       <c r="F352" s="1" t="s">
-        <v>171</v>
+        <v>70</v>
       </c>
       <c r="G352">
         <v>40</v>
       </c>
       <c r="H352" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="I352" t="s">
-        <v>111</v>
+        <v>163</v>
       </c>
       <c r="J352" s="1">
         <v>3030101</v>
@@ -12193,16 +12193,16 @@
         <v>43</v>
       </c>
       <c r="F353" s="1" t="s">
-        <v>171</v>
+        <v>70</v>
       </c>
       <c r="G353">
         <v>40</v>
       </c>
       <c r="H353" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="I353" t="s">
-        <v>110</v>
+        <v>162</v>
       </c>
       <c r="J353" s="1">
         <v>3010101</v>
@@ -12225,16 +12225,16 @@
         <v>43</v>
       </c>
       <c r="F354" s="1" t="s">
-        <v>171</v>
+        <v>70</v>
       </c>
       <c r="G354">
         <v>40</v>
       </c>
       <c r="H354" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="I354" t="s">
-        <v>111</v>
+        <v>163</v>
       </c>
       <c r="J354" s="1">
         <v>3030101</v>
@@ -12257,16 +12257,16 @@
         <v>43</v>
       </c>
       <c r="F355" s="1" t="s">
-        <v>171</v>
+        <v>70</v>
       </c>
       <c r="G355">
         <v>40</v>
       </c>
       <c r="H355" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="I355" t="s">
-        <v>110</v>
+        <v>162</v>
       </c>
       <c r="J355" s="1">
         <v>3010101</v>
@@ -12289,16 +12289,16 @@
         <v>43</v>
       </c>
       <c r="F356" s="1" t="s">
-        <v>171</v>
+        <v>70</v>
       </c>
       <c r="G356">
         <v>40</v>
       </c>
       <c r="H356" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="I356" t="s">
-        <v>110</v>
+        <v>162</v>
       </c>
       <c r="J356" s="1">
         <v>3010101</v>
@@ -12321,16 +12321,16 @@
         <v>44</v>
       </c>
       <c r="F357" s="1" t="s">
-        <v>172</v>
+        <v>71</v>
       </c>
       <c r="G357">
         <v>40</v>
       </c>
       <c r="H357" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="I357" t="s">
-        <v>112</v>
+        <v>164</v>
       </c>
       <c r="J357" s="1">
         <v>3010101</v>
@@ -12353,16 +12353,16 @@
         <v>44</v>
       </c>
       <c r="F358" s="1" t="s">
-        <v>172</v>
+        <v>71</v>
       </c>
       <c r="G358">
         <v>40</v>
       </c>
       <c r="H358" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="I358" t="s">
-        <v>113</v>
+        <v>165</v>
       </c>
       <c r="J358" s="1">
         <v>3030101</v>
@@ -12385,16 +12385,16 @@
         <v>44</v>
       </c>
       <c r="F359" s="1" t="s">
-        <v>172</v>
+        <v>71</v>
       </c>
       <c r="G359">
         <v>40</v>
       </c>
       <c r="H359" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="I359" t="s">
-        <v>113</v>
+        <v>165</v>
       </c>
       <c r="J359" s="1">
         <v>3030101</v>
@@ -12417,16 +12417,16 @@
         <v>44</v>
       </c>
       <c r="F360" s="1" t="s">
-        <v>172</v>
+        <v>71</v>
       </c>
       <c r="G360">
         <v>40</v>
       </c>
       <c r="H360" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="I360" t="s">
-        <v>113</v>
+        <v>165</v>
       </c>
       <c r="J360" s="1">
         <v>3030101</v>
@@ -12449,16 +12449,16 @@
         <v>44</v>
       </c>
       <c r="F361" s="1" t="s">
-        <v>172</v>
+        <v>71</v>
       </c>
       <c r="G361">
         <v>40</v>
       </c>
       <c r="H361" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="I361" t="s">
-        <v>112</v>
+        <v>164</v>
       </c>
       <c r="J361" s="1">
         <v>3010101</v>
@@ -12481,16 +12481,16 @@
         <v>44</v>
       </c>
       <c r="F362" s="1" t="s">
-        <v>172</v>
+        <v>71</v>
       </c>
       <c r="G362">
         <v>40</v>
       </c>
       <c r="H362" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="I362" t="s">
-        <v>113</v>
+        <v>165</v>
       </c>
       <c r="J362" s="1">
         <v>3030101</v>
@@ -12513,16 +12513,16 @@
         <v>44</v>
       </c>
       <c r="F363" s="1" t="s">
-        <v>172</v>
+        <v>71</v>
       </c>
       <c r="G363">
         <v>40</v>
       </c>
       <c r="H363" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="I363" t="s">
-        <v>112</v>
+        <v>164</v>
       </c>
       <c r="J363" s="1">
         <v>3010101</v>
@@ -12545,16 +12545,16 @@
         <v>44</v>
       </c>
       <c r="F364" s="1" t="s">
-        <v>172</v>
+        <v>71</v>
       </c>
       <c r="G364">
         <v>40</v>
       </c>
       <c r="H364" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="I364" t="s">
-        <v>112</v>
+        <v>164</v>
       </c>
       <c r="J364" s="1">
         <v>3010101</v>
@@ -12577,16 +12577,16 @@
         <v>45</v>
       </c>
       <c r="F365" s="1" t="s">
-        <v>173</v>
+        <v>72</v>
       </c>
       <c r="G365">
         <v>40</v>
       </c>
       <c r="H365" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="I365" t="s">
-        <v>114</v>
+        <v>166</v>
       </c>
       <c r="J365" s="1">
         <v>3010101</v>
@@ -12609,16 +12609,16 @@
         <v>45</v>
       </c>
       <c r="F366" s="1" t="s">
-        <v>173</v>
+        <v>72</v>
       </c>
       <c r="G366">
         <v>40</v>
       </c>
       <c r="H366" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="I366" t="s">
-        <v>115</v>
+        <v>167</v>
       </c>
       <c r="J366" s="1">
         <v>3030101</v>
@@ -12641,16 +12641,16 @@
         <v>45</v>
       </c>
       <c r="F367" s="1" t="s">
-        <v>173</v>
+        <v>72</v>
       </c>
       <c r="G367">
         <v>40</v>
       </c>
       <c r="H367" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="I367" t="s">
-        <v>115</v>
+        <v>167</v>
       </c>
       <c r="J367" s="1">
         <v>3030101</v>
@@ -12673,16 +12673,16 @@
         <v>45</v>
       </c>
       <c r="F368" s="1" t="s">
-        <v>173</v>
+        <v>72</v>
       </c>
       <c r="G368">
         <v>40</v>
       </c>
       <c r="H368" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="I368" t="s">
-        <v>115</v>
+        <v>167</v>
       </c>
       <c r="J368" s="1">
         <v>3030101</v>
@@ -12705,16 +12705,16 @@
         <v>45</v>
       </c>
       <c r="F369" s="1" t="s">
-        <v>173</v>
+        <v>72</v>
       </c>
       <c r="G369">
         <v>40</v>
       </c>
       <c r="H369" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="I369" t="s">
-        <v>114</v>
+        <v>166</v>
       </c>
       <c r="J369" s="1">
         <v>3010101</v>
@@ -12737,16 +12737,16 @@
         <v>45</v>
       </c>
       <c r="F370" s="1" t="s">
-        <v>173</v>
+        <v>72</v>
       </c>
       <c r="G370">
         <v>40</v>
       </c>
       <c r="H370" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="I370" t="s">
-        <v>115</v>
+        <v>167</v>
       </c>
       <c r="J370" s="1">
         <v>3030101</v>
@@ -12769,16 +12769,16 @@
         <v>45</v>
       </c>
       <c r="F371" s="1" t="s">
-        <v>173</v>
+        <v>72</v>
       </c>
       <c r="G371">
         <v>40</v>
       </c>
       <c r="H371" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="I371" t="s">
-        <v>114</v>
+        <v>166</v>
       </c>
       <c r="J371" s="1">
         <v>3010101</v>
@@ -12801,16 +12801,16 @@
         <v>45</v>
       </c>
       <c r="F372" s="1" t="s">
-        <v>173</v>
+        <v>72</v>
       </c>
       <c r="G372">
         <v>40</v>
       </c>
       <c r="H372" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="I372" t="s">
-        <v>114</v>
+        <v>166</v>
       </c>
       <c r="J372" s="1">
         <v>3010101</v>
@@ -12833,16 +12833,16 @@
         <v>46</v>
       </c>
       <c r="F373" s="1" t="s">
-        <v>174</v>
+        <v>73</v>
       </c>
       <c r="G373">
         <v>40</v>
       </c>
       <c r="H373" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="I373" t="s">
-        <v>116</v>
+        <v>168</v>
       </c>
       <c r="J373" s="1">
         <v>3010101</v>
@@ -12865,16 +12865,16 @@
         <v>46</v>
       </c>
       <c r="F374" s="1" t="s">
-        <v>174</v>
+        <v>73</v>
       </c>
       <c r="G374">
         <v>40</v>
       </c>
       <c r="H374" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="I374" t="s">
-        <v>117</v>
+        <v>169</v>
       </c>
       <c r="J374" s="1">
         <v>3030101</v>
@@ -12897,16 +12897,16 @@
         <v>46</v>
       </c>
       <c r="F375" s="1" t="s">
-        <v>174</v>
+        <v>73</v>
       </c>
       <c r="G375">
         <v>40</v>
       </c>
       <c r="H375" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="I375" t="s">
-        <v>117</v>
+        <v>169</v>
       </c>
       <c r="J375" s="1">
         <v>3030101</v>
@@ -12929,16 +12929,16 @@
         <v>46</v>
       </c>
       <c r="F376" s="1" t="s">
-        <v>174</v>
+        <v>73</v>
       </c>
       <c r="G376">
         <v>40</v>
       </c>
       <c r="H376" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="I376" t="s">
-        <v>117</v>
+        <v>169</v>
       </c>
       <c r="J376" s="1">
         <v>3030101</v>
@@ -12961,16 +12961,16 @@
         <v>46</v>
       </c>
       <c r="F377" s="1" t="s">
-        <v>174</v>
+        <v>73</v>
       </c>
       <c r="G377">
         <v>40</v>
       </c>
       <c r="H377" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="I377" t="s">
-        <v>116</v>
+        <v>168</v>
       </c>
       <c r="J377" s="1">
         <v>3010101</v>
@@ -12993,16 +12993,16 @@
         <v>46</v>
       </c>
       <c r="F378" s="1" t="s">
-        <v>174</v>
+        <v>73</v>
       </c>
       <c r="G378">
         <v>40</v>
       </c>
       <c r="H378" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="I378" t="s">
-        <v>117</v>
+        <v>169</v>
       </c>
       <c r="J378" s="1">
         <v>3030101</v>
@@ -13025,16 +13025,16 @@
         <v>46</v>
       </c>
       <c r="F379" s="1" t="s">
-        <v>174</v>
+        <v>73</v>
       </c>
       <c r="G379">
         <v>40</v>
       </c>
       <c r="H379" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="I379" t="s">
-        <v>116</v>
+        <v>168</v>
       </c>
       <c r="J379" s="1">
         <v>3010101</v>
@@ -13057,16 +13057,16 @@
         <v>46</v>
       </c>
       <c r="F380" s="1" t="s">
-        <v>174</v>
+        <v>73</v>
       </c>
       <c r="G380">
         <v>40</v>
       </c>
       <c r="H380" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="I380" t="s">
-        <v>116</v>
+        <v>168</v>
       </c>
       <c r="J380" s="1">
         <v>3010101</v>
@@ -13089,16 +13089,16 @@
         <v>47</v>
       </c>
       <c r="F381" s="1" t="s">
-        <v>175</v>
+        <v>74</v>
       </c>
       <c r="G381">
         <v>40</v>
       </c>
       <c r="H381" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="I381" t="s">
-        <v>118</v>
+        <v>170</v>
       </c>
       <c r="J381" s="1">
         <v>3010101</v>
@@ -13121,16 +13121,16 @@
         <v>47</v>
       </c>
       <c r="F382" s="1" t="s">
-        <v>175</v>
+        <v>74</v>
       </c>
       <c r="G382">
         <v>40</v>
       </c>
       <c r="H382" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="I382" t="s">
-        <v>119</v>
+        <v>171</v>
       </c>
       <c r="J382" s="1">
         <v>3030101</v>
@@ -13153,16 +13153,16 @@
         <v>47</v>
       </c>
       <c r="F383" s="1" t="s">
-        <v>175</v>
+        <v>74</v>
       </c>
       <c r="G383">
         <v>40</v>
       </c>
       <c r="H383" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="I383" t="s">
-        <v>119</v>
+        <v>171</v>
       </c>
       <c r="J383" s="1">
         <v>3030101</v>
@@ -13185,16 +13185,16 @@
         <v>47</v>
       </c>
       <c r="F384" s="1" t="s">
-        <v>175</v>
+        <v>74</v>
       </c>
       <c r="G384">
         <v>40</v>
       </c>
       <c r="H384" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="I384" t="s">
-        <v>119</v>
+        <v>171</v>
       </c>
       <c r="J384" s="1">
         <v>3030101</v>
@@ -13217,16 +13217,16 @@
         <v>47</v>
       </c>
       <c r="F385" s="1" t="s">
-        <v>175</v>
+        <v>74</v>
       </c>
       <c r="G385">
         <v>40</v>
       </c>
       <c r="H385" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="I385" t="s">
-        <v>118</v>
+        <v>170</v>
       </c>
       <c r="J385" s="1">
         <v>3010101</v>
@@ -13249,16 +13249,16 @@
         <v>47</v>
       </c>
       <c r="F386" s="1" t="s">
-        <v>175</v>
+        <v>74</v>
       </c>
       <c r="G386">
         <v>40</v>
       </c>
       <c r="H386" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="I386" t="s">
-        <v>119</v>
+        <v>171</v>
       </c>
       <c r="J386" s="1">
         <v>3030101</v>
@@ -13281,16 +13281,16 @@
         <v>47</v>
       </c>
       <c r="F387" s="1" t="s">
-        <v>175</v>
+        <v>74</v>
       </c>
       <c r="G387">
         <v>40</v>
       </c>
       <c r="H387" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="I387" t="s">
-        <v>118</v>
+        <v>170</v>
       </c>
       <c r="J387" s="1">
         <v>3010101</v>
@@ -13313,16 +13313,16 @@
         <v>47</v>
       </c>
       <c r="F388" s="1" t="s">
-        <v>175</v>
+        <v>74</v>
       </c>
       <c r="G388">
         <v>40</v>
       </c>
       <c r="H388" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="I388" t="s">
-        <v>118</v>
+        <v>170</v>
       </c>
       <c r="J388" s="1">
         <v>3010101</v>
@@ -13345,16 +13345,16 @@
         <v>48</v>
       </c>
       <c r="F389" s="1" t="s">
-        <v>176</v>
+        <v>75</v>
       </c>
       <c r="G389">
         <v>40</v>
       </c>
       <c r="H389" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="I389" t="s">
-        <v>120</v>
+        <v>172</v>
       </c>
       <c r="J389" s="1">
         <v>3010101</v>
@@ -13377,16 +13377,16 @@
         <v>48</v>
       </c>
       <c r="F390" s="1" t="s">
-        <v>176</v>
+        <v>75</v>
       </c>
       <c r="G390">
         <v>40</v>
       </c>
       <c r="H390" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="I390" t="s">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="J390" s="1">
         <v>3030101</v>
@@ -13409,16 +13409,16 @@
         <v>48</v>
       </c>
       <c r="F391" s="1" t="s">
-        <v>176</v>
+        <v>75</v>
       </c>
       <c r="G391">
         <v>40</v>
       </c>
       <c r="H391" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="I391" t="s">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="J391" s="1">
         <v>3030101</v>
@@ -13441,16 +13441,16 @@
         <v>48</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>176</v>
+        <v>75</v>
       </c>
       <c r="G392">
         <v>40</v>
       </c>
       <c r="H392" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="I392" t="s">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="J392" s="1">
         <v>3030101</v>
@@ -13473,16 +13473,16 @@
         <v>48</v>
       </c>
       <c r="F393" s="1" t="s">
-        <v>176</v>
+        <v>75</v>
       </c>
       <c r="G393">
         <v>40</v>
       </c>
       <c r="H393" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="I393" t="s">
-        <v>120</v>
+        <v>172</v>
       </c>
       <c r="J393" s="1">
         <v>3010101</v>
@@ -13505,16 +13505,16 @@
         <v>48</v>
       </c>
       <c r="F394" s="1" t="s">
-        <v>176</v>
+        <v>75</v>
       </c>
       <c r="G394">
         <v>40</v>
       </c>
       <c r="H394" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="I394" t="s">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="J394" s="1">
         <v>3030101</v>
@@ -13537,16 +13537,16 @@
         <v>48</v>
       </c>
       <c r="F395" s="1" t="s">
-        <v>176</v>
+        <v>75</v>
       </c>
       <c r="G395">
         <v>40</v>
       </c>
       <c r="H395" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="I395" t="s">
-        <v>120</v>
+        <v>172</v>
       </c>
       <c r="J395" s="1">
         <v>3010101</v>
@@ -13569,16 +13569,16 @@
         <v>48</v>
       </c>
       <c r="F396" s="1" t="s">
-        <v>176</v>
+        <v>75</v>
       </c>
       <c r="G396">
         <v>40</v>
       </c>
       <c r="H396" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="I396" t="s">
-        <v>120</v>
+        <v>172</v>
       </c>
       <c r="J396" s="1">
         <v>3010101</v>
@@ -13601,16 +13601,16 @@
         <v>49</v>
       </c>
       <c r="F397" s="1" t="s">
-        <v>177</v>
+        <v>76</v>
       </c>
       <c r="G397">
         <v>40</v>
       </c>
       <c r="H397" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I397" t="s">
-        <v>122</v>
+        <v>174</v>
       </c>
       <c r="J397" s="1">
         <v>3010101</v>
@@ -13633,16 +13633,16 @@
         <v>49</v>
       </c>
       <c r="F398" s="1" t="s">
-        <v>177</v>
+        <v>76</v>
       </c>
       <c r="G398">
         <v>40</v>
       </c>
       <c r="H398" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="I398" t="s">
-        <v>123</v>
+        <v>175</v>
       </c>
       <c r="J398" s="1">
         <v>3030101</v>
@@ -13665,16 +13665,16 @@
         <v>49</v>
       </c>
       <c r="F399" s="1" t="s">
-        <v>177</v>
+        <v>76</v>
       </c>
       <c r="G399">
         <v>40</v>
       </c>
       <c r="H399" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="I399" t="s">
-        <v>123</v>
+        <v>175</v>
       </c>
       <c r="J399" s="1">
         <v>3030101</v>
@@ -13697,16 +13697,16 @@
         <v>49</v>
       </c>
       <c r="F400" s="1" t="s">
-        <v>177</v>
+        <v>76</v>
       </c>
       <c r="G400">
         <v>40</v>
       </c>
       <c r="H400" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="I400" t="s">
-        <v>123</v>
+        <v>175</v>
       </c>
       <c r="J400" s="1">
         <v>3030101</v>
@@ -13729,16 +13729,16 @@
         <v>49</v>
       </c>
       <c r="F401" s="1" t="s">
-        <v>177</v>
+        <v>76</v>
       </c>
       <c r="G401">
         <v>40</v>
       </c>
       <c r="H401" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I401" t="s">
-        <v>122</v>
+        <v>174</v>
       </c>
       <c r="J401" s="1">
         <v>3010101</v>
@@ -13761,16 +13761,16 @@
         <v>49</v>
       </c>
       <c r="F402" s="1" t="s">
-        <v>177</v>
+        <v>76</v>
       </c>
       <c r="G402">
         <v>40</v>
       </c>
       <c r="H402" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="I402" t="s">
-        <v>123</v>
+        <v>175</v>
       </c>
       <c r="J402" s="1">
         <v>3030101</v>
@@ -13793,16 +13793,16 @@
         <v>49</v>
       </c>
       <c r="F403" s="1" t="s">
-        <v>177</v>
+        <v>76</v>
       </c>
       <c r="G403">
         <v>40</v>
       </c>
       <c r="H403" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I403" t="s">
-        <v>122</v>
+        <v>174</v>
       </c>
       <c r="J403" s="1">
         <v>3010101</v>
@@ -13825,16 +13825,16 @@
         <v>49</v>
       </c>
       <c r="F404" s="1" t="s">
-        <v>177</v>
+        <v>76</v>
       </c>
       <c r="G404">
         <v>40</v>
       </c>
       <c r="H404" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I404" t="s">
-        <v>122</v>
+        <v>174</v>
       </c>
       <c r="J404" s="1">
         <v>3010101</v>
@@ -13857,16 +13857,16 @@
         <v>50</v>
       </c>
       <c r="F405" s="1" t="s">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="G405">
         <v>50</v>
       </c>
       <c r="H405" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I405" t="s">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="J405" s="1">
         <v>3010101</v>
@@ -13889,16 +13889,16 @@
         <v>50</v>
       </c>
       <c r="F406" s="1" t="s">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="G406">
         <v>50</v>
       </c>
       <c r="H406" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I406" t="s">
-        <v>125</v>
+        <v>177</v>
       </c>
       <c r="J406" s="1">
         <v>3030101</v>
@@ -13921,16 +13921,16 @@
         <v>50</v>
       </c>
       <c r="F407" s="1" t="s">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="G407">
         <v>50</v>
       </c>
       <c r="H407" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I407" t="s">
-        <v>125</v>
+        <v>177</v>
       </c>
       <c r="J407" s="1">
         <v>3030101</v>
@@ -13953,16 +13953,16 @@
         <v>50</v>
       </c>
       <c r="F408" s="1" t="s">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="G408">
         <v>50</v>
       </c>
       <c r="H408" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I408" t="s">
-        <v>125</v>
+        <v>177</v>
       </c>
       <c r="J408" s="1">
         <v>3030101</v>
@@ -13985,16 +13985,16 @@
         <v>50</v>
       </c>
       <c r="F409" s="1" t="s">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="G409">
         <v>50</v>
       </c>
       <c r="H409" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I409" t="s">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="J409" s="1">
         <v>3010101</v>
@@ -14017,16 +14017,16 @@
         <v>50</v>
       </c>
       <c r="F410" s="1" t="s">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="G410">
         <v>50</v>
       </c>
       <c r="H410" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I410" t="s">
-        <v>125</v>
+        <v>177</v>
       </c>
       <c r="J410" s="1">
         <v>3030101</v>
@@ -14049,16 +14049,16 @@
         <v>50</v>
       </c>
       <c r="F411" s="1" t="s">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="G411">
         <v>50</v>
       </c>
       <c r="H411" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I411" t="s">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="J411" s="1">
         <v>3010101</v>
@@ -14081,16 +14081,16 @@
         <v>50</v>
       </c>
       <c r="F412" s="1" t="s">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="G412">
         <v>50</v>
       </c>
       <c r="H412" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I412" t="s">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="J412" s="1">
         <v>3010101</v>

--- a/servers/maze_main_server/conf.d/data/maze_equip_pos_lv_v8【迷宫-装备-部位强化等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_equip_pos_lv_v8【迷宫-装备-部位强化等级】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD327C64-3907-4706-867A-5B2CC47490B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54FC6266-A460-4EE5-8F3D-1E0EF451DF8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -127,9 +127,6 @@
     <t>展示属性排序</t>
   </si>
   <si>
-    <t>0:0</t>
-  </si>
-  <si>
     <t>升到下一级需要探险等级</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -138,159 +135,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>46200001:10_46700001:2</t>
-  </si>
-  <si>
-    <t>46200001:50_46700001:4</t>
-  </si>
-  <si>
-    <t>46200001:100_46700001:6</t>
-  </si>
-  <si>
-    <t>46200001:150_46700001:8</t>
-  </si>
-  <si>
-    <t>46200001:200_46700001:10</t>
-  </si>
-  <si>
-    <t>46200001:250_46700001:12</t>
-  </si>
-  <si>
-    <t>46200001:300_46700001:14</t>
-  </si>
-  <si>
-    <t>46200001:350_46700001:16</t>
-  </si>
-  <si>
-    <t>46200001:400_46700001:18</t>
-  </si>
-  <si>
-    <t>46200001:450_46700001:20</t>
-  </si>
-  <si>
-    <t>46200001:500_46700001:22</t>
-  </si>
-  <si>
-    <t>46200001:550_46700001:24</t>
-  </si>
-  <si>
-    <t>46200001:600_46700001:26</t>
-  </si>
-  <si>
-    <t>46200001:650_46700001:28</t>
-  </si>
-  <si>
-    <t>46200001:700_46700001:30</t>
-  </si>
-  <si>
-    <t>46200001:750_46700001:32</t>
-  </si>
-  <si>
-    <t>46200001:800_46700001:34</t>
-  </si>
-  <si>
-    <t>46200001:850_46700001:36</t>
-  </si>
-  <si>
-    <t>46200001:900_46700001:38</t>
-  </si>
-  <si>
-    <t>46200001:950_46700001:40</t>
-  </si>
-  <si>
-    <t>46200001:1000_46700001:42</t>
-  </si>
-  <si>
-    <t>46200001:1050_46700001:44</t>
-  </si>
-  <si>
-    <t>46200001:1100_46700001:46</t>
-  </si>
-  <si>
-    <t>46200001:1150_46700001:48</t>
-  </si>
-  <si>
-    <t>46200001:1200_46700001:50</t>
-  </si>
-  <si>
-    <t>46200001:1250_46700001:52</t>
-  </si>
-  <si>
-    <t>46200001:1300_46700001:54</t>
-  </si>
-  <si>
-    <t>46200001:1350_46700001:56</t>
-  </si>
-  <si>
-    <t>46200001:1400_46700001:58</t>
-  </si>
-  <si>
-    <t>46200001:1450_46700001:60</t>
-  </si>
-  <si>
-    <t>46200001:1500_46700001:62</t>
-  </si>
-  <si>
-    <t>46200001:1550_46700001:64</t>
-  </si>
-  <si>
-    <t>46200001:1600_46700001:66</t>
-  </si>
-  <si>
-    <t>46200001:1650_46700001:68</t>
-  </si>
-  <si>
-    <t>46200001:1700_46700001:70</t>
-  </si>
-  <si>
-    <t>46200001:1750_46700001:72</t>
-  </si>
-  <si>
-    <t>46200001:1800_46700001:74</t>
-  </si>
-  <si>
-    <t>46200001:1850_46700001:76</t>
-  </si>
-  <si>
-    <t>46200001:1900_46700001:78</t>
-  </si>
-  <si>
-    <t>46200001:1950_46700001:80</t>
-  </si>
-  <si>
-    <t>46200001:2000_46700001:82</t>
-  </si>
-  <si>
-    <t>46200001:2050_46700001:84</t>
-  </si>
-  <si>
-    <t>46200001:2100_46700001:86</t>
-  </si>
-  <si>
-    <t>46200001:2150_46700001:88</t>
-  </si>
-  <si>
-    <t>46200001:2200_46700001:90</t>
-  </si>
-  <si>
-    <t>46200001:2250_46700001:92</t>
-  </si>
-  <si>
-    <t>46200001:2300_46700001:94</t>
-  </si>
-  <si>
-    <t>46200001:2350_46700001:96</t>
-  </si>
-  <si>
-    <t>46200001:2400_46700001:98</t>
-  </si>
-  <si>
-    <t>46200001:2450_46700001:100</t>
-  </si>
-  <si>
-    <t>46200001:2500_46700001:102</t>
-  </si>
-  <si>
     <t>3010101:2</t>
   </si>
   <si>
@@ -595,6 +439,162 @@
   </si>
   <si>
     <t>3030101:0</t>
+  </si>
+  <si>
+    <t>46200001:20_46700001:2</t>
+  </si>
+  <si>
+    <t>46200001:50_46700001:6</t>
+  </si>
+  <si>
+    <t>46200001:80_46700001:10</t>
+  </si>
+  <si>
+    <t>46200001:120_46700001:15</t>
+  </si>
+  <si>
+    <t>46200001:160_46700001:20</t>
+  </si>
+  <si>
+    <t>46200001:200_46700001:25</t>
+  </si>
+  <si>
+    <t>46200001:250_46700001:30</t>
+  </si>
+  <si>
+    <t>46200001:300_46700001:35</t>
+  </si>
+  <si>
+    <t>46200001:350_46700001:40</t>
+  </si>
+  <si>
+    <t>46200001:400_46700001:45</t>
+  </si>
+  <si>
+    <t>46200001:450_46700001:50</t>
+  </si>
+  <si>
+    <t>46200001:500_46700001:55</t>
+  </si>
+  <si>
+    <t>46200001:550_46700001:60</t>
+  </si>
+  <si>
+    <t>46200001:600_46700001:65</t>
+  </si>
+  <si>
+    <t>46200001:650_46700001:70</t>
+  </si>
+  <si>
+    <t>46200001:700_46700001:75</t>
+  </si>
+  <si>
+    <t>46200001:750_46700001:80</t>
+  </si>
+  <si>
+    <t>46200001:800_46700001:85</t>
+  </si>
+  <si>
+    <t>46200001:850_46700001:90</t>
+  </si>
+  <si>
+    <t>46200001:900_46700001:95</t>
+  </si>
+  <si>
+    <t>46200001:950_46700001:100</t>
+  </si>
+  <si>
+    <t>46200001:1000_46700001:105</t>
+  </si>
+  <si>
+    <t>46200001:1050_46700001:110</t>
+  </si>
+  <si>
+    <t>46200001:1100_46700001:115</t>
+  </si>
+  <si>
+    <t>46200001:1150_46700001:120</t>
+  </si>
+  <si>
+    <t>46200001:1200_46700001:125</t>
+  </si>
+  <si>
+    <t>46200001:1250_46700001:130</t>
+  </si>
+  <si>
+    <t>46200001:1300_46700001:135</t>
+  </si>
+  <si>
+    <t>46200001:1350_46700001:140</t>
+  </si>
+  <si>
+    <t>46200001:1400_46700001:145</t>
+  </si>
+  <si>
+    <t>46200001:1450_46700001:150</t>
+  </si>
+  <si>
+    <t>46200001:1500_46700001:155</t>
+  </si>
+  <si>
+    <t>46200001:1550_46700001:160</t>
+  </si>
+  <si>
+    <t>46200001:1600_46700001:165</t>
+  </si>
+  <si>
+    <t>46200001:1650_46700001:170</t>
+  </si>
+  <si>
+    <t>46200001:1700_46700001:175</t>
+  </si>
+  <si>
+    <t>46200001:1750_46700001:180</t>
+  </si>
+  <si>
+    <t>46200001:1800_46700001:185</t>
+  </si>
+  <si>
+    <t>46200001:1850_46700001:190</t>
+  </si>
+  <si>
+    <t>46200001:1900_46700001:195</t>
+  </si>
+  <si>
+    <t>46200001:1950_46700001:200</t>
+  </si>
+  <si>
+    <t>46200001:2000_46700001:205</t>
+  </si>
+  <si>
+    <t>46200001:2050_46700001:210</t>
+  </si>
+  <si>
+    <t>46200001:2100_46700001:215</t>
+  </si>
+  <si>
+    <t>46200001:2150_46700001:220</t>
+  </si>
+  <si>
+    <t>46200001:2200_46700001:225</t>
+  </si>
+  <si>
+    <t>46200001:2250_46700001:230</t>
+  </si>
+  <si>
+    <t>46200001:2300_46700001:235</t>
+  </si>
+  <si>
+    <t>46200001:2350_46700001:240</t>
+  </si>
+  <si>
+    <t>46200001:2400_46700001:245</t>
+  </si>
+  <si>
+    <t>46200001:2450_46700001:250</t>
+  </si>
+  <si>
+    <t>8101:0</t>
   </si>
 </sst>
 </file>
@@ -996,7 +996,7 @@
         <v>10</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
         <v>18</v>
@@ -1028,7 +1028,7 @@
         <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H4" t="s">
         <v>21</v>
@@ -1057,16 +1057,16 @@
         <v>0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>27</v>
+        <v>128</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>24</v>
+        <v>179</v>
       </c>
       <c r="I5" t="s">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="J5">
         <v>3010101</v>
@@ -1089,16 +1089,16 @@
         <v>0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>27</v>
+        <v>128</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>24</v>
+        <v>179</v>
       </c>
       <c r="I6" t="s">
-        <v>179</v>
+        <v>127</v>
       </c>
       <c r="J6">
         <v>3030101</v>
@@ -1121,16 +1121,16 @@
         <v>0</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>27</v>
+        <v>128</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>24</v>
+        <v>179</v>
       </c>
       <c r="I7" t="s">
-        <v>179</v>
+        <v>127</v>
       </c>
       <c r="J7">
         <v>3030101</v>
@@ -1153,16 +1153,16 @@
         <v>0</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>27</v>
+        <v>128</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>24</v>
+        <v>179</v>
       </c>
       <c r="I8" t="s">
-        <v>179</v>
+        <v>127</v>
       </c>
       <c r="J8">
         <v>3030101</v>
@@ -1185,16 +1185,16 @@
         <v>0</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>27</v>
+        <v>128</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>24</v>
+        <v>179</v>
       </c>
       <c r="I9" t="s">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="J9">
         <v>3010101</v>
@@ -1217,16 +1217,16 @@
         <v>0</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>27</v>
+        <v>128</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>24</v>
+        <v>179</v>
       </c>
       <c r="I10" t="s">
-        <v>179</v>
+        <v>127</v>
       </c>
       <c r="J10">
         <v>3030101</v>
@@ -1249,16 +1249,16 @@
         <v>0</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>27</v>
+        <v>128</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>24</v>
+        <v>179</v>
       </c>
       <c r="I11" t="s">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="J11">
         <v>3010101</v>
@@ -1281,16 +1281,16 @@
         <v>0</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>27</v>
+        <v>128</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>24</v>
+        <v>179</v>
       </c>
       <c r="I12" t="s">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="J12">
         <v>3010101</v>
@@ -1313,16 +1313,16 @@
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>28</v>
+        <v>129</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="I13" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="J13" s="1">
         <v>3010101</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>28</v>
+        <v>129</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>79</v>
+        <v>179</v>
       </c>
       <c r="I14" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="J14" s="1">
         <v>3030101</v>
@@ -1377,16 +1377,16 @@
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>28</v>
+        <v>129</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>79</v>
+        <v>179</v>
       </c>
       <c r="I15" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="J15" s="1">
         <v>3030101</v>
@@ -1409,16 +1409,16 @@
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>28</v>
+        <v>129</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>79</v>
+        <v>179</v>
       </c>
       <c r="I16" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="J16" s="1">
         <v>3030101</v>
@@ -1441,16 +1441,16 @@
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>28</v>
+        <v>129</v>
       </c>
       <c r="G17">
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="I17" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="J17" s="1">
         <v>3010101</v>
@@ -1473,16 +1473,16 @@
         <v>1</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>28</v>
+        <v>129</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>79</v>
+        <v>179</v>
       </c>
       <c r="I18" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="J18" s="1">
         <v>3030101</v>
@@ -1505,16 +1505,16 @@
         <v>1</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>28</v>
+        <v>129</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="I19" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="J19" s="1">
         <v>3010101</v>
@@ -1537,16 +1537,16 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>28</v>
+        <v>129</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="I20" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="J20" s="1">
         <v>3010101</v>
@@ -1569,16 +1569,16 @@
         <v>2</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>29</v>
+        <v>130</v>
       </c>
       <c r="G21">
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="I21" t="s">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="J21" s="1">
         <v>3010101</v>
@@ -1601,16 +1601,16 @@
         <v>2</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>29</v>
+        <v>130</v>
       </c>
       <c r="G22">
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>81</v>
+        <v>179</v>
       </c>
       <c r="I22" t="s">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="J22" s="1">
         <v>3030101</v>
@@ -1633,16 +1633,16 @@
         <v>2</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>29</v>
+        <v>130</v>
       </c>
       <c r="G23">
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>81</v>
+        <v>179</v>
       </c>
       <c r="I23" t="s">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="J23" s="1">
         <v>3030101</v>
@@ -1665,16 +1665,16 @@
         <v>2</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>29</v>
+        <v>130</v>
       </c>
       <c r="G24">
         <v>0</v>
       </c>
       <c r="H24" t="s">
-        <v>81</v>
+        <v>179</v>
       </c>
       <c r="I24" t="s">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="J24" s="1">
         <v>3030101</v>
@@ -1697,16 +1697,16 @@
         <v>2</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>29</v>
+        <v>130</v>
       </c>
       <c r="G25">
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="I25" t="s">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="J25" s="1">
         <v>3010101</v>
@@ -1729,16 +1729,16 @@
         <v>2</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>29</v>
+        <v>130</v>
       </c>
       <c r="G26">
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>81</v>
+        <v>179</v>
       </c>
       <c r="I26" t="s">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="J26" s="1">
         <v>3030101</v>
@@ -1761,16 +1761,16 @@
         <v>2</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>29</v>
+        <v>130</v>
       </c>
       <c r="G27">
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="I27" t="s">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="J27" s="1">
         <v>3010101</v>
@@ -1793,16 +1793,16 @@
         <v>2</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>29</v>
+        <v>130</v>
       </c>
       <c r="G28">
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="I28" t="s">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="J28" s="1">
         <v>3010101</v>
@@ -1825,16 +1825,16 @@
         <v>3</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>30</v>
+        <v>131</v>
       </c>
       <c r="G29">
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="I29" t="s">
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="J29" s="1">
         <v>3010101</v>
@@ -1857,16 +1857,16 @@
         <v>3</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>30</v>
+        <v>131</v>
       </c>
       <c r="G30">
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>83</v>
+        <v>179</v>
       </c>
       <c r="I30" t="s">
-        <v>83</v>
+        <v>31</v>
       </c>
       <c r="J30" s="1">
         <v>3030101</v>
@@ -1889,16 +1889,16 @@
         <v>3</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>30</v>
+        <v>131</v>
       </c>
       <c r="G31">
         <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>83</v>
+        <v>179</v>
       </c>
       <c r="I31" t="s">
-        <v>83</v>
+        <v>31</v>
       </c>
       <c r="J31" s="1">
         <v>3030101</v>
@@ -1921,16 +1921,16 @@
         <v>3</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>30</v>
+        <v>131</v>
       </c>
       <c r="G32">
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>83</v>
+        <v>179</v>
       </c>
       <c r="I32" t="s">
-        <v>83</v>
+        <v>31</v>
       </c>
       <c r="J32" s="1">
         <v>3030101</v>
@@ -1953,16 +1953,16 @@
         <v>3</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>30</v>
+        <v>131</v>
       </c>
       <c r="G33">
         <v>0</v>
       </c>
       <c r="H33" t="s">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="I33" t="s">
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="J33" s="1">
         <v>3010101</v>
@@ -1985,16 +1985,16 @@
         <v>3</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>30</v>
+        <v>131</v>
       </c>
       <c r="G34">
         <v>0</v>
       </c>
       <c r="H34" t="s">
-        <v>83</v>
+        <v>179</v>
       </c>
       <c r="I34" t="s">
-        <v>83</v>
+        <v>31</v>
       </c>
       <c r="J34" s="1">
         <v>3030101</v>
@@ -2017,16 +2017,16 @@
         <v>3</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>30</v>
+        <v>131</v>
       </c>
       <c r="G35">
         <v>0</v>
       </c>
       <c r="H35" t="s">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="I35" t="s">
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="J35" s="1">
         <v>3010101</v>
@@ -2049,16 +2049,16 @@
         <v>3</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>30</v>
+        <v>131</v>
       </c>
       <c r="G36">
         <v>0</v>
       </c>
       <c r="H36" t="s">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="I36" t="s">
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="J36" s="1">
         <v>3010101</v>
@@ -2081,16 +2081,16 @@
         <v>4</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>31</v>
+        <v>132</v>
       </c>
       <c r="G37">
         <v>0</v>
       </c>
       <c r="H37" t="s">
-        <v>84</v>
+        <v>179</v>
       </c>
       <c r="I37" t="s">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="J37" s="1">
         <v>3010101</v>
@@ -2113,16 +2113,16 @@
         <v>4</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>31</v>
+        <v>132</v>
       </c>
       <c r="G38">
         <v>0</v>
       </c>
       <c r="H38" t="s">
-        <v>85</v>
+        <v>179</v>
       </c>
       <c r="I38" t="s">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="J38" s="1">
         <v>3030101</v>
@@ -2145,16 +2145,16 @@
         <v>4</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>31</v>
+        <v>132</v>
       </c>
       <c r="G39">
         <v>0</v>
       </c>
       <c r="H39" t="s">
-        <v>85</v>
+        <v>179</v>
       </c>
       <c r="I39" t="s">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="J39" s="1">
         <v>3030101</v>
@@ -2177,16 +2177,16 @@
         <v>4</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>31</v>
+        <v>132</v>
       </c>
       <c r="G40">
         <v>0</v>
       </c>
       <c r="H40" t="s">
-        <v>85</v>
+        <v>179</v>
       </c>
       <c r="I40" t="s">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="J40" s="1">
         <v>3030101</v>
@@ -2209,16 +2209,16 @@
         <v>4</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>31</v>
+        <v>132</v>
       </c>
       <c r="G41">
         <v>0</v>
       </c>
       <c r="H41" t="s">
-        <v>84</v>
+        <v>179</v>
       </c>
       <c r="I41" t="s">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="J41" s="1">
         <v>3010101</v>
@@ -2241,16 +2241,16 @@
         <v>4</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>31</v>
+        <v>132</v>
       </c>
       <c r="G42">
         <v>0</v>
       </c>
       <c r="H42" t="s">
-        <v>85</v>
+        <v>179</v>
       </c>
       <c r="I42" t="s">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="J42" s="1">
         <v>3030101</v>
@@ -2273,16 +2273,16 @@
         <v>4</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>31</v>
+        <v>132</v>
       </c>
       <c r="G43">
         <v>0</v>
       </c>
       <c r="H43" t="s">
-        <v>84</v>
+        <v>179</v>
       </c>
       <c r="I43" t="s">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="J43" s="1">
         <v>3010101</v>
@@ -2305,16 +2305,16 @@
         <v>4</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>31</v>
+        <v>132</v>
       </c>
       <c r="G44">
         <v>0</v>
       </c>
       <c r="H44" t="s">
-        <v>84</v>
+        <v>179</v>
       </c>
       <c r="I44" t="s">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="J44" s="1">
         <v>3010101</v>
@@ -2337,16 +2337,16 @@
         <v>5</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="G45">
         <v>0</v>
       </c>
       <c r="H45" t="s">
-        <v>86</v>
+        <v>179</v>
       </c>
       <c r="I45" t="s">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="J45" s="1">
         <v>3010101</v>
@@ -2369,16 +2369,16 @@
         <v>5</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="G46">
         <v>0</v>
       </c>
       <c r="H46" t="s">
-        <v>87</v>
+        <v>179</v>
       </c>
       <c r="I46" t="s">
-        <v>87</v>
+        <v>35</v>
       </c>
       <c r="J46" s="1">
         <v>3030101</v>
@@ -2401,16 +2401,16 @@
         <v>5</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="G47">
         <v>0</v>
       </c>
       <c r="H47" t="s">
-        <v>87</v>
+        <v>179</v>
       </c>
       <c r="I47" t="s">
-        <v>87</v>
+        <v>35</v>
       </c>
       <c r="J47" s="1">
         <v>3030101</v>
@@ -2433,16 +2433,16 @@
         <v>5</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="G48">
         <v>0</v>
       </c>
       <c r="H48" t="s">
-        <v>87</v>
+        <v>179</v>
       </c>
       <c r="I48" t="s">
-        <v>87</v>
+        <v>35</v>
       </c>
       <c r="J48" s="1">
         <v>3030101</v>
@@ -2465,16 +2465,16 @@
         <v>5</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="G49">
         <v>0</v>
       </c>
       <c r="H49" t="s">
-        <v>86</v>
+        <v>179</v>
       </c>
       <c r="I49" t="s">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="J49" s="1">
         <v>3010101</v>
@@ -2497,16 +2497,16 @@
         <v>5</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="G50">
         <v>0</v>
       </c>
       <c r="H50" t="s">
-        <v>87</v>
+        <v>179</v>
       </c>
       <c r="I50" t="s">
-        <v>87</v>
+        <v>35</v>
       </c>
       <c r="J50" s="1">
         <v>3030101</v>
@@ -2529,16 +2529,16 @@
         <v>5</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="G51">
         <v>0</v>
       </c>
       <c r="H51" t="s">
-        <v>86</v>
+        <v>179</v>
       </c>
       <c r="I51" t="s">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="J51" s="1">
         <v>3010101</v>
@@ -2561,16 +2561,16 @@
         <v>5</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="G52">
         <v>0</v>
       </c>
       <c r="H52" t="s">
-        <v>86</v>
+        <v>179</v>
       </c>
       <c r="I52" t="s">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="J52" s="1">
         <v>3010101</v>
@@ -2593,16 +2593,16 @@
         <v>6</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>33</v>
+        <v>134</v>
       </c>
       <c r="G53">
         <v>0</v>
       </c>
       <c r="H53" t="s">
-        <v>88</v>
+        <v>179</v>
       </c>
       <c r="I53" t="s">
-        <v>88</v>
+        <v>36</v>
       </c>
       <c r="J53" s="1">
         <v>3010101</v>
@@ -2625,16 +2625,16 @@
         <v>6</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>33</v>
+        <v>134</v>
       </c>
       <c r="G54">
         <v>0</v>
       </c>
       <c r="H54" t="s">
-        <v>89</v>
+        <v>179</v>
       </c>
       <c r="I54" t="s">
-        <v>89</v>
+        <v>37</v>
       </c>
       <c r="J54" s="1">
         <v>3030101</v>
@@ -2657,16 +2657,16 @@
         <v>6</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>33</v>
+        <v>134</v>
       </c>
       <c r="G55">
         <v>0</v>
       </c>
       <c r="H55" t="s">
-        <v>89</v>
+        <v>179</v>
       </c>
       <c r="I55" t="s">
-        <v>89</v>
+        <v>37</v>
       </c>
       <c r="J55" s="1">
         <v>3030101</v>
@@ -2689,16 +2689,16 @@
         <v>6</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>33</v>
+        <v>134</v>
       </c>
       <c r="G56">
         <v>0</v>
       </c>
       <c r="H56" t="s">
-        <v>89</v>
+        <v>179</v>
       </c>
       <c r="I56" t="s">
-        <v>89</v>
+        <v>37</v>
       </c>
       <c r="J56" s="1">
         <v>3030101</v>
@@ -2721,16 +2721,16 @@
         <v>6</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>33</v>
+        <v>134</v>
       </c>
       <c r="G57">
         <v>0</v>
       </c>
       <c r="H57" t="s">
-        <v>88</v>
+        <v>179</v>
       </c>
       <c r="I57" t="s">
-        <v>88</v>
+        <v>36</v>
       </c>
       <c r="J57" s="1">
         <v>3010101</v>
@@ -2753,16 +2753,16 @@
         <v>6</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>33</v>
+        <v>134</v>
       </c>
       <c r="G58">
         <v>0</v>
       </c>
       <c r="H58" t="s">
-        <v>89</v>
+        <v>179</v>
       </c>
       <c r="I58" t="s">
-        <v>89</v>
+        <v>37</v>
       </c>
       <c r="J58" s="1">
         <v>3030101</v>
@@ -2785,16 +2785,16 @@
         <v>6</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>33</v>
+        <v>134</v>
       </c>
       <c r="G59">
         <v>0</v>
       </c>
       <c r="H59" t="s">
-        <v>88</v>
+        <v>179</v>
       </c>
       <c r="I59" t="s">
-        <v>88</v>
+        <v>36</v>
       </c>
       <c r="J59" s="1">
         <v>3010101</v>
@@ -2817,16 +2817,16 @@
         <v>6</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>33</v>
+        <v>134</v>
       </c>
       <c r="G60">
         <v>0</v>
       </c>
       <c r="H60" t="s">
-        <v>88</v>
+        <v>179</v>
       </c>
       <c r="I60" t="s">
-        <v>88</v>
+        <v>36</v>
       </c>
       <c r="J60" s="1">
         <v>3010101</v>
@@ -2849,16 +2849,16 @@
         <v>7</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>34</v>
+        <v>135</v>
       </c>
       <c r="G61">
         <v>0</v>
       </c>
       <c r="H61" t="s">
-        <v>90</v>
+        <v>179</v>
       </c>
       <c r="I61" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="J61" s="1">
         <v>3010101</v>
@@ -2881,16 +2881,16 @@
         <v>7</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>34</v>
+        <v>135</v>
       </c>
       <c r="G62">
         <v>0</v>
       </c>
       <c r="H62" t="s">
-        <v>91</v>
+        <v>179</v>
       </c>
       <c r="I62" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="J62" s="1">
         <v>3030101</v>
@@ -2913,16 +2913,16 @@
         <v>7</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>34</v>
+        <v>135</v>
       </c>
       <c r="G63">
         <v>0</v>
       </c>
       <c r="H63" t="s">
-        <v>91</v>
+        <v>179</v>
       </c>
       <c r="I63" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="J63" s="1">
         <v>3030101</v>
@@ -2945,16 +2945,16 @@
         <v>7</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>34</v>
+        <v>135</v>
       </c>
       <c r="G64">
         <v>0</v>
       </c>
       <c r="H64" t="s">
-        <v>91</v>
+        <v>179</v>
       </c>
       <c r="I64" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="J64" s="1">
         <v>3030101</v>
@@ -2977,16 +2977,16 @@
         <v>7</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>34</v>
+        <v>135</v>
       </c>
       <c r="G65">
         <v>0</v>
       </c>
       <c r="H65" t="s">
-        <v>90</v>
+        <v>179</v>
       </c>
       <c r="I65" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="J65" s="1">
         <v>3010101</v>
@@ -3009,16 +3009,16 @@
         <v>7</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>34</v>
+        <v>135</v>
       </c>
       <c r="G66">
         <v>0</v>
       </c>
       <c r="H66" t="s">
-        <v>91</v>
+        <v>179</v>
       </c>
       <c r="I66" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="J66" s="1">
         <v>3030101</v>
@@ -3041,16 +3041,16 @@
         <v>7</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>34</v>
+        <v>135</v>
       </c>
       <c r="G67">
         <v>0</v>
       </c>
       <c r="H67" t="s">
-        <v>90</v>
+        <v>179</v>
       </c>
       <c r="I67" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="J67" s="1">
         <v>3010101</v>
@@ -3073,16 +3073,16 @@
         <v>7</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>34</v>
+        <v>135</v>
       </c>
       <c r="G68">
         <v>0</v>
       </c>
       <c r="H68" t="s">
-        <v>90</v>
+        <v>179</v>
       </c>
       <c r="I68" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="J68" s="1">
         <v>3010101</v>
@@ -3105,16 +3105,16 @@
         <v>8</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>35</v>
+        <v>136</v>
       </c>
       <c r="G69">
         <v>0</v>
       </c>
       <c r="H69" t="s">
-        <v>92</v>
+        <v>179</v>
       </c>
       <c r="I69" t="s">
-        <v>92</v>
+        <v>40</v>
       </c>
       <c r="J69" s="1">
         <v>3010101</v>
@@ -3137,16 +3137,16 @@
         <v>8</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>35</v>
+        <v>136</v>
       </c>
       <c r="G70">
         <v>0</v>
       </c>
       <c r="H70" t="s">
-        <v>93</v>
+        <v>179</v>
       </c>
       <c r="I70" t="s">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="J70" s="1">
         <v>3030101</v>
@@ -3169,16 +3169,16 @@
         <v>8</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>35</v>
+        <v>136</v>
       </c>
       <c r="G71">
         <v>0</v>
       </c>
       <c r="H71" t="s">
-        <v>93</v>
+        <v>179</v>
       </c>
       <c r="I71" t="s">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="J71" s="1">
         <v>3030101</v>
@@ -3201,16 +3201,16 @@
         <v>8</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>35</v>
+        <v>136</v>
       </c>
       <c r="G72">
         <v>0</v>
       </c>
       <c r="H72" t="s">
-        <v>93</v>
+        <v>179</v>
       </c>
       <c r="I72" t="s">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="J72" s="1">
         <v>3030101</v>
@@ -3233,16 +3233,16 @@
         <v>8</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>35</v>
+        <v>136</v>
       </c>
       <c r="G73">
         <v>0</v>
       </c>
       <c r="H73" t="s">
-        <v>92</v>
+        <v>179</v>
       </c>
       <c r="I73" t="s">
-        <v>92</v>
+        <v>40</v>
       </c>
       <c r="J73" s="1">
         <v>3010101</v>
@@ -3265,16 +3265,16 @@
         <v>8</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>35</v>
+        <v>136</v>
       </c>
       <c r="G74">
         <v>0</v>
       </c>
       <c r="H74" t="s">
-        <v>93</v>
+        <v>179</v>
       </c>
       <c r="I74" t="s">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="J74" s="1">
         <v>3030101</v>
@@ -3297,16 +3297,16 @@
         <v>8</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>35</v>
+        <v>136</v>
       </c>
       <c r="G75">
         <v>0</v>
       </c>
       <c r="H75" t="s">
-        <v>92</v>
+        <v>179</v>
       </c>
       <c r="I75" t="s">
-        <v>92</v>
+        <v>40</v>
       </c>
       <c r="J75" s="1">
         <v>3010101</v>
@@ -3329,16 +3329,16 @@
         <v>8</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>35</v>
+        <v>136</v>
       </c>
       <c r="G76">
         <v>0</v>
       </c>
       <c r="H76" t="s">
-        <v>92</v>
+        <v>179</v>
       </c>
       <c r="I76" t="s">
-        <v>92</v>
+        <v>40</v>
       </c>
       <c r="J76" s="1">
         <v>3010101</v>
@@ -3361,16 +3361,16 @@
         <v>9</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>36</v>
+        <v>137</v>
       </c>
       <c r="G77">
         <v>0</v>
       </c>
       <c r="H77" t="s">
-        <v>94</v>
+        <v>179</v>
       </c>
       <c r="I77" t="s">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="J77" s="1">
         <v>3010101</v>
@@ -3393,16 +3393,16 @@
         <v>9</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>36</v>
+        <v>137</v>
       </c>
       <c r="G78">
         <v>0</v>
       </c>
       <c r="H78" t="s">
-        <v>95</v>
+        <v>179</v>
       </c>
       <c r="I78" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="J78" s="1">
         <v>3030101</v>
@@ -3425,16 +3425,16 @@
         <v>9</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>36</v>
+        <v>137</v>
       </c>
       <c r="G79">
         <v>0</v>
       </c>
       <c r="H79" t="s">
-        <v>95</v>
+        <v>179</v>
       </c>
       <c r="I79" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="J79" s="1">
         <v>3030101</v>
@@ -3457,16 +3457,16 @@
         <v>9</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>36</v>
+        <v>137</v>
       </c>
       <c r="G80">
         <v>0</v>
       </c>
       <c r="H80" t="s">
-        <v>95</v>
+        <v>179</v>
       </c>
       <c r="I80" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="J80" s="1">
         <v>3030101</v>
@@ -3489,16 +3489,16 @@
         <v>9</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>36</v>
+        <v>137</v>
       </c>
       <c r="G81">
         <v>0</v>
       </c>
       <c r="H81" t="s">
-        <v>94</v>
+        <v>179</v>
       </c>
       <c r="I81" t="s">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="J81" s="1">
         <v>3010101</v>
@@ -3521,16 +3521,16 @@
         <v>9</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>36</v>
+        <v>137</v>
       </c>
       <c r="G82">
         <v>0</v>
       </c>
       <c r="H82" t="s">
-        <v>95</v>
+        <v>179</v>
       </c>
       <c r="I82" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="J82" s="1">
         <v>3030101</v>
@@ -3553,16 +3553,16 @@
         <v>9</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>36</v>
+        <v>137</v>
       </c>
       <c r="G83">
         <v>0</v>
       </c>
       <c r="H83" t="s">
-        <v>94</v>
+        <v>179</v>
       </c>
       <c r="I83" t="s">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="J83" s="1">
         <v>3010101</v>
@@ -3585,16 +3585,16 @@
         <v>9</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>36</v>
+        <v>137</v>
       </c>
       <c r="G84">
         <v>0</v>
       </c>
       <c r="H84" t="s">
-        <v>94</v>
+        <v>179</v>
       </c>
       <c r="I84" t="s">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="J84" s="1">
         <v>3010101</v>
@@ -3617,16 +3617,16 @@
         <v>10</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>37</v>
+        <v>138</v>
       </c>
       <c r="G85">
         <v>10</v>
       </c>
       <c r="H85" t="s">
-        <v>96</v>
+        <v>179</v>
       </c>
       <c r="I85" t="s">
-        <v>96</v>
+        <v>44</v>
       </c>
       <c r="J85" s="1">
         <v>3010101</v>
@@ -3649,16 +3649,16 @@
         <v>10</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>37</v>
+        <v>138</v>
       </c>
       <c r="G86">
         <v>10</v>
       </c>
       <c r="H86" t="s">
-        <v>97</v>
+        <v>179</v>
       </c>
       <c r="I86" t="s">
-        <v>97</v>
+        <v>45</v>
       </c>
       <c r="J86" s="1">
         <v>3030101</v>
@@ -3681,16 +3681,16 @@
         <v>10</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>37</v>
+        <v>138</v>
       </c>
       <c r="G87">
         <v>10</v>
       </c>
       <c r="H87" t="s">
-        <v>97</v>
+        <v>179</v>
       </c>
       <c r="I87" t="s">
-        <v>97</v>
+        <v>45</v>
       </c>
       <c r="J87" s="1">
         <v>3030101</v>
@@ -3713,16 +3713,16 @@
         <v>10</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>37</v>
+        <v>138</v>
       </c>
       <c r="G88">
         <v>10</v>
       </c>
       <c r="H88" t="s">
-        <v>97</v>
+        <v>179</v>
       </c>
       <c r="I88" t="s">
-        <v>97</v>
+        <v>45</v>
       </c>
       <c r="J88" s="1">
         <v>3030101</v>
@@ -3745,16 +3745,16 @@
         <v>10</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>37</v>
+        <v>138</v>
       </c>
       <c r="G89">
         <v>10</v>
       </c>
       <c r="H89" t="s">
-        <v>96</v>
+        <v>179</v>
       </c>
       <c r="I89" t="s">
-        <v>96</v>
+        <v>44</v>
       </c>
       <c r="J89" s="1">
         <v>3010101</v>
@@ -3777,16 +3777,16 @@
         <v>10</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>37</v>
+        <v>138</v>
       </c>
       <c r="G90">
         <v>10</v>
       </c>
       <c r="H90" t="s">
-        <v>97</v>
+        <v>179</v>
       </c>
       <c r="I90" t="s">
-        <v>97</v>
+        <v>45</v>
       </c>
       <c r="J90" s="1">
         <v>3030101</v>
@@ -3809,16 +3809,16 @@
         <v>10</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>37</v>
+        <v>138</v>
       </c>
       <c r="G91">
         <v>10</v>
       </c>
       <c r="H91" t="s">
-        <v>96</v>
+        <v>179</v>
       </c>
       <c r="I91" t="s">
-        <v>96</v>
+        <v>44</v>
       </c>
       <c r="J91" s="1">
         <v>3010101</v>
@@ -3841,16 +3841,16 @@
         <v>10</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>37</v>
+        <v>138</v>
       </c>
       <c r="G92">
         <v>10</v>
       </c>
       <c r="H92" t="s">
-        <v>96</v>
+        <v>179</v>
       </c>
       <c r="I92" t="s">
-        <v>96</v>
+        <v>44</v>
       </c>
       <c r="J92" s="1">
         <v>3010101</v>
@@ -3873,16 +3873,16 @@
         <v>11</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>38</v>
+        <v>139</v>
       </c>
       <c r="G93">
         <v>10</v>
       </c>
       <c r="H93" t="s">
-        <v>98</v>
+        <v>179</v>
       </c>
       <c r="I93" t="s">
-        <v>98</v>
+        <v>46</v>
       </c>
       <c r="J93" s="1">
         <v>3010101</v>
@@ -3905,16 +3905,16 @@
         <v>11</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>38</v>
+        <v>139</v>
       </c>
       <c r="G94">
         <v>10</v>
       </c>
       <c r="H94" t="s">
-        <v>99</v>
+        <v>179</v>
       </c>
       <c r="I94" t="s">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="J94" s="1">
         <v>3030101</v>
@@ -3937,16 +3937,16 @@
         <v>11</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>38</v>
+        <v>139</v>
       </c>
       <c r="G95">
         <v>10</v>
       </c>
       <c r="H95" t="s">
-        <v>99</v>
+        <v>179</v>
       </c>
       <c r="I95" t="s">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="J95" s="1">
         <v>3030101</v>
@@ -3969,16 +3969,16 @@
         <v>11</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>38</v>
+        <v>139</v>
       </c>
       <c r="G96">
         <v>10</v>
       </c>
       <c r="H96" t="s">
-        <v>99</v>
+        <v>179</v>
       </c>
       <c r="I96" t="s">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="J96" s="1">
         <v>3030101</v>
@@ -4001,16 +4001,16 @@
         <v>11</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>38</v>
+        <v>139</v>
       </c>
       <c r="G97">
         <v>10</v>
       </c>
       <c r="H97" t="s">
-        <v>98</v>
+        <v>179</v>
       </c>
       <c r="I97" t="s">
-        <v>98</v>
+        <v>46</v>
       </c>
       <c r="J97" s="1">
         <v>3010101</v>
@@ -4033,16 +4033,16 @@
         <v>11</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>38</v>
+        <v>139</v>
       </c>
       <c r="G98">
         <v>10</v>
       </c>
       <c r="H98" t="s">
-        <v>99</v>
+        <v>179</v>
       </c>
       <c r="I98" t="s">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="J98" s="1">
         <v>3030101</v>
@@ -4065,16 +4065,16 @@
         <v>11</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>38</v>
+        <v>139</v>
       </c>
       <c r="G99">
         <v>10</v>
       </c>
       <c r="H99" t="s">
-        <v>98</v>
+        <v>179</v>
       </c>
       <c r="I99" t="s">
-        <v>98</v>
+        <v>46</v>
       </c>
       <c r="J99" s="1">
         <v>3010101</v>
@@ -4097,16 +4097,16 @@
         <v>11</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>38</v>
+        <v>139</v>
       </c>
       <c r="G100">
         <v>10</v>
       </c>
       <c r="H100" t="s">
-        <v>98</v>
+        <v>179</v>
       </c>
       <c r="I100" t="s">
-        <v>98</v>
+        <v>46</v>
       </c>
       <c r="J100" s="1">
         <v>3010101</v>
@@ -4129,16 +4129,16 @@
         <v>12</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="G101">
         <v>10</v>
       </c>
       <c r="H101" t="s">
-        <v>100</v>
+        <v>179</v>
       </c>
       <c r="I101" t="s">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="J101" s="1">
         <v>3010101</v>
@@ -4161,16 +4161,16 @@
         <v>12</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="G102">
         <v>10</v>
       </c>
       <c r="H102" t="s">
-        <v>101</v>
+        <v>179</v>
       </c>
       <c r="I102" t="s">
-        <v>101</v>
+        <v>49</v>
       </c>
       <c r="J102" s="1">
         <v>3030101</v>
@@ -4193,16 +4193,16 @@
         <v>12</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="G103">
         <v>10</v>
       </c>
       <c r="H103" t="s">
-        <v>101</v>
+        <v>179</v>
       </c>
       <c r="I103" t="s">
-        <v>101</v>
+        <v>49</v>
       </c>
       <c r="J103" s="1">
         <v>3030101</v>
@@ -4225,16 +4225,16 @@
         <v>12</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="G104">
         <v>10</v>
       </c>
       <c r="H104" t="s">
-        <v>101</v>
+        <v>179</v>
       </c>
       <c r="I104" t="s">
-        <v>101</v>
+        <v>49</v>
       </c>
       <c r="J104" s="1">
         <v>3030101</v>
@@ -4257,16 +4257,16 @@
         <v>12</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="G105">
         <v>10</v>
       </c>
       <c r="H105" t="s">
-        <v>100</v>
+        <v>179</v>
       </c>
       <c r="I105" t="s">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="J105" s="1">
         <v>3010101</v>
@@ -4289,16 +4289,16 @@
         <v>12</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="G106">
         <v>10</v>
       </c>
       <c r="H106" t="s">
-        <v>101</v>
+        <v>179</v>
       </c>
       <c r="I106" t="s">
-        <v>101</v>
+        <v>49</v>
       </c>
       <c r="J106" s="1">
         <v>3030101</v>
@@ -4321,16 +4321,16 @@
         <v>12</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="G107">
         <v>10</v>
       </c>
       <c r="H107" t="s">
-        <v>100</v>
+        <v>179</v>
       </c>
       <c r="I107" t="s">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="J107" s="1">
         <v>3010101</v>
@@ -4353,16 +4353,16 @@
         <v>12</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="G108">
         <v>10</v>
       </c>
       <c r="H108" t="s">
-        <v>100</v>
+        <v>179</v>
       </c>
       <c r="I108" t="s">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="J108" s="1">
         <v>3010101</v>
@@ -4385,16 +4385,16 @@
         <v>13</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>40</v>
+        <v>141</v>
       </c>
       <c r="G109">
         <v>10</v>
       </c>
       <c r="H109" t="s">
-        <v>102</v>
+        <v>179</v>
       </c>
       <c r="I109" t="s">
-        <v>102</v>
+        <v>50</v>
       </c>
       <c r="J109" s="1">
         <v>3010101</v>
@@ -4417,16 +4417,16 @@
         <v>13</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>40</v>
+        <v>141</v>
       </c>
       <c r="G110">
         <v>10</v>
       </c>
       <c r="H110" t="s">
-        <v>103</v>
+        <v>179</v>
       </c>
       <c r="I110" t="s">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="J110" s="1">
         <v>3030101</v>
@@ -4449,16 +4449,16 @@
         <v>13</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>40</v>
+        <v>141</v>
       </c>
       <c r="G111">
         <v>10</v>
       </c>
       <c r="H111" t="s">
-        <v>103</v>
+        <v>179</v>
       </c>
       <c r="I111" t="s">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="J111" s="1">
         <v>3030101</v>
@@ -4481,16 +4481,16 @@
         <v>13</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>40</v>
+        <v>141</v>
       </c>
       <c r="G112">
         <v>10</v>
       </c>
       <c r="H112" t="s">
-        <v>103</v>
+        <v>179</v>
       </c>
       <c r="I112" t="s">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="J112" s="1">
         <v>3030101</v>
@@ -4513,16 +4513,16 @@
         <v>13</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>40</v>
+        <v>141</v>
       </c>
       <c r="G113">
         <v>10</v>
       </c>
       <c r="H113" t="s">
-        <v>102</v>
+        <v>179</v>
       </c>
       <c r="I113" t="s">
-        <v>102</v>
+        <v>50</v>
       </c>
       <c r="J113" s="1">
         <v>3010101</v>
@@ -4545,16 +4545,16 @@
         <v>13</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>40</v>
+        <v>141</v>
       </c>
       <c r="G114">
         <v>10</v>
       </c>
       <c r="H114" t="s">
-        <v>103</v>
+        <v>179</v>
       </c>
       <c r="I114" t="s">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="J114" s="1">
         <v>3030101</v>
@@ -4577,16 +4577,16 @@
         <v>13</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>40</v>
+        <v>141</v>
       </c>
       <c r="G115">
         <v>10</v>
       </c>
       <c r="H115" t="s">
-        <v>102</v>
+        <v>179</v>
       </c>
       <c r="I115" t="s">
-        <v>102</v>
+        <v>50</v>
       </c>
       <c r="J115" s="1">
         <v>3010101</v>
@@ -4609,16 +4609,16 @@
         <v>13</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>40</v>
+        <v>141</v>
       </c>
       <c r="G116">
         <v>10</v>
       </c>
       <c r="H116" t="s">
-        <v>102</v>
+        <v>179</v>
       </c>
       <c r="I116" t="s">
-        <v>102</v>
+        <v>50</v>
       </c>
       <c r="J116" s="1">
         <v>3010101</v>
@@ -4641,16 +4641,16 @@
         <v>14</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="G117">
         <v>10</v>
       </c>
       <c r="H117" t="s">
-        <v>104</v>
+        <v>179</v>
       </c>
       <c r="I117" t="s">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="J117" s="1">
         <v>3010101</v>
@@ -4673,16 +4673,16 @@
         <v>14</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="G118">
         <v>10</v>
       </c>
       <c r="H118" t="s">
-        <v>105</v>
+        <v>179</v>
       </c>
       <c r="I118" t="s">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="J118" s="1">
         <v>3030101</v>
@@ -4705,16 +4705,16 @@
         <v>14</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="G119">
         <v>10</v>
       </c>
       <c r="H119" t="s">
-        <v>105</v>
+        <v>179</v>
       </c>
       <c r="I119" t="s">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="J119" s="1">
         <v>3030101</v>
@@ -4737,16 +4737,16 @@
         <v>14</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="G120">
         <v>10</v>
       </c>
       <c r="H120" t="s">
-        <v>105</v>
+        <v>179</v>
       </c>
       <c r="I120" t="s">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="J120" s="1">
         <v>3030101</v>
@@ -4769,16 +4769,16 @@
         <v>14</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="G121">
         <v>10</v>
       </c>
       <c r="H121" t="s">
-        <v>104</v>
+        <v>179</v>
       </c>
       <c r="I121" t="s">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="J121" s="1">
         <v>3010101</v>
@@ -4801,16 +4801,16 @@
         <v>14</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="G122">
         <v>10</v>
       </c>
       <c r="H122" t="s">
-        <v>105</v>
+        <v>179</v>
       </c>
       <c r="I122" t="s">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="J122" s="1">
         <v>3030101</v>
@@ -4833,16 +4833,16 @@
         <v>14</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="G123">
         <v>10</v>
       </c>
       <c r="H123" t="s">
-        <v>104</v>
+        <v>179</v>
       </c>
       <c r="I123" t="s">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="J123" s="1">
         <v>3010101</v>
@@ -4865,16 +4865,16 @@
         <v>14</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="G124">
         <v>10</v>
       </c>
       <c r="H124" t="s">
-        <v>104</v>
+        <v>179</v>
       </c>
       <c r="I124" t="s">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="J124" s="1">
         <v>3010101</v>
@@ -4897,16 +4897,16 @@
         <v>15</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="G125">
         <v>10</v>
       </c>
       <c r="H125" t="s">
-        <v>106</v>
+        <v>179</v>
       </c>
       <c r="I125" t="s">
-        <v>106</v>
+        <v>54</v>
       </c>
       <c r="J125" s="1">
         <v>3010101</v>
@@ -4929,16 +4929,16 @@
         <v>15</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="G126">
         <v>10</v>
       </c>
       <c r="H126" t="s">
-        <v>107</v>
+        <v>179</v>
       </c>
       <c r="I126" t="s">
-        <v>107</v>
+        <v>55</v>
       </c>
       <c r="J126" s="1">
         <v>3030101</v>
@@ -4961,16 +4961,16 @@
         <v>15</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="G127">
         <v>10</v>
       </c>
       <c r="H127" t="s">
-        <v>107</v>
+        <v>179</v>
       </c>
       <c r="I127" t="s">
-        <v>107</v>
+        <v>55</v>
       </c>
       <c r="J127" s="1">
         <v>3030101</v>
@@ -4993,16 +4993,16 @@
         <v>15</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="G128">
         <v>10</v>
       </c>
       <c r="H128" t="s">
-        <v>107</v>
+        <v>179</v>
       </c>
       <c r="I128" t="s">
-        <v>107</v>
+        <v>55</v>
       </c>
       <c r="J128" s="1">
         <v>3030101</v>
@@ -5025,16 +5025,16 @@
         <v>15</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="G129">
         <v>10</v>
       </c>
       <c r="H129" t="s">
-        <v>106</v>
+        <v>179</v>
       </c>
       <c r="I129" t="s">
-        <v>106</v>
+        <v>54</v>
       </c>
       <c r="J129" s="1">
         <v>3010101</v>
@@ -5057,16 +5057,16 @@
         <v>15</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="G130">
         <v>10</v>
       </c>
       <c r="H130" t="s">
-        <v>107</v>
+        <v>179</v>
       </c>
       <c r="I130" t="s">
-        <v>107</v>
+        <v>55</v>
       </c>
       <c r="J130" s="1">
         <v>3030101</v>
@@ -5089,16 +5089,16 @@
         <v>15</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="G131">
         <v>10</v>
       </c>
       <c r="H131" t="s">
-        <v>106</v>
+        <v>179</v>
       </c>
       <c r="I131" t="s">
-        <v>106</v>
+        <v>54</v>
       </c>
       <c r="J131" s="1">
         <v>3010101</v>
@@ -5121,16 +5121,16 @@
         <v>15</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="G132">
         <v>10</v>
       </c>
       <c r="H132" t="s">
-        <v>106</v>
+        <v>179</v>
       </c>
       <c r="I132" t="s">
-        <v>106</v>
+        <v>54</v>
       </c>
       <c r="J132" s="1">
         <v>3010101</v>
@@ -5153,16 +5153,16 @@
         <v>16</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>43</v>
+        <v>144</v>
       </c>
       <c r="G133">
         <v>10</v>
       </c>
       <c r="H133" t="s">
-        <v>108</v>
+        <v>179</v>
       </c>
       <c r="I133" t="s">
-        <v>108</v>
+        <v>56</v>
       </c>
       <c r="J133" s="1">
         <v>3010101</v>
@@ -5185,16 +5185,16 @@
         <v>16</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>43</v>
+        <v>144</v>
       </c>
       <c r="G134">
         <v>10</v>
       </c>
       <c r="H134" t="s">
-        <v>109</v>
+        <v>179</v>
       </c>
       <c r="I134" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J134" s="1">
         <v>3030101</v>
@@ -5217,16 +5217,16 @@
         <v>16</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>43</v>
+        <v>144</v>
       </c>
       <c r="G135">
         <v>10</v>
       </c>
       <c r="H135" t="s">
-        <v>109</v>
+        <v>179</v>
       </c>
       <c r="I135" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J135" s="1">
         <v>3030101</v>
@@ -5249,16 +5249,16 @@
         <v>16</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>43</v>
+        <v>144</v>
       </c>
       <c r="G136">
         <v>10</v>
       </c>
       <c r="H136" t="s">
-        <v>109</v>
+        <v>179</v>
       </c>
       <c r="I136" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J136" s="1">
         <v>3030101</v>
@@ -5281,16 +5281,16 @@
         <v>16</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>43</v>
+        <v>144</v>
       </c>
       <c r="G137">
         <v>10</v>
       </c>
       <c r="H137" t="s">
-        <v>108</v>
+        <v>179</v>
       </c>
       <c r="I137" t="s">
-        <v>108</v>
+        <v>56</v>
       </c>
       <c r="J137" s="1">
         <v>3010101</v>
@@ -5313,16 +5313,16 @@
         <v>16</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>43</v>
+        <v>144</v>
       </c>
       <c r="G138">
         <v>10</v>
       </c>
       <c r="H138" t="s">
-        <v>109</v>
+        <v>179</v>
       </c>
       <c r="I138" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J138" s="1">
         <v>3030101</v>
@@ -5345,16 +5345,16 @@
         <v>16</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>43</v>
+        <v>144</v>
       </c>
       <c r="G139">
         <v>10</v>
       </c>
       <c r="H139" t="s">
-        <v>108</v>
+        <v>179</v>
       </c>
       <c r="I139" t="s">
-        <v>108</v>
+        <v>56</v>
       </c>
       <c r="J139" s="1">
         <v>3010101</v>
@@ -5377,16 +5377,16 @@
         <v>16</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>43</v>
+        <v>144</v>
       </c>
       <c r="G140">
         <v>10</v>
       </c>
       <c r="H140" t="s">
-        <v>108</v>
+        <v>179</v>
       </c>
       <c r="I140" t="s">
-        <v>108</v>
+        <v>56</v>
       </c>
       <c r="J140" s="1">
         <v>3010101</v>
@@ -5409,16 +5409,16 @@
         <v>17</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>44</v>
+        <v>145</v>
       </c>
       <c r="G141">
         <v>10</v>
       </c>
       <c r="H141" t="s">
-        <v>110</v>
+        <v>179</v>
       </c>
       <c r="I141" t="s">
-        <v>110</v>
+        <v>58</v>
       </c>
       <c r="J141" s="1">
         <v>3010101</v>
@@ -5441,16 +5441,16 @@
         <v>17</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>44</v>
+        <v>145</v>
       </c>
       <c r="G142">
         <v>10</v>
       </c>
       <c r="H142" t="s">
-        <v>111</v>
+        <v>179</v>
       </c>
       <c r="I142" t="s">
-        <v>111</v>
+        <v>59</v>
       </c>
       <c r="J142" s="1">
         <v>3030101</v>
@@ -5473,16 +5473,16 @@
         <v>17</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>44</v>
+        <v>145</v>
       </c>
       <c r="G143">
         <v>10</v>
       </c>
       <c r="H143" t="s">
-        <v>111</v>
+        <v>179</v>
       </c>
       <c r="I143" t="s">
-        <v>111</v>
+        <v>59</v>
       </c>
       <c r="J143" s="1">
         <v>3030101</v>
@@ -5505,16 +5505,16 @@
         <v>17</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>44</v>
+        <v>145</v>
       </c>
       <c r="G144">
         <v>10</v>
       </c>
       <c r="H144" t="s">
-        <v>111</v>
+        <v>179</v>
       </c>
       <c r="I144" t="s">
-        <v>111</v>
+        <v>59</v>
       </c>
       <c r="J144" s="1">
         <v>3030101</v>
@@ -5537,16 +5537,16 @@
         <v>17</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>44</v>
+        <v>145</v>
       </c>
       <c r="G145">
         <v>10</v>
       </c>
       <c r="H145" t="s">
-        <v>110</v>
+        <v>179</v>
       </c>
       <c r="I145" t="s">
-        <v>110</v>
+        <v>58</v>
       </c>
       <c r="J145" s="1">
         <v>3010101</v>
@@ -5569,16 +5569,16 @@
         <v>17</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>44</v>
+        <v>145</v>
       </c>
       <c r="G146">
         <v>10</v>
       </c>
       <c r="H146" t="s">
-        <v>111</v>
+        <v>179</v>
       </c>
       <c r="I146" t="s">
-        <v>111</v>
+        <v>59</v>
       </c>
       <c r="J146" s="1">
         <v>3030101</v>
@@ -5601,16 +5601,16 @@
         <v>17</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>44</v>
+        <v>145</v>
       </c>
       <c r="G147">
         <v>10</v>
       </c>
       <c r="H147" t="s">
-        <v>110</v>
+        <v>179</v>
       </c>
       <c r="I147" t="s">
-        <v>110</v>
+        <v>58</v>
       </c>
       <c r="J147" s="1">
         <v>3010101</v>
@@ -5633,16 +5633,16 @@
         <v>17</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>44</v>
+        <v>145</v>
       </c>
       <c r="G148">
         <v>10</v>
       </c>
       <c r="H148" t="s">
-        <v>110</v>
+        <v>179</v>
       </c>
       <c r="I148" t="s">
-        <v>110</v>
+        <v>58</v>
       </c>
       <c r="J148" s="1">
         <v>3010101</v>
@@ -5665,16 +5665,16 @@
         <v>18</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>45</v>
+        <v>146</v>
       </c>
       <c r="G149">
         <v>10</v>
       </c>
       <c r="H149" t="s">
-        <v>112</v>
+        <v>179</v>
       </c>
       <c r="I149" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="J149" s="1">
         <v>3010101</v>
@@ -5697,16 +5697,16 @@
         <v>18</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>45</v>
+        <v>146</v>
       </c>
       <c r="G150">
         <v>10</v>
       </c>
       <c r="H150" t="s">
-        <v>113</v>
+        <v>179</v>
       </c>
       <c r="I150" t="s">
-        <v>113</v>
+        <v>61</v>
       </c>
       <c r="J150" s="1">
         <v>3030101</v>
@@ -5729,16 +5729,16 @@
         <v>18</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>45</v>
+        <v>146</v>
       </c>
       <c r="G151">
         <v>10</v>
       </c>
       <c r="H151" t="s">
-        <v>113</v>
+        <v>179</v>
       </c>
       <c r="I151" t="s">
-        <v>113</v>
+        <v>61</v>
       </c>
       <c r="J151" s="1">
         <v>3030101</v>
@@ -5761,16 +5761,16 @@
         <v>18</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>45</v>
+        <v>146</v>
       </c>
       <c r="G152">
         <v>10</v>
       </c>
       <c r="H152" t="s">
-        <v>113</v>
+        <v>179</v>
       </c>
       <c r="I152" t="s">
-        <v>113</v>
+        <v>61</v>
       </c>
       <c r="J152" s="1">
         <v>3030101</v>
@@ -5793,16 +5793,16 @@
         <v>18</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>45</v>
+        <v>146</v>
       </c>
       <c r="G153">
         <v>10</v>
       </c>
       <c r="H153" t="s">
-        <v>112</v>
+        <v>179</v>
       </c>
       <c r="I153" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="J153" s="1">
         <v>3010101</v>
@@ -5825,16 +5825,16 @@
         <v>18</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>45</v>
+        <v>146</v>
       </c>
       <c r="G154">
         <v>10</v>
       </c>
       <c r="H154" t="s">
-        <v>113</v>
+        <v>179</v>
       </c>
       <c r="I154" t="s">
-        <v>113</v>
+        <v>61</v>
       </c>
       <c r="J154" s="1">
         <v>3030101</v>
@@ -5857,16 +5857,16 @@
         <v>18</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>45</v>
+        <v>146</v>
       </c>
       <c r="G155">
         <v>10</v>
       </c>
       <c r="H155" t="s">
-        <v>112</v>
+        <v>179</v>
       </c>
       <c r="I155" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="J155" s="1">
         <v>3010101</v>
@@ -5889,16 +5889,16 @@
         <v>18</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>45</v>
+        <v>146</v>
       </c>
       <c r="G156">
         <v>10</v>
       </c>
       <c r="H156" t="s">
-        <v>112</v>
+        <v>179</v>
       </c>
       <c r="I156" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="J156" s="1">
         <v>3010101</v>
@@ -5921,16 +5921,16 @@
         <v>19</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>46</v>
+        <v>147</v>
       </c>
       <c r="G157">
         <v>10</v>
       </c>
       <c r="H157" t="s">
-        <v>114</v>
+        <v>179</v>
       </c>
       <c r="I157" t="s">
-        <v>114</v>
+        <v>62</v>
       </c>
       <c r="J157" s="1">
         <v>3010101</v>
@@ -5953,16 +5953,16 @@
         <v>19</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>46</v>
+        <v>147</v>
       </c>
       <c r="G158">
         <v>10</v>
       </c>
       <c r="H158" t="s">
-        <v>115</v>
+        <v>179</v>
       </c>
       <c r="I158" t="s">
-        <v>115</v>
+        <v>63</v>
       </c>
       <c r="J158" s="1">
         <v>3030101</v>
@@ -5985,16 +5985,16 @@
         <v>19</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>46</v>
+        <v>147</v>
       </c>
       <c r="G159">
         <v>10</v>
       </c>
       <c r="H159" t="s">
-        <v>115</v>
+        <v>179</v>
       </c>
       <c r="I159" t="s">
-        <v>115</v>
+        <v>63</v>
       </c>
       <c r="J159" s="1">
         <v>3030101</v>
@@ -6017,16 +6017,16 @@
         <v>19</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>46</v>
+        <v>147</v>
       </c>
       <c r="G160">
         <v>10</v>
       </c>
       <c r="H160" t="s">
-        <v>115</v>
+        <v>179</v>
       </c>
       <c r="I160" t="s">
-        <v>115</v>
+        <v>63</v>
       </c>
       <c r="J160" s="1">
         <v>3030101</v>
@@ -6049,16 +6049,16 @@
         <v>19</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>46</v>
+        <v>147</v>
       </c>
       <c r="G161">
         <v>10</v>
       </c>
       <c r="H161" t="s">
-        <v>114</v>
+        <v>179</v>
       </c>
       <c r="I161" t="s">
-        <v>114</v>
+        <v>62</v>
       </c>
       <c r="J161" s="1">
         <v>3010101</v>
@@ -6081,16 +6081,16 @@
         <v>19</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>46</v>
+        <v>147</v>
       </c>
       <c r="G162">
         <v>10</v>
       </c>
       <c r="H162" t="s">
-        <v>115</v>
+        <v>179</v>
       </c>
       <c r="I162" t="s">
-        <v>115</v>
+        <v>63</v>
       </c>
       <c r="J162" s="1">
         <v>3030101</v>
@@ -6113,16 +6113,16 @@
         <v>19</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>46</v>
+        <v>147</v>
       </c>
       <c r="G163">
         <v>10</v>
       </c>
       <c r="H163" t="s">
-        <v>114</v>
+        <v>179</v>
       </c>
       <c r="I163" t="s">
-        <v>114</v>
+        <v>62</v>
       </c>
       <c r="J163" s="1">
         <v>3010101</v>
@@ -6145,16 +6145,16 @@
         <v>19</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>46</v>
+        <v>147</v>
       </c>
       <c r="G164">
         <v>10</v>
       </c>
       <c r="H164" t="s">
-        <v>114</v>
+        <v>179</v>
       </c>
       <c r="I164" t="s">
-        <v>114</v>
+        <v>62</v>
       </c>
       <c r="J164" s="1">
         <v>3010101</v>
@@ -6177,16 +6177,16 @@
         <v>20</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>47</v>
+        <v>148</v>
       </c>
       <c r="G165">
         <v>20</v>
       </c>
       <c r="H165" t="s">
-        <v>116</v>
+        <v>179</v>
       </c>
       <c r="I165" t="s">
-        <v>116</v>
+        <v>64</v>
       </c>
       <c r="J165" s="1">
         <v>3010101</v>
@@ -6209,16 +6209,16 @@
         <v>20</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>47</v>
+        <v>148</v>
       </c>
       <c r="G166">
         <v>20</v>
       </c>
       <c r="H166" t="s">
-        <v>117</v>
+        <v>179</v>
       </c>
       <c r="I166" t="s">
-        <v>117</v>
+        <v>65</v>
       </c>
       <c r="J166" s="1">
         <v>3030101</v>
@@ -6241,16 +6241,16 @@
         <v>20</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>47</v>
+        <v>148</v>
       </c>
       <c r="G167">
         <v>20</v>
       </c>
       <c r="H167" t="s">
-        <v>117</v>
+        <v>179</v>
       </c>
       <c r="I167" t="s">
-        <v>117</v>
+        <v>65</v>
       </c>
       <c r="J167" s="1">
         <v>3030101</v>
@@ -6273,16 +6273,16 @@
         <v>20</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>47</v>
+        <v>148</v>
       </c>
       <c r="G168">
         <v>20</v>
       </c>
       <c r="H168" t="s">
-        <v>117</v>
+        <v>179</v>
       </c>
       <c r="I168" t="s">
-        <v>117</v>
+        <v>65</v>
       </c>
       <c r="J168" s="1">
         <v>3030101</v>
@@ -6305,16 +6305,16 @@
         <v>20</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>47</v>
+        <v>148</v>
       </c>
       <c r="G169">
         <v>20</v>
       </c>
       <c r="H169" t="s">
-        <v>116</v>
+        <v>179</v>
       </c>
       <c r="I169" t="s">
-        <v>116</v>
+        <v>64</v>
       </c>
       <c r="J169" s="1">
         <v>3010101</v>
@@ -6337,16 +6337,16 @@
         <v>20</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>47</v>
+        <v>148</v>
       </c>
       <c r="G170">
         <v>20</v>
       </c>
       <c r="H170" t="s">
-        <v>117</v>
+        <v>179</v>
       </c>
       <c r="I170" t="s">
-        <v>117</v>
+        <v>65</v>
       </c>
       <c r="J170" s="1">
         <v>3030101</v>
@@ -6369,16 +6369,16 @@
         <v>20</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>47</v>
+        <v>148</v>
       </c>
       <c r="G171">
         <v>20</v>
       </c>
       <c r="H171" t="s">
-        <v>116</v>
+        <v>179</v>
       </c>
       <c r="I171" t="s">
-        <v>116</v>
+        <v>64</v>
       </c>
       <c r="J171" s="1">
         <v>3010101</v>
@@ -6401,16 +6401,16 @@
         <v>20</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>47</v>
+        <v>148</v>
       </c>
       <c r="G172">
         <v>20</v>
       </c>
       <c r="H172" t="s">
-        <v>116</v>
+        <v>179</v>
       </c>
       <c r="I172" t="s">
-        <v>116</v>
+        <v>64</v>
       </c>
       <c r="J172" s="1">
         <v>3010101</v>
@@ -6433,16 +6433,16 @@
         <v>21</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>48</v>
+        <v>149</v>
       </c>
       <c r="G173">
         <v>20</v>
       </c>
       <c r="H173" t="s">
-        <v>118</v>
+        <v>179</v>
       </c>
       <c r="I173" t="s">
-        <v>118</v>
+        <v>66</v>
       </c>
       <c r="J173" s="1">
         <v>3010101</v>
@@ -6465,16 +6465,16 @@
         <v>21</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>48</v>
+        <v>149</v>
       </c>
       <c r="G174">
         <v>20</v>
       </c>
       <c r="H174" t="s">
-        <v>119</v>
+        <v>179</v>
       </c>
       <c r="I174" t="s">
-        <v>119</v>
+        <v>67</v>
       </c>
       <c r="J174" s="1">
         <v>3030101</v>
@@ -6497,16 +6497,16 @@
         <v>21</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>48</v>
+        <v>149</v>
       </c>
       <c r="G175">
         <v>20</v>
       </c>
       <c r="H175" t="s">
-        <v>119</v>
+        <v>179</v>
       </c>
       <c r="I175" t="s">
-        <v>119</v>
+        <v>67</v>
       </c>
       <c r="J175" s="1">
         <v>3030101</v>
@@ -6529,16 +6529,16 @@
         <v>21</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>48</v>
+        <v>149</v>
       </c>
       <c r="G176">
         <v>20</v>
       </c>
       <c r="H176" t="s">
-        <v>119</v>
+        <v>179</v>
       </c>
       <c r="I176" t="s">
-        <v>119</v>
+        <v>67</v>
       </c>
       <c r="J176" s="1">
         <v>3030101</v>
@@ -6561,16 +6561,16 @@
         <v>21</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>48</v>
+        <v>149</v>
       </c>
       <c r="G177">
         <v>20</v>
       </c>
       <c r="H177" t="s">
-        <v>118</v>
+        <v>179</v>
       </c>
       <c r="I177" t="s">
-        <v>118</v>
+        <v>66</v>
       </c>
       <c r="J177" s="1">
         <v>3010101</v>
@@ -6593,16 +6593,16 @@
         <v>21</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>48</v>
+        <v>149</v>
       </c>
       <c r="G178">
         <v>20</v>
       </c>
       <c r="H178" t="s">
-        <v>119</v>
+        <v>179</v>
       </c>
       <c r="I178" t="s">
-        <v>119</v>
+        <v>67</v>
       </c>
       <c r="J178" s="1">
         <v>3030101</v>
@@ -6625,16 +6625,16 @@
         <v>21</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>48</v>
+        <v>149</v>
       </c>
       <c r="G179">
         <v>20</v>
       </c>
       <c r="H179" t="s">
-        <v>118</v>
+        <v>179</v>
       </c>
       <c r="I179" t="s">
-        <v>118</v>
+        <v>66</v>
       </c>
       <c r="J179" s="1">
         <v>3010101</v>
@@ -6657,16 +6657,16 @@
         <v>21</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>48</v>
+        <v>149</v>
       </c>
       <c r="G180">
         <v>20</v>
       </c>
       <c r="H180" t="s">
-        <v>118</v>
+        <v>179</v>
       </c>
       <c r="I180" t="s">
-        <v>118</v>
+        <v>66</v>
       </c>
       <c r="J180" s="1">
         <v>3010101</v>
@@ -6689,16 +6689,16 @@
         <v>22</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>49</v>
+        <v>150</v>
       </c>
       <c r="G181">
         <v>20</v>
       </c>
       <c r="H181" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="I181" t="s">
-        <v>120</v>
+        <v>68</v>
       </c>
       <c r="J181" s="1">
         <v>3010101</v>
@@ -6721,16 +6721,16 @@
         <v>22</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>49</v>
+        <v>150</v>
       </c>
       <c r="G182">
         <v>20</v>
       </c>
       <c r="H182" t="s">
-        <v>121</v>
+        <v>179</v>
       </c>
       <c r="I182" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
       <c r="J182" s="1">
         <v>3030101</v>
@@ -6753,16 +6753,16 @@
         <v>22</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>49</v>
+        <v>150</v>
       </c>
       <c r="G183">
         <v>20</v>
       </c>
       <c r="H183" t="s">
-        <v>121</v>
+        <v>179</v>
       </c>
       <c r="I183" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
       <c r="J183" s="1">
         <v>3030101</v>
@@ -6785,16 +6785,16 @@
         <v>22</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>49</v>
+        <v>150</v>
       </c>
       <c r="G184">
         <v>20</v>
       </c>
       <c r="H184" t="s">
-        <v>121</v>
+        <v>179</v>
       </c>
       <c r="I184" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
       <c r="J184" s="1">
         <v>3030101</v>
@@ -6817,16 +6817,16 @@
         <v>22</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>49</v>
+        <v>150</v>
       </c>
       <c r="G185">
         <v>20</v>
       </c>
       <c r="H185" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="I185" t="s">
-        <v>120</v>
+        <v>68</v>
       </c>
       <c r="J185" s="1">
         <v>3010101</v>
@@ -6849,16 +6849,16 @@
         <v>22</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>49</v>
+        <v>150</v>
       </c>
       <c r="G186">
         <v>20</v>
       </c>
       <c r="H186" t="s">
-        <v>121</v>
+        <v>179</v>
       </c>
       <c r="I186" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
       <c r="J186" s="1">
         <v>3030101</v>
@@ -6881,16 +6881,16 @@
         <v>22</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>49</v>
+        <v>150</v>
       </c>
       <c r="G187">
         <v>20</v>
       </c>
       <c r="H187" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="I187" t="s">
-        <v>120</v>
+        <v>68</v>
       </c>
       <c r="J187" s="1">
         <v>3010101</v>
@@ -6913,16 +6913,16 @@
         <v>22</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>49</v>
+        <v>150</v>
       </c>
       <c r="G188">
         <v>20</v>
       </c>
       <c r="H188" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="I188" t="s">
-        <v>120</v>
+        <v>68</v>
       </c>
       <c r="J188" s="1">
         <v>3010101</v>
@@ -6945,16 +6945,16 @@
         <v>23</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>50</v>
+        <v>151</v>
       </c>
       <c r="G189">
         <v>20</v>
       </c>
       <c r="H189" t="s">
-        <v>122</v>
+        <v>179</v>
       </c>
       <c r="I189" t="s">
-        <v>122</v>
+        <v>70</v>
       </c>
       <c r="J189" s="1">
         <v>3010101</v>
@@ -6977,16 +6977,16 @@
         <v>23</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>50</v>
+        <v>151</v>
       </c>
       <c r="G190">
         <v>20</v>
       </c>
       <c r="H190" t="s">
-        <v>123</v>
+        <v>179</v>
       </c>
       <c r="I190" t="s">
-        <v>123</v>
+        <v>71</v>
       </c>
       <c r="J190" s="1">
         <v>3030101</v>
@@ -7009,16 +7009,16 @@
         <v>23</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>50</v>
+        <v>151</v>
       </c>
       <c r="G191">
         <v>20</v>
       </c>
       <c r="H191" t="s">
-        <v>123</v>
+        <v>179</v>
       </c>
       <c r="I191" t="s">
-        <v>123</v>
+        <v>71</v>
       </c>
       <c r="J191" s="1">
         <v>3030101</v>
@@ -7041,16 +7041,16 @@
         <v>23</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>50</v>
+        <v>151</v>
       </c>
       <c r="G192">
         <v>20</v>
       </c>
       <c r="H192" t="s">
-        <v>123</v>
+        <v>179</v>
       </c>
       <c r="I192" t="s">
-        <v>123</v>
+        <v>71</v>
       </c>
       <c r="J192" s="1">
         <v>3030101</v>
@@ -7073,16 +7073,16 @@
         <v>23</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>50</v>
+        <v>151</v>
       </c>
       <c r="G193">
         <v>20</v>
       </c>
       <c r="H193" t="s">
-        <v>122</v>
+        <v>179</v>
       </c>
       <c r="I193" t="s">
-        <v>122</v>
+        <v>70</v>
       </c>
       <c r="J193" s="1">
         <v>3010101</v>
@@ -7105,16 +7105,16 @@
         <v>23</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>50</v>
+        <v>151</v>
       </c>
       <c r="G194">
         <v>20</v>
       </c>
       <c r="H194" t="s">
-        <v>123</v>
+        <v>179</v>
       </c>
       <c r="I194" t="s">
-        <v>123</v>
+        <v>71</v>
       </c>
       <c r="J194" s="1">
         <v>3030101</v>
@@ -7137,16 +7137,16 @@
         <v>23</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>50</v>
+        <v>151</v>
       </c>
       <c r="G195">
         <v>20</v>
       </c>
       <c r="H195" t="s">
-        <v>122</v>
+        <v>179</v>
       </c>
       <c r="I195" t="s">
-        <v>122</v>
+        <v>70</v>
       </c>
       <c r="J195" s="1">
         <v>3010101</v>
@@ -7169,16 +7169,16 @@
         <v>23</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>50</v>
+        <v>151</v>
       </c>
       <c r="G196">
         <v>20</v>
       </c>
       <c r="H196" t="s">
-        <v>122</v>
+        <v>179</v>
       </c>
       <c r="I196" t="s">
-        <v>122</v>
+        <v>70</v>
       </c>
       <c r="J196" s="1">
         <v>3010101</v>
@@ -7201,16 +7201,16 @@
         <v>24</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>51</v>
+        <v>152</v>
       </c>
       <c r="G197">
         <v>20</v>
       </c>
       <c r="H197" t="s">
-        <v>124</v>
+        <v>179</v>
       </c>
       <c r="I197" t="s">
-        <v>124</v>
+        <v>72</v>
       </c>
       <c r="J197" s="1">
         <v>3010101</v>
@@ -7233,16 +7233,16 @@
         <v>24</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>51</v>
+        <v>152</v>
       </c>
       <c r="G198">
         <v>20</v>
       </c>
       <c r="H198" t="s">
-        <v>125</v>
+        <v>179</v>
       </c>
       <c r="I198" t="s">
-        <v>125</v>
+        <v>73</v>
       </c>
       <c r="J198" s="1">
         <v>3030101</v>
@@ -7265,16 +7265,16 @@
         <v>24</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>51</v>
+        <v>152</v>
       </c>
       <c r="G199">
         <v>20</v>
       </c>
       <c r="H199" t="s">
-        <v>125</v>
+        <v>179</v>
       </c>
       <c r="I199" t="s">
-        <v>125</v>
+        <v>73</v>
       </c>
       <c r="J199" s="1">
         <v>3030101</v>
@@ -7297,16 +7297,16 @@
         <v>24</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>51</v>
+        <v>152</v>
       </c>
       <c r="G200">
         <v>20</v>
       </c>
       <c r="H200" t="s">
-        <v>125</v>
+        <v>179</v>
       </c>
       <c r="I200" t="s">
-        <v>125</v>
+        <v>73</v>
       </c>
       <c r="J200" s="1">
         <v>3030101</v>
@@ -7329,16 +7329,16 @@
         <v>24</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>51</v>
+        <v>152</v>
       </c>
       <c r="G201">
         <v>20</v>
       </c>
       <c r="H201" t="s">
-        <v>124</v>
+        <v>179</v>
       </c>
       <c r="I201" t="s">
-        <v>124</v>
+        <v>72</v>
       </c>
       <c r="J201" s="1">
         <v>3010101</v>
@@ -7361,16 +7361,16 @@
         <v>24</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>51</v>
+        <v>152</v>
       </c>
       <c r="G202">
         <v>20</v>
       </c>
       <c r="H202" t="s">
-        <v>125</v>
+        <v>179</v>
       </c>
       <c r="I202" t="s">
-        <v>125</v>
+        <v>73</v>
       </c>
       <c r="J202" s="1">
         <v>3030101</v>
@@ -7393,16 +7393,16 @@
         <v>24</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>51</v>
+        <v>152</v>
       </c>
       <c r="G203">
         <v>20</v>
       </c>
       <c r="H203" t="s">
-        <v>124</v>
+        <v>179</v>
       </c>
       <c r="I203" t="s">
-        <v>124</v>
+        <v>72</v>
       </c>
       <c r="J203" s="1">
         <v>3010101</v>
@@ -7425,16 +7425,16 @@
         <v>24</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>51</v>
+        <v>152</v>
       </c>
       <c r="G204">
         <v>20</v>
       </c>
       <c r="H204" t="s">
-        <v>124</v>
+        <v>179</v>
       </c>
       <c r="I204" t="s">
-        <v>124</v>
+        <v>72</v>
       </c>
       <c r="J204" s="1">
         <v>3010101</v>
@@ -7457,16 +7457,16 @@
         <v>25</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>52</v>
+        <v>153</v>
       </c>
       <c r="G205">
         <v>20</v>
       </c>
       <c r="H205" t="s">
-        <v>126</v>
+        <v>179</v>
       </c>
       <c r="I205" t="s">
-        <v>126</v>
+        <v>74</v>
       </c>
       <c r="J205" s="1">
         <v>3010101</v>
@@ -7489,16 +7489,16 @@
         <v>25</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>52</v>
+        <v>153</v>
       </c>
       <c r="G206">
         <v>20</v>
       </c>
       <c r="H206" t="s">
-        <v>127</v>
+        <v>179</v>
       </c>
       <c r="I206" t="s">
-        <v>127</v>
+        <v>75</v>
       </c>
       <c r="J206" s="1">
         <v>3030101</v>
@@ -7521,16 +7521,16 @@
         <v>25</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>52</v>
+        <v>153</v>
       </c>
       <c r="G207">
         <v>20</v>
       </c>
       <c r="H207" t="s">
-        <v>127</v>
+        <v>179</v>
       </c>
       <c r="I207" t="s">
-        <v>127</v>
+        <v>75</v>
       </c>
       <c r="J207" s="1">
         <v>3030101</v>
@@ -7553,16 +7553,16 @@
         <v>25</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>52</v>
+        <v>153</v>
       </c>
       <c r="G208">
         <v>20</v>
       </c>
       <c r="H208" t="s">
-        <v>127</v>
+        <v>179</v>
       </c>
       <c r="I208" t="s">
-        <v>127</v>
+        <v>75</v>
       </c>
       <c r="J208" s="1">
         <v>3030101</v>
@@ -7585,16 +7585,16 @@
         <v>25</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>52</v>
+        <v>153</v>
       </c>
       <c r="G209">
         <v>20</v>
       </c>
       <c r="H209" t="s">
-        <v>126</v>
+        <v>179</v>
       </c>
       <c r="I209" t="s">
-        <v>126</v>
+        <v>74</v>
       </c>
       <c r="J209" s="1">
         <v>3010101</v>
@@ -7617,16 +7617,16 @@
         <v>25</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>52</v>
+        <v>153</v>
       </c>
       <c r="G210">
         <v>20</v>
       </c>
       <c r="H210" t="s">
-        <v>127</v>
+        <v>179</v>
       </c>
       <c r="I210" t="s">
-        <v>127</v>
+        <v>75</v>
       </c>
       <c r="J210" s="1">
         <v>3030101</v>
@@ -7649,16 +7649,16 @@
         <v>25</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>52</v>
+        <v>153</v>
       </c>
       <c r="G211">
         <v>20</v>
       </c>
       <c r="H211" t="s">
-        <v>126</v>
+        <v>179</v>
       </c>
       <c r="I211" t="s">
-        <v>126</v>
+        <v>74</v>
       </c>
       <c r="J211" s="1">
         <v>3010101</v>
@@ -7681,16 +7681,16 @@
         <v>25</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>52</v>
+        <v>153</v>
       </c>
       <c r="G212">
         <v>20</v>
       </c>
       <c r="H212" t="s">
-        <v>126</v>
+        <v>179</v>
       </c>
       <c r="I212" t="s">
-        <v>126</v>
+        <v>74</v>
       </c>
       <c r="J212" s="1">
         <v>3010101</v>
@@ -7713,16 +7713,16 @@
         <v>26</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>53</v>
+        <v>154</v>
       </c>
       <c r="G213">
         <v>20</v>
       </c>
       <c r="H213" t="s">
-        <v>128</v>
+        <v>179</v>
       </c>
       <c r="I213" t="s">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="J213" s="1">
         <v>3010101</v>
@@ -7745,16 +7745,16 @@
         <v>26</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>53</v>
+        <v>154</v>
       </c>
       <c r="G214">
         <v>20</v>
       </c>
       <c r="H214" t="s">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="I214" t="s">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="J214" s="1">
         <v>3030101</v>
@@ -7777,16 +7777,16 @@
         <v>26</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>53</v>
+        <v>154</v>
       </c>
       <c r="G215">
         <v>20</v>
       </c>
       <c r="H215" t="s">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="I215" t="s">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="J215" s="1">
         <v>3030101</v>
@@ -7809,16 +7809,16 @@
         <v>26</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>53</v>
+        <v>154</v>
       </c>
       <c r="G216">
         <v>20</v>
       </c>
       <c r="H216" t="s">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="I216" t="s">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="J216" s="1">
         <v>3030101</v>
@@ -7841,16 +7841,16 @@
         <v>26</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>53</v>
+        <v>154</v>
       </c>
       <c r="G217">
         <v>20</v>
       </c>
       <c r="H217" t="s">
-        <v>128</v>
+        <v>179</v>
       </c>
       <c r="I217" t="s">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="J217" s="1">
         <v>3010101</v>
@@ -7873,16 +7873,16 @@
         <v>26</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>53</v>
+        <v>154</v>
       </c>
       <c r="G218">
         <v>20</v>
       </c>
       <c r="H218" t="s">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="I218" t="s">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="J218" s="1">
         <v>3030101</v>
@@ -7905,16 +7905,16 @@
         <v>26</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>53</v>
+        <v>154</v>
       </c>
       <c r="G219">
         <v>20</v>
       </c>
       <c r="H219" t="s">
-        <v>128</v>
+        <v>179</v>
       </c>
       <c r="I219" t="s">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="J219" s="1">
         <v>3010101</v>
@@ -7937,16 +7937,16 @@
         <v>26</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>53</v>
+        <v>154</v>
       </c>
       <c r="G220">
         <v>20</v>
       </c>
       <c r="H220" t="s">
-        <v>128</v>
+        <v>179</v>
       </c>
       <c r="I220" t="s">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="J220" s="1">
         <v>3010101</v>
@@ -7969,16 +7969,16 @@
         <v>27</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>54</v>
+        <v>155</v>
       </c>
       <c r="G221">
         <v>20</v>
       </c>
       <c r="H221" t="s">
-        <v>130</v>
+        <v>179</v>
       </c>
       <c r="I221" t="s">
-        <v>130</v>
+        <v>78</v>
       </c>
       <c r="J221" s="1">
         <v>3010101</v>
@@ -8001,16 +8001,16 @@
         <v>27</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>54</v>
+        <v>155</v>
       </c>
       <c r="G222">
         <v>20</v>
       </c>
       <c r="H222" t="s">
-        <v>131</v>
+        <v>179</v>
       </c>
       <c r="I222" t="s">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="J222" s="1">
         <v>3030101</v>
@@ -8033,16 +8033,16 @@
         <v>27</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>54</v>
+        <v>155</v>
       </c>
       <c r="G223">
         <v>20</v>
       </c>
       <c r="H223" t="s">
-        <v>131</v>
+        <v>179</v>
       </c>
       <c r="I223" t="s">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="J223" s="1">
         <v>3030101</v>
@@ -8065,16 +8065,16 @@
         <v>27</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>54</v>
+        <v>155</v>
       </c>
       <c r="G224">
         <v>20</v>
       </c>
       <c r="H224" t="s">
-        <v>131</v>
+        <v>179</v>
       </c>
       <c r="I224" t="s">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="J224" s="1">
         <v>3030101</v>
@@ -8097,16 +8097,16 @@
         <v>27</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>54</v>
+        <v>155</v>
       </c>
       <c r="G225">
         <v>20</v>
       </c>
       <c r="H225" t="s">
-        <v>130</v>
+        <v>179</v>
       </c>
       <c r="I225" t="s">
-        <v>130</v>
+        <v>78</v>
       </c>
       <c r="J225" s="1">
         <v>3010101</v>
@@ -8129,16 +8129,16 @@
         <v>27</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>54</v>
+        <v>155</v>
       </c>
       <c r="G226">
         <v>20</v>
       </c>
       <c r="H226" t="s">
-        <v>131</v>
+        <v>179</v>
       </c>
       <c r="I226" t="s">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="J226" s="1">
         <v>3030101</v>
@@ -8161,16 +8161,16 @@
         <v>27</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>54</v>
+        <v>155</v>
       </c>
       <c r="G227">
         <v>20</v>
       </c>
       <c r="H227" t="s">
-        <v>130</v>
+        <v>179</v>
       </c>
       <c r="I227" t="s">
-        <v>130</v>
+        <v>78</v>
       </c>
       <c r="J227" s="1">
         <v>3010101</v>
@@ -8193,16 +8193,16 @@
         <v>27</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>54</v>
+        <v>155</v>
       </c>
       <c r="G228">
         <v>20</v>
       </c>
       <c r="H228" t="s">
-        <v>130</v>
+        <v>179</v>
       </c>
       <c r="I228" t="s">
-        <v>130</v>
+        <v>78</v>
       </c>
       <c r="J228" s="1">
         <v>3010101</v>
@@ -8225,16 +8225,16 @@
         <v>28</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>55</v>
+        <v>156</v>
       </c>
       <c r="G229">
         <v>20</v>
       </c>
       <c r="H229" t="s">
-        <v>132</v>
+        <v>179</v>
       </c>
       <c r="I229" t="s">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="J229" s="1">
         <v>3010101</v>
@@ -8257,16 +8257,16 @@
         <v>28</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>55</v>
+        <v>156</v>
       </c>
       <c r="G230">
         <v>20</v>
       </c>
       <c r="H230" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="I230" t="s">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="J230" s="1">
         <v>3030101</v>
@@ -8289,16 +8289,16 @@
         <v>28</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>55</v>
+        <v>156</v>
       </c>
       <c r="G231">
         <v>20</v>
       </c>
       <c r="H231" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="I231" t="s">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="J231" s="1">
         <v>3030101</v>
@@ -8321,16 +8321,16 @@
         <v>28</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>55</v>
+        <v>156</v>
       </c>
       <c r="G232">
         <v>20</v>
       </c>
       <c r="H232" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="I232" t="s">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="J232" s="1">
         <v>3030101</v>
@@ -8353,16 +8353,16 @@
         <v>28</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>55</v>
+        <v>156</v>
       </c>
       <c r="G233">
         <v>20</v>
       </c>
       <c r="H233" t="s">
-        <v>132</v>
+        <v>179</v>
       </c>
       <c r="I233" t="s">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="J233" s="1">
         <v>3010101</v>
@@ -8385,16 +8385,16 @@
         <v>28</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>55</v>
+        <v>156</v>
       </c>
       <c r="G234">
         <v>20</v>
       </c>
       <c r="H234" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="I234" t="s">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="J234" s="1">
         <v>3030101</v>
@@ -8417,16 +8417,16 @@
         <v>28</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>55</v>
+        <v>156</v>
       </c>
       <c r="G235">
         <v>20</v>
       </c>
       <c r="H235" t="s">
-        <v>132</v>
+        <v>179</v>
       </c>
       <c r="I235" t="s">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="J235" s="1">
         <v>3010101</v>
@@ -8449,16 +8449,16 @@
         <v>28</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>55</v>
+        <v>156</v>
       </c>
       <c r="G236">
         <v>20</v>
       </c>
       <c r="H236" t="s">
-        <v>132</v>
+        <v>179</v>
       </c>
       <c r="I236" t="s">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="J236" s="1">
         <v>3010101</v>
@@ -8481,16 +8481,16 @@
         <v>29</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>56</v>
+        <v>157</v>
       </c>
       <c r="G237">
         <v>20</v>
       </c>
       <c r="H237" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="I237" t="s">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="J237" s="1">
         <v>3010101</v>
@@ -8513,16 +8513,16 @@
         <v>29</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>56</v>
+        <v>157</v>
       </c>
       <c r="G238">
         <v>20</v>
       </c>
       <c r="H238" t="s">
-        <v>135</v>
+        <v>179</v>
       </c>
       <c r="I238" t="s">
-        <v>135</v>
+        <v>83</v>
       </c>
       <c r="J238" s="1">
         <v>3030101</v>
@@ -8545,16 +8545,16 @@
         <v>29</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>56</v>
+        <v>157</v>
       </c>
       <c r="G239">
         <v>20</v>
       </c>
       <c r="H239" t="s">
-        <v>135</v>
+        <v>179</v>
       </c>
       <c r="I239" t="s">
-        <v>135</v>
+        <v>83</v>
       </c>
       <c r="J239" s="1">
         <v>3030101</v>
@@ -8577,16 +8577,16 @@
         <v>29</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>56</v>
+        <v>157</v>
       </c>
       <c r="G240">
         <v>20</v>
       </c>
       <c r="H240" t="s">
-        <v>135</v>
+        <v>179</v>
       </c>
       <c r="I240" t="s">
-        <v>135</v>
+        <v>83</v>
       </c>
       <c r="J240" s="1">
         <v>3030101</v>
@@ -8609,16 +8609,16 @@
         <v>29</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>56</v>
+        <v>157</v>
       </c>
       <c r="G241">
         <v>20</v>
       </c>
       <c r="H241" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="I241" t="s">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="J241" s="1">
         <v>3010101</v>
@@ -8641,16 +8641,16 @@
         <v>29</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>56</v>
+        <v>157</v>
       </c>
       <c r="G242">
         <v>20</v>
       </c>
       <c r="H242" t="s">
-        <v>135</v>
+        <v>179</v>
       </c>
       <c r="I242" t="s">
-        <v>135</v>
+        <v>83</v>
       </c>
       <c r="J242" s="1">
         <v>3030101</v>
@@ -8673,16 +8673,16 @@
         <v>29</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>56</v>
+        <v>157</v>
       </c>
       <c r="G243">
         <v>20</v>
       </c>
       <c r="H243" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="I243" t="s">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="J243" s="1">
         <v>3010101</v>
@@ -8705,16 +8705,16 @@
         <v>29</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>56</v>
+        <v>157</v>
       </c>
       <c r="G244">
         <v>20</v>
       </c>
       <c r="H244" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="I244" t="s">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="J244" s="1">
         <v>3010101</v>
@@ -8737,16 +8737,16 @@
         <v>30</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>57</v>
+        <v>158</v>
       </c>
       <c r="G245">
         <v>30</v>
       </c>
       <c r="H245" t="s">
-        <v>136</v>
+        <v>179</v>
       </c>
       <c r="I245" t="s">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="J245" s="1">
         <v>3010101</v>
@@ -8769,16 +8769,16 @@
         <v>30</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>57</v>
+        <v>158</v>
       </c>
       <c r="G246">
         <v>30</v>
       </c>
       <c r="H246" t="s">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c r="I246" t="s">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="J246" s="1">
         <v>3030101</v>
@@ -8801,16 +8801,16 @@
         <v>30</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>57</v>
+        <v>158</v>
       </c>
       <c r="G247">
         <v>30</v>
       </c>
       <c r="H247" t="s">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c r="I247" t="s">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="J247" s="1">
         <v>3030101</v>
@@ -8833,16 +8833,16 @@
         <v>30</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>57</v>
+        <v>158</v>
       </c>
       <c r="G248">
         <v>30</v>
       </c>
       <c r="H248" t="s">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c r="I248" t="s">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="J248" s="1">
         <v>3030101</v>
@@ -8865,16 +8865,16 @@
         <v>30</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>57</v>
+        <v>158</v>
       </c>
       <c r="G249">
         <v>30</v>
       </c>
       <c r="H249" t="s">
-        <v>136</v>
+        <v>179</v>
       </c>
       <c r="I249" t="s">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="J249" s="1">
         <v>3010101</v>
@@ -8897,16 +8897,16 @@
         <v>30</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>57</v>
+        <v>158</v>
       </c>
       <c r="G250">
         <v>30</v>
       </c>
       <c r="H250" t="s">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c r="I250" t="s">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="J250" s="1">
         <v>3030101</v>
@@ -8929,16 +8929,16 @@
         <v>30</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>57</v>
+        <v>158</v>
       </c>
       <c r="G251">
         <v>30</v>
       </c>
       <c r="H251" t="s">
-        <v>136</v>
+        <v>179</v>
       </c>
       <c r="I251" t="s">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="J251" s="1">
         <v>3010101</v>
@@ -8961,16 +8961,16 @@
         <v>30</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>57</v>
+        <v>158</v>
       </c>
       <c r="G252">
         <v>30</v>
       </c>
       <c r="H252" t="s">
-        <v>136</v>
+        <v>179</v>
       </c>
       <c r="I252" t="s">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="J252" s="1">
         <v>3010101</v>
@@ -8993,16 +8993,16 @@
         <v>31</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>58</v>
+        <v>159</v>
       </c>
       <c r="G253">
         <v>30</v>
       </c>
       <c r="H253" t="s">
-        <v>138</v>
+        <v>179</v>
       </c>
       <c r="I253" t="s">
-        <v>138</v>
+        <v>86</v>
       </c>
       <c r="J253" s="1">
         <v>3010101</v>
@@ -9025,16 +9025,16 @@
         <v>31</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>58</v>
+        <v>159</v>
       </c>
       <c r="G254">
         <v>30</v>
       </c>
       <c r="H254" t="s">
-        <v>139</v>
+        <v>179</v>
       </c>
       <c r="I254" t="s">
-        <v>139</v>
+        <v>87</v>
       </c>
       <c r="J254" s="1">
         <v>3030101</v>
@@ -9057,16 +9057,16 @@
         <v>31</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>58</v>
+        <v>159</v>
       </c>
       <c r="G255">
         <v>30</v>
       </c>
       <c r="H255" t="s">
-        <v>139</v>
+        <v>179</v>
       </c>
       <c r="I255" t="s">
-        <v>139</v>
+        <v>87</v>
       </c>
       <c r="J255" s="1">
         <v>3030101</v>
@@ -9089,16 +9089,16 @@
         <v>31</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>58</v>
+        <v>159</v>
       </c>
       <c r="G256">
         <v>30</v>
       </c>
       <c r="H256" t="s">
-        <v>139</v>
+        <v>179</v>
       </c>
       <c r="I256" t="s">
-        <v>139</v>
+        <v>87</v>
       </c>
       <c r="J256" s="1">
         <v>3030101</v>
@@ -9121,16 +9121,16 @@
         <v>31</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>58</v>
+        <v>159</v>
       </c>
       <c r="G257">
         <v>30</v>
       </c>
       <c r="H257" t="s">
-        <v>138</v>
+        <v>179</v>
       </c>
       <c r="I257" t="s">
-        <v>138</v>
+        <v>86</v>
       </c>
       <c r="J257" s="1">
         <v>3010101</v>
@@ -9153,16 +9153,16 @@
         <v>31</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>58</v>
+        <v>159</v>
       </c>
       <c r="G258">
         <v>30</v>
       </c>
       <c r="H258" t="s">
-        <v>139</v>
+        <v>179</v>
       </c>
       <c r="I258" t="s">
-        <v>139</v>
+        <v>87</v>
       </c>
       <c r="J258" s="1">
         <v>3030101</v>
@@ -9185,16 +9185,16 @@
         <v>31</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>58</v>
+        <v>159</v>
       </c>
       <c r="G259">
         <v>30</v>
       </c>
       <c r="H259" t="s">
-        <v>138</v>
+        <v>179</v>
       </c>
       <c r="I259" t="s">
-        <v>138</v>
+        <v>86</v>
       </c>
       <c r="J259" s="1">
         <v>3010101</v>
@@ -9217,16 +9217,16 @@
         <v>31</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>58</v>
+        <v>159</v>
       </c>
       <c r="G260">
         <v>30</v>
       </c>
       <c r="H260" t="s">
-        <v>138</v>
+        <v>179</v>
       </c>
       <c r="I260" t="s">
-        <v>138</v>
+        <v>86</v>
       </c>
       <c r="J260" s="1">
         <v>3010101</v>
@@ -9249,16 +9249,16 @@
         <v>32</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>59</v>
+        <v>160</v>
       </c>
       <c r="G261">
         <v>30</v>
       </c>
       <c r="H261" t="s">
-        <v>140</v>
+        <v>179</v>
       </c>
       <c r="I261" t="s">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="J261" s="1">
         <v>3010101</v>
@@ -9281,16 +9281,16 @@
         <v>32</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>59</v>
+        <v>160</v>
       </c>
       <c r="G262">
         <v>30</v>
       </c>
       <c r="H262" t="s">
-        <v>141</v>
+        <v>179</v>
       </c>
       <c r="I262" t="s">
-        <v>141</v>
+        <v>89</v>
       </c>
       <c r="J262" s="1">
         <v>3030101</v>
@@ -9313,16 +9313,16 @@
         <v>32</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>59</v>
+        <v>160</v>
       </c>
       <c r="G263">
         <v>30</v>
       </c>
       <c r="H263" t="s">
-        <v>141</v>
+        <v>179</v>
       </c>
       <c r="I263" t="s">
-        <v>141</v>
+        <v>89</v>
       </c>
       <c r="J263" s="1">
         <v>3030101</v>
@@ -9345,16 +9345,16 @@
         <v>32</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>59</v>
+        <v>160</v>
       </c>
       <c r="G264">
         <v>30</v>
       </c>
       <c r="H264" t="s">
-        <v>141</v>
+        <v>179</v>
       </c>
       <c r="I264" t="s">
-        <v>141</v>
+        <v>89</v>
       </c>
       <c r="J264" s="1">
         <v>3030101</v>
@@ -9377,16 +9377,16 @@
         <v>32</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>59</v>
+        <v>160</v>
       </c>
       <c r="G265">
         <v>30</v>
       </c>
       <c r="H265" t="s">
-        <v>140</v>
+        <v>179</v>
       </c>
       <c r="I265" t="s">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="J265" s="1">
         <v>3010101</v>
@@ -9409,16 +9409,16 @@
         <v>32</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>59</v>
+        <v>160</v>
       </c>
       <c r="G266">
         <v>30</v>
       </c>
       <c r="H266" t="s">
-        <v>141</v>
+        <v>179</v>
       </c>
       <c r="I266" t="s">
-        <v>141</v>
+        <v>89</v>
       </c>
       <c r="J266" s="1">
         <v>3030101</v>
@@ -9441,16 +9441,16 @@
         <v>32</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>59</v>
+        <v>160</v>
       </c>
       <c r="G267">
         <v>30</v>
       </c>
       <c r="H267" t="s">
-        <v>140</v>
+        <v>179</v>
       </c>
       <c r="I267" t="s">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="J267" s="1">
         <v>3010101</v>
@@ -9473,16 +9473,16 @@
         <v>32</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>59</v>
+        <v>160</v>
       </c>
       <c r="G268">
         <v>30</v>
       </c>
       <c r="H268" t="s">
-        <v>140</v>
+        <v>179</v>
       </c>
       <c r="I268" t="s">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="J268" s="1">
         <v>3010101</v>
@@ -9505,16 +9505,16 @@
         <v>33</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>60</v>
+        <v>161</v>
       </c>
       <c r="G269">
         <v>30</v>
       </c>
       <c r="H269" t="s">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="I269" t="s">
-        <v>142</v>
+        <v>90</v>
       </c>
       <c r="J269" s="1">
         <v>3010101</v>
@@ -9537,16 +9537,16 @@
         <v>33</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>60</v>
+        <v>161</v>
       </c>
       <c r="G270">
         <v>30</v>
       </c>
       <c r="H270" t="s">
-        <v>143</v>
+        <v>179</v>
       </c>
       <c r="I270" t="s">
-        <v>143</v>
+        <v>91</v>
       </c>
       <c r="J270" s="1">
         <v>3030101</v>
@@ -9569,16 +9569,16 @@
         <v>33</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>60</v>
+        <v>161</v>
       </c>
       <c r="G271">
         <v>30</v>
       </c>
       <c r="H271" t="s">
-        <v>143</v>
+        <v>179</v>
       </c>
       <c r="I271" t="s">
-        <v>143</v>
+        <v>91</v>
       </c>
       <c r="J271" s="1">
         <v>3030101</v>
@@ -9601,16 +9601,16 @@
         <v>33</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>60</v>
+        <v>161</v>
       </c>
       <c r="G272">
         <v>30</v>
       </c>
       <c r="H272" t="s">
-        <v>143</v>
+        <v>179</v>
       </c>
       <c r="I272" t="s">
-        <v>143</v>
+        <v>91</v>
       </c>
       <c r="J272" s="1">
         <v>3030101</v>
@@ -9633,16 +9633,16 @@
         <v>33</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>60</v>
+        <v>161</v>
       </c>
       <c r="G273">
         <v>30</v>
       </c>
       <c r="H273" t="s">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="I273" t="s">
-        <v>142</v>
+        <v>90</v>
       </c>
       <c r="J273" s="1">
         <v>3010101</v>
@@ -9665,16 +9665,16 @@
         <v>33</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>60</v>
+        <v>161</v>
       </c>
       <c r="G274">
         <v>30</v>
       </c>
       <c r="H274" t="s">
-        <v>143</v>
+        <v>179</v>
       </c>
       <c r="I274" t="s">
-        <v>143</v>
+        <v>91</v>
       </c>
       <c r="J274" s="1">
         <v>3030101</v>
@@ -9697,16 +9697,16 @@
         <v>33</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>60</v>
+        <v>161</v>
       </c>
       <c r="G275">
         <v>30</v>
       </c>
       <c r="H275" t="s">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="I275" t="s">
-        <v>142</v>
+        <v>90</v>
       </c>
       <c r="J275" s="1">
         <v>3010101</v>
@@ -9729,16 +9729,16 @@
         <v>33</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>60</v>
+        <v>161</v>
       </c>
       <c r="G276">
         <v>30</v>
       </c>
       <c r="H276" t="s">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="I276" t="s">
-        <v>142</v>
+        <v>90</v>
       </c>
       <c r="J276" s="1">
         <v>3010101</v>
@@ -9761,16 +9761,16 @@
         <v>34</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>61</v>
+        <v>162</v>
       </c>
       <c r="G277">
         <v>30</v>
       </c>
       <c r="H277" t="s">
-        <v>144</v>
+        <v>179</v>
       </c>
       <c r="I277" t="s">
-        <v>144</v>
+        <v>92</v>
       </c>
       <c r="J277" s="1">
         <v>3010101</v>
@@ -9793,16 +9793,16 @@
         <v>34</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>61</v>
+        <v>162</v>
       </c>
       <c r="G278">
         <v>30</v>
       </c>
       <c r="H278" t="s">
-        <v>145</v>
+        <v>179</v>
       </c>
       <c r="I278" t="s">
-        <v>145</v>
+        <v>93</v>
       </c>
       <c r="J278" s="1">
         <v>3030101</v>
@@ -9825,16 +9825,16 @@
         <v>34</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>61</v>
+        <v>162</v>
       </c>
       <c r="G279">
         <v>30</v>
       </c>
       <c r="H279" t="s">
-        <v>145</v>
+        <v>179</v>
       </c>
       <c r="I279" t="s">
-        <v>145</v>
+        <v>93</v>
       </c>
       <c r="J279" s="1">
         <v>3030101</v>
@@ -9857,16 +9857,16 @@
         <v>34</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>61</v>
+        <v>162</v>
       </c>
       <c r="G280">
         <v>30</v>
       </c>
       <c r="H280" t="s">
-        <v>145</v>
+        <v>179</v>
       </c>
       <c r="I280" t="s">
-        <v>145</v>
+        <v>93</v>
       </c>
       <c r="J280" s="1">
         <v>3030101</v>
@@ -9889,16 +9889,16 @@
         <v>34</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>61</v>
+        <v>162</v>
       </c>
       <c r="G281">
         <v>30</v>
       </c>
       <c r="H281" t="s">
-        <v>144</v>
+        <v>179</v>
       </c>
       <c r="I281" t="s">
-        <v>144</v>
+        <v>92</v>
       </c>
       <c r="J281" s="1">
         <v>3010101</v>
@@ -9921,16 +9921,16 @@
         <v>34</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>61</v>
+        <v>162</v>
       </c>
       <c r="G282">
         <v>30</v>
       </c>
       <c r="H282" t="s">
-        <v>145</v>
+        <v>179</v>
       </c>
       <c r="I282" t="s">
-        <v>145</v>
+        <v>93</v>
       </c>
       <c r="J282" s="1">
         <v>3030101</v>
@@ -9953,16 +9953,16 @@
         <v>34</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>61</v>
+        <v>162</v>
       </c>
       <c r="G283">
         <v>30</v>
       </c>
       <c r="H283" t="s">
-        <v>144</v>
+        <v>179</v>
       </c>
       <c r="I283" t="s">
-        <v>144</v>
+        <v>92</v>
       </c>
       <c r="J283" s="1">
         <v>3010101</v>
@@ -9985,16 +9985,16 @@
         <v>34</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>61</v>
+        <v>162</v>
       </c>
       <c r="G284">
         <v>30</v>
       </c>
       <c r="H284" t="s">
-        <v>144</v>
+        <v>179</v>
       </c>
       <c r="I284" t="s">
-        <v>144</v>
+        <v>92</v>
       </c>
       <c r="J284" s="1">
         <v>3010101</v>
@@ -10017,16 +10017,16 @@
         <v>35</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>62</v>
+        <v>163</v>
       </c>
       <c r="G285">
         <v>30</v>
       </c>
       <c r="H285" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="I285" t="s">
-        <v>146</v>
+        <v>94</v>
       </c>
       <c r="J285" s="1">
         <v>3010101</v>
@@ -10049,16 +10049,16 @@
         <v>35</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>62</v>
+        <v>163</v>
       </c>
       <c r="G286">
         <v>30</v>
       </c>
       <c r="H286" t="s">
-        <v>147</v>
+        <v>179</v>
       </c>
       <c r="I286" t="s">
-        <v>147</v>
+        <v>95</v>
       </c>
       <c r="J286" s="1">
         <v>3030101</v>
@@ -10081,16 +10081,16 @@
         <v>35</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>62</v>
+        <v>163</v>
       </c>
       <c r="G287">
         <v>30</v>
       </c>
       <c r="H287" t="s">
-        <v>147</v>
+        <v>179</v>
       </c>
       <c r="I287" t="s">
-        <v>147</v>
+        <v>95</v>
       </c>
       <c r="J287" s="1">
         <v>3030101</v>
@@ -10113,16 +10113,16 @@
         <v>35</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>62</v>
+        <v>163</v>
       </c>
       <c r="G288">
         <v>30</v>
       </c>
       <c r="H288" t="s">
-        <v>147</v>
+        <v>179</v>
       </c>
       <c r="I288" t="s">
-        <v>147</v>
+        <v>95</v>
       </c>
       <c r="J288" s="1">
         <v>3030101</v>
@@ -10145,16 +10145,16 @@
         <v>35</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>62</v>
+        <v>163</v>
       </c>
       <c r="G289">
         <v>30</v>
       </c>
       <c r="H289" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="I289" t="s">
-        <v>146</v>
+        <v>94</v>
       </c>
       <c r="J289" s="1">
         <v>3010101</v>
@@ -10177,16 +10177,16 @@
         <v>35</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>62</v>
+        <v>163</v>
       </c>
       <c r="G290">
         <v>30</v>
       </c>
       <c r="H290" t="s">
-        <v>147</v>
+        <v>179</v>
       </c>
       <c r="I290" t="s">
-        <v>147</v>
+        <v>95</v>
       </c>
       <c r="J290" s="1">
         <v>3030101</v>
@@ -10209,16 +10209,16 @@
         <v>35</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>62</v>
+        <v>163</v>
       </c>
       <c r="G291">
         <v>30</v>
       </c>
       <c r="H291" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="I291" t="s">
-        <v>146</v>
+        <v>94</v>
       </c>
       <c r="J291" s="1">
         <v>3010101</v>
@@ -10241,16 +10241,16 @@
         <v>35</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>62</v>
+        <v>163</v>
       </c>
       <c r="G292">
         <v>30</v>
       </c>
       <c r="H292" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="I292" t="s">
-        <v>146</v>
+        <v>94</v>
       </c>
       <c r="J292" s="1">
         <v>3010101</v>
@@ -10273,16 +10273,16 @@
         <v>36</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>63</v>
+        <v>164</v>
       </c>
       <c r="G293">
         <v>30</v>
       </c>
       <c r="H293" t="s">
-        <v>148</v>
+        <v>179</v>
       </c>
       <c r="I293" t="s">
-        <v>148</v>
+        <v>96</v>
       </c>
       <c r="J293" s="1">
         <v>3010101</v>
@@ -10305,16 +10305,16 @@
         <v>36</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>63</v>
+        <v>164</v>
       </c>
       <c r="G294">
         <v>30</v>
       </c>
       <c r="H294" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="I294" t="s">
-        <v>149</v>
+        <v>97</v>
       </c>
       <c r="J294" s="1">
         <v>3030101</v>
@@ -10337,16 +10337,16 @@
         <v>36</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>63</v>
+        <v>164</v>
       </c>
       <c r="G295">
         <v>30</v>
       </c>
       <c r="H295" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="I295" t="s">
-        <v>149</v>
+        <v>97</v>
       </c>
       <c r="J295" s="1">
         <v>3030101</v>
@@ -10369,16 +10369,16 @@
         <v>36</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>63</v>
+        <v>164</v>
       </c>
       <c r="G296">
         <v>30</v>
       </c>
       <c r="H296" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="I296" t="s">
-        <v>149</v>
+        <v>97</v>
       </c>
       <c r="J296" s="1">
         <v>3030101</v>
@@ -10401,16 +10401,16 @@
         <v>36</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>63</v>
+        <v>164</v>
       </c>
       <c r="G297">
         <v>30</v>
       </c>
       <c r="H297" t="s">
-        <v>148</v>
+        <v>179</v>
       </c>
       <c r="I297" t="s">
-        <v>148</v>
+        <v>96</v>
       </c>
       <c r="J297" s="1">
         <v>3010101</v>
@@ -10433,16 +10433,16 @@
         <v>36</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>63</v>
+        <v>164</v>
       </c>
       <c r="G298">
         <v>30</v>
       </c>
       <c r="H298" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="I298" t="s">
-        <v>149</v>
+        <v>97</v>
       </c>
       <c r="J298" s="1">
         <v>3030101</v>
@@ -10465,16 +10465,16 @@
         <v>36</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>63</v>
+        <v>164</v>
       </c>
       <c r="G299">
         <v>30</v>
       </c>
       <c r="H299" t="s">
-        <v>148</v>
+        <v>179</v>
       </c>
       <c r="I299" t="s">
-        <v>148</v>
+        <v>96</v>
       </c>
       <c r="J299" s="1">
         <v>3010101</v>
@@ -10497,16 +10497,16 @@
         <v>36</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>63</v>
+        <v>164</v>
       </c>
       <c r="G300">
         <v>30</v>
       </c>
       <c r="H300" t="s">
-        <v>148</v>
+        <v>179</v>
       </c>
       <c r="I300" t="s">
-        <v>148</v>
+        <v>96</v>
       </c>
       <c r="J300" s="1">
         <v>3010101</v>
@@ -10529,16 +10529,16 @@
         <v>37</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>64</v>
+        <v>165</v>
       </c>
       <c r="G301">
         <v>30</v>
       </c>
       <c r="H301" t="s">
-        <v>150</v>
+        <v>179</v>
       </c>
       <c r="I301" t="s">
-        <v>150</v>
+        <v>98</v>
       </c>
       <c r="J301" s="1">
         <v>3010101</v>
@@ -10561,16 +10561,16 @@
         <v>37</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>64</v>
+        <v>165</v>
       </c>
       <c r="G302">
         <v>30</v>
       </c>
       <c r="H302" t="s">
-        <v>151</v>
+        <v>179</v>
       </c>
       <c r="I302" t="s">
-        <v>151</v>
+        <v>99</v>
       </c>
       <c r="J302" s="1">
         <v>3030101</v>
@@ -10593,16 +10593,16 @@
         <v>37</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>64</v>
+        <v>165</v>
       </c>
       <c r="G303">
         <v>30</v>
       </c>
       <c r="H303" t="s">
-        <v>151</v>
+        <v>179</v>
       </c>
       <c r="I303" t="s">
-        <v>151</v>
+        <v>99</v>
       </c>
       <c r="J303" s="1">
         <v>3030101</v>
@@ -10625,16 +10625,16 @@
         <v>37</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>64</v>
+        <v>165</v>
       </c>
       <c r="G304">
         <v>30</v>
       </c>
       <c r="H304" t="s">
-        <v>151</v>
+        <v>179</v>
       </c>
       <c r="I304" t="s">
-        <v>151</v>
+        <v>99</v>
       </c>
       <c r="J304" s="1">
         <v>3030101</v>
@@ -10657,16 +10657,16 @@
         <v>37</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>64</v>
+        <v>165</v>
       </c>
       <c r="G305">
         <v>30</v>
       </c>
       <c r="H305" t="s">
-        <v>150</v>
+        <v>179</v>
       </c>
       <c r="I305" t="s">
-        <v>150</v>
+        <v>98</v>
       </c>
       <c r="J305" s="1">
         <v>3010101</v>
@@ -10689,16 +10689,16 @@
         <v>37</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>64</v>
+        <v>165</v>
       </c>
       <c r="G306">
         <v>30</v>
       </c>
       <c r="H306" t="s">
-        <v>151</v>
+        <v>179</v>
       </c>
       <c r="I306" t="s">
-        <v>151</v>
+        <v>99</v>
       </c>
       <c r="J306" s="1">
         <v>3030101</v>
@@ -10721,16 +10721,16 @@
         <v>37</v>
       </c>
       <c r="F307" s="1" t="s">
-        <v>64</v>
+        <v>165</v>
       </c>
       <c r="G307">
         <v>30</v>
       </c>
       <c r="H307" t="s">
-        <v>150</v>
+        <v>179</v>
       </c>
       <c r="I307" t="s">
-        <v>150</v>
+        <v>98</v>
       </c>
       <c r="J307" s="1">
         <v>3010101</v>
@@ -10753,16 +10753,16 @@
         <v>37</v>
       </c>
       <c r="F308" s="1" t="s">
-        <v>64</v>
+        <v>165</v>
       </c>
       <c r="G308">
         <v>30</v>
       </c>
       <c r="H308" t="s">
-        <v>150</v>
+        <v>179</v>
       </c>
       <c r="I308" t="s">
-        <v>150</v>
+        <v>98</v>
       </c>
       <c r="J308" s="1">
         <v>3010101</v>
@@ -10785,16 +10785,16 @@
         <v>38</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>65</v>
+        <v>166</v>
       </c>
       <c r="G309">
         <v>30</v>
       </c>
       <c r="H309" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="I309" t="s">
-        <v>152</v>
+        <v>100</v>
       </c>
       <c r="J309" s="1">
         <v>3010101</v>
@@ -10817,16 +10817,16 @@
         <v>38</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>65</v>
+        <v>166</v>
       </c>
       <c r="G310">
         <v>30</v>
       </c>
       <c r="H310" t="s">
-        <v>153</v>
+        <v>179</v>
       </c>
       <c r="I310" t="s">
-        <v>153</v>
+        <v>101</v>
       </c>
       <c r="J310" s="1">
         <v>3030101</v>
@@ -10849,16 +10849,16 @@
         <v>38</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>65</v>
+        <v>166</v>
       </c>
       <c r="G311">
         <v>30</v>
       </c>
       <c r="H311" t="s">
-        <v>153</v>
+        <v>179</v>
       </c>
       <c r="I311" t="s">
-        <v>153</v>
+        <v>101</v>
       </c>
       <c r="J311" s="1">
         <v>3030101</v>
@@ -10881,16 +10881,16 @@
         <v>38</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>65</v>
+        <v>166</v>
       </c>
       <c r="G312">
         <v>30</v>
       </c>
       <c r="H312" t="s">
-        <v>153</v>
+        <v>179</v>
       </c>
       <c r="I312" t="s">
-        <v>153</v>
+        <v>101</v>
       </c>
       <c r="J312" s="1">
         <v>3030101</v>
@@ -10913,16 +10913,16 @@
         <v>38</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>65</v>
+        <v>166</v>
       </c>
       <c r="G313">
         <v>30</v>
       </c>
       <c r="H313" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="I313" t="s">
-        <v>152</v>
+        <v>100</v>
       </c>
       <c r="J313" s="1">
         <v>3010101</v>
@@ -10945,16 +10945,16 @@
         <v>38</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>65</v>
+        <v>166</v>
       </c>
       <c r="G314">
         <v>30</v>
       </c>
       <c r="H314" t="s">
-        <v>153</v>
+        <v>179</v>
       </c>
       <c r="I314" t="s">
-        <v>153</v>
+        <v>101</v>
       </c>
       <c r="J314" s="1">
         <v>3030101</v>
@@ -10977,16 +10977,16 @@
         <v>38</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>65</v>
+        <v>166</v>
       </c>
       <c r="G315">
         <v>30</v>
       </c>
       <c r="H315" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="I315" t="s">
-        <v>152</v>
+        <v>100</v>
       </c>
       <c r="J315" s="1">
         <v>3010101</v>
@@ -11009,16 +11009,16 @@
         <v>38</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>65</v>
+        <v>166</v>
       </c>
       <c r="G316">
         <v>30</v>
       </c>
       <c r="H316" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="I316" t="s">
-        <v>152</v>
+        <v>100</v>
       </c>
       <c r="J316" s="1">
         <v>3010101</v>
@@ -11041,16 +11041,16 @@
         <v>39</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>66</v>
+        <v>167</v>
       </c>
       <c r="G317">
         <v>30</v>
       </c>
       <c r="H317" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="I317" t="s">
-        <v>154</v>
+        <v>102</v>
       </c>
       <c r="J317" s="1">
         <v>3010101</v>
@@ -11073,16 +11073,16 @@
         <v>39</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>66</v>
+        <v>167</v>
       </c>
       <c r="G318">
         <v>30</v>
       </c>
       <c r="H318" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="I318" t="s">
-        <v>155</v>
+        <v>103</v>
       </c>
       <c r="J318" s="1">
         <v>3030101</v>
@@ -11105,16 +11105,16 @@
         <v>39</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>66</v>
+        <v>167</v>
       </c>
       <c r="G319">
         <v>30</v>
       </c>
       <c r="H319" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="I319" t="s">
-        <v>155</v>
+        <v>103</v>
       </c>
       <c r="J319" s="1">
         <v>3030101</v>
@@ -11137,16 +11137,16 @@
         <v>39</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>66</v>
+        <v>167</v>
       </c>
       <c r="G320">
         <v>30</v>
       </c>
       <c r="H320" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="I320" t="s">
-        <v>155</v>
+        <v>103</v>
       </c>
       <c r="J320" s="1">
         <v>3030101</v>
@@ -11169,16 +11169,16 @@
         <v>39</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>66</v>
+        <v>167</v>
       </c>
       <c r="G321">
         <v>30</v>
       </c>
       <c r="H321" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="I321" t="s">
-        <v>154</v>
+        <v>102</v>
       </c>
       <c r="J321" s="1">
         <v>3010101</v>
@@ -11201,16 +11201,16 @@
         <v>39</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>66</v>
+        <v>167</v>
       </c>
       <c r="G322">
         <v>30</v>
       </c>
       <c r="H322" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="I322" t="s">
-        <v>155</v>
+        <v>103</v>
       </c>
       <c r="J322" s="1">
         <v>3030101</v>
@@ -11233,16 +11233,16 @@
         <v>39</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>66</v>
+        <v>167</v>
       </c>
       <c r="G323">
         <v>30</v>
       </c>
       <c r="H323" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="I323" t="s">
-        <v>154</v>
+        <v>102</v>
       </c>
       <c r="J323" s="1">
         <v>3010101</v>
@@ -11265,16 +11265,16 @@
         <v>39</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>66</v>
+        <v>167</v>
       </c>
       <c r="G324">
         <v>30</v>
       </c>
       <c r="H324" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="I324" t="s">
-        <v>154</v>
+        <v>102</v>
       </c>
       <c r="J324" s="1">
         <v>3010101</v>
@@ -11297,16 +11297,16 @@
         <v>40</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>67</v>
+        <v>168</v>
       </c>
       <c r="G325">
         <v>40</v>
       </c>
       <c r="H325" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="I325" t="s">
-        <v>156</v>
+        <v>104</v>
       </c>
       <c r="J325" s="1">
         <v>3010101</v>
@@ -11329,16 +11329,16 @@
         <v>40</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>67</v>
+        <v>168</v>
       </c>
       <c r="G326">
         <v>40</v>
       </c>
       <c r="H326" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="I326" t="s">
-        <v>157</v>
+        <v>105</v>
       </c>
       <c r="J326" s="1">
         <v>3030101</v>
@@ -11361,16 +11361,16 @@
         <v>40</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>67</v>
+        <v>168</v>
       </c>
       <c r="G327">
         <v>40</v>
       </c>
       <c r="H327" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="I327" t="s">
-        <v>157</v>
+        <v>105</v>
       </c>
       <c r="J327" s="1">
         <v>3030101</v>
@@ -11393,16 +11393,16 @@
         <v>40</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>67</v>
+        <v>168</v>
       </c>
       <c r="G328">
         <v>40</v>
       </c>
       <c r="H328" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="I328" t="s">
-        <v>157</v>
+        <v>105</v>
       </c>
       <c r="J328" s="1">
         <v>3030101</v>
@@ -11425,16 +11425,16 @@
         <v>40</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>67</v>
+        <v>168</v>
       </c>
       <c r="G329">
         <v>40</v>
       </c>
       <c r="H329" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="I329" t="s">
-        <v>156</v>
+        <v>104</v>
       </c>
       <c r="J329" s="1">
         <v>3010101</v>
@@ -11457,16 +11457,16 @@
         <v>40</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>67</v>
+        <v>168</v>
       </c>
       <c r="G330">
         <v>40</v>
       </c>
       <c r="H330" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="I330" t="s">
-        <v>157</v>
+        <v>105</v>
       </c>
       <c r="J330" s="1">
         <v>3030101</v>
@@ -11489,16 +11489,16 @@
         <v>40</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>67</v>
+        <v>168</v>
       </c>
       <c r="G331">
         <v>40</v>
       </c>
       <c r="H331" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="I331" t="s">
-        <v>156</v>
+        <v>104</v>
       </c>
       <c r="J331" s="1">
         <v>3010101</v>
@@ -11521,16 +11521,16 @@
         <v>40</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>67</v>
+        <v>168</v>
       </c>
       <c r="G332">
         <v>40</v>
       </c>
       <c r="H332" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="I332" t="s">
-        <v>156</v>
+        <v>104</v>
       </c>
       <c r="J332" s="1">
         <v>3010101</v>
@@ -11553,16 +11553,16 @@
         <v>41</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>68</v>
+        <v>169</v>
       </c>
       <c r="G333">
         <v>40</v>
       </c>
       <c r="H333" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="I333" t="s">
-        <v>158</v>
+        <v>106</v>
       </c>
       <c r="J333" s="1">
         <v>3010101</v>
@@ -11585,16 +11585,16 @@
         <v>41</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>68</v>
+        <v>169</v>
       </c>
       <c r="G334">
         <v>40</v>
       </c>
       <c r="H334" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="I334" t="s">
-        <v>159</v>
+        <v>107</v>
       </c>
       <c r="J334" s="1">
         <v>3030101</v>
@@ -11617,16 +11617,16 @@
         <v>41</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>68</v>
+        <v>169</v>
       </c>
       <c r="G335">
         <v>40</v>
       </c>
       <c r="H335" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="I335" t="s">
-        <v>159</v>
+        <v>107</v>
       </c>
       <c r="J335" s="1">
         <v>3030101</v>
@@ -11649,16 +11649,16 @@
         <v>41</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>68</v>
+        <v>169</v>
       </c>
       <c r="G336">
         <v>40</v>
       </c>
       <c r="H336" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="I336" t="s">
-        <v>159</v>
+        <v>107</v>
       </c>
       <c r="J336" s="1">
         <v>3030101</v>
@@ -11681,16 +11681,16 @@
         <v>41</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>68</v>
+        <v>169</v>
       </c>
       <c r="G337">
         <v>40</v>
       </c>
       <c r="H337" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="I337" t="s">
-        <v>158</v>
+        <v>106</v>
       </c>
       <c r="J337" s="1">
         <v>3010101</v>
@@ -11713,16 +11713,16 @@
         <v>41</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>68</v>
+        <v>169</v>
       </c>
       <c r="G338">
         <v>40</v>
       </c>
       <c r="H338" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="I338" t="s">
-        <v>159</v>
+        <v>107</v>
       </c>
       <c r="J338" s="1">
         <v>3030101</v>
@@ -11745,16 +11745,16 @@
         <v>41</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>68</v>
+        <v>169</v>
       </c>
       <c r="G339">
         <v>40</v>
       </c>
       <c r="H339" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="I339" t="s">
-        <v>158</v>
+        <v>106</v>
       </c>
       <c r="J339" s="1">
         <v>3010101</v>
@@ -11777,16 +11777,16 @@
         <v>41</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>68</v>
+        <v>169</v>
       </c>
       <c r="G340">
         <v>40</v>
       </c>
       <c r="H340" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="I340" t="s">
-        <v>158</v>
+        <v>106</v>
       </c>
       <c r="J340" s="1">
         <v>3010101</v>
@@ -11809,16 +11809,16 @@
         <v>42</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>69</v>
+        <v>170</v>
       </c>
       <c r="G341">
         <v>40</v>
       </c>
       <c r="H341" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="I341" t="s">
-        <v>160</v>
+        <v>108</v>
       </c>
       <c r="J341" s="1">
         <v>3010101</v>
@@ -11841,16 +11841,16 @@
         <v>42</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>69</v>
+        <v>170</v>
       </c>
       <c r="G342">
         <v>40</v>
       </c>
       <c r="H342" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="I342" t="s">
-        <v>161</v>
+        <v>109</v>
       </c>
       <c r="J342" s="1">
         <v>3030101</v>
@@ -11873,16 +11873,16 @@
         <v>42</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>69</v>
+        <v>170</v>
       </c>
       <c r="G343">
         <v>40</v>
       </c>
       <c r="H343" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="I343" t="s">
-        <v>161</v>
+        <v>109</v>
       </c>
       <c r="J343" s="1">
         <v>3030101</v>
@@ -11905,16 +11905,16 @@
         <v>42</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>69</v>
+        <v>170</v>
       </c>
       <c r="G344">
         <v>40</v>
       </c>
       <c r="H344" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="I344" t="s">
-        <v>161</v>
+        <v>109</v>
       </c>
       <c r="J344" s="1">
         <v>3030101</v>
@@ -11937,16 +11937,16 @@
         <v>42</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>69</v>
+        <v>170</v>
       </c>
       <c r="G345">
         <v>40</v>
       </c>
       <c r="H345" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="I345" t="s">
-        <v>160</v>
+        <v>108</v>
       </c>
       <c r="J345" s="1">
         <v>3010101</v>
@@ -11969,16 +11969,16 @@
         <v>42</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>69</v>
+        <v>170</v>
       </c>
       <c r="G346">
         <v>40</v>
       </c>
       <c r="H346" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="I346" t="s">
-        <v>161</v>
+        <v>109</v>
       </c>
       <c r="J346" s="1">
         <v>3030101</v>
@@ -12001,16 +12001,16 @@
         <v>42</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>69</v>
+        <v>170</v>
       </c>
       <c r="G347">
         <v>40</v>
       </c>
       <c r="H347" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="I347" t="s">
-        <v>160</v>
+        <v>108</v>
       </c>
       <c r="J347" s="1">
         <v>3010101</v>
@@ -12033,16 +12033,16 @@
         <v>42</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>69</v>
+        <v>170</v>
       </c>
       <c r="G348">
         <v>40</v>
       </c>
       <c r="H348" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="I348" t="s">
-        <v>160</v>
+        <v>108</v>
       </c>
       <c r="J348" s="1">
         <v>3010101</v>
@@ -12065,16 +12065,16 @@
         <v>43</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>70</v>
+        <v>171</v>
       </c>
       <c r="G349">
         <v>40</v>
       </c>
       <c r="H349" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="I349" t="s">
-        <v>162</v>
+        <v>110</v>
       </c>
       <c r="J349" s="1">
         <v>3010101</v>
@@ -12097,16 +12097,16 @@
         <v>43</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>70</v>
+        <v>171</v>
       </c>
       <c r="G350">
         <v>40</v>
       </c>
       <c r="H350" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="I350" t="s">
-        <v>163</v>
+        <v>111</v>
       </c>
       <c r="J350" s="1">
         <v>3030101</v>
@@ -12129,16 +12129,16 @@
         <v>43</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>70</v>
+        <v>171</v>
       </c>
       <c r="G351">
         <v>40</v>
       </c>
       <c r="H351" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="I351" t="s">
-        <v>163</v>
+        <v>111</v>
       </c>
       <c r="J351" s="1">
         <v>3030101</v>
@@ -12161,16 +12161,16 @@
         <v>43</v>
       </c>
       <c r="F352" s="1" t="s">
-        <v>70</v>
+        <v>171</v>
       </c>
       <c r="G352">
         <v>40</v>
       </c>
       <c r="H352" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="I352" t="s">
-        <v>163</v>
+        <v>111</v>
       </c>
       <c r="J352" s="1">
         <v>3030101</v>
@@ -12193,16 +12193,16 @@
         <v>43</v>
       </c>
       <c r="F353" s="1" t="s">
-        <v>70</v>
+        <v>171</v>
       </c>
       <c r="G353">
         <v>40</v>
       </c>
       <c r="H353" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="I353" t="s">
-        <v>162</v>
+        <v>110</v>
       </c>
       <c r="J353" s="1">
         <v>3010101</v>
@@ -12225,16 +12225,16 @@
         <v>43</v>
       </c>
       <c r="F354" s="1" t="s">
-        <v>70</v>
+        <v>171</v>
       </c>
       <c r="G354">
         <v>40</v>
       </c>
       <c r="H354" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="I354" t="s">
-        <v>163</v>
+        <v>111</v>
       </c>
       <c r="J354" s="1">
         <v>3030101</v>
@@ -12257,16 +12257,16 @@
         <v>43</v>
       </c>
       <c r="F355" s="1" t="s">
-        <v>70</v>
+        <v>171</v>
       </c>
       <c r="G355">
         <v>40</v>
       </c>
       <c r="H355" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="I355" t="s">
-        <v>162</v>
+        <v>110</v>
       </c>
       <c r="J355" s="1">
         <v>3010101</v>
@@ -12289,16 +12289,16 @@
         <v>43</v>
       </c>
       <c r="F356" s="1" t="s">
-        <v>70</v>
+        <v>171</v>
       </c>
       <c r="G356">
         <v>40</v>
       </c>
       <c r="H356" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="I356" t="s">
-        <v>162</v>
+        <v>110</v>
       </c>
       <c r="J356" s="1">
         <v>3010101</v>
@@ -12321,16 +12321,16 @@
         <v>44</v>
       </c>
       <c r="F357" s="1" t="s">
-        <v>71</v>
+        <v>172</v>
       </c>
       <c r="G357">
         <v>40</v>
       </c>
       <c r="H357" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="I357" t="s">
-        <v>164</v>
+        <v>112</v>
       </c>
       <c r="J357" s="1">
         <v>3010101</v>
@@ -12353,16 +12353,16 @@
         <v>44</v>
       </c>
       <c r="F358" s="1" t="s">
-        <v>71</v>
+        <v>172</v>
       </c>
       <c r="G358">
         <v>40</v>
       </c>
       <c r="H358" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="I358" t="s">
-        <v>165</v>
+        <v>113</v>
       </c>
       <c r="J358" s="1">
         <v>3030101</v>
@@ -12385,16 +12385,16 @@
         <v>44</v>
       </c>
       <c r="F359" s="1" t="s">
-        <v>71</v>
+        <v>172</v>
       </c>
       <c r="G359">
         <v>40</v>
       </c>
       <c r="H359" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="I359" t="s">
-        <v>165</v>
+        <v>113</v>
       </c>
       <c r="J359" s="1">
         <v>3030101</v>
@@ -12417,16 +12417,16 @@
         <v>44</v>
       </c>
       <c r="F360" s="1" t="s">
-        <v>71</v>
+        <v>172</v>
       </c>
       <c r="G360">
         <v>40</v>
       </c>
       <c r="H360" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="I360" t="s">
-        <v>165</v>
+        <v>113</v>
       </c>
       <c r="J360" s="1">
         <v>3030101</v>
@@ -12449,16 +12449,16 @@
         <v>44</v>
       </c>
       <c r="F361" s="1" t="s">
-        <v>71</v>
+        <v>172</v>
       </c>
       <c r="G361">
         <v>40</v>
       </c>
       <c r="H361" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="I361" t="s">
-        <v>164</v>
+        <v>112</v>
       </c>
       <c r="J361" s="1">
         <v>3010101</v>
@@ -12481,16 +12481,16 @@
         <v>44</v>
       </c>
       <c r="F362" s="1" t="s">
-        <v>71</v>
+        <v>172</v>
       </c>
       <c r="G362">
         <v>40</v>
       </c>
       <c r="H362" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="I362" t="s">
-        <v>165</v>
+        <v>113</v>
       </c>
       <c r="J362" s="1">
         <v>3030101</v>
@@ -12513,16 +12513,16 @@
         <v>44</v>
       </c>
       <c r="F363" s="1" t="s">
-        <v>71</v>
+        <v>172</v>
       </c>
       <c r="G363">
         <v>40</v>
       </c>
       <c r="H363" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="I363" t="s">
-        <v>164</v>
+        <v>112</v>
       </c>
       <c r="J363" s="1">
         <v>3010101</v>
@@ -12545,16 +12545,16 @@
         <v>44</v>
       </c>
       <c r="F364" s="1" t="s">
-        <v>71</v>
+        <v>172</v>
       </c>
       <c r="G364">
         <v>40</v>
       </c>
       <c r="H364" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="I364" t="s">
-        <v>164</v>
+        <v>112</v>
       </c>
       <c r="J364" s="1">
         <v>3010101</v>
@@ -12577,16 +12577,16 @@
         <v>45</v>
       </c>
       <c r="F365" s="1" t="s">
-        <v>72</v>
+        <v>173</v>
       </c>
       <c r="G365">
         <v>40</v>
       </c>
       <c r="H365" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="I365" t="s">
-        <v>166</v>
+        <v>114</v>
       </c>
       <c r="J365" s="1">
         <v>3010101</v>
@@ -12609,16 +12609,16 @@
         <v>45</v>
       </c>
       <c r="F366" s="1" t="s">
-        <v>72</v>
+        <v>173</v>
       </c>
       <c r="G366">
         <v>40</v>
       </c>
       <c r="H366" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="I366" t="s">
-        <v>167</v>
+        <v>115</v>
       </c>
       <c r="J366" s="1">
         <v>3030101</v>
@@ -12641,16 +12641,16 @@
         <v>45</v>
       </c>
       <c r="F367" s="1" t="s">
-        <v>72</v>
+        <v>173</v>
       </c>
       <c r="G367">
         <v>40</v>
       </c>
       <c r="H367" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="I367" t="s">
-        <v>167</v>
+        <v>115</v>
       </c>
       <c r="J367" s="1">
         <v>3030101</v>
@@ -12673,16 +12673,16 @@
         <v>45</v>
       </c>
       <c r="F368" s="1" t="s">
-        <v>72</v>
+        <v>173</v>
       </c>
       <c r="G368">
         <v>40</v>
       </c>
       <c r="H368" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="I368" t="s">
-        <v>167</v>
+        <v>115</v>
       </c>
       <c r="J368" s="1">
         <v>3030101</v>
@@ -12705,16 +12705,16 @@
         <v>45</v>
       </c>
       <c r="F369" s="1" t="s">
-        <v>72</v>
+        <v>173</v>
       </c>
       <c r="G369">
         <v>40</v>
       </c>
       <c r="H369" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="I369" t="s">
-        <v>166</v>
+        <v>114</v>
       </c>
       <c r="J369" s="1">
         <v>3010101</v>
@@ -12737,16 +12737,16 @@
         <v>45</v>
       </c>
       <c r="F370" s="1" t="s">
-        <v>72</v>
+        <v>173</v>
       </c>
       <c r="G370">
         <v>40</v>
       </c>
       <c r="H370" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="I370" t="s">
-        <v>167</v>
+        <v>115</v>
       </c>
       <c r="J370" s="1">
         <v>3030101</v>
@@ -12769,16 +12769,16 @@
         <v>45</v>
       </c>
       <c r="F371" s="1" t="s">
-        <v>72</v>
+        <v>173</v>
       </c>
       <c r="G371">
         <v>40</v>
       </c>
       <c r="H371" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="I371" t="s">
-        <v>166</v>
+        <v>114</v>
       </c>
       <c r="J371" s="1">
         <v>3010101</v>
@@ -12801,16 +12801,16 @@
         <v>45</v>
       </c>
       <c r="F372" s="1" t="s">
-        <v>72</v>
+        <v>173</v>
       </c>
       <c r="G372">
         <v>40</v>
       </c>
       <c r="H372" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="I372" t="s">
-        <v>166</v>
+        <v>114</v>
       </c>
       <c r="J372" s="1">
         <v>3010101</v>
@@ -12833,16 +12833,16 @@
         <v>46</v>
       </c>
       <c r="F373" s="1" t="s">
-        <v>73</v>
+        <v>174</v>
       </c>
       <c r="G373">
         <v>40</v>
       </c>
       <c r="H373" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="I373" t="s">
-        <v>168</v>
+        <v>116</v>
       </c>
       <c r="J373" s="1">
         <v>3010101</v>
@@ -12865,16 +12865,16 @@
         <v>46</v>
       </c>
       <c r="F374" s="1" t="s">
-        <v>73</v>
+        <v>174</v>
       </c>
       <c r="G374">
         <v>40</v>
       </c>
       <c r="H374" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="I374" t="s">
-        <v>169</v>
+        <v>117</v>
       </c>
       <c r="J374" s="1">
         <v>3030101</v>
@@ -12897,16 +12897,16 @@
         <v>46</v>
       </c>
       <c r="F375" s="1" t="s">
-        <v>73</v>
+        <v>174</v>
       </c>
       <c r="G375">
         <v>40</v>
       </c>
       <c r="H375" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="I375" t="s">
-        <v>169</v>
+        <v>117</v>
       </c>
       <c r="J375" s="1">
         <v>3030101</v>
@@ -12929,16 +12929,16 @@
         <v>46</v>
       </c>
       <c r="F376" s="1" t="s">
-        <v>73</v>
+        <v>174</v>
       </c>
       <c r="G376">
         <v>40</v>
       </c>
       <c r="H376" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="I376" t="s">
-        <v>169</v>
+        <v>117</v>
       </c>
       <c r="J376" s="1">
         <v>3030101</v>
@@ -12961,16 +12961,16 @@
         <v>46</v>
       </c>
       <c r="F377" s="1" t="s">
-        <v>73</v>
+        <v>174</v>
       </c>
       <c r="G377">
         <v>40</v>
       </c>
       <c r="H377" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="I377" t="s">
-        <v>168</v>
+        <v>116</v>
       </c>
       <c r="J377" s="1">
         <v>3010101</v>
@@ -12993,16 +12993,16 @@
         <v>46</v>
       </c>
       <c r="F378" s="1" t="s">
-        <v>73</v>
+        <v>174</v>
       </c>
       <c r="G378">
         <v>40</v>
       </c>
       <c r="H378" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="I378" t="s">
-        <v>169</v>
+        <v>117</v>
       </c>
       <c r="J378" s="1">
         <v>3030101</v>
@@ -13025,16 +13025,16 @@
         <v>46</v>
       </c>
       <c r="F379" s="1" t="s">
-        <v>73</v>
+        <v>174</v>
       </c>
       <c r="G379">
         <v>40</v>
       </c>
       <c r="H379" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="I379" t="s">
-        <v>168</v>
+        <v>116</v>
       </c>
       <c r="J379" s="1">
         <v>3010101</v>
@@ -13057,16 +13057,16 @@
         <v>46</v>
       </c>
       <c r="F380" s="1" t="s">
-        <v>73</v>
+        <v>174</v>
       </c>
       <c r="G380">
         <v>40</v>
       </c>
       <c r="H380" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="I380" t="s">
-        <v>168</v>
+        <v>116</v>
       </c>
       <c r="J380" s="1">
         <v>3010101</v>
@@ -13089,16 +13089,16 @@
         <v>47</v>
       </c>
       <c r="F381" s="1" t="s">
-        <v>74</v>
+        <v>175</v>
       </c>
       <c r="G381">
         <v>40</v>
       </c>
       <c r="H381" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="I381" t="s">
-        <v>170</v>
+        <v>118</v>
       </c>
       <c r="J381" s="1">
         <v>3010101</v>
@@ -13121,16 +13121,16 @@
         <v>47</v>
       </c>
       <c r="F382" s="1" t="s">
-        <v>74</v>
+        <v>175</v>
       </c>
       <c r="G382">
         <v>40</v>
       </c>
       <c r="H382" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="I382" t="s">
-        <v>171</v>
+        <v>119</v>
       </c>
       <c r="J382" s="1">
         <v>3030101</v>
@@ -13153,16 +13153,16 @@
         <v>47</v>
       </c>
       <c r="F383" s="1" t="s">
-        <v>74</v>
+        <v>175</v>
       </c>
       <c r="G383">
         <v>40</v>
       </c>
       <c r="H383" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="I383" t="s">
-        <v>171</v>
+        <v>119</v>
       </c>
       <c r="J383" s="1">
         <v>3030101</v>
@@ -13185,16 +13185,16 @@
         <v>47</v>
       </c>
       <c r="F384" s="1" t="s">
-        <v>74</v>
+        <v>175</v>
       </c>
       <c r="G384">
         <v>40</v>
       </c>
       <c r="H384" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="I384" t="s">
-        <v>171</v>
+        <v>119</v>
       </c>
       <c r="J384" s="1">
         <v>3030101</v>
@@ -13217,16 +13217,16 @@
         <v>47</v>
       </c>
       <c r="F385" s="1" t="s">
-        <v>74</v>
+        <v>175</v>
       </c>
       <c r="G385">
         <v>40</v>
       </c>
       <c r="H385" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="I385" t="s">
-        <v>170</v>
+        <v>118</v>
       </c>
       <c r="J385" s="1">
         <v>3010101</v>
@@ -13249,16 +13249,16 @@
         <v>47</v>
       </c>
       <c r="F386" s="1" t="s">
-        <v>74</v>
+        <v>175</v>
       </c>
       <c r="G386">
         <v>40</v>
       </c>
       <c r="H386" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="I386" t="s">
-        <v>171</v>
+        <v>119</v>
       </c>
       <c r="J386" s="1">
         <v>3030101</v>
@@ -13281,16 +13281,16 @@
         <v>47</v>
       </c>
       <c r="F387" s="1" t="s">
-        <v>74</v>
+        <v>175</v>
       </c>
       <c r="G387">
         <v>40</v>
       </c>
       <c r="H387" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="I387" t="s">
-        <v>170</v>
+        <v>118</v>
       </c>
       <c r="J387" s="1">
         <v>3010101</v>
@@ -13313,16 +13313,16 @@
         <v>47</v>
       </c>
       <c r="F388" s="1" t="s">
-        <v>74</v>
+        <v>175</v>
       </c>
       <c r="G388">
         <v>40</v>
       </c>
       <c r="H388" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="I388" t="s">
-        <v>170</v>
+        <v>118</v>
       </c>
       <c r="J388" s="1">
         <v>3010101</v>
@@ -13345,16 +13345,16 @@
         <v>48</v>
       </c>
       <c r="F389" s="1" t="s">
-        <v>75</v>
+        <v>176</v>
       </c>
       <c r="G389">
         <v>40</v>
       </c>
       <c r="H389" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="I389" t="s">
-        <v>172</v>
+        <v>120</v>
       </c>
       <c r="J389" s="1">
         <v>3010101</v>
@@ -13377,16 +13377,16 @@
         <v>48</v>
       </c>
       <c r="F390" s="1" t="s">
-        <v>75</v>
+        <v>176</v>
       </c>
       <c r="G390">
         <v>40</v>
       </c>
       <c r="H390" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="I390" t="s">
-        <v>173</v>
+        <v>121</v>
       </c>
       <c r="J390" s="1">
         <v>3030101</v>
@@ -13409,16 +13409,16 @@
         <v>48</v>
       </c>
       <c r="F391" s="1" t="s">
-        <v>75</v>
+        <v>176</v>
       </c>
       <c r="G391">
         <v>40</v>
       </c>
       <c r="H391" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="I391" t="s">
-        <v>173</v>
+        <v>121</v>
       </c>
       <c r="J391" s="1">
         <v>3030101</v>
@@ -13441,16 +13441,16 @@
         <v>48</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>75</v>
+        <v>176</v>
       </c>
       <c r="G392">
         <v>40</v>
       </c>
       <c r="H392" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="I392" t="s">
-        <v>173</v>
+        <v>121</v>
       </c>
       <c r="J392" s="1">
         <v>3030101</v>
@@ -13473,16 +13473,16 @@
         <v>48</v>
       </c>
       <c r="F393" s="1" t="s">
-        <v>75</v>
+        <v>176</v>
       </c>
       <c r="G393">
         <v>40</v>
       </c>
       <c r="H393" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="I393" t="s">
-        <v>172</v>
+        <v>120</v>
       </c>
       <c r="J393" s="1">
         <v>3010101</v>
@@ -13505,16 +13505,16 @@
         <v>48</v>
       </c>
       <c r="F394" s="1" t="s">
-        <v>75</v>
+        <v>176</v>
       </c>
       <c r="G394">
         <v>40</v>
       </c>
       <c r="H394" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="I394" t="s">
-        <v>173</v>
+        <v>121</v>
       </c>
       <c r="J394" s="1">
         <v>3030101</v>
@@ -13537,16 +13537,16 @@
         <v>48</v>
       </c>
       <c r="F395" s="1" t="s">
-        <v>75</v>
+        <v>176</v>
       </c>
       <c r="G395">
         <v>40</v>
       </c>
       <c r="H395" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="I395" t="s">
-        <v>172</v>
+        <v>120</v>
       </c>
       <c r="J395" s="1">
         <v>3010101</v>
@@ -13569,16 +13569,16 @@
         <v>48</v>
       </c>
       <c r="F396" s="1" t="s">
-        <v>75</v>
+        <v>176</v>
       </c>
       <c r="G396">
         <v>40</v>
       </c>
       <c r="H396" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="I396" t="s">
-        <v>172</v>
+        <v>120</v>
       </c>
       <c r="J396" s="1">
         <v>3010101</v>
@@ -13601,16 +13601,16 @@
         <v>49</v>
       </c>
       <c r="F397" s="1" t="s">
-        <v>76</v>
+        <v>177</v>
       </c>
       <c r="G397">
         <v>40</v>
       </c>
       <c r="H397" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="I397" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="J397" s="1">
         <v>3010101</v>
@@ -13633,16 +13633,16 @@
         <v>49</v>
       </c>
       <c r="F398" s="1" t="s">
-        <v>76</v>
+        <v>177</v>
       </c>
       <c r="G398">
         <v>40</v>
       </c>
       <c r="H398" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="I398" t="s">
-        <v>175</v>
+        <v>123</v>
       </c>
       <c r="J398" s="1">
         <v>3030101</v>
@@ -13665,16 +13665,16 @@
         <v>49</v>
       </c>
       <c r="F399" s="1" t="s">
-        <v>76</v>
+        <v>177</v>
       </c>
       <c r="G399">
         <v>40</v>
       </c>
       <c r="H399" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="I399" t="s">
-        <v>175</v>
+        <v>123</v>
       </c>
       <c r="J399" s="1">
         <v>3030101</v>
@@ -13697,16 +13697,16 @@
         <v>49</v>
       </c>
       <c r="F400" s="1" t="s">
-        <v>76</v>
+        <v>177</v>
       </c>
       <c r="G400">
         <v>40</v>
       </c>
       <c r="H400" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="I400" t="s">
-        <v>175</v>
+        <v>123</v>
       </c>
       <c r="J400" s="1">
         <v>3030101</v>
@@ -13729,16 +13729,16 @@
         <v>49</v>
       </c>
       <c r="F401" s="1" t="s">
-        <v>76</v>
+        <v>177</v>
       </c>
       <c r="G401">
         <v>40</v>
       </c>
       <c r="H401" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="I401" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="J401" s="1">
         <v>3010101</v>
@@ -13761,16 +13761,16 @@
         <v>49</v>
       </c>
       <c r="F402" s="1" t="s">
-        <v>76</v>
+        <v>177</v>
       </c>
       <c r="G402">
         <v>40</v>
       </c>
       <c r="H402" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="I402" t="s">
-        <v>175</v>
+        <v>123</v>
       </c>
       <c r="J402" s="1">
         <v>3030101</v>
@@ -13793,16 +13793,16 @@
         <v>49</v>
       </c>
       <c r="F403" s="1" t="s">
-        <v>76</v>
+        <v>177</v>
       </c>
       <c r="G403">
         <v>40</v>
       </c>
       <c r="H403" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="I403" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="J403" s="1">
         <v>3010101</v>
@@ -13825,16 +13825,16 @@
         <v>49</v>
       </c>
       <c r="F404" s="1" t="s">
-        <v>76</v>
+        <v>177</v>
       </c>
       <c r="G404">
         <v>40</v>
       </c>
       <c r="H404" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="I404" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="J404" s="1">
         <v>3010101</v>
@@ -13857,16 +13857,16 @@
         <v>50</v>
       </c>
       <c r="F405" s="1" t="s">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="G405">
         <v>50</v>
       </c>
       <c r="H405" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="I405" t="s">
-        <v>176</v>
+        <v>124</v>
       </c>
       <c r="J405" s="1">
         <v>3010101</v>
@@ -13889,16 +13889,16 @@
         <v>50</v>
       </c>
       <c r="F406" s="1" t="s">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="G406">
         <v>50</v>
       </c>
       <c r="H406" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I406" t="s">
-        <v>177</v>
+        <v>125</v>
       </c>
       <c r="J406" s="1">
         <v>3030101</v>
@@ -13921,16 +13921,16 @@
         <v>50</v>
       </c>
       <c r="F407" s="1" t="s">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="G407">
         <v>50</v>
       </c>
       <c r="H407" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I407" t="s">
-        <v>177</v>
+        <v>125</v>
       </c>
       <c r="J407" s="1">
         <v>3030101</v>
@@ -13953,16 +13953,16 @@
         <v>50</v>
       </c>
       <c r="F408" s="1" t="s">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="G408">
         <v>50</v>
       </c>
       <c r="H408" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I408" t="s">
-        <v>177</v>
+        <v>125</v>
       </c>
       <c r="J408" s="1">
         <v>3030101</v>
@@ -13985,16 +13985,16 @@
         <v>50</v>
       </c>
       <c r="F409" s="1" t="s">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="G409">
         <v>50</v>
       </c>
       <c r="H409" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="I409" t="s">
-        <v>176</v>
+        <v>124</v>
       </c>
       <c r="J409" s="1">
         <v>3010101</v>
@@ -14017,16 +14017,16 @@
         <v>50</v>
       </c>
       <c r="F410" s="1" t="s">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="G410">
         <v>50</v>
       </c>
       <c r="H410" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I410" t="s">
-        <v>177</v>
+        <v>125</v>
       </c>
       <c r="J410" s="1">
         <v>3030101</v>
@@ -14049,16 +14049,16 @@
         <v>50</v>
       </c>
       <c r="F411" s="1" t="s">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="G411">
         <v>50</v>
       </c>
       <c r="H411" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="I411" t="s">
-        <v>176</v>
+        <v>124</v>
       </c>
       <c r="J411" s="1">
         <v>3010101</v>
@@ -14081,16 +14081,16 @@
         <v>50</v>
       </c>
       <c r="F412" s="1" t="s">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="G412">
         <v>50</v>
       </c>
       <c r="H412" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="I412" t="s">
-        <v>176</v>
+        <v>124</v>
       </c>
       <c r="J412" s="1">
         <v>3010101</v>

--- a/servers/maze_main_server/conf.d/data/maze_equip_pos_lv_v8【迷宫-装备-部位强化等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_equip_pos_lv_v8【迷宫-装备-部位强化等级】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54FC6266-A460-4EE5-8F3D-1E0EF451DF8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84E06714-9ABF-4FC3-B10D-8D660DAD31C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1255" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1255" uniqueCount="221">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -135,306 +135,18 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>3010101:2</t>
-  </si>
-  <si>
-    <t>3030101:36</t>
-  </si>
-  <si>
-    <t>3010101:6</t>
-  </si>
-  <si>
-    <t>3030101:120</t>
-  </si>
-  <si>
     <t>3010101:10</t>
   </si>
   <si>
-    <t>3030101:192</t>
-  </si>
-  <si>
-    <t>3010101:13</t>
-  </si>
-  <si>
-    <t>3030101:264</t>
-  </si>
-  <si>
     <t>3010101:17</t>
   </si>
   <si>
-    <t>3030101:336</t>
-  </si>
-  <si>
-    <t>3010101:23</t>
-  </si>
-  <si>
-    <t>3030101:456</t>
-  </si>
-  <si>
-    <t>3010101:28</t>
-  </si>
-  <si>
-    <t>3030101:564</t>
-  </si>
-  <si>
     <t>3010101:35</t>
   </si>
   <si>
-    <t>3030101:708</t>
-  </si>
-  <si>
-    <t>3010101:41</t>
-  </si>
-  <si>
-    <t>3030101:828</t>
-  </si>
-  <si>
     <t>3010101:70</t>
   </si>
   <si>
-    <t>3030101:1392</t>
-  </si>
-  <si>
-    <t>3010101:435</t>
-  </si>
-  <si>
-    <t>3030101:8700</t>
-  </si>
-  <si>
-    <t>3010101:694</t>
-  </si>
-  <si>
-    <t>3030101:13880</t>
-  </si>
-  <si>
-    <t>3010101:963</t>
-  </si>
-  <si>
-    <t>3030101:19260</t>
-  </si>
-  <si>
-    <t>3010101:1262</t>
-  </si>
-  <si>
-    <t>3030101:25240</t>
-  </si>
-  <si>
-    <t>3010101:1571</t>
-  </si>
-  <si>
-    <t>3030101:31420</t>
-  </si>
-  <si>
-    <t>3010101:1910</t>
-  </si>
-  <si>
-    <t>3030101:38200</t>
-  </si>
-  <si>
-    <t>3010101:2259</t>
-  </si>
-  <si>
-    <t>3030101:45180</t>
-  </si>
-  <si>
-    <t>3010101:2638</t>
-  </si>
-  <si>
-    <t>3030101:52760</t>
-  </si>
-  <si>
-    <t>3010101:3027</t>
-  </si>
-  <si>
-    <t>3030101:60540</t>
-  </si>
-  <si>
-    <t>3010101:3446</t>
-  </si>
-  <si>
-    <t>3030101:68920</t>
-  </si>
-  <si>
-    <t>3010101:3875</t>
-  </si>
-  <si>
-    <t>3030101:77500</t>
-  </si>
-  <si>
-    <t>3010101:4334</t>
-  </si>
-  <si>
-    <t>3030101:86680</t>
-  </si>
-  <si>
-    <t>3010101:4803</t>
-  </si>
-  <si>
-    <t>3030101:96060</t>
-  </si>
-  <si>
-    <t>3010101:5302</t>
-  </si>
-  <si>
-    <t>3030101:106040</t>
-  </si>
-  <si>
-    <t>3010101:5811</t>
-  </si>
-  <si>
-    <t>3030101:116220</t>
-  </si>
-  <si>
-    <t>3010101:6350</t>
-  </si>
-  <si>
-    <t>3030101:127000</t>
-  </si>
-  <si>
-    <t>3010101:6899</t>
-  </si>
-  <si>
-    <t>3030101:137980</t>
-  </si>
-  <si>
-    <t>3010101:7478</t>
-  </si>
-  <si>
-    <t>3030101:149560</t>
-  </si>
-  <si>
-    <t>3010101:8067</t>
-  </si>
-  <si>
-    <t>3030101:161340</t>
-  </si>
-  <si>
-    <t>3010101:8686</t>
-  </si>
-  <si>
-    <t>3030101:173720</t>
-  </si>
-  <si>
-    <t>3010101:9315</t>
-  </si>
-  <si>
-    <t>3030101:186300</t>
-  </si>
-  <si>
-    <t>3010101:9974</t>
-  </si>
-  <si>
-    <t>3030101:199480</t>
-  </si>
-  <si>
-    <t>3010101:10643</t>
-  </si>
-  <si>
-    <t>3030101:212860</t>
-  </si>
-  <si>
-    <t>3010101:11342</t>
-  </si>
-  <si>
-    <t>3030101:226840</t>
-  </si>
-  <si>
-    <t>3010101:12051</t>
-  </si>
-  <si>
-    <t>3030101:241020</t>
-  </si>
-  <si>
-    <t>3010101:12790</t>
-  </si>
-  <si>
-    <t>3030101:255800</t>
-  </si>
-  <si>
-    <t>3010101:13539</t>
-  </si>
-  <si>
-    <t>3030101:270780</t>
-  </si>
-  <si>
-    <t>3010101:14318</t>
-  </si>
-  <si>
-    <t>3030101:286360</t>
-  </si>
-  <si>
-    <t>3010101:15107</t>
-  </si>
-  <si>
-    <t>3030101:302140</t>
-  </si>
-  <si>
-    <t>3010101:15926</t>
-  </si>
-  <si>
-    <t>3030101:318520</t>
-  </si>
-  <si>
-    <t>3010101:16755</t>
-  </si>
-  <si>
-    <t>3030101:335100</t>
-  </si>
-  <si>
-    <t>3010101:17614</t>
-  </si>
-  <si>
-    <t>3030101:352280</t>
-  </si>
-  <si>
-    <t>3010101:18483</t>
-  </si>
-  <si>
-    <t>3030101:369660</t>
-  </si>
-  <si>
-    <t>3010101:19382</t>
-  </si>
-  <si>
-    <t>3030101:387640</t>
-  </si>
-  <si>
-    <t>3010101:20310</t>
-  </si>
-  <si>
-    <t>3030101:406200</t>
-  </si>
-  <si>
-    <t>3010101:21280</t>
-  </si>
-  <si>
-    <t>3030101:425600</t>
-  </si>
-  <si>
-    <t>3010101:22290</t>
-  </si>
-  <si>
-    <t>3030101:445800</t>
-  </si>
-  <si>
-    <t>3010101:23340</t>
-  </si>
-  <si>
-    <t>3030101:466800</t>
-  </si>
-  <si>
-    <t>3010101:24430</t>
-  </si>
-  <si>
-    <t>3030101:488600</t>
-  </si>
-  <si>
-    <t>3010101:25560</t>
-  </si>
-  <si>
-    <t>3030101:511200</t>
-  </si>
-  <si>
     <t>3010101:0</t>
   </si>
   <si>
@@ -594,7 +306,418 @@
     <t>46200001:2450_46700001:250</t>
   </si>
   <si>
-    <t>8101:0</t>
+    <t>9101:0</t>
+  </si>
+  <si>
+    <t>3010101:4</t>
+  </si>
+  <si>
+    <t>3030101:130</t>
+  </si>
+  <si>
+    <t>3030101:320</t>
+  </si>
+  <si>
+    <t>3030101:540</t>
+  </si>
+  <si>
+    <t>3010101:25</t>
+  </si>
+  <si>
+    <t>3030101:820</t>
+  </si>
+  <si>
+    <t>3030101:1100</t>
+  </si>
+  <si>
+    <t>3010101:47</t>
+  </si>
+  <si>
+    <t>3030101:1500</t>
+  </si>
+  <si>
+    <t>3010101:58</t>
+  </si>
+  <si>
+    <t>3030101:1800</t>
+  </si>
+  <si>
+    <t>3030101:2200</t>
+  </si>
+  <si>
+    <t>3010101:81</t>
+  </si>
+  <si>
+    <t>3030101:2600</t>
+  </si>
+  <si>
+    <t>3010101:92</t>
+  </si>
+  <si>
+    <t>3030101:2900</t>
+  </si>
+  <si>
+    <t>3010101:150</t>
+  </si>
+  <si>
+    <t>3030101:4800</t>
+  </si>
+  <si>
+    <t>3010101:160</t>
+  </si>
+  <si>
+    <t>3030101:5300</t>
+  </si>
+  <si>
+    <t>3010101:180</t>
+  </si>
+  <si>
+    <t>3030101:5800</t>
+  </si>
+  <si>
+    <t>3010101:190</t>
+  </si>
+  <si>
+    <t>3030101:6300</t>
+  </si>
+  <si>
+    <t>3010101:210</t>
+  </si>
+  <si>
+    <t>3030101:6800</t>
+  </si>
+  <si>
+    <t>3010101:230</t>
+  </si>
+  <si>
+    <t>3030101:7300</t>
+  </si>
+  <si>
+    <t>3010101:240</t>
+  </si>
+  <si>
+    <t>3030101:7800</t>
+  </si>
+  <si>
+    <t>3010101:260</t>
+  </si>
+  <si>
+    <t>3030101:8300</t>
+  </si>
+  <si>
+    <t>3010101:270</t>
+  </si>
+  <si>
+    <t>3030101:8800</t>
+  </si>
+  <si>
+    <t>3010101:290</t>
+  </si>
+  <si>
+    <t>3030101:9300</t>
+  </si>
+  <si>
+    <t>3010101:330</t>
+  </si>
+  <si>
+    <t>3030101:10000</t>
+  </si>
+  <si>
+    <t>3010101:340</t>
+  </si>
+  <si>
+    <t>3030101:11000</t>
+  </si>
+  <si>
+    <t>3010101:360</t>
+  </si>
+  <si>
+    <t>3010101:380</t>
+  </si>
+  <si>
+    <t>3030101:12000</t>
+  </si>
+  <si>
+    <t>3010101:400</t>
+  </si>
+  <si>
+    <t>3010101:410</t>
+  </si>
+  <si>
+    <t>3030101:13000</t>
+  </si>
+  <si>
+    <t>3010101:430</t>
+  </si>
+  <si>
+    <t>3010101:450</t>
+  </si>
+  <si>
+    <t>3030101:14000</t>
+  </si>
+  <si>
+    <t>3010101:460</t>
+  </si>
+  <si>
+    <t>3030101:15000</t>
+  </si>
+  <si>
+    <t>3010101:480</t>
+  </si>
+  <si>
+    <t>3010101:530</t>
+  </si>
+  <si>
+    <t>3030101:17000</t>
+  </si>
+  <si>
+    <t>3010101:550</t>
+  </si>
+  <si>
+    <t>3010101:580</t>
+  </si>
+  <si>
+    <t>3030101:18000</t>
+  </si>
+  <si>
+    <t>3010101:600</t>
+  </si>
+  <si>
+    <t>3030101:19000</t>
+  </si>
+  <si>
+    <t>3010101:620</t>
+  </si>
+  <si>
+    <t>3030101:20000</t>
+  </si>
+  <si>
+    <t>3010101:650</t>
+  </si>
+  <si>
+    <t>3010101:670</t>
+  </si>
+  <si>
+    <t>3030101:21000</t>
+  </si>
+  <si>
+    <t>3010101:700</t>
+  </si>
+  <si>
+    <t>3030101:22000</t>
+  </si>
+  <si>
+    <t>3010101:730</t>
+  </si>
+  <si>
+    <t>3030101:23000</t>
+  </si>
+  <si>
+    <t>3010101:760</t>
+  </si>
+  <si>
+    <t>3030101:24000</t>
+  </si>
+  <si>
+    <t>3010101:840</t>
+  </si>
+  <si>
+    <t>3030101:26000</t>
+  </si>
+  <si>
+    <t>3010101:870</t>
+  </si>
+  <si>
+    <t>3030101:27000</t>
+  </si>
+  <si>
+    <t>3010101:900</t>
+  </si>
+  <si>
+    <t>3030101:29000</t>
+  </si>
+  <si>
+    <t>3010101:940</t>
+  </si>
+  <si>
+    <t>3030101:30000</t>
+  </si>
+  <si>
+    <t>3010101:980</t>
+  </si>
+  <si>
+    <t>3030101:31000</t>
+  </si>
+  <si>
+    <t>3010101:1000</t>
+  </si>
+  <si>
+    <t>3030101:32000</t>
+  </si>
+  <si>
+    <t>3030101:34000</t>
+  </si>
+  <si>
+    <t>3010101:1100</t>
+  </si>
+  <si>
+    <t>3030101:35000</t>
+  </si>
+  <si>
+    <t>3030101:36000</t>
+  </si>
+  <si>
+    <t>3030101:38000</t>
+  </si>
+  <si>
+    <t>9101:8</t>
+  </si>
+  <si>
+    <t>9101:20</t>
+  </si>
+  <si>
+    <t>9101:34</t>
+  </si>
+  <si>
+    <t>9101:51</t>
+  </si>
+  <si>
+    <t>9101:71</t>
+  </si>
+  <si>
+    <t>9101:94</t>
+  </si>
+  <si>
+    <t>9101:117</t>
+  </si>
+  <si>
+    <t>9101:140</t>
+  </si>
+  <si>
+    <t>9101:163</t>
+  </si>
+  <si>
+    <t>9101:185</t>
+  </si>
+  <si>
+    <t>9101:303</t>
+  </si>
+  <si>
+    <t>9101:334</t>
+  </si>
+  <si>
+    <t>9101:366</t>
+  </si>
+  <si>
+    <t>9101:397</t>
+  </si>
+  <si>
+    <t>9101:428</t>
+  </si>
+  <si>
+    <t>9101:460</t>
+  </si>
+  <si>
+    <t>9101:491</t>
+  </si>
+  <si>
+    <t>9101:523</t>
+  </si>
+  <si>
+    <t>9101:554</t>
+  </si>
+  <si>
+    <t>9101:585</t>
+  </si>
+  <si>
+    <t>9101:664</t>
+  </si>
+  <si>
+    <t>9101:698</t>
+  </si>
+  <si>
+    <t>9101:732</t>
+  </si>
+  <si>
+    <t>9101:766</t>
+  </si>
+  <si>
+    <t>9101:800</t>
+  </si>
+  <si>
+    <t>9101:835</t>
+  </si>
+  <si>
+    <t>9101:869</t>
+  </si>
+  <si>
+    <t>9101:903</t>
+  </si>
+  <si>
+    <t>9101:939</t>
+  </si>
+  <si>
+    <t>9101:976</t>
+  </si>
+  <si>
+    <t>9101:1074</t>
+  </si>
+  <si>
+    <t>9101:1117</t>
+  </si>
+  <si>
+    <t>9101:1161</t>
+  </si>
+  <si>
+    <t>9101:1208</t>
+  </si>
+  <si>
+    <t>9101:1256</t>
+  </si>
+  <si>
+    <t>9101:1306</t>
+  </si>
+  <si>
+    <t>9101:1359</t>
+  </si>
+  <si>
+    <t>9101:1413</t>
+  </si>
+  <si>
+    <t>9101:1470</t>
+  </si>
+  <si>
+    <t>9101:1529</t>
+  </si>
+  <si>
+    <t>9101:1681</t>
+  </si>
+  <si>
+    <t>9101:1748</t>
+  </si>
+  <si>
+    <t>9101:1818</t>
+  </si>
+  <si>
+    <t>9101:1891</t>
+  </si>
+  <si>
+    <t>9101:1966</t>
+  </si>
+  <si>
+    <t>9101:2044</t>
+  </si>
+  <si>
+    <t>9101:2126</t>
+  </si>
+  <si>
+    <t>9101:2211</t>
+  </si>
+  <si>
+    <t>9101:2299</t>
+  </si>
+  <si>
+    <t>9101:2392</t>
   </si>
 </sst>
 </file>
@@ -1057,16 +1180,16 @@
         <v>0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>179</v>
+        <v>83</v>
       </c>
       <c r="I5" t="s">
-        <v>126</v>
+        <v>30</v>
       </c>
       <c r="J5">
         <v>3010101</v>
@@ -1089,16 +1212,16 @@
         <v>0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>179</v>
+        <v>83</v>
       </c>
       <c r="I6" t="s">
-        <v>127</v>
+        <v>31</v>
       </c>
       <c r="J6">
         <v>3030101</v>
@@ -1121,16 +1244,16 @@
         <v>0</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>179</v>
+        <v>83</v>
       </c>
       <c r="I7" t="s">
-        <v>127</v>
+        <v>31</v>
       </c>
       <c r="J7">
         <v>3030101</v>
@@ -1153,16 +1276,16 @@
         <v>0</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>179</v>
+        <v>83</v>
       </c>
       <c r="I8" t="s">
-        <v>127</v>
+        <v>31</v>
       </c>
       <c r="J8">
         <v>3030101</v>
@@ -1185,16 +1308,16 @@
         <v>0</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>179</v>
+        <v>83</v>
       </c>
       <c r="I9" t="s">
-        <v>126</v>
+        <v>30</v>
       </c>
       <c r="J9">
         <v>3010101</v>
@@ -1217,16 +1340,16 @@
         <v>0</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>179</v>
+        <v>83</v>
       </c>
       <c r="I10" t="s">
-        <v>127</v>
+        <v>31</v>
       </c>
       <c r="J10">
         <v>3030101</v>
@@ -1249,16 +1372,16 @@
         <v>0</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>179</v>
+        <v>83</v>
       </c>
       <c r="I11" t="s">
-        <v>126</v>
+        <v>30</v>
       </c>
       <c r="J11">
         <v>3010101</v>
@@ -1281,16 +1404,16 @@
         <v>0</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>179</v>
+        <v>83</v>
       </c>
       <c r="I12" t="s">
-        <v>126</v>
+        <v>30</v>
       </c>
       <c r="J12">
         <v>3010101</v>
@@ -1313,16 +1436,16 @@
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>129</v>
+        <v>33</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="I13" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="J13" s="1">
         <v>3010101</v>
@@ -1345,16 +1468,16 @@
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>129</v>
+        <v>33</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="I14" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="J14" s="1">
         <v>3030101</v>
@@ -1377,16 +1500,16 @@
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>129</v>
+        <v>33</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="I15" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="J15" s="1">
         <v>3030101</v>
@@ -1409,16 +1532,16 @@
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>129</v>
+        <v>33</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="I16" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="J16" s="1">
         <v>3030101</v>
@@ -1441,16 +1564,16 @@
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>129</v>
+        <v>33</v>
       </c>
       <c r="G17">
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="I17" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="J17" s="1">
         <v>3010101</v>
@@ -1473,16 +1596,16 @@
         <v>1</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>129</v>
+        <v>33</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="I18" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="J18" s="1">
         <v>3030101</v>
@@ -1505,16 +1628,16 @@
         <v>1</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>129</v>
+        <v>33</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="I19" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="J19" s="1">
         <v>3010101</v>
@@ -1537,16 +1660,16 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>129</v>
+        <v>33</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="I20" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="J20" s="1">
         <v>3010101</v>
@@ -1569,16 +1692,16 @@
         <v>2</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>130</v>
+        <v>34</v>
       </c>
       <c r="G21">
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="I21" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J21" s="1">
         <v>3010101</v>
@@ -1601,16 +1724,16 @@
         <v>2</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>130</v>
+        <v>34</v>
       </c>
       <c r="G22">
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="I22" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
       <c r="J22" s="1">
         <v>3030101</v>
@@ -1633,16 +1756,16 @@
         <v>2</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>130</v>
+        <v>34</v>
       </c>
       <c r="G23">
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="I23" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
       <c r="J23" s="1">
         <v>3030101</v>
@@ -1665,16 +1788,16 @@
         <v>2</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>130</v>
+        <v>34</v>
       </c>
       <c r="G24">
         <v>0</v>
       </c>
       <c r="H24" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="I24" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
       <c r="J24" s="1">
         <v>3030101</v>
@@ -1697,16 +1820,16 @@
         <v>2</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>130</v>
+        <v>34</v>
       </c>
       <c r="G25">
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="I25" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J25" s="1">
         <v>3010101</v>
@@ -1729,16 +1852,16 @@
         <v>2</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>130</v>
+        <v>34</v>
       </c>
       <c r="G26">
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="I26" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
       <c r="J26" s="1">
         <v>3030101</v>
@@ -1761,16 +1884,16 @@
         <v>2</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>130</v>
+        <v>34</v>
       </c>
       <c r="G27">
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="I27" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J27" s="1">
         <v>3010101</v>
@@ -1793,16 +1916,16 @@
         <v>2</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>130</v>
+        <v>34</v>
       </c>
       <c r="G28">
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="I28" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J28" s="1">
         <v>3010101</v>
@@ -1825,16 +1948,16 @@
         <v>3</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="G29">
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="I29" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J29" s="1">
         <v>3010101</v>
@@ -1857,16 +1980,16 @@
         <v>3</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="G30">
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="I30" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="J30" s="1">
         <v>3030101</v>
@@ -1889,16 +2012,16 @@
         <v>3</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="G31">
         <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="I31" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="J31" s="1">
         <v>3030101</v>
@@ -1921,16 +2044,16 @@
         <v>3</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="G32">
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="I32" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="J32" s="1">
         <v>3030101</v>
@@ -1953,16 +2076,16 @@
         <v>3</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="G33">
         <v>0</v>
       </c>
       <c r="H33" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="I33" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J33" s="1">
         <v>3010101</v>
@@ -1985,16 +2108,16 @@
         <v>3</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="G34">
         <v>0</v>
       </c>
       <c r="H34" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="I34" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="J34" s="1">
         <v>3030101</v>
@@ -2017,16 +2140,16 @@
         <v>3</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="G35">
         <v>0</v>
       </c>
       <c r="H35" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="I35" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J35" s="1">
         <v>3010101</v>
@@ -2049,16 +2172,16 @@
         <v>3</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="G36">
         <v>0</v>
       </c>
       <c r="H36" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="I36" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J36" s="1">
         <v>3010101</v>
@@ -2081,16 +2204,16 @@
         <v>4</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>132</v>
+        <v>36</v>
       </c>
       <c r="G37">
         <v>0</v>
       </c>
       <c r="H37" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I37" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="J37" s="1">
         <v>3010101</v>
@@ -2113,16 +2236,16 @@
         <v>4</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>132</v>
+        <v>36</v>
       </c>
       <c r="G38">
         <v>0</v>
       </c>
       <c r="H38" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I38" t="s">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="J38" s="1">
         <v>3030101</v>
@@ -2145,16 +2268,16 @@
         <v>4</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>132</v>
+        <v>36</v>
       </c>
       <c r="G39">
         <v>0</v>
       </c>
       <c r="H39" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I39" t="s">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="J39" s="1">
         <v>3030101</v>
@@ -2177,16 +2300,16 @@
         <v>4</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>132</v>
+        <v>36</v>
       </c>
       <c r="G40">
         <v>0</v>
       </c>
       <c r="H40" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I40" t="s">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="J40" s="1">
         <v>3030101</v>
@@ -2209,16 +2332,16 @@
         <v>4</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>132</v>
+        <v>36</v>
       </c>
       <c r="G41">
         <v>0</v>
       </c>
       <c r="H41" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I41" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="J41" s="1">
         <v>3010101</v>
@@ -2241,16 +2364,16 @@
         <v>4</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>132</v>
+        <v>36</v>
       </c>
       <c r="G42">
         <v>0</v>
       </c>
       <c r="H42" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I42" t="s">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="J42" s="1">
         <v>3030101</v>
@@ -2273,16 +2396,16 @@
         <v>4</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>132</v>
+        <v>36</v>
       </c>
       <c r="G43">
         <v>0</v>
       </c>
       <c r="H43" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I43" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="J43" s="1">
         <v>3010101</v>
@@ -2305,16 +2428,16 @@
         <v>4</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>132</v>
+        <v>36</v>
       </c>
       <c r="G44">
         <v>0</v>
       </c>
       <c r="H44" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I44" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="J44" s="1">
         <v>3010101</v>
@@ -2337,16 +2460,16 @@
         <v>5</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>133</v>
+        <v>37</v>
       </c>
       <c r="G45">
         <v>0</v>
       </c>
       <c r="H45" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="I45" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="J45" s="1">
         <v>3010101</v>
@@ -2369,16 +2492,16 @@
         <v>5</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>133</v>
+        <v>37</v>
       </c>
       <c r="G46">
         <v>0</v>
       </c>
       <c r="H46" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="I46" t="s">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="J46" s="1">
         <v>3030101</v>
@@ -2401,16 +2524,16 @@
         <v>5</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>133</v>
+        <v>37</v>
       </c>
       <c r="G47">
         <v>0</v>
       </c>
       <c r="H47" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="I47" t="s">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="J47" s="1">
         <v>3030101</v>
@@ -2433,16 +2556,16 @@
         <v>5</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>133</v>
+        <v>37</v>
       </c>
       <c r="G48">
         <v>0</v>
       </c>
       <c r="H48" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="I48" t="s">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="J48" s="1">
         <v>3030101</v>
@@ -2465,16 +2588,16 @@
         <v>5</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>133</v>
+        <v>37</v>
       </c>
       <c r="G49">
         <v>0</v>
       </c>
       <c r="H49" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="I49" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="J49" s="1">
         <v>3010101</v>
@@ -2497,16 +2620,16 @@
         <v>5</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>133</v>
+        <v>37</v>
       </c>
       <c r="G50">
         <v>0</v>
       </c>
       <c r="H50" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="I50" t="s">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="J50" s="1">
         <v>3030101</v>
@@ -2529,16 +2652,16 @@
         <v>5</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>133</v>
+        <v>37</v>
       </c>
       <c r="G51">
         <v>0</v>
       </c>
       <c r="H51" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="I51" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="J51" s="1">
         <v>3010101</v>
@@ -2561,16 +2684,16 @@
         <v>5</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>133</v>
+        <v>37</v>
       </c>
       <c r="G52">
         <v>0</v>
       </c>
       <c r="H52" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="I52" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="J52" s="1">
         <v>3010101</v>
@@ -2593,16 +2716,16 @@
         <v>6</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>134</v>
+        <v>38</v>
       </c>
       <c r="G53">
         <v>0</v>
       </c>
       <c r="H53" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I53" t="s">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="J53" s="1">
         <v>3010101</v>
@@ -2625,16 +2748,16 @@
         <v>6</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>134</v>
+        <v>38</v>
       </c>
       <c r="G54">
         <v>0</v>
       </c>
       <c r="H54" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I54" t="s">
-        <v>37</v>
+        <v>92</v>
       </c>
       <c r="J54" s="1">
         <v>3030101</v>
@@ -2657,16 +2780,16 @@
         <v>6</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>134</v>
+        <v>38</v>
       </c>
       <c r="G55">
         <v>0</v>
       </c>
       <c r="H55" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I55" t="s">
-        <v>37</v>
+        <v>92</v>
       </c>
       <c r="J55" s="1">
         <v>3030101</v>
@@ -2689,16 +2812,16 @@
         <v>6</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>134</v>
+        <v>38</v>
       </c>
       <c r="G56">
         <v>0</v>
       </c>
       <c r="H56" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I56" t="s">
-        <v>37</v>
+        <v>92</v>
       </c>
       <c r="J56" s="1">
         <v>3030101</v>
@@ -2721,16 +2844,16 @@
         <v>6</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>134</v>
+        <v>38</v>
       </c>
       <c r="G57">
         <v>0</v>
       </c>
       <c r="H57" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I57" t="s">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="J57" s="1">
         <v>3010101</v>
@@ -2753,16 +2876,16 @@
         <v>6</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>134</v>
+        <v>38</v>
       </c>
       <c r="G58">
         <v>0</v>
       </c>
       <c r="H58" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I58" t="s">
-        <v>37</v>
+        <v>92</v>
       </c>
       <c r="J58" s="1">
         <v>3030101</v>
@@ -2785,16 +2908,16 @@
         <v>6</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>134</v>
+        <v>38</v>
       </c>
       <c r="G59">
         <v>0</v>
       </c>
       <c r="H59" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I59" t="s">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="J59" s="1">
         <v>3010101</v>
@@ -2817,16 +2940,16 @@
         <v>6</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>134</v>
+        <v>38</v>
       </c>
       <c r="G60">
         <v>0</v>
       </c>
       <c r="H60" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I60" t="s">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="J60" s="1">
         <v>3010101</v>
@@ -2849,16 +2972,16 @@
         <v>7</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>135</v>
+        <v>39</v>
       </c>
       <c r="G61">
         <v>0</v>
       </c>
       <c r="H61" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I61" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="J61" s="1">
         <v>3010101</v>
@@ -2881,16 +3004,16 @@
         <v>7</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>135</v>
+        <v>39</v>
       </c>
       <c r="G62">
         <v>0</v>
       </c>
       <c r="H62" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I62" t="s">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="J62" s="1">
         <v>3030101</v>
@@ -2913,16 +3036,16 @@
         <v>7</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>135</v>
+        <v>39</v>
       </c>
       <c r="G63">
         <v>0</v>
       </c>
       <c r="H63" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I63" t="s">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="J63" s="1">
         <v>3030101</v>
@@ -2945,16 +3068,16 @@
         <v>7</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>135</v>
+        <v>39</v>
       </c>
       <c r="G64">
         <v>0</v>
       </c>
       <c r="H64" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I64" t="s">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="J64" s="1">
         <v>3030101</v>
@@ -2977,16 +3100,16 @@
         <v>7</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>135</v>
+        <v>39</v>
       </c>
       <c r="G65">
         <v>0</v>
       </c>
       <c r="H65" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I65" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="J65" s="1">
         <v>3010101</v>
@@ -3009,16 +3132,16 @@
         <v>7</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>135</v>
+        <v>39</v>
       </c>
       <c r="G66">
         <v>0</v>
       </c>
       <c r="H66" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I66" t="s">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="J66" s="1">
         <v>3030101</v>
@@ -3041,16 +3164,16 @@
         <v>7</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>135</v>
+        <v>39</v>
       </c>
       <c r="G67">
         <v>0</v>
       </c>
       <c r="H67" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I67" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="J67" s="1">
         <v>3010101</v>
@@ -3073,16 +3196,16 @@
         <v>7</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>135</v>
+        <v>39</v>
       </c>
       <c r="G68">
         <v>0</v>
       </c>
       <c r="H68" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I68" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="J68" s="1">
         <v>3010101</v>
@@ -3105,16 +3228,16 @@
         <v>8</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>136</v>
+        <v>40</v>
       </c>
       <c r="G69">
         <v>0</v>
       </c>
       <c r="H69" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I69" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="J69" s="1">
         <v>3010101</v>
@@ -3137,16 +3260,16 @@
         <v>8</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>136</v>
+        <v>40</v>
       </c>
       <c r="G70">
         <v>0</v>
       </c>
       <c r="H70" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I70" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="J70" s="1">
         <v>3030101</v>
@@ -3169,16 +3292,16 @@
         <v>8</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>136</v>
+        <v>40</v>
       </c>
       <c r="G71">
         <v>0</v>
       </c>
       <c r="H71" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I71" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="J71" s="1">
         <v>3030101</v>
@@ -3201,16 +3324,16 @@
         <v>8</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>136</v>
+        <v>40</v>
       </c>
       <c r="G72">
         <v>0</v>
       </c>
       <c r="H72" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I72" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="J72" s="1">
         <v>3030101</v>
@@ -3233,16 +3356,16 @@
         <v>8</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>136</v>
+        <v>40</v>
       </c>
       <c r="G73">
         <v>0</v>
       </c>
       <c r="H73" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I73" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="J73" s="1">
         <v>3010101</v>
@@ -3265,16 +3388,16 @@
         <v>8</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>136</v>
+        <v>40</v>
       </c>
       <c r="G74">
         <v>0</v>
       </c>
       <c r="H74" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I74" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="J74" s="1">
         <v>3030101</v>
@@ -3297,16 +3420,16 @@
         <v>8</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>136</v>
+        <v>40</v>
       </c>
       <c r="G75">
         <v>0</v>
       </c>
       <c r="H75" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I75" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="J75" s="1">
         <v>3010101</v>
@@ -3329,16 +3452,16 @@
         <v>8</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>136</v>
+        <v>40</v>
       </c>
       <c r="G76">
         <v>0</v>
       </c>
       <c r="H76" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I76" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="J76" s="1">
         <v>3010101</v>
@@ -3361,7 +3484,7 @@
         <v>9</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>137</v>
+        <v>41</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -3370,7 +3493,7 @@
         <v>179</v>
       </c>
       <c r="I77" t="s">
-        <v>42</v>
+        <v>96</v>
       </c>
       <c r="J77" s="1">
         <v>3010101</v>
@@ -3393,7 +3516,7 @@
         <v>9</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>137</v>
+        <v>41</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -3402,7 +3525,7 @@
         <v>179</v>
       </c>
       <c r="I78" t="s">
-        <v>43</v>
+        <v>97</v>
       </c>
       <c r="J78" s="1">
         <v>3030101</v>
@@ -3425,7 +3548,7 @@
         <v>9</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>137</v>
+        <v>41</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -3434,7 +3557,7 @@
         <v>179</v>
       </c>
       <c r="I79" t="s">
-        <v>43</v>
+        <v>97</v>
       </c>
       <c r="J79" s="1">
         <v>3030101</v>
@@ -3457,7 +3580,7 @@
         <v>9</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>137</v>
+        <v>41</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -3466,7 +3589,7 @@
         <v>179</v>
       </c>
       <c r="I80" t="s">
-        <v>43</v>
+        <v>97</v>
       </c>
       <c r="J80" s="1">
         <v>3030101</v>
@@ -3489,7 +3612,7 @@
         <v>9</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>137</v>
+        <v>41</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -3498,7 +3621,7 @@
         <v>179</v>
       </c>
       <c r="I81" t="s">
-        <v>42</v>
+        <v>96</v>
       </c>
       <c r="J81" s="1">
         <v>3010101</v>
@@ -3521,7 +3644,7 @@
         <v>9</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>137</v>
+        <v>41</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -3530,7 +3653,7 @@
         <v>179</v>
       </c>
       <c r="I82" t="s">
-        <v>43</v>
+        <v>97</v>
       </c>
       <c r="J82" s="1">
         <v>3030101</v>
@@ -3553,7 +3676,7 @@
         <v>9</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>137</v>
+        <v>41</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -3562,7 +3685,7 @@
         <v>179</v>
       </c>
       <c r="I83" t="s">
-        <v>42</v>
+        <v>96</v>
       </c>
       <c r="J83" s="1">
         <v>3010101</v>
@@ -3585,7 +3708,7 @@
         <v>9</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>137</v>
+        <v>41</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -3594,7 +3717,7 @@
         <v>179</v>
       </c>
       <c r="I84" t="s">
-        <v>42</v>
+        <v>96</v>
       </c>
       <c r="J84" s="1">
         <v>3010101</v>
@@ -3617,16 +3740,16 @@
         <v>10</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>138</v>
+        <v>42</v>
       </c>
       <c r="G85">
         <v>10</v>
       </c>
       <c r="H85" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I85" t="s">
-        <v>44</v>
+        <v>98</v>
       </c>
       <c r="J85" s="1">
         <v>3010101</v>
@@ -3649,16 +3772,16 @@
         <v>10</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>138</v>
+        <v>42</v>
       </c>
       <c r="G86">
         <v>10</v>
       </c>
       <c r="H86" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I86" t="s">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="J86" s="1">
         <v>3030101</v>
@@ -3681,16 +3804,16 @@
         <v>10</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>138</v>
+        <v>42</v>
       </c>
       <c r="G87">
         <v>10</v>
       </c>
       <c r="H87" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I87" t="s">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="J87" s="1">
         <v>3030101</v>
@@ -3713,16 +3836,16 @@
         <v>10</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>138</v>
+        <v>42</v>
       </c>
       <c r="G88">
         <v>10</v>
       </c>
       <c r="H88" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I88" t="s">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="J88" s="1">
         <v>3030101</v>
@@ -3745,16 +3868,16 @@
         <v>10</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>138</v>
+        <v>42</v>
       </c>
       <c r="G89">
         <v>10</v>
       </c>
       <c r="H89" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I89" t="s">
-        <v>44</v>
+        <v>98</v>
       </c>
       <c r="J89" s="1">
         <v>3010101</v>
@@ -3777,16 +3900,16 @@
         <v>10</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>138</v>
+        <v>42</v>
       </c>
       <c r="G90">
         <v>10</v>
       </c>
       <c r="H90" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I90" t="s">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="J90" s="1">
         <v>3030101</v>
@@ -3809,16 +3932,16 @@
         <v>10</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>138</v>
+        <v>42</v>
       </c>
       <c r="G91">
         <v>10</v>
       </c>
       <c r="H91" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I91" t="s">
-        <v>44</v>
+        <v>98</v>
       </c>
       <c r="J91" s="1">
         <v>3010101</v>
@@ -3841,16 +3964,16 @@
         <v>10</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>138</v>
+        <v>42</v>
       </c>
       <c r="G92">
         <v>10</v>
       </c>
       <c r="H92" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I92" t="s">
-        <v>44</v>
+        <v>98</v>
       </c>
       <c r="J92" s="1">
         <v>3010101</v>
@@ -3873,16 +3996,16 @@
         <v>11</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>139</v>
+        <v>43</v>
       </c>
       <c r="G93">
         <v>10</v>
       </c>
       <c r="H93" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I93" t="s">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="J93" s="1">
         <v>3010101</v>
@@ -3905,16 +4028,16 @@
         <v>11</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>139</v>
+        <v>43</v>
       </c>
       <c r="G94">
         <v>10</v>
       </c>
       <c r="H94" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I94" t="s">
-        <v>47</v>
+        <v>101</v>
       </c>
       <c r="J94" s="1">
         <v>3030101</v>
@@ -3937,16 +4060,16 @@
         <v>11</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>139</v>
+        <v>43</v>
       </c>
       <c r="G95">
         <v>10</v>
       </c>
       <c r="H95" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I95" t="s">
-        <v>47</v>
+        <v>101</v>
       </c>
       <c r="J95" s="1">
         <v>3030101</v>
@@ -3969,16 +4092,16 @@
         <v>11</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>139</v>
+        <v>43</v>
       </c>
       <c r="G96">
         <v>10</v>
       </c>
       <c r="H96" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I96" t="s">
-        <v>47</v>
+        <v>101</v>
       </c>
       <c r="J96" s="1">
         <v>3030101</v>
@@ -4001,16 +4124,16 @@
         <v>11</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>139</v>
+        <v>43</v>
       </c>
       <c r="G97">
         <v>10</v>
       </c>
       <c r="H97" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I97" t="s">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="J97" s="1">
         <v>3010101</v>
@@ -4033,16 +4156,16 @@
         <v>11</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>139</v>
+        <v>43</v>
       </c>
       <c r="G98">
         <v>10</v>
       </c>
       <c r="H98" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I98" t="s">
-        <v>47</v>
+        <v>101</v>
       </c>
       <c r="J98" s="1">
         <v>3030101</v>
@@ -4065,16 +4188,16 @@
         <v>11</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>139</v>
+        <v>43</v>
       </c>
       <c r="G99">
         <v>10</v>
       </c>
       <c r="H99" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I99" t="s">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="J99" s="1">
         <v>3010101</v>
@@ -4097,16 +4220,16 @@
         <v>11</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>139</v>
+        <v>43</v>
       </c>
       <c r="G100">
         <v>10</v>
       </c>
       <c r="H100" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I100" t="s">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="J100" s="1">
         <v>3010101</v>
@@ -4129,16 +4252,16 @@
         <v>12</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>140</v>
+        <v>44</v>
       </c>
       <c r="G101">
         <v>10</v>
       </c>
       <c r="H101" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I101" t="s">
-        <v>48</v>
+        <v>102</v>
       </c>
       <c r="J101" s="1">
         <v>3010101</v>
@@ -4161,16 +4284,16 @@
         <v>12</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>140</v>
+        <v>44</v>
       </c>
       <c r="G102">
         <v>10</v>
       </c>
       <c r="H102" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I102" t="s">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="J102" s="1">
         <v>3030101</v>
@@ -4193,16 +4316,16 @@
         <v>12</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>140</v>
+        <v>44</v>
       </c>
       <c r="G103">
         <v>10</v>
       </c>
       <c r="H103" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I103" t="s">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="J103" s="1">
         <v>3030101</v>
@@ -4225,16 +4348,16 @@
         <v>12</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>140</v>
+        <v>44</v>
       </c>
       <c r="G104">
         <v>10</v>
       </c>
       <c r="H104" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I104" t="s">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="J104" s="1">
         <v>3030101</v>
@@ -4257,16 +4380,16 @@
         <v>12</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>140</v>
+        <v>44</v>
       </c>
       <c r="G105">
         <v>10</v>
       </c>
       <c r="H105" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I105" t="s">
-        <v>48</v>
+        <v>102</v>
       </c>
       <c r="J105" s="1">
         <v>3010101</v>
@@ -4289,16 +4412,16 @@
         <v>12</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>140</v>
+        <v>44</v>
       </c>
       <c r="G106">
         <v>10</v>
       </c>
       <c r="H106" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I106" t="s">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="J106" s="1">
         <v>3030101</v>
@@ -4321,16 +4444,16 @@
         <v>12</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>140</v>
+        <v>44</v>
       </c>
       <c r="G107">
         <v>10</v>
       </c>
       <c r="H107" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I107" t="s">
-        <v>48</v>
+        <v>102</v>
       </c>
       <c r="J107" s="1">
         <v>3010101</v>
@@ -4353,16 +4476,16 @@
         <v>12</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>140</v>
+        <v>44</v>
       </c>
       <c r="G108">
         <v>10</v>
       </c>
       <c r="H108" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I108" t="s">
-        <v>48</v>
+        <v>102</v>
       </c>
       <c r="J108" s="1">
         <v>3010101</v>
@@ -4385,16 +4508,16 @@
         <v>13</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>141</v>
+        <v>45</v>
       </c>
       <c r="G109">
         <v>10</v>
       </c>
       <c r="H109" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="I109" t="s">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="J109" s="1">
         <v>3010101</v>
@@ -4417,16 +4540,16 @@
         <v>13</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>141</v>
+        <v>45</v>
       </c>
       <c r="G110">
         <v>10</v>
       </c>
       <c r="H110" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="I110" t="s">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="J110" s="1">
         <v>3030101</v>
@@ -4449,16 +4572,16 @@
         <v>13</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>141</v>
+        <v>45</v>
       </c>
       <c r="G111">
         <v>10</v>
       </c>
       <c r="H111" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="I111" t="s">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="J111" s="1">
         <v>3030101</v>
@@ -4481,16 +4604,16 @@
         <v>13</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>141</v>
+        <v>45</v>
       </c>
       <c r="G112">
         <v>10</v>
       </c>
       <c r="H112" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="I112" t="s">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="J112" s="1">
         <v>3030101</v>
@@ -4513,16 +4636,16 @@
         <v>13</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>141</v>
+        <v>45</v>
       </c>
       <c r="G113">
         <v>10</v>
       </c>
       <c r="H113" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="I113" t="s">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="J113" s="1">
         <v>3010101</v>
@@ -4545,16 +4668,16 @@
         <v>13</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>141</v>
+        <v>45</v>
       </c>
       <c r="G114">
         <v>10</v>
       </c>
       <c r="H114" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="I114" t="s">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="J114" s="1">
         <v>3030101</v>
@@ -4577,16 +4700,16 @@
         <v>13</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>141</v>
+        <v>45</v>
       </c>
       <c r="G115">
         <v>10</v>
       </c>
       <c r="H115" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="I115" t="s">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="J115" s="1">
         <v>3010101</v>
@@ -4609,16 +4732,16 @@
         <v>13</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>141</v>
+        <v>45</v>
       </c>
       <c r="G116">
         <v>10</v>
       </c>
       <c r="H116" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="I116" t="s">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="J116" s="1">
         <v>3010101</v>
@@ -4641,16 +4764,16 @@
         <v>14</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>142</v>
+        <v>46</v>
       </c>
       <c r="G117">
         <v>10</v>
       </c>
       <c r="H117" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="I117" t="s">
-        <v>52</v>
+        <v>106</v>
       </c>
       <c r="J117" s="1">
         <v>3010101</v>
@@ -4673,16 +4796,16 @@
         <v>14</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>142</v>
+        <v>46</v>
       </c>
       <c r="G118">
         <v>10</v>
       </c>
       <c r="H118" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="I118" t="s">
-        <v>53</v>
+        <v>107</v>
       </c>
       <c r="J118" s="1">
         <v>3030101</v>
@@ -4705,16 +4828,16 @@
         <v>14</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>142</v>
+        <v>46</v>
       </c>
       <c r="G119">
         <v>10</v>
       </c>
       <c r="H119" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="I119" t="s">
-        <v>53</v>
+        <v>107</v>
       </c>
       <c r="J119" s="1">
         <v>3030101</v>
@@ -4737,16 +4860,16 @@
         <v>14</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>142</v>
+        <v>46</v>
       </c>
       <c r="G120">
         <v>10</v>
       </c>
       <c r="H120" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="I120" t="s">
-        <v>53</v>
+        <v>107</v>
       </c>
       <c r="J120" s="1">
         <v>3030101</v>
@@ -4769,16 +4892,16 @@
         <v>14</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>142</v>
+        <v>46</v>
       </c>
       <c r="G121">
         <v>10</v>
       </c>
       <c r="H121" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="I121" t="s">
-        <v>52</v>
+        <v>106</v>
       </c>
       <c r="J121" s="1">
         <v>3010101</v>
@@ -4801,16 +4924,16 @@
         <v>14</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>142</v>
+        <v>46</v>
       </c>
       <c r="G122">
         <v>10</v>
       </c>
       <c r="H122" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="I122" t="s">
-        <v>53</v>
+        <v>107</v>
       </c>
       <c r="J122" s="1">
         <v>3030101</v>
@@ -4833,16 +4956,16 @@
         <v>14</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>142</v>
+        <v>46</v>
       </c>
       <c r="G123">
         <v>10</v>
       </c>
       <c r="H123" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="I123" t="s">
-        <v>52</v>
+        <v>106</v>
       </c>
       <c r="J123" s="1">
         <v>3010101</v>
@@ -4865,16 +4988,16 @@
         <v>14</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>142</v>
+        <v>46</v>
       </c>
       <c r="G124">
         <v>10</v>
       </c>
       <c r="H124" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="I124" t="s">
-        <v>52</v>
+        <v>106</v>
       </c>
       <c r="J124" s="1">
         <v>3010101</v>
@@ -4897,16 +5020,16 @@
         <v>15</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>143</v>
+        <v>47</v>
       </c>
       <c r="G125">
         <v>10</v>
       </c>
       <c r="H125" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="I125" t="s">
-        <v>54</v>
+        <v>108</v>
       </c>
       <c r="J125" s="1">
         <v>3010101</v>
@@ -4929,16 +5052,16 @@
         <v>15</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>143</v>
+        <v>47</v>
       </c>
       <c r="G126">
         <v>10</v>
       </c>
       <c r="H126" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="I126" t="s">
-        <v>55</v>
+        <v>109</v>
       </c>
       <c r="J126" s="1">
         <v>3030101</v>
@@ -4961,16 +5084,16 @@
         <v>15</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>143</v>
+        <v>47</v>
       </c>
       <c r="G127">
         <v>10</v>
       </c>
       <c r="H127" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="I127" t="s">
-        <v>55</v>
+        <v>109</v>
       </c>
       <c r="J127" s="1">
         <v>3030101</v>
@@ -4993,16 +5116,16 @@
         <v>15</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>143</v>
+        <v>47</v>
       </c>
       <c r="G128">
         <v>10</v>
       </c>
       <c r="H128" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="I128" t="s">
-        <v>55</v>
+        <v>109</v>
       </c>
       <c r="J128" s="1">
         <v>3030101</v>
@@ -5025,16 +5148,16 @@
         <v>15</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>143</v>
+        <v>47</v>
       </c>
       <c r="G129">
         <v>10</v>
       </c>
       <c r="H129" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="I129" t="s">
-        <v>54</v>
+        <v>108</v>
       </c>
       <c r="J129" s="1">
         <v>3010101</v>
@@ -5057,16 +5180,16 @@
         <v>15</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>143</v>
+        <v>47</v>
       </c>
       <c r="G130">
         <v>10</v>
       </c>
       <c r="H130" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="I130" t="s">
-        <v>55</v>
+        <v>109</v>
       </c>
       <c r="J130" s="1">
         <v>3030101</v>
@@ -5089,16 +5212,16 @@
         <v>15</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>143</v>
+        <v>47</v>
       </c>
       <c r="G131">
         <v>10</v>
       </c>
       <c r="H131" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="I131" t="s">
-        <v>54</v>
+        <v>108</v>
       </c>
       <c r="J131" s="1">
         <v>3010101</v>
@@ -5121,16 +5244,16 @@
         <v>15</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>143</v>
+        <v>47</v>
       </c>
       <c r="G132">
         <v>10</v>
       </c>
       <c r="H132" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="I132" t="s">
-        <v>54</v>
+        <v>108</v>
       </c>
       <c r="J132" s="1">
         <v>3010101</v>
@@ -5153,16 +5276,16 @@
         <v>16</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>144</v>
+        <v>48</v>
       </c>
       <c r="G133">
         <v>10</v>
       </c>
       <c r="H133" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="I133" t="s">
-        <v>56</v>
+        <v>110</v>
       </c>
       <c r="J133" s="1">
         <v>3010101</v>
@@ -5185,16 +5308,16 @@
         <v>16</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>144</v>
+        <v>48</v>
       </c>
       <c r="G134">
         <v>10</v>
       </c>
       <c r="H134" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="I134" t="s">
-        <v>57</v>
+        <v>111</v>
       </c>
       <c r="J134" s="1">
         <v>3030101</v>
@@ -5217,16 +5340,16 @@
         <v>16</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>144</v>
+        <v>48</v>
       </c>
       <c r="G135">
         <v>10</v>
       </c>
       <c r="H135" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="I135" t="s">
-        <v>57</v>
+        <v>111</v>
       </c>
       <c r="J135" s="1">
         <v>3030101</v>
@@ -5249,16 +5372,16 @@
         <v>16</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>144</v>
+        <v>48</v>
       </c>
       <c r="G136">
         <v>10</v>
       </c>
       <c r="H136" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="I136" t="s">
-        <v>57</v>
+        <v>111</v>
       </c>
       <c r="J136" s="1">
         <v>3030101</v>
@@ -5281,16 +5404,16 @@
         <v>16</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>144</v>
+        <v>48</v>
       </c>
       <c r="G137">
         <v>10</v>
       </c>
       <c r="H137" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="I137" t="s">
-        <v>56</v>
+        <v>110</v>
       </c>
       <c r="J137" s="1">
         <v>3010101</v>
@@ -5313,16 +5436,16 @@
         <v>16</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>144</v>
+        <v>48</v>
       </c>
       <c r="G138">
         <v>10</v>
       </c>
       <c r="H138" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="I138" t="s">
-        <v>57</v>
+        <v>111</v>
       </c>
       <c r="J138" s="1">
         <v>3030101</v>
@@ -5345,16 +5468,16 @@
         <v>16</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>144</v>
+        <v>48</v>
       </c>
       <c r="G139">
         <v>10</v>
       </c>
       <c r="H139" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="I139" t="s">
-        <v>56</v>
+        <v>110</v>
       </c>
       <c r="J139" s="1">
         <v>3010101</v>
@@ -5377,16 +5500,16 @@
         <v>16</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>144</v>
+        <v>48</v>
       </c>
       <c r="G140">
         <v>10</v>
       </c>
       <c r="H140" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="I140" t="s">
-        <v>56</v>
+        <v>110</v>
       </c>
       <c r="J140" s="1">
         <v>3010101</v>
@@ -5409,16 +5532,16 @@
         <v>17</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>145</v>
+        <v>49</v>
       </c>
       <c r="G141">
         <v>10</v>
       </c>
       <c r="H141" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="I141" t="s">
-        <v>58</v>
+        <v>112</v>
       </c>
       <c r="J141" s="1">
         <v>3010101</v>
@@ -5441,16 +5564,16 @@
         <v>17</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>145</v>
+        <v>49</v>
       </c>
       <c r="G142">
         <v>10</v>
       </c>
       <c r="H142" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="I142" t="s">
-        <v>59</v>
+        <v>113</v>
       </c>
       <c r="J142" s="1">
         <v>3030101</v>
@@ -5473,16 +5596,16 @@
         <v>17</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>145</v>
+        <v>49</v>
       </c>
       <c r="G143">
         <v>10</v>
       </c>
       <c r="H143" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="I143" t="s">
-        <v>59</v>
+        <v>113</v>
       </c>
       <c r="J143" s="1">
         <v>3030101</v>
@@ -5505,16 +5628,16 @@
         <v>17</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>145</v>
+        <v>49</v>
       </c>
       <c r="G144">
         <v>10</v>
       </c>
       <c r="H144" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="I144" t="s">
-        <v>59</v>
+        <v>113</v>
       </c>
       <c r="J144" s="1">
         <v>3030101</v>
@@ -5537,16 +5660,16 @@
         <v>17</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>145</v>
+        <v>49</v>
       </c>
       <c r="G145">
         <v>10</v>
       </c>
       <c r="H145" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="I145" t="s">
-        <v>58</v>
+        <v>112</v>
       </c>
       <c r="J145" s="1">
         <v>3010101</v>
@@ -5569,16 +5692,16 @@
         <v>17</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>145</v>
+        <v>49</v>
       </c>
       <c r="G146">
         <v>10</v>
       </c>
       <c r="H146" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="I146" t="s">
-        <v>59</v>
+        <v>113</v>
       </c>
       <c r="J146" s="1">
         <v>3030101</v>
@@ -5601,16 +5724,16 @@
         <v>17</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>145</v>
+        <v>49</v>
       </c>
       <c r="G147">
         <v>10</v>
       </c>
       <c r="H147" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="I147" t="s">
-        <v>58</v>
+        <v>112</v>
       </c>
       <c r="J147" s="1">
         <v>3010101</v>
@@ -5633,16 +5756,16 @@
         <v>17</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>145</v>
+        <v>49</v>
       </c>
       <c r="G148">
         <v>10</v>
       </c>
       <c r="H148" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="I148" t="s">
-        <v>58</v>
+        <v>112</v>
       </c>
       <c r="J148" s="1">
         <v>3010101</v>
@@ -5665,16 +5788,16 @@
         <v>18</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>146</v>
+        <v>50</v>
       </c>
       <c r="G149">
         <v>10</v>
       </c>
       <c r="H149" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="I149" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="J149" s="1">
         <v>3010101</v>
@@ -5697,16 +5820,16 @@
         <v>18</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>146</v>
+        <v>50</v>
       </c>
       <c r="G150">
         <v>10</v>
       </c>
       <c r="H150" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="I150" t="s">
-        <v>61</v>
+        <v>115</v>
       </c>
       <c r="J150" s="1">
         <v>3030101</v>
@@ -5729,16 +5852,16 @@
         <v>18</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>146</v>
+        <v>50</v>
       </c>
       <c r="G151">
         <v>10</v>
       </c>
       <c r="H151" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="I151" t="s">
-        <v>61</v>
+        <v>115</v>
       </c>
       <c r="J151" s="1">
         <v>3030101</v>
@@ -5761,16 +5884,16 @@
         <v>18</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>146</v>
+        <v>50</v>
       </c>
       <c r="G152">
         <v>10</v>
       </c>
       <c r="H152" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="I152" t="s">
-        <v>61</v>
+        <v>115</v>
       </c>
       <c r="J152" s="1">
         <v>3030101</v>
@@ -5793,16 +5916,16 @@
         <v>18</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>146</v>
+        <v>50</v>
       </c>
       <c r="G153">
         <v>10</v>
       </c>
       <c r="H153" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="I153" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="J153" s="1">
         <v>3010101</v>
@@ -5825,16 +5948,16 @@
         <v>18</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>146</v>
+        <v>50</v>
       </c>
       <c r="G154">
         <v>10</v>
       </c>
       <c r="H154" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="I154" t="s">
-        <v>61</v>
+        <v>115</v>
       </c>
       <c r="J154" s="1">
         <v>3030101</v>
@@ -5857,16 +5980,16 @@
         <v>18</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>146</v>
+        <v>50</v>
       </c>
       <c r="G155">
         <v>10</v>
       </c>
       <c r="H155" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="I155" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="J155" s="1">
         <v>3010101</v>
@@ -5889,16 +6012,16 @@
         <v>18</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>146</v>
+        <v>50</v>
       </c>
       <c r="G156">
         <v>10</v>
       </c>
       <c r="H156" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="I156" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="J156" s="1">
         <v>3010101</v>
@@ -5921,16 +6044,16 @@
         <v>19</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>147</v>
+        <v>51</v>
       </c>
       <c r="G157">
         <v>10</v>
       </c>
       <c r="H157" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="I157" t="s">
-        <v>62</v>
+        <v>116</v>
       </c>
       <c r="J157" s="1">
         <v>3010101</v>
@@ -5953,16 +6076,16 @@
         <v>19</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>147</v>
+        <v>51</v>
       </c>
       <c r="G158">
         <v>10</v>
       </c>
       <c r="H158" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="I158" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="J158" s="1">
         <v>3030101</v>
@@ -5985,16 +6108,16 @@
         <v>19</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>147</v>
+        <v>51</v>
       </c>
       <c r="G159">
         <v>10</v>
       </c>
       <c r="H159" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="I159" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="J159" s="1">
         <v>3030101</v>
@@ -6017,16 +6140,16 @@
         <v>19</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>147</v>
+        <v>51</v>
       </c>
       <c r="G160">
         <v>10</v>
       </c>
       <c r="H160" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="I160" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="J160" s="1">
         <v>3030101</v>
@@ -6049,16 +6172,16 @@
         <v>19</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>147</v>
+        <v>51</v>
       </c>
       <c r="G161">
         <v>10</v>
       </c>
       <c r="H161" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="I161" t="s">
-        <v>62</v>
+        <v>116</v>
       </c>
       <c r="J161" s="1">
         <v>3010101</v>
@@ -6081,16 +6204,16 @@
         <v>19</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>147</v>
+        <v>51</v>
       </c>
       <c r="G162">
         <v>10</v>
       </c>
       <c r="H162" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="I162" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="J162" s="1">
         <v>3030101</v>
@@ -6113,16 +6236,16 @@
         <v>19</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>147</v>
+        <v>51</v>
       </c>
       <c r="G163">
         <v>10</v>
       </c>
       <c r="H163" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="I163" t="s">
-        <v>62</v>
+        <v>116</v>
       </c>
       <c r="J163" s="1">
         <v>3010101</v>
@@ -6145,16 +6268,16 @@
         <v>19</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>147</v>
+        <v>51</v>
       </c>
       <c r="G164">
         <v>10</v>
       </c>
       <c r="H164" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="I164" t="s">
-        <v>62</v>
+        <v>116</v>
       </c>
       <c r="J164" s="1">
         <v>3010101</v>
@@ -6177,16 +6300,16 @@
         <v>20</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="G165">
         <v>20</v>
       </c>
       <c r="H165" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="I165" t="s">
-        <v>64</v>
+        <v>118</v>
       </c>
       <c r="J165" s="1">
         <v>3010101</v>
@@ -6209,16 +6332,16 @@
         <v>20</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="G166">
         <v>20</v>
       </c>
       <c r="H166" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="I166" t="s">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="J166" s="1">
         <v>3030101</v>
@@ -6241,16 +6364,16 @@
         <v>20</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="G167">
         <v>20</v>
       </c>
       <c r="H167" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="I167" t="s">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="J167" s="1">
         <v>3030101</v>
@@ -6273,16 +6396,16 @@
         <v>20</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="G168">
         <v>20</v>
       </c>
       <c r="H168" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="I168" t="s">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="J168" s="1">
         <v>3030101</v>
@@ -6305,16 +6428,16 @@
         <v>20</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="G169">
         <v>20</v>
       </c>
       <c r="H169" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="I169" t="s">
-        <v>64</v>
+        <v>118</v>
       </c>
       <c r="J169" s="1">
         <v>3010101</v>
@@ -6337,16 +6460,16 @@
         <v>20</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="G170">
         <v>20</v>
       </c>
       <c r="H170" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="I170" t="s">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="J170" s="1">
         <v>3030101</v>
@@ -6369,16 +6492,16 @@
         <v>20</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="G171">
         <v>20</v>
       </c>
       <c r="H171" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="I171" t="s">
-        <v>64</v>
+        <v>118</v>
       </c>
       <c r="J171" s="1">
         <v>3010101</v>
@@ -6401,16 +6524,16 @@
         <v>20</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="G172">
         <v>20</v>
       </c>
       <c r="H172" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="I172" t="s">
-        <v>64</v>
+        <v>118</v>
       </c>
       <c r="J172" s="1">
         <v>3010101</v>
@@ -6433,16 +6556,16 @@
         <v>21</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>149</v>
+        <v>53</v>
       </c>
       <c r="G173">
         <v>20</v>
       </c>
       <c r="H173" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="I173" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="J173" s="1">
         <v>3010101</v>
@@ -6465,16 +6588,16 @@
         <v>21</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>149</v>
+        <v>53</v>
       </c>
       <c r="G174">
         <v>20</v>
       </c>
       <c r="H174" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="I174" t="s">
-        <v>67</v>
+        <v>121</v>
       </c>
       <c r="J174" s="1">
         <v>3030101</v>
@@ -6497,16 +6620,16 @@
         <v>21</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>149</v>
+        <v>53</v>
       </c>
       <c r="G175">
         <v>20</v>
       </c>
       <c r="H175" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="I175" t="s">
-        <v>67</v>
+        <v>121</v>
       </c>
       <c r="J175" s="1">
         <v>3030101</v>
@@ -6529,16 +6652,16 @@
         <v>21</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>149</v>
+        <v>53</v>
       </c>
       <c r="G176">
         <v>20</v>
       </c>
       <c r="H176" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="I176" t="s">
-        <v>67</v>
+        <v>121</v>
       </c>
       <c r="J176" s="1">
         <v>3030101</v>
@@ -6561,16 +6684,16 @@
         <v>21</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>149</v>
+        <v>53</v>
       </c>
       <c r="G177">
         <v>20</v>
       </c>
       <c r="H177" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="I177" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="J177" s="1">
         <v>3010101</v>
@@ -6593,16 +6716,16 @@
         <v>21</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>149</v>
+        <v>53</v>
       </c>
       <c r="G178">
         <v>20</v>
       </c>
       <c r="H178" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="I178" t="s">
-        <v>67</v>
+        <v>121</v>
       </c>
       <c r="J178" s="1">
         <v>3030101</v>
@@ -6625,16 +6748,16 @@
         <v>21</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>149</v>
+        <v>53</v>
       </c>
       <c r="G179">
         <v>20</v>
       </c>
       <c r="H179" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="I179" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="J179" s="1">
         <v>3010101</v>
@@ -6657,16 +6780,16 @@
         <v>21</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>149</v>
+        <v>53</v>
       </c>
       <c r="G180">
         <v>20</v>
       </c>
       <c r="H180" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="I180" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="J180" s="1">
         <v>3010101</v>
@@ -6689,16 +6812,16 @@
         <v>22</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>150</v>
+        <v>54</v>
       </c>
       <c r="G181">
         <v>20</v>
       </c>
       <c r="H181" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="I181" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="J181" s="1">
         <v>3010101</v>
@@ -6721,16 +6844,16 @@
         <v>22</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>150</v>
+        <v>54</v>
       </c>
       <c r="G182">
         <v>20</v>
       </c>
       <c r="H182" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="I182" t="s">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="J182" s="1">
         <v>3030101</v>
@@ -6753,16 +6876,16 @@
         <v>22</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>150</v>
+        <v>54</v>
       </c>
       <c r="G183">
         <v>20</v>
       </c>
       <c r="H183" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="I183" t="s">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="J183" s="1">
         <v>3030101</v>
@@ -6785,16 +6908,16 @@
         <v>22</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>150</v>
+        <v>54</v>
       </c>
       <c r="G184">
         <v>20</v>
       </c>
       <c r="H184" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="I184" t="s">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="J184" s="1">
         <v>3030101</v>
@@ -6817,16 +6940,16 @@
         <v>22</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>150</v>
+        <v>54</v>
       </c>
       <c r="G185">
         <v>20</v>
       </c>
       <c r="H185" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="I185" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="J185" s="1">
         <v>3010101</v>
@@ -6849,16 +6972,16 @@
         <v>22</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>150</v>
+        <v>54</v>
       </c>
       <c r="G186">
         <v>20</v>
       </c>
       <c r="H186" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="I186" t="s">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="J186" s="1">
         <v>3030101</v>
@@ -6881,16 +7004,16 @@
         <v>22</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>150</v>
+        <v>54</v>
       </c>
       <c r="G187">
         <v>20</v>
       </c>
       <c r="H187" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="I187" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="J187" s="1">
         <v>3010101</v>
@@ -6913,16 +7036,16 @@
         <v>22</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>150</v>
+        <v>54</v>
       </c>
       <c r="G188">
         <v>20</v>
       </c>
       <c r="H188" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="I188" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="J188" s="1">
         <v>3010101</v>
@@ -6945,16 +7068,16 @@
         <v>23</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>151</v>
+        <v>55</v>
       </c>
       <c r="G189">
         <v>20</v>
       </c>
       <c r="H189" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="I189" t="s">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="J189" s="1">
         <v>3010101</v>
@@ -6977,16 +7100,16 @@
         <v>23</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>151</v>
+        <v>55</v>
       </c>
       <c r="G190">
         <v>20</v>
       </c>
       <c r="H190" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="I190" t="s">
-        <v>71</v>
+        <v>123</v>
       </c>
       <c r="J190" s="1">
         <v>3030101</v>
@@ -7009,16 +7132,16 @@
         <v>23</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>151</v>
+        <v>55</v>
       </c>
       <c r="G191">
         <v>20</v>
       </c>
       <c r="H191" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="I191" t="s">
-        <v>71</v>
+        <v>123</v>
       </c>
       <c r="J191" s="1">
         <v>3030101</v>
@@ -7041,16 +7164,16 @@
         <v>23</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>151</v>
+        <v>55</v>
       </c>
       <c r="G192">
         <v>20</v>
       </c>
       <c r="H192" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="I192" t="s">
-        <v>71</v>
+        <v>123</v>
       </c>
       <c r="J192" s="1">
         <v>3030101</v>
@@ -7073,16 +7196,16 @@
         <v>23</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>151</v>
+        <v>55</v>
       </c>
       <c r="G193">
         <v>20</v>
       </c>
       <c r="H193" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="I193" t="s">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="J193" s="1">
         <v>3010101</v>
@@ -7105,16 +7228,16 @@
         <v>23</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>151</v>
+        <v>55</v>
       </c>
       <c r="G194">
         <v>20</v>
       </c>
       <c r="H194" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="I194" t="s">
-        <v>71</v>
+        <v>123</v>
       </c>
       <c r="J194" s="1">
         <v>3030101</v>
@@ -7137,16 +7260,16 @@
         <v>23</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>151</v>
+        <v>55</v>
       </c>
       <c r="G195">
         <v>20</v>
       </c>
       <c r="H195" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="I195" t="s">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="J195" s="1">
         <v>3010101</v>
@@ -7169,16 +7292,16 @@
         <v>23</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>151</v>
+        <v>55</v>
       </c>
       <c r="G196">
         <v>20</v>
       </c>
       <c r="H196" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="I196" t="s">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="J196" s="1">
         <v>3010101</v>
@@ -7201,16 +7324,16 @@
         <v>24</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>152</v>
+        <v>56</v>
       </c>
       <c r="G197">
         <v>20</v>
       </c>
       <c r="H197" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="I197" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="J197" s="1">
         <v>3010101</v>
@@ -7233,16 +7356,16 @@
         <v>24</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>152</v>
+        <v>56</v>
       </c>
       <c r="G198">
         <v>20</v>
       </c>
       <c r="H198" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="I198" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="J198" s="1">
         <v>3030101</v>
@@ -7265,16 +7388,16 @@
         <v>24</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>152</v>
+        <v>56</v>
       </c>
       <c r="G199">
         <v>20</v>
       </c>
       <c r="H199" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="I199" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="J199" s="1">
         <v>3030101</v>
@@ -7297,16 +7420,16 @@
         <v>24</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>152</v>
+        <v>56</v>
       </c>
       <c r="G200">
         <v>20</v>
       </c>
       <c r="H200" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="I200" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="J200" s="1">
         <v>3030101</v>
@@ -7329,16 +7452,16 @@
         <v>24</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>152</v>
+        <v>56</v>
       </c>
       <c r="G201">
         <v>20</v>
       </c>
       <c r="H201" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="I201" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="J201" s="1">
         <v>3010101</v>
@@ -7361,16 +7484,16 @@
         <v>24</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>152</v>
+        <v>56</v>
       </c>
       <c r="G202">
         <v>20</v>
       </c>
       <c r="H202" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="I202" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="J202" s="1">
         <v>3030101</v>
@@ -7393,16 +7516,16 @@
         <v>24</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>152</v>
+        <v>56</v>
       </c>
       <c r="G203">
         <v>20</v>
       </c>
       <c r="H203" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="I203" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="J203" s="1">
         <v>3010101</v>
@@ -7425,16 +7548,16 @@
         <v>24</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>152</v>
+        <v>56</v>
       </c>
       <c r="G204">
         <v>20</v>
       </c>
       <c r="H204" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="I204" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="J204" s="1">
         <v>3010101</v>
@@ -7457,16 +7580,16 @@
         <v>25</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>153</v>
+        <v>57</v>
       </c>
       <c r="G205">
         <v>20</v>
       </c>
       <c r="H205" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="I205" t="s">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="J205" s="1">
         <v>3010101</v>
@@ -7489,16 +7612,16 @@
         <v>25</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>153</v>
+        <v>57</v>
       </c>
       <c r="G206">
         <v>20</v>
       </c>
       <c r="H206" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="I206" t="s">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="J206" s="1">
         <v>3030101</v>
@@ -7521,16 +7644,16 @@
         <v>25</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>153</v>
+        <v>57</v>
       </c>
       <c r="G207">
         <v>20</v>
       </c>
       <c r="H207" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="I207" t="s">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="J207" s="1">
         <v>3030101</v>
@@ -7553,16 +7676,16 @@
         <v>25</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>153</v>
+        <v>57</v>
       </c>
       <c r="G208">
         <v>20</v>
       </c>
       <c r="H208" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="I208" t="s">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="J208" s="1">
         <v>3030101</v>
@@ -7585,16 +7708,16 @@
         <v>25</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>153</v>
+        <v>57</v>
       </c>
       <c r="G209">
         <v>20</v>
       </c>
       <c r="H209" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="I209" t="s">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="J209" s="1">
         <v>3010101</v>
@@ -7617,16 +7740,16 @@
         <v>25</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>153</v>
+        <v>57</v>
       </c>
       <c r="G210">
         <v>20</v>
       </c>
       <c r="H210" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="I210" t="s">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="J210" s="1">
         <v>3030101</v>
@@ -7649,16 +7772,16 @@
         <v>25</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>153</v>
+        <v>57</v>
       </c>
       <c r="G211">
         <v>20</v>
       </c>
       <c r="H211" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="I211" t="s">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="J211" s="1">
         <v>3010101</v>
@@ -7681,16 +7804,16 @@
         <v>25</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>153</v>
+        <v>57</v>
       </c>
       <c r="G212">
         <v>20</v>
       </c>
       <c r="H212" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="I212" t="s">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="J212" s="1">
         <v>3010101</v>
@@ -7713,16 +7836,16 @@
         <v>26</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>154</v>
+        <v>58</v>
       </c>
       <c r="G213">
         <v>20</v>
       </c>
       <c r="H213" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="I213" t="s">
-        <v>76</v>
+        <v>128</v>
       </c>
       <c r="J213" s="1">
         <v>3010101</v>
@@ -7745,16 +7868,16 @@
         <v>26</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>154</v>
+        <v>58</v>
       </c>
       <c r="G214">
         <v>20</v>
       </c>
       <c r="H214" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="I214" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="J214" s="1">
         <v>3030101</v>
@@ -7777,16 +7900,16 @@
         <v>26</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>154</v>
+        <v>58</v>
       </c>
       <c r="G215">
         <v>20</v>
       </c>
       <c r="H215" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="I215" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="J215" s="1">
         <v>3030101</v>
@@ -7809,16 +7932,16 @@
         <v>26</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>154</v>
+        <v>58</v>
       </c>
       <c r="G216">
         <v>20</v>
       </c>
       <c r="H216" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="I216" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="J216" s="1">
         <v>3030101</v>
@@ -7841,16 +7964,16 @@
         <v>26</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>154</v>
+        <v>58</v>
       </c>
       <c r="G217">
         <v>20</v>
       </c>
       <c r="H217" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="I217" t="s">
-        <v>76</v>
+        <v>128</v>
       </c>
       <c r="J217" s="1">
         <v>3010101</v>
@@ -7873,16 +7996,16 @@
         <v>26</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>154</v>
+        <v>58</v>
       </c>
       <c r="G218">
         <v>20</v>
       </c>
       <c r="H218" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="I218" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="J218" s="1">
         <v>3030101</v>
@@ -7905,16 +8028,16 @@
         <v>26</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>154</v>
+        <v>58</v>
       </c>
       <c r="G219">
         <v>20</v>
       </c>
       <c r="H219" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="I219" t="s">
-        <v>76</v>
+        <v>128</v>
       </c>
       <c r="J219" s="1">
         <v>3010101</v>
@@ -7937,16 +8060,16 @@
         <v>26</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>154</v>
+        <v>58</v>
       </c>
       <c r="G220">
         <v>20</v>
       </c>
       <c r="H220" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="I220" t="s">
-        <v>76</v>
+        <v>128</v>
       </c>
       <c r="J220" s="1">
         <v>3010101</v>
@@ -7969,16 +8092,16 @@
         <v>27</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>155</v>
+        <v>59</v>
       </c>
       <c r="G221">
         <v>20</v>
       </c>
       <c r="H221" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="I221" t="s">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="J221" s="1">
         <v>3010101</v>
@@ -8001,16 +8124,16 @@
         <v>27</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>155</v>
+        <v>59</v>
       </c>
       <c r="G222">
         <v>20</v>
       </c>
       <c r="H222" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="I222" t="s">
-        <v>79</v>
+        <v>129</v>
       </c>
       <c r="J222" s="1">
         <v>3030101</v>
@@ -8033,16 +8156,16 @@
         <v>27</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>155</v>
+        <v>59</v>
       </c>
       <c r="G223">
         <v>20</v>
       </c>
       <c r="H223" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="I223" t="s">
-        <v>79</v>
+        <v>129</v>
       </c>
       <c r="J223" s="1">
         <v>3030101</v>
@@ -8065,16 +8188,16 @@
         <v>27</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>155</v>
+        <v>59</v>
       </c>
       <c r="G224">
         <v>20</v>
       </c>
       <c r="H224" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="I224" t="s">
-        <v>79</v>
+        <v>129</v>
       </c>
       <c r="J224" s="1">
         <v>3030101</v>
@@ -8097,16 +8220,16 @@
         <v>27</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>155</v>
+        <v>59</v>
       </c>
       <c r="G225">
         <v>20</v>
       </c>
       <c r="H225" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="I225" t="s">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="J225" s="1">
         <v>3010101</v>
@@ -8129,16 +8252,16 @@
         <v>27</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>155</v>
+        <v>59</v>
       </c>
       <c r="G226">
         <v>20</v>
       </c>
       <c r="H226" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="I226" t="s">
-        <v>79</v>
+        <v>129</v>
       </c>
       <c r="J226" s="1">
         <v>3030101</v>
@@ -8161,16 +8284,16 @@
         <v>27</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>155</v>
+        <v>59</v>
       </c>
       <c r="G227">
         <v>20</v>
       </c>
       <c r="H227" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="I227" t="s">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="J227" s="1">
         <v>3010101</v>
@@ -8193,16 +8316,16 @@
         <v>27</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>155</v>
+        <v>59</v>
       </c>
       <c r="G228">
         <v>20</v>
       </c>
       <c r="H228" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="I228" t="s">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="J228" s="1">
         <v>3010101</v>
@@ -8225,16 +8348,16 @@
         <v>28</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>156</v>
+        <v>60</v>
       </c>
       <c r="G229">
         <v>20</v>
       </c>
       <c r="H229" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="I229" t="s">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="J229" s="1">
         <v>3010101</v>
@@ -8257,16 +8380,16 @@
         <v>28</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>156</v>
+        <v>60</v>
       </c>
       <c r="G230">
         <v>20</v>
       </c>
       <c r="H230" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="I230" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="J230" s="1">
         <v>3030101</v>
@@ -8289,16 +8412,16 @@
         <v>28</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>156</v>
+        <v>60</v>
       </c>
       <c r="G231">
         <v>20</v>
       </c>
       <c r="H231" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="I231" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="J231" s="1">
         <v>3030101</v>
@@ -8321,16 +8444,16 @@
         <v>28</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>156</v>
+        <v>60</v>
       </c>
       <c r="G232">
         <v>20</v>
       </c>
       <c r="H232" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="I232" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="J232" s="1">
         <v>3030101</v>
@@ -8353,16 +8476,16 @@
         <v>28</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>156</v>
+        <v>60</v>
       </c>
       <c r="G233">
         <v>20</v>
       </c>
       <c r="H233" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="I233" t="s">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="J233" s="1">
         <v>3010101</v>
@@ -8385,16 +8508,16 @@
         <v>28</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>156</v>
+        <v>60</v>
       </c>
       <c r="G234">
         <v>20</v>
       </c>
       <c r="H234" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="I234" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="J234" s="1">
         <v>3030101</v>
@@ -8417,16 +8540,16 @@
         <v>28</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>156</v>
+        <v>60</v>
       </c>
       <c r="G235">
         <v>20</v>
       </c>
       <c r="H235" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="I235" t="s">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="J235" s="1">
         <v>3010101</v>
@@ -8449,16 +8572,16 @@
         <v>28</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>156</v>
+        <v>60</v>
       </c>
       <c r="G236">
         <v>20</v>
       </c>
       <c r="H236" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="I236" t="s">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="J236" s="1">
         <v>3010101</v>
@@ -8481,16 +8604,16 @@
         <v>29</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>157</v>
+        <v>61</v>
       </c>
       <c r="G237">
         <v>20</v>
       </c>
       <c r="H237" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="I237" t="s">
-        <v>82</v>
+        <v>133</v>
       </c>
       <c r="J237" s="1">
         <v>3010101</v>
@@ -8513,16 +8636,16 @@
         <v>29</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>157</v>
+        <v>61</v>
       </c>
       <c r="G238">
         <v>20</v>
       </c>
       <c r="H238" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="I238" t="s">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="J238" s="1">
         <v>3030101</v>
@@ -8545,16 +8668,16 @@
         <v>29</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>157</v>
+        <v>61</v>
       </c>
       <c r="G239">
         <v>20</v>
       </c>
       <c r="H239" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="I239" t="s">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="J239" s="1">
         <v>3030101</v>
@@ -8577,16 +8700,16 @@
         <v>29</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>157</v>
+        <v>61</v>
       </c>
       <c r="G240">
         <v>20</v>
       </c>
       <c r="H240" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="I240" t="s">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="J240" s="1">
         <v>3030101</v>
@@ -8609,16 +8732,16 @@
         <v>29</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>157</v>
+        <v>61</v>
       </c>
       <c r="G241">
         <v>20</v>
       </c>
       <c r="H241" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="I241" t="s">
-        <v>82</v>
+        <v>133</v>
       </c>
       <c r="J241" s="1">
         <v>3010101</v>
@@ -8641,16 +8764,16 @@
         <v>29</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>157</v>
+        <v>61</v>
       </c>
       <c r="G242">
         <v>20</v>
       </c>
       <c r="H242" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="I242" t="s">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="J242" s="1">
         <v>3030101</v>
@@ -8673,16 +8796,16 @@
         <v>29</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>157</v>
+        <v>61</v>
       </c>
       <c r="G243">
         <v>20</v>
       </c>
       <c r="H243" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="I243" t="s">
-        <v>82</v>
+        <v>133</v>
       </c>
       <c r="J243" s="1">
         <v>3010101</v>
@@ -8705,16 +8828,16 @@
         <v>29</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>157</v>
+        <v>61</v>
       </c>
       <c r="G244">
         <v>20</v>
       </c>
       <c r="H244" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="I244" t="s">
-        <v>82</v>
+        <v>133</v>
       </c>
       <c r="J244" s="1">
         <v>3010101</v>
@@ -8737,16 +8860,16 @@
         <v>30</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>158</v>
+        <v>62</v>
       </c>
       <c r="G245">
         <v>30</v>
       </c>
       <c r="H245" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="I245" t="s">
-        <v>84</v>
+        <v>135</v>
       </c>
       <c r="J245" s="1">
         <v>3010101</v>
@@ -8769,16 +8892,16 @@
         <v>30</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>158</v>
+        <v>62</v>
       </c>
       <c r="G246">
         <v>30</v>
       </c>
       <c r="H246" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="I246" t="s">
-        <v>85</v>
+        <v>134</v>
       </c>
       <c r="J246" s="1">
         <v>3030101</v>
@@ -8801,16 +8924,16 @@
         <v>30</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>158</v>
+        <v>62</v>
       </c>
       <c r="G247">
         <v>30</v>
       </c>
       <c r="H247" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="I247" t="s">
-        <v>85</v>
+        <v>134</v>
       </c>
       <c r="J247" s="1">
         <v>3030101</v>
@@ -8833,16 +8956,16 @@
         <v>30</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>158</v>
+        <v>62</v>
       </c>
       <c r="G248">
         <v>30</v>
       </c>
       <c r="H248" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="I248" t="s">
-        <v>85</v>
+        <v>134</v>
       </c>
       <c r="J248" s="1">
         <v>3030101</v>
@@ -8865,16 +8988,16 @@
         <v>30</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>158</v>
+        <v>62</v>
       </c>
       <c r="G249">
         <v>30</v>
       </c>
       <c r="H249" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="I249" t="s">
-        <v>84</v>
+        <v>135</v>
       </c>
       <c r="J249" s="1">
         <v>3010101</v>
@@ -8897,16 +9020,16 @@
         <v>30</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>158</v>
+        <v>62</v>
       </c>
       <c r="G250">
         <v>30</v>
       </c>
       <c r="H250" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="I250" t="s">
-        <v>85</v>
+        <v>134</v>
       </c>
       <c r="J250" s="1">
         <v>3030101</v>
@@ -8929,16 +9052,16 @@
         <v>30</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>158</v>
+        <v>62</v>
       </c>
       <c r="G251">
         <v>30</v>
       </c>
       <c r="H251" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="I251" t="s">
-        <v>84</v>
+        <v>135</v>
       </c>
       <c r="J251" s="1">
         <v>3010101</v>
@@ -8961,16 +9084,16 @@
         <v>30</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>158</v>
+        <v>62</v>
       </c>
       <c r="G252">
         <v>30</v>
       </c>
       <c r="H252" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="I252" t="s">
-        <v>84</v>
+        <v>135</v>
       </c>
       <c r="J252" s="1">
         <v>3010101</v>
@@ -8993,16 +9116,16 @@
         <v>31</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>159</v>
+        <v>63</v>
       </c>
       <c r="G253">
         <v>30</v>
       </c>
       <c r="H253" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="I253" t="s">
-        <v>86</v>
+        <v>136</v>
       </c>
       <c r="J253" s="1">
         <v>3010101</v>
@@ -9025,16 +9148,16 @@
         <v>31</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>159</v>
+        <v>63</v>
       </c>
       <c r="G254">
         <v>30</v>
       </c>
       <c r="H254" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="I254" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="J254" s="1">
         <v>3030101</v>
@@ -9057,16 +9180,16 @@
         <v>31</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>159</v>
+        <v>63</v>
       </c>
       <c r="G255">
         <v>30</v>
       </c>
       <c r="H255" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="I255" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="J255" s="1">
         <v>3030101</v>
@@ -9089,16 +9212,16 @@
         <v>31</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>159</v>
+        <v>63</v>
       </c>
       <c r="G256">
         <v>30</v>
       </c>
       <c r="H256" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="I256" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="J256" s="1">
         <v>3030101</v>
@@ -9121,16 +9244,16 @@
         <v>31</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>159</v>
+        <v>63</v>
       </c>
       <c r="G257">
         <v>30</v>
       </c>
       <c r="H257" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="I257" t="s">
-        <v>86</v>
+        <v>136</v>
       </c>
       <c r="J257" s="1">
         <v>3010101</v>
@@ -9153,16 +9276,16 @@
         <v>31</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>159</v>
+        <v>63</v>
       </c>
       <c r="G258">
         <v>30</v>
       </c>
       <c r="H258" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="I258" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="J258" s="1">
         <v>3030101</v>
@@ -9185,16 +9308,16 @@
         <v>31</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>159</v>
+        <v>63</v>
       </c>
       <c r="G259">
         <v>30</v>
       </c>
       <c r="H259" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="I259" t="s">
-        <v>86</v>
+        <v>136</v>
       </c>
       <c r="J259" s="1">
         <v>3010101</v>
@@ -9217,16 +9340,16 @@
         <v>31</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>159</v>
+        <v>63</v>
       </c>
       <c r="G260">
         <v>30</v>
       </c>
       <c r="H260" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="I260" t="s">
-        <v>86</v>
+        <v>136</v>
       </c>
       <c r="J260" s="1">
         <v>3010101</v>
@@ -9249,16 +9372,16 @@
         <v>32</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>160</v>
+        <v>64</v>
       </c>
       <c r="G261">
         <v>30</v>
       </c>
       <c r="H261" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="I261" t="s">
-        <v>88</v>
+        <v>138</v>
       </c>
       <c r="J261" s="1">
         <v>3010101</v>
@@ -9281,16 +9404,16 @@
         <v>32</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>160</v>
+        <v>64</v>
       </c>
       <c r="G262">
         <v>30</v>
       </c>
       <c r="H262" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="I262" t="s">
-        <v>89</v>
+        <v>137</v>
       </c>
       <c r="J262" s="1">
         <v>3030101</v>
@@ -9313,16 +9436,16 @@
         <v>32</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>160</v>
+        <v>64</v>
       </c>
       <c r="G263">
         <v>30</v>
       </c>
       <c r="H263" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="I263" t="s">
-        <v>89</v>
+        <v>137</v>
       </c>
       <c r="J263" s="1">
         <v>3030101</v>
@@ -9345,16 +9468,16 @@
         <v>32</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>160</v>
+        <v>64</v>
       </c>
       <c r="G264">
         <v>30</v>
       </c>
       <c r="H264" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="I264" t="s">
-        <v>89</v>
+        <v>137</v>
       </c>
       <c r="J264" s="1">
         <v>3030101</v>
@@ -9377,16 +9500,16 @@
         <v>32</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>160</v>
+        <v>64</v>
       </c>
       <c r="G265">
         <v>30</v>
       </c>
       <c r="H265" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="I265" t="s">
-        <v>88</v>
+        <v>138</v>
       </c>
       <c r="J265" s="1">
         <v>3010101</v>
@@ -9409,16 +9532,16 @@
         <v>32</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>160</v>
+        <v>64</v>
       </c>
       <c r="G266">
         <v>30</v>
       </c>
       <c r="H266" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="I266" t="s">
-        <v>89</v>
+        <v>137</v>
       </c>
       <c r="J266" s="1">
         <v>3030101</v>
@@ -9441,16 +9564,16 @@
         <v>32</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>160</v>
+        <v>64</v>
       </c>
       <c r="G267">
         <v>30</v>
       </c>
       <c r="H267" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="I267" t="s">
-        <v>88</v>
+        <v>138</v>
       </c>
       <c r="J267" s="1">
         <v>3010101</v>
@@ -9473,16 +9596,16 @@
         <v>32</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>160</v>
+        <v>64</v>
       </c>
       <c r="G268">
         <v>30</v>
       </c>
       <c r="H268" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="I268" t="s">
-        <v>88</v>
+        <v>138</v>
       </c>
       <c r="J268" s="1">
         <v>3010101</v>
@@ -9505,16 +9628,16 @@
         <v>33</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>161</v>
+        <v>65</v>
       </c>
       <c r="G269">
         <v>30</v>
       </c>
       <c r="H269" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="I269" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="J269" s="1">
         <v>3010101</v>
@@ -9537,16 +9660,16 @@
         <v>33</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>161</v>
+        <v>65</v>
       </c>
       <c r="G270">
         <v>30</v>
       </c>
       <c r="H270" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="I270" t="s">
-        <v>91</v>
+        <v>140</v>
       </c>
       <c r="J270" s="1">
         <v>3030101</v>
@@ -9569,16 +9692,16 @@
         <v>33</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>161</v>
+        <v>65</v>
       </c>
       <c r="G271">
         <v>30</v>
       </c>
       <c r="H271" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="I271" t="s">
-        <v>91</v>
+        <v>140</v>
       </c>
       <c r="J271" s="1">
         <v>3030101</v>
@@ -9601,16 +9724,16 @@
         <v>33</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>161</v>
+        <v>65</v>
       </c>
       <c r="G272">
         <v>30</v>
       </c>
       <c r="H272" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="I272" t="s">
-        <v>91</v>
+        <v>140</v>
       </c>
       <c r="J272" s="1">
         <v>3030101</v>
@@ -9633,16 +9756,16 @@
         <v>33</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>161</v>
+        <v>65</v>
       </c>
       <c r="G273">
         <v>30</v>
       </c>
       <c r="H273" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="I273" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="J273" s="1">
         <v>3010101</v>
@@ -9665,16 +9788,16 @@
         <v>33</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>161</v>
+        <v>65</v>
       </c>
       <c r="G274">
         <v>30</v>
       </c>
       <c r="H274" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="I274" t="s">
-        <v>91</v>
+        <v>140</v>
       </c>
       <c r="J274" s="1">
         <v>3030101</v>
@@ -9697,16 +9820,16 @@
         <v>33</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>161</v>
+        <v>65</v>
       </c>
       <c r="G275">
         <v>30</v>
       </c>
       <c r="H275" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="I275" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="J275" s="1">
         <v>3010101</v>
@@ -9729,16 +9852,16 @@
         <v>33</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>161</v>
+        <v>65</v>
       </c>
       <c r="G276">
         <v>30</v>
       </c>
       <c r="H276" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="I276" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="J276" s="1">
         <v>3010101</v>
@@ -9761,16 +9884,16 @@
         <v>34</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>162</v>
+        <v>66</v>
       </c>
       <c r="G277">
         <v>30</v>
       </c>
       <c r="H277" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="I277" t="s">
-        <v>92</v>
+        <v>141</v>
       </c>
       <c r="J277" s="1">
         <v>3010101</v>
@@ -9793,16 +9916,16 @@
         <v>34</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>162</v>
+        <v>66</v>
       </c>
       <c r="G278">
         <v>30</v>
       </c>
       <c r="H278" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="I278" t="s">
-        <v>93</v>
+        <v>142</v>
       </c>
       <c r="J278" s="1">
         <v>3030101</v>
@@ -9825,16 +9948,16 @@
         <v>34</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>162</v>
+        <v>66</v>
       </c>
       <c r="G279">
         <v>30</v>
       </c>
       <c r="H279" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="I279" t="s">
-        <v>93</v>
+        <v>142</v>
       </c>
       <c r="J279" s="1">
         <v>3030101</v>
@@ -9857,16 +9980,16 @@
         <v>34</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>162</v>
+        <v>66</v>
       </c>
       <c r="G280">
         <v>30</v>
       </c>
       <c r="H280" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="I280" t="s">
-        <v>93</v>
+        <v>142</v>
       </c>
       <c r="J280" s="1">
         <v>3030101</v>
@@ -9889,16 +10012,16 @@
         <v>34</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>162</v>
+        <v>66</v>
       </c>
       <c r="G281">
         <v>30</v>
       </c>
       <c r="H281" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="I281" t="s">
-        <v>92</v>
+        <v>141</v>
       </c>
       <c r="J281" s="1">
         <v>3010101</v>
@@ -9921,16 +10044,16 @@
         <v>34</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>162</v>
+        <v>66</v>
       </c>
       <c r="G282">
         <v>30</v>
       </c>
       <c r="H282" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="I282" t="s">
-        <v>93</v>
+        <v>142</v>
       </c>
       <c r="J282" s="1">
         <v>3030101</v>
@@ -9953,16 +10076,16 @@
         <v>34</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>162</v>
+        <v>66</v>
       </c>
       <c r="G283">
         <v>30</v>
       </c>
       <c r="H283" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="I283" t="s">
-        <v>92</v>
+        <v>141</v>
       </c>
       <c r="J283" s="1">
         <v>3010101</v>
@@ -9985,16 +10108,16 @@
         <v>34</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>162</v>
+        <v>66</v>
       </c>
       <c r="G284">
         <v>30</v>
       </c>
       <c r="H284" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="I284" t="s">
-        <v>92</v>
+        <v>141</v>
       </c>
       <c r="J284" s="1">
         <v>3010101</v>
@@ -10017,16 +10140,16 @@
         <v>35</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>163</v>
+        <v>67</v>
       </c>
       <c r="G285">
         <v>30</v>
       </c>
       <c r="H285" t="s">
-        <v>179</v>
+        <v>205</v>
       </c>
       <c r="I285" t="s">
-        <v>94</v>
+        <v>143</v>
       </c>
       <c r="J285" s="1">
         <v>3010101</v>
@@ -10049,16 +10172,16 @@
         <v>35</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>163</v>
+        <v>67</v>
       </c>
       <c r="G286">
         <v>30</v>
       </c>
       <c r="H286" t="s">
-        <v>179</v>
+        <v>205</v>
       </c>
       <c r="I286" t="s">
-        <v>95</v>
+        <v>144</v>
       </c>
       <c r="J286" s="1">
         <v>3030101</v>
@@ -10081,16 +10204,16 @@
         <v>35</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>163</v>
+        <v>67</v>
       </c>
       <c r="G287">
         <v>30</v>
       </c>
       <c r="H287" t="s">
-        <v>179</v>
+        <v>205</v>
       </c>
       <c r="I287" t="s">
-        <v>95</v>
+        <v>144</v>
       </c>
       <c r="J287" s="1">
         <v>3030101</v>
@@ -10113,16 +10236,16 @@
         <v>35</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>163</v>
+        <v>67</v>
       </c>
       <c r="G288">
         <v>30</v>
       </c>
       <c r="H288" t="s">
-        <v>179</v>
+        <v>205</v>
       </c>
       <c r="I288" t="s">
-        <v>95</v>
+        <v>144</v>
       </c>
       <c r="J288" s="1">
         <v>3030101</v>
@@ -10145,16 +10268,16 @@
         <v>35</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>163</v>
+        <v>67</v>
       </c>
       <c r="G289">
         <v>30</v>
       </c>
       <c r="H289" t="s">
-        <v>179</v>
+        <v>205</v>
       </c>
       <c r="I289" t="s">
-        <v>94</v>
+        <v>143</v>
       </c>
       <c r="J289" s="1">
         <v>3010101</v>
@@ -10177,16 +10300,16 @@
         <v>35</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>163</v>
+        <v>67</v>
       </c>
       <c r="G290">
         <v>30</v>
       </c>
       <c r="H290" t="s">
-        <v>179</v>
+        <v>205</v>
       </c>
       <c r="I290" t="s">
-        <v>95</v>
+        <v>144</v>
       </c>
       <c r="J290" s="1">
         <v>3030101</v>
@@ -10209,16 +10332,16 @@
         <v>35</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>163</v>
+        <v>67</v>
       </c>
       <c r="G291">
         <v>30</v>
       </c>
       <c r="H291" t="s">
-        <v>179</v>
+        <v>205</v>
       </c>
       <c r="I291" t="s">
-        <v>94</v>
+        <v>143</v>
       </c>
       <c r="J291" s="1">
         <v>3010101</v>
@@ -10241,16 +10364,16 @@
         <v>35</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>163</v>
+        <v>67</v>
       </c>
       <c r="G292">
         <v>30</v>
       </c>
       <c r="H292" t="s">
-        <v>179</v>
+        <v>205</v>
       </c>
       <c r="I292" t="s">
-        <v>94</v>
+        <v>143</v>
       </c>
       <c r="J292" s="1">
         <v>3010101</v>
@@ -10273,16 +10396,16 @@
         <v>36</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>164</v>
+        <v>68</v>
       </c>
       <c r="G293">
         <v>30</v>
       </c>
       <c r="H293" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="I293" t="s">
-        <v>96</v>
+        <v>145</v>
       </c>
       <c r="J293" s="1">
         <v>3010101</v>
@@ -10305,16 +10428,16 @@
         <v>36</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>164</v>
+        <v>68</v>
       </c>
       <c r="G294">
         <v>30</v>
       </c>
       <c r="H294" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="I294" t="s">
-        <v>97</v>
+        <v>144</v>
       </c>
       <c r="J294" s="1">
         <v>3030101</v>
@@ -10337,16 +10460,16 @@
         <v>36</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>164</v>
+        <v>68</v>
       </c>
       <c r="G295">
         <v>30</v>
       </c>
       <c r="H295" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="I295" t="s">
-        <v>97</v>
+        <v>144</v>
       </c>
       <c r="J295" s="1">
         <v>3030101</v>
@@ -10369,16 +10492,16 @@
         <v>36</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>164</v>
+        <v>68</v>
       </c>
       <c r="G296">
         <v>30</v>
       </c>
       <c r="H296" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="I296" t="s">
-        <v>97</v>
+        <v>144</v>
       </c>
       <c r="J296" s="1">
         <v>3030101</v>
@@ -10401,16 +10524,16 @@
         <v>36</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>164</v>
+        <v>68</v>
       </c>
       <c r="G297">
         <v>30</v>
       </c>
       <c r="H297" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="I297" t="s">
-        <v>96</v>
+        <v>145</v>
       </c>
       <c r="J297" s="1">
         <v>3010101</v>
@@ -10433,16 +10556,16 @@
         <v>36</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>164</v>
+        <v>68</v>
       </c>
       <c r="G298">
         <v>30</v>
       </c>
       <c r="H298" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="I298" t="s">
-        <v>97</v>
+        <v>144</v>
       </c>
       <c r="J298" s="1">
         <v>3030101</v>
@@ -10465,16 +10588,16 @@
         <v>36</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>164</v>
+        <v>68</v>
       </c>
       <c r="G299">
         <v>30</v>
       </c>
       <c r="H299" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="I299" t="s">
-        <v>96</v>
+        <v>145</v>
       </c>
       <c r="J299" s="1">
         <v>3010101</v>
@@ -10497,16 +10620,16 @@
         <v>36</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>164</v>
+        <v>68</v>
       </c>
       <c r="G300">
         <v>30</v>
       </c>
       <c r="H300" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="I300" t="s">
-        <v>96</v>
+        <v>145</v>
       </c>
       <c r="J300" s="1">
         <v>3010101</v>
@@ -10529,16 +10652,16 @@
         <v>37</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>165</v>
+        <v>69</v>
       </c>
       <c r="G301">
         <v>30</v>
       </c>
       <c r="H301" t="s">
-        <v>179</v>
+        <v>207</v>
       </c>
       <c r="I301" t="s">
-        <v>98</v>
+        <v>146</v>
       </c>
       <c r="J301" s="1">
         <v>3010101</v>
@@ -10561,16 +10684,16 @@
         <v>37</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>165</v>
+        <v>69</v>
       </c>
       <c r="G302">
         <v>30</v>
       </c>
       <c r="H302" t="s">
-        <v>179</v>
+        <v>207</v>
       </c>
       <c r="I302" t="s">
-        <v>99</v>
+        <v>147</v>
       </c>
       <c r="J302" s="1">
         <v>3030101</v>
@@ -10593,16 +10716,16 @@
         <v>37</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>165</v>
+        <v>69</v>
       </c>
       <c r="G303">
         <v>30</v>
       </c>
       <c r="H303" t="s">
-        <v>179</v>
+        <v>207</v>
       </c>
       <c r="I303" t="s">
-        <v>99</v>
+        <v>147</v>
       </c>
       <c r="J303" s="1">
         <v>3030101</v>
@@ -10625,16 +10748,16 @@
         <v>37</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>165</v>
+        <v>69</v>
       </c>
       <c r="G304">
         <v>30</v>
       </c>
       <c r="H304" t="s">
-        <v>179</v>
+        <v>207</v>
       </c>
       <c r="I304" t="s">
-        <v>99</v>
+        <v>147</v>
       </c>
       <c r="J304" s="1">
         <v>3030101</v>
@@ -10657,16 +10780,16 @@
         <v>37</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>165</v>
+        <v>69</v>
       </c>
       <c r="G305">
         <v>30</v>
       </c>
       <c r="H305" t="s">
-        <v>179</v>
+        <v>207</v>
       </c>
       <c r="I305" t="s">
-        <v>98</v>
+        <v>146</v>
       </c>
       <c r="J305" s="1">
         <v>3010101</v>
@@ -10689,16 +10812,16 @@
         <v>37</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>165</v>
+        <v>69</v>
       </c>
       <c r="G306">
         <v>30</v>
       </c>
       <c r="H306" t="s">
-        <v>179</v>
+        <v>207</v>
       </c>
       <c r="I306" t="s">
-        <v>99</v>
+        <v>147</v>
       </c>
       <c r="J306" s="1">
         <v>3030101</v>
@@ -10721,16 +10844,16 @@
         <v>37</v>
       </c>
       <c r="F307" s="1" t="s">
-        <v>165</v>
+        <v>69</v>
       </c>
       <c r="G307">
         <v>30</v>
       </c>
       <c r="H307" t="s">
-        <v>179</v>
+        <v>207</v>
       </c>
       <c r="I307" t="s">
-        <v>98</v>
+        <v>146</v>
       </c>
       <c r="J307" s="1">
         <v>3010101</v>
@@ -10753,16 +10876,16 @@
         <v>37</v>
       </c>
       <c r="F308" s="1" t="s">
-        <v>165</v>
+        <v>69</v>
       </c>
       <c r="G308">
         <v>30</v>
       </c>
       <c r="H308" t="s">
-        <v>179</v>
+        <v>207</v>
       </c>
       <c r="I308" t="s">
-        <v>98</v>
+        <v>146</v>
       </c>
       <c r="J308" s="1">
         <v>3010101</v>
@@ -10785,16 +10908,16 @@
         <v>38</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>166</v>
+        <v>70</v>
       </c>
       <c r="G309">
         <v>30</v>
       </c>
       <c r="H309" t="s">
-        <v>179</v>
+        <v>208</v>
       </c>
       <c r="I309" t="s">
-        <v>100</v>
+        <v>148</v>
       </c>
       <c r="J309" s="1">
         <v>3010101</v>
@@ -10817,16 +10940,16 @@
         <v>38</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>166</v>
+        <v>70</v>
       </c>
       <c r="G310">
         <v>30</v>
       </c>
       <c r="H310" t="s">
-        <v>179</v>
+        <v>208</v>
       </c>
       <c r="I310" t="s">
-        <v>101</v>
+        <v>149</v>
       </c>
       <c r="J310" s="1">
         <v>3030101</v>
@@ -10849,16 +10972,16 @@
         <v>38</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>166</v>
+        <v>70</v>
       </c>
       <c r="G311">
         <v>30</v>
       </c>
       <c r="H311" t="s">
-        <v>179</v>
+        <v>208</v>
       </c>
       <c r="I311" t="s">
-        <v>101</v>
+        <v>149</v>
       </c>
       <c r="J311" s="1">
         <v>3030101</v>
@@ -10881,16 +11004,16 @@
         <v>38</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>166</v>
+        <v>70</v>
       </c>
       <c r="G312">
         <v>30</v>
       </c>
       <c r="H312" t="s">
-        <v>179</v>
+        <v>208</v>
       </c>
       <c r="I312" t="s">
-        <v>101</v>
+        <v>149</v>
       </c>
       <c r="J312" s="1">
         <v>3030101</v>
@@ -10913,16 +11036,16 @@
         <v>38</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>166</v>
+        <v>70</v>
       </c>
       <c r="G313">
         <v>30</v>
       </c>
       <c r="H313" t="s">
-        <v>179</v>
+        <v>208</v>
       </c>
       <c r="I313" t="s">
-        <v>100</v>
+        <v>148</v>
       </c>
       <c r="J313" s="1">
         <v>3010101</v>
@@ -10945,16 +11068,16 @@
         <v>38</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>166</v>
+        <v>70</v>
       </c>
       <c r="G314">
         <v>30</v>
       </c>
       <c r="H314" t="s">
-        <v>179</v>
+        <v>208</v>
       </c>
       <c r="I314" t="s">
-        <v>101</v>
+        <v>149</v>
       </c>
       <c r="J314" s="1">
         <v>3030101</v>
@@ -10977,16 +11100,16 @@
         <v>38</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>166</v>
+        <v>70</v>
       </c>
       <c r="G315">
         <v>30</v>
       </c>
       <c r="H315" t="s">
-        <v>179</v>
+        <v>208</v>
       </c>
       <c r="I315" t="s">
-        <v>100</v>
+        <v>148</v>
       </c>
       <c r="J315" s="1">
         <v>3010101</v>
@@ -11009,16 +11132,16 @@
         <v>38</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>166</v>
+        <v>70</v>
       </c>
       <c r="G316">
         <v>30</v>
       </c>
       <c r="H316" t="s">
-        <v>179</v>
+        <v>208</v>
       </c>
       <c r="I316" t="s">
-        <v>100</v>
+        <v>148</v>
       </c>
       <c r="J316" s="1">
         <v>3010101</v>
@@ -11041,16 +11164,16 @@
         <v>39</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>167</v>
+        <v>71</v>
       </c>
       <c r="G317">
         <v>30</v>
       </c>
       <c r="H317" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="I317" t="s">
-        <v>102</v>
+        <v>150</v>
       </c>
       <c r="J317" s="1">
         <v>3010101</v>
@@ -11073,16 +11196,16 @@
         <v>39</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>167</v>
+        <v>71</v>
       </c>
       <c r="G318">
         <v>30</v>
       </c>
       <c r="H318" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="I318" t="s">
-        <v>103</v>
+        <v>151</v>
       </c>
       <c r="J318" s="1">
         <v>3030101</v>
@@ -11105,16 +11228,16 @@
         <v>39</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>167</v>
+        <v>71</v>
       </c>
       <c r="G319">
         <v>30</v>
       </c>
       <c r="H319" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="I319" t="s">
-        <v>103</v>
+        <v>151</v>
       </c>
       <c r="J319" s="1">
         <v>3030101</v>
@@ -11137,16 +11260,16 @@
         <v>39</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>167</v>
+        <v>71</v>
       </c>
       <c r="G320">
         <v>30</v>
       </c>
       <c r="H320" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="I320" t="s">
-        <v>103</v>
+        <v>151</v>
       </c>
       <c r="J320" s="1">
         <v>3030101</v>
@@ -11169,16 +11292,16 @@
         <v>39</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>167</v>
+        <v>71</v>
       </c>
       <c r="G321">
         <v>30</v>
       </c>
       <c r="H321" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="I321" t="s">
-        <v>102</v>
+        <v>150</v>
       </c>
       <c r="J321" s="1">
         <v>3010101</v>
@@ -11201,16 +11324,16 @@
         <v>39</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>167</v>
+        <v>71</v>
       </c>
       <c r="G322">
         <v>30</v>
       </c>
       <c r="H322" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="I322" t="s">
-        <v>103</v>
+        <v>151</v>
       </c>
       <c r="J322" s="1">
         <v>3030101</v>
@@ -11233,16 +11356,16 @@
         <v>39</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>167</v>
+        <v>71</v>
       </c>
       <c r="G323">
         <v>30</v>
       </c>
       <c r="H323" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="I323" t="s">
-        <v>102</v>
+        <v>150</v>
       </c>
       <c r="J323" s="1">
         <v>3010101</v>
@@ -11265,16 +11388,16 @@
         <v>39</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>167</v>
+        <v>71</v>
       </c>
       <c r="G324">
         <v>30</v>
       </c>
       <c r="H324" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="I324" t="s">
-        <v>102</v>
+        <v>150</v>
       </c>
       <c r="J324" s="1">
         <v>3010101</v>
@@ -11297,16 +11420,16 @@
         <v>40</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>168</v>
+        <v>72</v>
       </c>
       <c r="G325">
         <v>40</v>
       </c>
       <c r="H325" t="s">
-        <v>179</v>
+        <v>210</v>
       </c>
       <c r="I325" t="s">
-        <v>104</v>
+        <v>152</v>
       </c>
       <c r="J325" s="1">
         <v>3010101</v>
@@ -11329,16 +11452,16 @@
         <v>40</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>168</v>
+        <v>72</v>
       </c>
       <c r="G326">
         <v>40</v>
       </c>
       <c r="H326" t="s">
-        <v>179</v>
+        <v>210</v>
       </c>
       <c r="I326" t="s">
-        <v>105</v>
+        <v>153</v>
       </c>
       <c r="J326" s="1">
         <v>3030101</v>
@@ -11361,16 +11484,16 @@
         <v>40</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>168</v>
+        <v>72</v>
       </c>
       <c r="G327">
         <v>40</v>
       </c>
       <c r="H327" t="s">
-        <v>179</v>
+        <v>210</v>
       </c>
       <c r="I327" t="s">
-        <v>105</v>
+        <v>153</v>
       </c>
       <c r="J327" s="1">
         <v>3030101</v>
@@ -11393,16 +11516,16 @@
         <v>40</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>168</v>
+        <v>72</v>
       </c>
       <c r="G328">
         <v>40</v>
       </c>
       <c r="H328" t="s">
-        <v>179</v>
+        <v>210</v>
       </c>
       <c r="I328" t="s">
-        <v>105</v>
+        <v>153</v>
       </c>
       <c r="J328" s="1">
         <v>3030101</v>
@@ -11425,16 +11548,16 @@
         <v>40</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>168</v>
+        <v>72</v>
       </c>
       <c r="G329">
         <v>40</v>
       </c>
       <c r="H329" t="s">
-        <v>179</v>
+        <v>210</v>
       </c>
       <c r="I329" t="s">
-        <v>104</v>
+        <v>152</v>
       </c>
       <c r="J329" s="1">
         <v>3010101</v>
@@ -11457,16 +11580,16 @@
         <v>40</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>168</v>
+        <v>72</v>
       </c>
       <c r="G330">
         <v>40</v>
       </c>
       <c r="H330" t="s">
-        <v>179</v>
+        <v>210</v>
       </c>
       <c r="I330" t="s">
-        <v>105</v>
+        <v>153</v>
       </c>
       <c r="J330" s="1">
         <v>3030101</v>
@@ -11489,16 +11612,16 @@
         <v>40</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>168</v>
+        <v>72</v>
       </c>
       <c r="G331">
         <v>40</v>
       </c>
       <c r="H331" t="s">
-        <v>179</v>
+        <v>210</v>
       </c>
       <c r="I331" t="s">
-        <v>104</v>
+        <v>152</v>
       </c>
       <c r="J331" s="1">
         <v>3010101</v>
@@ -11521,16 +11644,16 @@
         <v>40</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>168</v>
+        <v>72</v>
       </c>
       <c r="G332">
         <v>40</v>
       </c>
       <c r="H332" t="s">
-        <v>179</v>
+        <v>210</v>
       </c>
       <c r="I332" t="s">
-        <v>104</v>
+        <v>152</v>
       </c>
       <c r="J332" s="1">
         <v>3010101</v>
@@ -11553,16 +11676,16 @@
         <v>41</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>169</v>
+        <v>73</v>
       </c>
       <c r="G333">
         <v>40</v>
       </c>
       <c r="H333" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="I333" t="s">
-        <v>106</v>
+        <v>154</v>
       </c>
       <c r="J333" s="1">
         <v>3010101</v>
@@ -11585,16 +11708,16 @@
         <v>41</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>169</v>
+        <v>73</v>
       </c>
       <c r="G334">
         <v>40</v>
       </c>
       <c r="H334" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="I334" t="s">
-        <v>107</v>
+        <v>155</v>
       </c>
       <c r="J334" s="1">
         <v>3030101</v>
@@ -11617,16 +11740,16 @@
         <v>41</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>169</v>
+        <v>73</v>
       </c>
       <c r="G335">
         <v>40</v>
       </c>
       <c r="H335" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="I335" t="s">
-        <v>107</v>
+        <v>155</v>
       </c>
       <c r="J335" s="1">
         <v>3030101</v>
@@ -11649,16 +11772,16 @@
         <v>41</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>169</v>
+        <v>73</v>
       </c>
       <c r="G336">
         <v>40</v>
       </c>
       <c r="H336" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="I336" t="s">
-        <v>107</v>
+        <v>155</v>
       </c>
       <c r="J336" s="1">
         <v>3030101</v>
@@ -11681,16 +11804,16 @@
         <v>41</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>169</v>
+        <v>73</v>
       </c>
       <c r="G337">
         <v>40</v>
       </c>
       <c r="H337" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="I337" t="s">
-        <v>106</v>
+        <v>154</v>
       </c>
       <c r="J337" s="1">
         <v>3010101</v>
@@ -11713,16 +11836,16 @@
         <v>41</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>169</v>
+        <v>73</v>
       </c>
       <c r="G338">
         <v>40</v>
       </c>
       <c r="H338" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="I338" t="s">
-        <v>107</v>
+        <v>155</v>
       </c>
       <c r="J338" s="1">
         <v>3030101</v>
@@ -11745,16 +11868,16 @@
         <v>41</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>169</v>
+        <v>73</v>
       </c>
       <c r="G339">
         <v>40</v>
       </c>
       <c r="H339" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="I339" t="s">
-        <v>106</v>
+        <v>154</v>
       </c>
       <c r="J339" s="1">
         <v>3010101</v>
@@ -11777,16 +11900,16 @@
         <v>41</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>169</v>
+        <v>73</v>
       </c>
       <c r="G340">
         <v>40</v>
       </c>
       <c r="H340" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="I340" t="s">
-        <v>106</v>
+        <v>154</v>
       </c>
       <c r="J340" s="1">
         <v>3010101</v>
@@ -11809,16 +11932,16 @@
         <v>42</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>170</v>
+        <v>74</v>
       </c>
       <c r="G341">
         <v>40</v>
       </c>
       <c r="H341" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="I341" t="s">
-        <v>108</v>
+        <v>156</v>
       </c>
       <c r="J341" s="1">
         <v>3010101</v>
@@ -11841,16 +11964,16 @@
         <v>42</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>170</v>
+        <v>74</v>
       </c>
       <c r="G342">
         <v>40</v>
       </c>
       <c r="H342" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="I342" t="s">
-        <v>109</v>
+        <v>157</v>
       </c>
       <c r="J342" s="1">
         <v>3030101</v>
@@ -11873,16 +11996,16 @@
         <v>42</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>170</v>
+        <v>74</v>
       </c>
       <c r="G343">
         <v>40</v>
       </c>
       <c r="H343" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="I343" t="s">
-        <v>109</v>
+        <v>157</v>
       </c>
       <c r="J343" s="1">
         <v>3030101</v>
@@ -11905,16 +12028,16 @@
         <v>42</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>170</v>
+        <v>74</v>
       </c>
       <c r="G344">
         <v>40</v>
       </c>
       <c r="H344" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="I344" t="s">
-        <v>109</v>
+        <v>157</v>
       </c>
       <c r="J344" s="1">
         <v>3030101</v>
@@ -11937,16 +12060,16 @@
         <v>42</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>170</v>
+        <v>74</v>
       </c>
       <c r="G345">
         <v>40</v>
       </c>
       <c r="H345" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="I345" t="s">
-        <v>108</v>
+        <v>156</v>
       </c>
       <c r="J345" s="1">
         <v>3010101</v>
@@ -11969,16 +12092,16 @@
         <v>42</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>170</v>
+        <v>74</v>
       </c>
       <c r="G346">
         <v>40</v>
       </c>
       <c r="H346" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="I346" t="s">
-        <v>109</v>
+        <v>157</v>
       </c>
       <c r="J346" s="1">
         <v>3030101</v>
@@ -12001,16 +12124,16 @@
         <v>42</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>170</v>
+        <v>74</v>
       </c>
       <c r="G347">
         <v>40</v>
       </c>
       <c r="H347" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="I347" t="s">
-        <v>108</v>
+        <v>156</v>
       </c>
       <c r="J347" s="1">
         <v>3010101</v>
@@ -12033,16 +12156,16 @@
         <v>42</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>170</v>
+        <v>74</v>
       </c>
       <c r="G348">
         <v>40</v>
       </c>
       <c r="H348" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="I348" t="s">
-        <v>108</v>
+        <v>156</v>
       </c>
       <c r="J348" s="1">
         <v>3010101</v>
@@ -12065,16 +12188,16 @@
         <v>43</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>171</v>
+        <v>75</v>
       </c>
       <c r="G349">
         <v>40</v>
       </c>
       <c r="H349" t="s">
-        <v>179</v>
+        <v>213</v>
       </c>
       <c r="I349" t="s">
-        <v>110</v>
+        <v>158</v>
       </c>
       <c r="J349" s="1">
         <v>3010101</v>
@@ -12097,16 +12220,16 @@
         <v>43</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>171</v>
+        <v>75</v>
       </c>
       <c r="G350">
         <v>40</v>
       </c>
       <c r="H350" t="s">
-        <v>179</v>
+        <v>213</v>
       </c>
       <c r="I350" t="s">
-        <v>111</v>
+        <v>159</v>
       </c>
       <c r="J350" s="1">
         <v>3030101</v>
@@ -12129,16 +12252,16 @@
         <v>43</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>171</v>
+        <v>75</v>
       </c>
       <c r="G351">
         <v>40</v>
       </c>
       <c r="H351" t="s">
-        <v>179</v>
+        <v>213</v>
       </c>
       <c r="I351" t="s">
-        <v>111</v>
+        <v>159</v>
       </c>
       <c r="J351" s="1">
         <v>3030101</v>
@@ -12161,16 +12284,16 @@
         <v>43</v>
       </c>
       <c r="F352" s="1" t="s">
-        <v>171</v>
+        <v>75</v>
       </c>
       <c r="G352">
         <v>40</v>
       </c>
       <c r="H352" t="s">
-        <v>179</v>
+        <v>213</v>
       </c>
       <c r="I352" t="s">
-        <v>111</v>
+        <v>159</v>
       </c>
       <c r="J352" s="1">
         <v>3030101</v>
@@ -12193,16 +12316,16 @@
         <v>43</v>
       </c>
       <c r="F353" s="1" t="s">
-        <v>171</v>
+        <v>75</v>
       </c>
       <c r="G353">
         <v>40</v>
       </c>
       <c r="H353" t="s">
-        <v>179</v>
+        <v>213</v>
       </c>
       <c r="I353" t="s">
-        <v>110</v>
+        <v>158</v>
       </c>
       <c r="J353" s="1">
         <v>3010101</v>
@@ -12225,16 +12348,16 @@
         <v>43</v>
       </c>
       <c r="F354" s="1" t="s">
-        <v>171</v>
+        <v>75</v>
       </c>
       <c r="G354">
         <v>40</v>
       </c>
       <c r="H354" t="s">
-        <v>179</v>
+        <v>213</v>
       </c>
       <c r="I354" t="s">
-        <v>111</v>
+        <v>159</v>
       </c>
       <c r="J354" s="1">
         <v>3030101</v>
@@ -12257,16 +12380,16 @@
         <v>43</v>
       </c>
       <c r="F355" s="1" t="s">
-        <v>171</v>
+        <v>75</v>
       </c>
       <c r="G355">
         <v>40</v>
       </c>
       <c r="H355" t="s">
-        <v>179</v>
+        <v>213</v>
       </c>
       <c r="I355" t="s">
-        <v>110</v>
+        <v>158</v>
       </c>
       <c r="J355" s="1">
         <v>3010101</v>
@@ -12289,16 +12412,16 @@
         <v>43</v>
       </c>
       <c r="F356" s="1" t="s">
-        <v>171</v>
+        <v>75</v>
       </c>
       <c r="G356">
         <v>40</v>
       </c>
       <c r="H356" t="s">
-        <v>179</v>
+        <v>213</v>
       </c>
       <c r="I356" t="s">
-        <v>110</v>
+        <v>158</v>
       </c>
       <c r="J356" s="1">
         <v>3010101</v>
@@ -12321,16 +12444,16 @@
         <v>44</v>
       </c>
       <c r="F357" s="1" t="s">
-        <v>172</v>
+        <v>76</v>
       </c>
       <c r="G357">
         <v>40</v>
       </c>
       <c r="H357" t="s">
-        <v>179</v>
+        <v>214</v>
       </c>
       <c r="I357" t="s">
-        <v>112</v>
+        <v>160</v>
       </c>
       <c r="J357" s="1">
         <v>3010101</v>
@@ -12353,16 +12476,16 @@
         <v>44</v>
       </c>
       <c r="F358" s="1" t="s">
-        <v>172</v>
+        <v>76</v>
       </c>
       <c r="G358">
         <v>40</v>
       </c>
       <c r="H358" t="s">
-        <v>179</v>
+        <v>214</v>
       </c>
       <c r="I358" t="s">
-        <v>113</v>
+        <v>161</v>
       </c>
       <c r="J358" s="1">
         <v>3030101</v>
@@ -12385,16 +12508,16 @@
         <v>44</v>
       </c>
       <c r="F359" s="1" t="s">
-        <v>172</v>
+        <v>76</v>
       </c>
       <c r="G359">
         <v>40</v>
       </c>
       <c r="H359" t="s">
-        <v>179</v>
+        <v>214</v>
       </c>
       <c r="I359" t="s">
-        <v>113</v>
+        <v>161</v>
       </c>
       <c r="J359" s="1">
         <v>3030101</v>
@@ -12417,16 +12540,16 @@
         <v>44</v>
       </c>
       <c r="F360" s="1" t="s">
-        <v>172</v>
+        <v>76</v>
       </c>
       <c r="G360">
         <v>40</v>
       </c>
       <c r="H360" t="s">
-        <v>179</v>
+        <v>214</v>
       </c>
       <c r="I360" t="s">
-        <v>113</v>
+        <v>161</v>
       </c>
       <c r="J360" s="1">
         <v>3030101</v>
@@ -12449,16 +12572,16 @@
         <v>44</v>
       </c>
       <c r="F361" s="1" t="s">
-        <v>172</v>
+        <v>76</v>
       </c>
       <c r="G361">
         <v>40</v>
       </c>
       <c r="H361" t="s">
-        <v>179</v>
+        <v>214</v>
       </c>
       <c r="I361" t="s">
-        <v>112</v>
+        <v>160</v>
       </c>
       <c r="J361" s="1">
         <v>3010101</v>
@@ -12481,16 +12604,16 @@
         <v>44</v>
       </c>
       <c r="F362" s="1" t="s">
-        <v>172</v>
+        <v>76</v>
       </c>
       <c r="G362">
         <v>40</v>
       </c>
       <c r="H362" t="s">
-        <v>179</v>
+        <v>214</v>
       </c>
       <c r="I362" t="s">
-        <v>113</v>
+        <v>161</v>
       </c>
       <c r="J362" s="1">
         <v>3030101</v>
@@ -12513,16 +12636,16 @@
         <v>44</v>
       </c>
       <c r="F363" s="1" t="s">
-        <v>172</v>
+        <v>76</v>
       </c>
       <c r="G363">
         <v>40</v>
       </c>
       <c r="H363" t="s">
-        <v>179</v>
+        <v>214</v>
       </c>
       <c r="I363" t="s">
-        <v>112</v>
+        <v>160</v>
       </c>
       <c r="J363" s="1">
         <v>3010101</v>
@@ -12545,16 +12668,16 @@
         <v>44</v>
       </c>
       <c r="F364" s="1" t="s">
-        <v>172</v>
+        <v>76</v>
       </c>
       <c r="G364">
         <v>40</v>
       </c>
       <c r="H364" t="s">
-        <v>179</v>
+        <v>214</v>
       </c>
       <c r="I364" t="s">
-        <v>112</v>
+        <v>160</v>
       </c>
       <c r="J364" s="1">
         <v>3010101</v>
@@ -12577,16 +12700,16 @@
         <v>45</v>
       </c>
       <c r="F365" s="1" t="s">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="G365">
         <v>40</v>
       </c>
       <c r="H365" t="s">
-        <v>179</v>
+        <v>215</v>
       </c>
       <c r="I365" t="s">
-        <v>114</v>
+        <v>162</v>
       </c>
       <c r="J365" s="1">
         <v>3010101</v>
@@ -12609,16 +12732,16 @@
         <v>45</v>
       </c>
       <c r="F366" s="1" t="s">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="G366">
         <v>40</v>
       </c>
       <c r="H366" t="s">
-        <v>179</v>
+        <v>215</v>
       </c>
       <c r="I366" t="s">
-        <v>115</v>
+        <v>163</v>
       </c>
       <c r="J366" s="1">
         <v>3030101</v>
@@ -12641,16 +12764,16 @@
         <v>45</v>
       </c>
       <c r="F367" s="1" t="s">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="G367">
         <v>40</v>
       </c>
       <c r="H367" t="s">
-        <v>179</v>
+        <v>215</v>
       </c>
       <c r="I367" t="s">
-        <v>115</v>
+        <v>163</v>
       </c>
       <c r="J367" s="1">
         <v>3030101</v>
@@ -12673,16 +12796,16 @@
         <v>45</v>
       </c>
       <c r="F368" s="1" t="s">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="G368">
         <v>40</v>
       </c>
       <c r="H368" t="s">
-        <v>179</v>
+        <v>215</v>
       </c>
       <c r="I368" t="s">
-        <v>115</v>
+        <v>163</v>
       </c>
       <c r="J368" s="1">
         <v>3030101</v>
@@ -12705,16 +12828,16 @@
         <v>45</v>
       </c>
       <c r="F369" s="1" t="s">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="G369">
         <v>40</v>
       </c>
       <c r="H369" t="s">
-        <v>179</v>
+        <v>215</v>
       </c>
       <c r="I369" t="s">
-        <v>114</v>
+        <v>162</v>
       </c>
       <c r="J369" s="1">
         <v>3010101</v>
@@ -12737,16 +12860,16 @@
         <v>45</v>
       </c>
       <c r="F370" s="1" t="s">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="G370">
         <v>40</v>
       </c>
       <c r="H370" t="s">
-        <v>179</v>
+        <v>215</v>
       </c>
       <c r="I370" t="s">
-        <v>115</v>
+        <v>163</v>
       </c>
       <c r="J370" s="1">
         <v>3030101</v>
@@ -12769,16 +12892,16 @@
         <v>45</v>
       </c>
       <c r="F371" s="1" t="s">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="G371">
         <v>40</v>
       </c>
       <c r="H371" t="s">
-        <v>179</v>
+        <v>215</v>
       </c>
       <c r="I371" t="s">
-        <v>114</v>
+        <v>162</v>
       </c>
       <c r="J371" s="1">
         <v>3010101</v>
@@ -12801,16 +12924,16 @@
         <v>45</v>
       </c>
       <c r="F372" s="1" t="s">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="G372">
         <v>40</v>
       </c>
       <c r="H372" t="s">
-        <v>179</v>
+        <v>215</v>
       </c>
       <c r="I372" t="s">
-        <v>114</v>
+        <v>162</v>
       </c>
       <c r="J372" s="1">
         <v>3010101</v>
@@ -12833,16 +12956,16 @@
         <v>46</v>
       </c>
       <c r="F373" s="1" t="s">
-        <v>174</v>
+        <v>78</v>
       </c>
       <c r="G373">
         <v>40</v>
       </c>
       <c r="H373" t="s">
-        <v>179</v>
+        <v>216</v>
       </c>
       <c r="I373" t="s">
-        <v>116</v>
+        <v>164</v>
       </c>
       <c r="J373" s="1">
         <v>3010101</v>
@@ -12865,16 +12988,16 @@
         <v>46</v>
       </c>
       <c r="F374" s="1" t="s">
-        <v>174</v>
+        <v>78</v>
       </c>
       <c r="G374">
         <v>40</v>
       </c>
       <c r="H374" t="s">
-        <v>179</v>
+        <v>216</v>
       </c>
       <c r="I374" t="s">
-        <v>117</v>
+        <v>165</v>
       </c>
       <c r="J374" s="1">
         <v>3030101</v>
@@ -12897,16 +13020,16 @@
         <v>46</v>
       </c>
       <c r="F375" s="1" t="s">
-        <v>174</v>
+        <v>78</v>
       </c>
       <c r="G375">
         <v>40</v>
       </c>
       <c r="H375" t="s">
-        <v>179</v>
+        <v>216</v>
       </c>
       <c r="I375" t="s">
-        <v>117</v>
+        <v>165</v>
       </c>
       <c r="J375" s="1">
         <v>3030101</v>
@@ -12929,16 +13052,16 @@
         <v>46</v>
       </c>
       <c r="F376" s="1" t="s">
-        <v>174</v>
+        <v>78</v>
       </c>
       <c r="G376">
         <v>40</v>
       </c>
       <c r="H376" t="s">
-        <v>179</v>
+        <v>216</v>
       </c>
       <c r="I376" t="s">
-        <v>117</v>
+        <v>165</v>
       </c>
       <c r="J376" s="1">
         <v>3030101</v>
@@ -12961,16 +13084,16 @@
         <v>46</v>
       </c>
       <c r="F377" s="1" t="s">
-        <v>174</v>
+        <v>78</v>
       </c>
       <c r="G377">
         <v>40</v>
       </c>
       <c r="H377" t="s">
-        <v>179</v>
+        <v>216</v>
       </c>
       <c r="I377" t="s">
-        <v>116</v>
+        <v>164</v>
       </c>
       <c r="J377" s="1">
         <v>3010101</v>
@@ -12993,16 +13116,16 @@
         <v>46</v>
       </c>
       <c r="F378" s="1" t="s">
-        <v>174</v>
+        <v>78</v>
       </c>
       <c r="G378">
         <v>40</v>
       </c>
       <c r="H378" t="s">
-        <v>179</v>
+        <v>216</v>
       </c>
       <c r="I378" t="s">
-        <v>117</v>
+        <v>165</v>
       </c>
       <c r="J378" s="1">
         <v>3030101</v>
@@ -13025,16 +13148,16 @@
         <v>46</v>
       </c>
       <c r="F379" s="1" t="s">
-        <v>174</v>
+        <v>78</v>
       </c>
       <c r="G379">
         <v>40</v>
       </c>
       <c r="H379" t="s">
-        <v>179</v>
+        <v>216</v>
       </c>
       <c r="I379" t="s">
-        <v>116</v>
+        <v>164</v>
       </c>
       <c r="J379" s="1">
         <v>3010101</v>
@@ -13057,16 +13180,16 @@
         <v>46</v>
       </c>
       <c r="F380" s="1" t="s">
-        <v>174</v>
+        <v>78</v>
       </c>
       <c r="G380">
         <v>40</v>
       </c>
       <c r="H380" t="s">
-        <v>179</v>
+        <v>216</v>
       </c>
       <c r="I380" t="s">
-        <v>116</v>
+        <v>164</v>
       </c>
       <c r="J380" s="1">
         <v>3010101</v>
@@ -13089,16 +13212,16 @@
         <v>47</v>
       </c>
       <c r="F381" s="1" t="s">
-        <v>175</v>
+        <v>79</v>
       </c>
       <c r="G381">
         <v>40</v>
       </c>
       <c r="H381" t="s">
-        <v>179</v>
+        <v>217</v>
       </c>
       <c r="I381" t="s">
-        <v>118</v>
+        <v>164</v>
       </c>
       <c r="J381" s="1">
         <v>3010101</v>
@@ -13121,16 +13244,16 @@
         <v>47</v>
       </c>
       <c r="F382" s="1" t="s">
-        <v>175</v>
+        <v>79</v>
       </c>
       <c r="G382">
         <v>40</v>
       </c>
       <c r="H382" t="s">
-        <v>179</v>
+        <v>217</v>
       </c>
       <c r="I382" t="s">
-        <v>119</v>
+        <v>166</v>
       </c>
       <c r="J382" s="1">
         <v>3030101</v>
@@ -13153,16 +13276,16 @@
         <v>47</v>
       </c>
       <c r="F383" s="1" t="s">
-        <v>175</v>
+        <v>79</v>
       </c>
       <c r="G383">
         <v>40</v>
       </c>
       <c r="H383" t="s">
-        <v>179</v>
+        <v>217</v>
       </c>
       <c r="I383" t="s">
-        <v>119</v>
+        <v>166</v>
       </c>
       <c r="J383" s="1">
         <v>3030101</v>
@@ -13185,16 +13308,16 @@
         <v>47</v>
       </c>
       <c r="F384" s="1" t="s">
-        <v>175</v>
+        <v>79</v>
       </c>
       <c r="G384">
         <v>40</v>
       </c>
       <c r="H384" t="s">
-        <v>179</v>
+        <v>217</v>
       </c>
       <c r="I384" t="s">
-        <v>119</v>
+        <v>166</v>
       </c>
       <c r="J384" s="1">
         <v>3030101</v>
@@ -13217,16 +13340,16 @@
         <v>47</v>
       </c>
       <c r="F385" s="1" t="s">
-        <v>175</v>
+        <v>79</v>
       </c>
       <c r="G385">
         <v>40</v>
       </c>
       <c r="H385" t="s">
-        <v>179</v>
+        <v>217</v>
       </c>
       <c r="I385" t="s">
-        <v>118</v>
+        <v>164</v>
       </c>
       <c r="J385" s="1">
         <v>3010101</v>
@@ -13249,16 +13372,16 @@
         <v>47</v>
       </c>
       <c r="F386" s="1" t="s">
-        <v>175</v>
+        <v>79</v>
       </c>
       <c r="G386">
         <v>40</v>
       </c>
       <c r="H386" t="s">
-        <v>179</v>
+        <v>217</v>
       </c>
       <c r="I386" t="s">
-        <v>119</v>
+        <v>166</v>
       </c>
       <c r="J386" s="1">
         <v>3030101</v>
@@ -13281,16 +13404,16 @@
         <v>47</v>
       </c>
       <c r="F387" s="1" t="s">
-        <v>175</v>
+        <v>79</v>
       </c>
       <c r="G387">
         <v>40</v>
       </c>
       <c r="H387" t="s">
-        <v>179</v>
+        <v>217</v>
       </c>
       <c r="I387" t="s">
-        <v>118</v>
+        <v>164</v>
       </c>
       <c r="J387" s="1">
         <v>3010101</v>
@@ -13313,16 +13436,16 @@
         <v>47</v>
       </c>
       <c r="F388" s="1" t="s">
-        <v>175</v>
+        <v>79</v>
       </c>
       <c r="G388">
         <v>40</v>
       </c>
       <c r="H388" t="s">
-        <v>179</v>
+        <v>217</v>
       </c>
       <c r="I388" t="s">
-        <v>118</v>
+        <v>164</v>
       </c>
       <c r="J388" s="1">
         <v>3010101</v>
@@ -13345,16 +13468,16 @@
         <v>48</v>
       </c>
       <c r="F389" s="1" t="s">
-        <v>176</v>
+        <v>80</v>
       </c>
       <c r="G389">
         <v>40</v>
       </c>
       <c r="H389" t="s">
-        <v>179</v>
+        <v>218</v>
       </c>
       <c r="I389" t="s">
-        <v>120</v>
+        <v>167</v>
       </c>
       <c r="J389" s="1">
         <v>3010101</v>
@@ -13377,16 +13500,16 @@
         <v>48</v>
       </c>
       <c r="F390" s="1" t="s">
-        <v>176</v>
+        <v>80</v>
       </c>
       <c r="G390">
         <v>40</v>
       </c>
       <c r="H390" t="s">
-        <v>179</v>
+        <v>218</v>
       </c>
       <c r="I390" t="s">
-        <v>121</v>
+        <v>168</v>
       </c>
       <c r="J390" s="1">
         <v>3030101</v>
@@ -13409,16 +13532,16 @@
         <v>48</v>
       </c>
       <c r="F391" s="1" t="s">
-        <v>176</v>
+        <v>80</v>
       </c>
       <c r="G391">
         <v>40</v>
       </c>
       <c r="H391" t="s">
-        <v>179</v>
+        <v>218</v>
       </c>
       <c r="I391" t="s">
-        <v>121</v>
+        <v>168</v>
       </c>
       <c r="J391" s="1">
         <v>3030101</v>
@@ -13441,16 +13564,16 @@
         <v>48</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>176</v>
+        <v>80</v>
       </c>
       <c r="G392">
         <v>40</v>
       </c>
       <c r="H392" t="s">
-        <v>179</v>
+        <v>218</v>
       </c>
       <c r="I392" t="s">
-        <v>121</v>
+        <v>168</v>
       </c>
       <c r="J392" s="1">
         <v>3030101</v>
@@ -13473,16 +13596,16 @@
         <v>48</v>
       </c>
       <c r="F393" s="1" t="s">
-        <v>176</v>
+        <v>80</v>
       </c>
       <c r="G393">
         <v>40</v>
       </c>
       <c r="H393" t="s">
-        <v>179</v>
+        <v>218</v>
       </c>
       <c r="I393" t="s">
-        <v>120</v>
+        <v>167</v>
       </c>
       <c r="J393" s="1">
         <v>3010101</v>
@@ -13505,16 +13628,16 @@
         <v>48</v>
       </c>
       <c r="F394" s="1" t="s">
-        <v>176</v>
+        <v>80</v>
       </c>
       <c r="G394">
         <v>40</v>
       </c>
       <c r="H394" t="s">
-        <v>179</v>
+        <v>218</v>
       </c>
       <c r="I394" t="s">
-        <v>121</v>
+        <v>168</v>
       </c>
       <c r="J394" s="1">
         <v>3030101</v>
@@ -13537,16 +13660,16 @@
         <v>48</v>
       </c>
       <c r="F395" s="1" t="s">
-        <v>176</v>
+        <v>80</v>
       </c>
       <c r="G395">
         <v>40</v>
       </c>
       <c r="H395" t="s">
-        <v>179</v>
+        <v>218</v>
       </c>
       <c r="I395" t="s">
-        <v>120</v>
+        <v>167</v>
       </c>
       <c r="J395" s="1">
         <v>3010101</v>
@@ -13569,16 +13692,16 @@
         <v>48</v>
       </c>
       <c r="F396" s="1" t="s">
-        <v>176</v>
+        <v>80</v>
       </c>
       <c r="G396">
         <v>40</v>
       </c>
       <c r="H396" t="s">
-        <v>179</v>
+        <v>218</v>
       </c>
       <c r="I396" t="s">
-        <v>120</v>
+        <v>167</v>
       </c>
       <c r="J396" s="1">
         <v>3010101</v>
@@ -13601,16 +13724,16 @@
         <v>49</v>
       </c>
       <c r="F397" s="1" t="s">
-        <v>177</v>
+        <v>81</v>
       </c>
       <c r="G397">
         <v>40</v>
       </c>
       <c r="H397" t="s">
-        <v>179</v>
+        <v>219</v>
       </c>
       <c r="I397" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="J397" s="1">
         <v>3010101</v>
@@ -13633,16 +13756,16 @@
         <v>49</v>
       </c>
       <c r="F398" s="1" t="s">
-        <v>177</v>
+        <v>81</v>
       </c>
       <c r="G398">
         <v>40</v>
       </c>
       <c r="H398" t="s">
-        <v>179</v>
+        <v>219</v>
       </c>
       <c r="I398" t="s">
-        <v>123</v>
+        <v>169</v>
       </c>
       <c r="J398" s="1">
         <v>3030101</v>
@@ -13665,16 +13788,16 @@
         <v>49</v>
       </c>
       <c r="F399" s="1" t="s">
-        <v>177</v>
+        <v>81</v>
       </c>
       <c r="G399">
         <v>40</v>
       </c>
       <c r="H399" t="s">
-        <v>179</v>
+        <v>219</v>
       </c>
       <c r="I399" t="s">
-        <v>123</v>
+        <v>169</v>
       </c>
       <c r="J399" s="1">
         <v>3030101</v>
@@ -13697,16 +13820,16 @@
         <v>49</v>
       </c>
       <c r="F400" s="1" t="s">
-        <v>177</v>
+        <v>81</v>
       </c>
       <c r="G400">
         <v>40</v>
       </c>
       <c r="H400" t="s">
-        <v>179</v>
+        <v>219</v>
       </c>
       <c r="I400" t="s">
-        <v>123</v>
+        <v>169</v>
       </c>
       <c r="J400" s="1">
         <v>3030101</v>
@@ -13729,16 +13852,16 @@
         <v>49</v>
       </c>
       <c r="F401" s="1" t="s">
-        <v>177</v>
+        <v>81</v>
       </c>
       <c r="G401">
         <v>40</v>
       </c>
       <c r="H401" t="s">
-        <v>179</v>
+        <v>219</v>
       </c>
       <c r="I401" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="J401" s="1">
         <v>3010101</v>
@@ -13761,16 +13884,16 @@
         <v>49</v>
       </c>
       <c r="F402" s="1" t="s">
-        <v>177</v>
+        <v>81</v>
       </c>
       <c r="G402">
         <v>40</v>
       </c>
       <c r="H402" t="s">
-        <v>179</v>
+        <v>219</v>
       </c>
       <c r="I402" t="s">
-        <v>123</v>
+        <v>169</v>
       </c>
       <c r="J402" s="1">
         <v>3030101</v>
@@ -13793,16 +13916,16 @@
         <v>49</v>
       </c>
       <c r="F403" s="1" t="s">
-        <v>177</v>
+        <v>81</v>
       </c>
       <c r="G403">
         <v>40</v>
       </c>
       <c r="H403" t="s">
-        <v>179</v>
+        <v>219</v>
       </c>
       <c r="I403" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="J403" s="1">
         <v>3010101</v>
@@ -13825,16 +13948,16 @@
         <v>49</v>
       </c>
       <c r="F404" s="1" t="s">
-        <v>177</v>
+        <v>81</v>
       </c>
       <c r="G404">
         <v>40</v>
       </c>
       <c r="H404" t="s">
-        <v>179</v>
+        <v>219</v>
       </c>
       <c r="I404" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="J404" s="1">
         <v>3010101</v>
@@ -13857,16 +13980,16 @@
         <v>50</v>
       </c>
       <c r="F405" s="1" t="s">
-        <v>178</v>
+        <v>82</v>
       </c>
       <c r="G405">
         <v>50</v>
       </c>
       <c r="H405" t="s">
-        <v>179</v>
+        <v>220</v>
       </c>
       <c r="I405" t="s">
-        <v>124</v>
+        <v>167</v>
       </c>
       <c r="J405" s="1">
         <v>3010101</v>
@@ -13889,16 +14012,16 @@
         <v>50</v>
       </c>
       <c r="F406" s="1" t="s">
-        <v>178</v>
+        <v>82</v>
       </c>
       <c r="G406">
         <v>50</v>
       </c>
       <c r="H406" t="s">
-        <v>179</v>
+        <v>220</v>
       </c>
       <c r="I406" t="s">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="J406" s="1">
         <v>3030101</v>
@@ -13921,16 +14044,16 @@
         <v>50</v>
       </c>
       <c r="F407" s="1" t="s">
-        <v>178</v>
+        <v>82</v>
       </c>
       <c r="G407">
         <v>50</v>
       </c>
       <c r="H407" t="s">
-        <v>179</v>
+        <v>220</v>
       </c>
       <c r="I407" t="s">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="J407" s="1">
         <v>3030101</v>
@@ -13953,16 +14076,16 @@
         <v>50</v>
       </c>
       <c r="F408" s="1" t="s">
-        <v>178</v>
+        <v>82</v>
       </c>
       <c r="G408">
         <v>50</v>
       </c>
       <c r="H408" t="s">
-        <v>179</v>
+        <v>220</v>
       </c>
       <c r="I408" t="s">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="J408" s="1">
         <v>3030101</v>
@@ -13985,16 +14108,16 @@
         <v>50</v>
       </c>
       <c r="F409" s="1" t="s">
-        <v>178</v>
+        <v>82</v>
       </c>
       <c r="G409">
         <v>50</v>
       </c>
       <c r="H409" t="s">
-        <v>179</v>
+        <v>220</v>
       </c>
       <c r="I409" t="s">
-        <v>124</v>
+        <v>167</v>
       </c>
       <c r="J409" s="1">
         <v>3010101</v>
@@ -14017,16 +14140,16 @@
         <v>50</v>
       </c>
       <c r="F410" s="1" t="s">
-        <v>178</v>
+        <v>82</v>
       </c>
       <c r="G410">
         <v>50</v>
       </c>
       <c r="H410" t="s">
-        <v>179</v>
+        <v>220</v>
       </c>
       <c r="I410" t="s">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="J410" s="1">
         <v>3030101</v>
@@ -14049,16 +14172,16 @@
         <v>50</v>
       </c>
       <c r="F411" s="1" t="s">
-        <v>178</v>
+        <v>82</v>
       </c>
       <c r="G411">
         <v>50</v>
       </c>
       <c r="H411" t="s">
-        <v>179</v>
+        <v>220</v>
       </c>
       <c r="I411" t="s">
-        <v>124</v>
+        <v>167</v>
       </c>
       <c r="J411" s="1">
         <v>3010101</v>
@@ -14081,16 +14204,16 @@
         <v>50</v>
       </c>
       <c r="F412" s="1" t="s">
-        <v>178</v>
+        <v>82</v>
       </c>
       <c r="G412">
         <v>50</v>
       </c>
       <c r="H412" t="s">
-        <v>179</v>
+        <v>220</v>
       </c>
       <c r="I412" t="s">
-        <v>124</v>
+        <v>167</v>
       </c>
       <c r="J412" s="1">
         <v>3010101</v>

--- a/servers/maze_main_server/conf.d/data/maze_equip_pos_lv_v8【迷宫-装备-部位强化等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_equip_pos_lv_v8【迷宫-装备-部位强化等级】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84E06714-9ABF-4FC3-B10D-8D660DAD31C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04BF05F0-FB64-423D-BB63-50C9A08DB3F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1433,7 +1433,7 @@
         <v>10002</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>33</v>
@@ -1465,7 +1465,7 @@
         <v>20002</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>33</v>
@@ -1497,7 +1497,7 @@
         <v>30002</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>33</v>
@@ -1529,7 +1529,7 @@
         <v>40002</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>33</v>
@@ -1561,7 +1561,7 @@
         <v>50002</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>33</v>
@@ -1593,7 +1593,7 @@
         <v>60002</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>33</v>
@@ -1625,7 +1625,7 @@
         <v>70002</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>33</v>
@@ -1657,7 +1657,7 @@
         <v>80002</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>33</v>
@@ -1689,7 +1689,7 @@
         <v>10003</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>34</v>
@@ -1721,7 +1721,7 @@
         <v>20003</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>34</v>
@@ -1753,7 +1753,7 @@
         <v>30003</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>34</v>
@@ -1785,7 +1785,7 @@
         <v>40003</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>34</v>
@@ -1817,7 +1817,7 @@
         <v>50003</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>34</v>
@@ -1849,7 +1849,7 @@
         <v>60003</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>34</v>
@@ -1881,7 +1881,7 @@
         <v>70003</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>34</v>
@@ -1913,7 +1913,7 @@
         <v>80003</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>34</v>
@@ -1945,7 +1945,7 @@
         <v>10004</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>35</v>
@@ -1977,7 +1977,7 @@
         <v>20004</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>35</v>
@@ -2009,7 +2009,7 @@
         <v>30004</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>35</v>
@@ -2041,7 +2041,7 @@
         <v>40004</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>35</v>
@@ -2073,7 +2073,7 @@
         <v>50004</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>35</v>
@@ -2105,7 +2105,7 @@
         <v>60004</v>
       </c>
       <c r="E34">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>35</v>
@@ -2137,7 +2137,7 @@
         <v>70004</v>
       </c>
       <c r="E35">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>35</v>
@@ -2169,7 +2169,7 @@
         <v>80004</v>
       </c>
       <c r="E36">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>35</v>
@@ -2201,7 +2201,7 @@
         <v>10005</v>
       </c>
       <c r="E37">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>36</v>
@@ -2233,7 +2233,7 @@
         <v>20005</v>
       </c>
       <c r="E38">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>36</v>
@@ -2265,7 +2265,7 @@
         <v>30005</v>
       </c>
       <c r="E39">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>36</v>
@@ -2297,7 +2297,7 @@
         <v>40005</v>
       </c>
       <c r="E40">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>36</v>
@@ -2329,7 +2329,7 @@
         <v>50005</v>
       </c>
       <c r="E41">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>36</v>
@@ -2361,7 +2361,7 @@
         <v>60005</v>
       </c>
       <c r="E42">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>36</v>
@@ -2393,7 +2393,7 @@
         <v>70005</v>
       </c>
       <c r="E43">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>36</v>
@@ -2425,7 +2425,7 @@
         <v>80005</v>
       </c>
       <c r="E44">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>36</v>
@@ -2457,7 +2457,7 @@
         <v>10006</v>
       </c>
       <c r="E45">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>37</v>
@@ -2489,7 +2489,7 @@
         <v>20006</v>
       </c>
       <c r="E46">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>37</v>
@@ -2521,7 +2521,7 @@
         <v>30006</v>
       </c>
       <c r="E47">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>37</v>
@@ -2553,7 +2553,7 @@
         <v>40006</v>
       </c>
       <c r="E48">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>37</v>
@@ -2585,7 +2585,7 @@
         <v>50006</v>
       </c>
       <c r="E49">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>37</v>
@@ -2617,7 +2617,7 @@
         <v>60006</v>
       </c>
       <c r="E50">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>37</v>
@@ -2649,7 +2649,7 @@
         <v>70006</v>
       </c>
       <c r="E51">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>37</v>
@@ -2681,7 +2681,7 @@
         <v>80006</v>
       </c>
       <c r="E52">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>37</v>
@@ -2713,7 +2713,7 @@
         <v>10007</v>
       </c>
       <c r="E53">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>38</v>
@@ -2745,7 +2745,7 @@
         <v>20007</v>
       </c>
       <c r="E54">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>38</v>
@@ -2777,7 +2777,7 @@
         <v>30007</v>
       </c>
       <c r="E55">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>38</v>
@@ -2809,7 +2809,7 @@
         <v>40007</v>
       </c>
       <c r="E56">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>38</v>
@@ -2841,7 +2841,7 @@
         <v>50007</v>
       </c>
       <c r="E57">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>38</v>
@@ -2873,7 +2873,7 @@
         <v>60007</v>
       </c>
       <c r="E58">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>38</v>
@@ -2905,7 +2905,7 @@
         <v>70007</v>
       </c>
       <c r="E59">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>38</v>
@@ -2937,7 +2937,7 @@
         <v>80007</v>
       </c>
       <c r="E60">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>38</v>
@@ -2969,7 +2969,7 @@
         <v>10008</v>
       </c>
       <c r="E61">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>39</v>
@@ -3001,7 +3001,7 @@
         <v>20008</v>
       </c>
       <c r="E62">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>39</v>
@@ -3033,7 +3033,7 @@
         <v>30008</v>
       </c>
       <c r="E63">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>39</v>
@@ -3065,7 +3065,7 @@
         <v>40008</v>
       </c>
       <c r="E64">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>39</v>
@@ -3097,7 +3097,7 @@
         <v>50008</v>
       </c>
       <c r="E65">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>39</v>
@@ -3129,7 +3129,7 @@
         <v>60008</v>
       </c>
       <c r="E66">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>39</v>
@@ -3161,7 +3161,7 @@
         <v>70008</v>
       </c>
       <c r="E67">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>39</v>
@@ -3193,7 +3193,7 @@
         <v>80008</v>
       </c>
       <c r="E68">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>39</v>
@@ -3225,7 +3225,7 @@
         <v>10009</v>
       </c>
       <c r="E69">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>40</v>
@@ -3257,7 +3257,7 @@
         <v>20009</v>
       </c>
       <c r="E70">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>40</v>
@@ -3289,7 +3289,7 @@
         <v>30009</v>
       </c>
       <c r="E71">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>40</v>
@@ -3321,7 +3321,7 @@
         <v>40009</v>
       </c>
       <c r="E72">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>40</v>
@@ -3353,7 +3353,7 @@
         <v>50009</v>
       </c>
       <c r="E73">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>40</v>
@@ -3385,7 +3385,7 @@
         <v>60009</v>
       </c>
       <c r="E74">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>40</v>
@@ -3417,7 +3417,7 @@
         <v>70009</v>
       </c>
       <c r="E75">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>40</v>
@@ -3449,7 +3449,7 @@
         <v>80009</v>
       </c>
       <c r="E76">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>40</v>
@@ -3481,7 +3481,7 @@
         <v>10010</v>
       </c>
       <c r="E77">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>41</v>
@@ -3513,7 +3513,7 @@
         <v>20010</v>
       </c>
       <c r="E78">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>41</v>
@@ -3545,7 +3545,7 @@
         <v>30010</v>
       </c>
       <c r="E79">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>41</v>
@@ -3577,7 +3577,7 @@
         <v>40010</v>
       </c>
       <c r="E80">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>41</v>
@@ -3609,7 +3609,7 @@
         <v>50010</v>
       </c>
       <c r="E81">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>41</v>
@@ -3641,7 +3641,7 @@
         <v>60010</v>
       </c>
       <c r="E82">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>41</v>
@@ -3673,7 +3673,7 @@
         <v>70010</v>
       </c>
       <c r="E83">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>41</v>
@@ -3705,7 +3705,7 @@
         <v>80010</v>
       </c>
       <c r="E84">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>41</v>
@@ -3737,7 +3737,7 @@
         <v>10011</v>
       </c>
       <c r="E85">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>42</v>
@@ -3769,7 +3769,7 @@
         <v>20011</v>
       </c>
       <c r="E86">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>42</v>
@@ -3801,7 +3801,7 @@
         <v>30011</v>
       </c>
       <c r="E87">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>42</v>
@@ -3833,7 +3833,7 @@
         <v>40011</v>
       </c>
       <c r="E88">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>42</v>
@@ -3865,7 +3865,7 @@
         <v>50011</v>
       </c>
       <c r="E89">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>42</v>
@@ -3897,7 +3897,7 @@
         <v>60011</v>
       </c>
       <c r="E90">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>42</v>
@@ -3929,7 +3929,7 @@
         <v>70011</v>
       </c>
       <c r="E91">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>42</v>
@@ -3961,7 +3961,7 @@
         <v>80011</v>
       </c>
       <c r="E92">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>42</v>
@@ -3993,7 +3993,7 @@
         <v>10012</v>
       </c>
       <c r="E93">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>43</v>
@@ -4025,7 +4025,7 @@
         <v>20012</v>
       </c>
       <c r="E94">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>43</v>
@@ -4057,7 +4057,7 @@
         <v>30012</v>
       </c>
       <c r="E95">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>43</v>
@@ -4089,7 +4089,7 @@
         <v>40012</v>
       </c>
       <c r="E96">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>43</v>
@@ -4121,7 +4121,7 @@
         <v>50012</v>
       </c>
       <c r="E97">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>43</v>
@@ -4153,7 +4153,7 @@
         <v>60012</v>
       </c>
       <c r="E98">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>43</v>
@@ -4185,7 +4185,7 @@
         <v>70012</v>
       </c>
       <c r="E99">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>43</v>
@@ -4217,7 +4217,7 @@
         <v>80012</v>
       </c>
       <c r="E100">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>43</v>
@@ -4249,7 +4249,7 @@
         <v>10013</v>
       </c>
       <c r="E101">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>44</v>
@@ -4281,7 +4281,7 @@
         <v>20013</v>
       </c>
       <c r="E102">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>44</v>
@@ -4313,7 +4313,7 @@
         <v>30013</v>
       </c>
       <c r="E103">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>44</v>
@@ -4345,7 +4345,7 @@
         <v>40013</v>
       </c>
       <c r="E104">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>44</v>
@@ -4377,7 +4377,7 @@
         <v>50013</v>
       </c>
       <c r="E105">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>44</v>
@@ -4409,7 +4409,7 @@
         <v>60013</v>
       </c>
       <c r="E106">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>44</v>
@@ -4441,7 +4441,7 @@
         <v>70013</v>
       </c>
       <c r="E107">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>44</v>
@@ -4473,7 +4473,7 @@
         <v>80013</v>
       </c>
       <c r="E108">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>44</v>
@@ -4505,7 +4505,7 @@
         <v>10014</v>
       </c>
       <c r="E109">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>45</v>
@@ -4537,7 +4537,7 @@
         <v>20014</v>
       </c>
       <c r="E110">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>45</v>
@@ -4569,7 +4569,7 @@
         <v>30014</v>
       </c>
       <c r="E111">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>45</v>
@@ -4601,7 +4601,7 @@
         <v>40014</v>
       </c>
       <c r="E112">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>45</v>
@@ -4633,7 +4633,7 @@
         <v>50014</v>
       </c>
       <c r="E113">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>45</v>
@@ -4665,7 +4665,7 @@
         <v>60014</v>
       </c>
       <c r="E114">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>45</v>
@@ -4697,7 +4697,7 @@
         <v>70014</v>
       </c>
       <c r="E115">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>45</v>
@@ -4729,7 +4729,7 @@
         <v>80014</v>
       </c>
       <c r="E116">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>45</v>
@@ -4761,7 +4761,7 @@
         <v>10015</v>
       </c>
       <c r="E117">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>46</v>
@@ -4793,7 +4793,7 @@
         <v>20015</v>
       </c>
       <c r="E118">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>46</v>
@@ -4825,7 +4825,7 @@
         <v>30015</v>
       </c>
       <c r="E119">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>46</v>
@@ -4857,7 +4857,7 @@
         <v>40015</v>
       </c>
       <c r="E120">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>46</v>
@@ -4889,7 +4889,7 @@
         <v>50015</v>
       </c>
       <c r="E121">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>46</v>
@@ -4921,7 +4921,7 @@
         <v>60015</v>
       </c>
       <c r="E122">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>46</v>
@@ -4953,7 +4953,7 @@
         <v>70015</v>
       </c>
       <c r="E123">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>46</v>
@@ -4985,7 +4985,7 @@
         <v>80015</v>
       </c>
       <c r="E124">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>46</v>
@@ -5017,7 +5017,7 @@
         <v>10016</v>
       </c>
       <c r="E125">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>47</v>
@@ -5049,7 +5049,7 @@
         <v>20016</v>
       </c>
       <c r="E126">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>47</v>
@@ -5081,7 +5081,7 @@
         <v>30016</v>
       </c>
       <c r="E127">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>47</v>
@@ -5113,7 +5113,7 @@
         <v>40016</v>
       </c>
       <c r="E128">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>47</v>
@@ -5145,7 +5145,7 @@
         <v>50016</v>
       </c>
       <c r="E129">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>47</v>
@@ -5177,7 +5177,7 @@
         <v>60016</v>
       </c>
       <c r="E130">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>47</v>
@@ -5209,7 +5209,7 @@
         <v>70016</v>
       </c>
       <c r="E131">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>47</v>
@@ -5241,7 +5241,7 @@
         <v>80016</v>
       </c>
       <c r="E132">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>47</v>
@@ -5273,7 +5273,7 @@
         <v>10017</v>
       </c>
       <c r="E133">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>48</v>
@@ -5305,7 +5305,7 @@
         <v>20017</v>
       </c>
       <c r="E134">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>48</v>
@@ -5337,7 +5337,7 @@
         <v>30017</v>
       </c>
       <c r="E135">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>48</v>
@@ -5369,7 +5369,7 @@
         <v>40017</v>
       </c>
       <c r="E136">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>48</v>
@@ -5401,7 +5401,7 @@
         <v>50017</v>
       </c>
       <c r="E137">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>48</v>
@@ -5433,7 +5433,7 @@
         <v>60017</v>
       </c>
       <c r="E138">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>48</v>
@@ -5465,7 +5465,7 @@
         <v>70017</v>
       </c>
       <c r="E139">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>48</v>
@@ -5497,7 +5497,7 @@
         <v>80017</v>
       </c>
       <c r="E140">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>48</v>
@@ -5529,7 +5529,7 @@
         <v>10018</v>
       </c>
       <c r="E141">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>49</v>
@@ -5561,7 +5561,7 @@
         <v>20018</v>
       </c>
       <c r="E142">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>49</v>
@@ -5593,7 +5593,7 @@
         <v>30018</v>
       </c>
       <c r="E143">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>49</v>
@@ -5625,7 +5625,7 @@
         <v>40018</v>
       </c>
       <c r="E144">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>49</v>
@@ -5657,7 +5657,7 @@
         <v>50018</v>
       </c>
       <c r="E145">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>49</v>
@@ -5689,7 +5689,7 @@
         <v>60018</v>
       </c>
       <c r="E146">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>49</v>
@@ -5721,7 +5721,7 @@
         <v>70018</v>
       </c>
       <c r="E147">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>49</v>
@@ -5753,7 +5753,7 @@
         <v>80018</v>
       </c>
       <c r="E148">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>49</v>
@@ -5785,7 +5785,7 @@
         <v>10019</v>
       </c>
       <c r="E149">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>50</v>
@@ -5817,7 +5817,7 @@
         <v>20019</v>
       </c>
       <c r="E150">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>50</v>
@@ -5849,7 +5849,7 @@
         <v>30019</v>
       </c>
       <c r="E151">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>50</v>
@@ -5881,7 +5881,7 @@
         <v>40019</v>
       </c>
       <c r="E152">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>50</v>
@@ -5913,7 +5913,7 @@
         <v>50019</v>
       </c>
       <c r="E153">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>50</v>
@@ -5945,7 +5945,7 @@
         <v>60019</v>
       </c>
       <c r="E154">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>50</v>
@@ -5977,7 +5977,7 @@
         <v>70019</v>
       </c>
       <c r="E155">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>50</v>
@@ -6009,7 +6009,7 @@
         <v>80019</v>
       </c>
       <c r="E156">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>50</v>
@@ -6041,7 +6041,7 @@
         <v>10020</v>
       </c>
       <c r="E157">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>51</v>
@@ -6073,7 +6073,7 @@
         <v>20020</v>
       </c>
       <c r="E158">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>51</v>
@@ -6105,7 +6105,7 @@
         <v>30020</v>
       </c>
       <c r="E159">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>51</v>
@@ -6137,7 +6137,7 @@
         <v>40020</v>
       </c>
       <c r="E160">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>51</v>
@@ -6169,7 +6169,7 @@
         <v>50020</v>
       </c>
       <c r="E161">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>51</v>
@@ -6201,7 +6201,7 @@
         <v>60020</v>
       </c>
       <c r="E162">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>51</v>
@@ -6233,7 +6233,7 @@
         <v>70020</v>
       </c>
       <c r="E163">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>51</v>
@@ -6265,7 +6265,7 @@
         <v>80020</v>
       </c>
       <c r="E164">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>51</v>
@@ -6297,7 +6297,7 @@
         <v>10021</v>
       </c>
       <c r="E165">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>52</v>
@@ -6329,7 +6329,7 @@
         <v>20021</v>
       </c>
       <c r="E166">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>52</v>
@@ -6361,7 +6361,7 @@
         <v>30021</v>
       </c>
       <c r="E167">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>52</v>
@@ -6393,7 +6393,7 @@
         <v>40021</v>
       </c>
       <c r="E168">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>52</v>
@@ -6425,7 +6425,7 @@
         <v>50021</v>
       </c>
       <c r="E169">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>52</v>
@@ -6457,7 +6457,7 @@
         <v>60021</v>
       </c>
       <c r="E170">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>52</v>
@@ -6489,7 +6489,7 @@
         <v>70021</v>
       </c>
       <c r="E171">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>52</v>
@@ -6521,7 +6521,7 @@
         <v>80021</v>
       </c>
       <c r="E172">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>52</v>
@@ -6553,7 +6553,7 @@
         <v>10022</v>
       </c>
       <c r="E173">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>53</v>
@@ -6585,7 +6585,7 @@
         <v>20022</v>
       </c>
       <c r="E174">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>53</v>
@@ -6617,7 +6617,7 @@
         <v>30022</v>
       </c>
       <c r="E175">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>53</v>
@@ -6649,7 +6649,7 @@
         <v>40022</v>
       </c>
       <c r="E176">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>53</v>
@@ -6681,7 +6681,7 @@
         <v>50022</v>
       </c>
       <c r="E177">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>53</v>
@@ -6713,7 +6713,7 @@
         <v>60022</v>
       </c>
       <c r="E178">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>53</v>
@@ -6745,7 +6745,7 @@
         <v>70022</v>
       </c>
       <c r="E179">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>53</v>
@@ -6777,7 +6777,7 @@
         <v>80022</v>
       </c>
       <c r="E180">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>53</v>
@@ -6809,7 +6809,7 @@
         <v>10023</v>
       </c>
       <c r="E181">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>54</v>
@@ -6841,7 +6841,7 @@
         <v>20023</v>
       </c>
       <c r="E182">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>54</v>
@@ -6873,7 +6873,7 @@
         <v>30023</v>
       </c>
       <c r="E183">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>54</v>
@@ -6905,7 +6905,7 @@
         <v>40023</v>
       </c>
       <c r="E184">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>54</v>
@@ -6937,7 +6937,7 @@
         <v>50023</v>
       </c>
       <c r="E185">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>54</v>
@@ -6969,7 +6969,7 @@
         <v>60023</v>
       </c>
       <c r="E186">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>54</v>
@@ -7001,7 +7001,7 @@
         <v>70023</v>
       </c>
       <c r="E187">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>54</v>
@@ -7033,7 +7033,7 @@
         <v>80023</v>
       </c>
       <c r="E188">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>54</v>
@@ -7065,7 +7065,7 @@
         <v>10024</v>
       </c>
       <c r="E189">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>55</v>
@@ -7097,7 +7097,7 @@
         <v>20024</v>
       </c>
       <c r="E190">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>55</v>
@@ -7129,7 +7129,7 @@
         <v>30024</v>
       </c>
       <c r="E191">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>55</v>
@@ -7161,7 +7161,7 @@
         <v>40024</v>
       </c>
       <c r="E192">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>55</v>
@@ -7193,7 +7193,7 @@
         <v>50024</v>
       </c>
       <c r="E193">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>55</v>
@@ -7225,7 +7225,7 @@
         <v>60024</v>
       </c>
       <c r="E194">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>55</v>
@@ -7257,7 +7257,7 @@
         <v>70024</v>
       </c>
       <c r="E195">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>55</v>
@@ -7289,7 +7289,7 @@
         <v>80024</v>
       </c>
       <c r="E196">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>55</v>
@@ -7321,7 +7321,7 @@
         <v>10025</v>
       </c>
       <c r="E197">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>56</v>
@@ -7353,7 +7353,7 @@
         <v>20025</v>
       </c>
       <c r="E198">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>56</v>
@@ -7385,7 +7385,7 @@
         <v>30025</v>
       </c>
       <c r="E199">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>56</v>
@@ -7417,7 +7417,7 @@
         <v>40025</v>
       </c>
       <c r="E200">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>56</v>
@@ -7449,7 +7449,7 @@
         <v>50025</v>
       </c>
       <c r="E201">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>56</v>
@@ -7481,7 +7481,7 @@
         <v>60025</v>
       </c>
       <c r="E202">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>56</v>
@@ -7513,7 +7513,7 @@
         <v>70025</v>
       </c>
       <c r="E203">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>56</v>
@@ -7545,7 +7545,7 @@
         <v>80025</v>
       </c>
       <c r="E204">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>56</v>
@@ -7577,7 +7577,7 @@
         <v>10026</v>
       </c>
       <c r="E205">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>57</v>
@@ -7609,7 +7609,7 @@
         <v>20026</v>
       </c>
       <c r="E206">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>57</v>
@@ -7641,7 +7641,7 @@
         <v>30026</v>
       </c>
       <c r="E207">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>57</v>
@@ -7673,7 +7673,7 @@
         <v>40026</v>
       </c>
       <c r="E208">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>57</v>
@@ -7705,7 +7705,7 @@
         <v>50026</v>
       </c>
       <c r="E209">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>57</v>
@@ -7737,7 +7737,7 @@
         <v>60026</v>
       </c>
       <c r="E210">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>57</v>
@@ -7769,7 +7769,7 @@
         <v>70026</v>
       </c>
       <c r="E211">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>57</v>
@@ -7801,7 +7801,7 @@
         <v>80026</v>
       </c>
       <c r="E212">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>57</v>
@@ -7833,7 +7833,7 @@
         <v>10027</v>
       </c>
       <c r="E213">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>58</v>
@@ -7865,7 +7865,7 @@
         <v>20027</v>
       </c>
       <c r="E214">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>58</v>
@@ -7897,7 +7897,7 @@
         <v>30027</v>
       </c>
       <c r="E215">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>58</v>
@@ -7929,7 +7929,7 @@
         <v>40027</v>
       </c>
       <c r="E216">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>58</v>
@@ -7961,7 +7961,7 @@
         <v>50027</v>
       </c>
       <c r="E217">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>58</v>
@@ -7993,7 +7993,7 @@
         <v>60027</v>
       </c>
       <c r="E218">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>58</v>
@@ -8025,7 +8025,7 @@
         <v>70027</v>
       </c>
       <c r="E219">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F219" s="1" t="s">
         <v>58</v>
@@ -8057,7 +8057,7 @@
         <v>80027</v>
       </c>
       <c r="E220">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F220" s="1" t="s">
         <v>58</v>
@@ -8089,7 +8089,7 @@
         <v>10028</v>
       </c>
       <c r="E221">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="F221" s="1" t="s">
         <v>59</v>
@@ -8121,7 +8121,7 @@
         <v>20028</v>
       </c>
       <c r="E222">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="F222" s="1" t="s">
         <v>59</v>
@@ -8153,7 +8153,7 @@
         <v>30028</v>
       </c>
       <c r="E223">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="F223" s="1" t="s">
         <v>59</v>
@@ -8185,7 +8185,7 @@
         <v>40028</v>
       </c>
       <c r="E224">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="F224" s="1" t="s">
         <v>59</v>
@@ -8217,7 +8217,7 @@
         <v>50028</v>
       </c>
       <c r="E225">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="F225" s="1" t="s">
         <v>59</v>
@@ -8249,7 +8249,7 @@
         <v>60028</v>
       </c>
       <c r="E226">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="F226" s="1" t="s">
         <v>59</v>
@@ -8281,7 +8281,7 @@
         <v>70028</v>
       </c>
       <c r="E227">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="F227" s="1" t="s">
         <v>59</v>
@@ -8313,7 +8313,7 @@
         <v>80028</v>
       </c>
       <c r="E228">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="F228" s="1" t="s">
         <v>59</v>
@@ -8345,7 +8345,7 @@
         <v>10029</v>
       </c>
       <c r="E229">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F229" s="1" t="s">
         <v>60</v>
@@ -8377,7 +8377,7 @@
         <v>20029</v>
       </c>
       <c r="E230">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F230" s="1" t="s">
         <v>60</v>
@@ -8409,7 +8409,7 @@
         <v>30029</v>
       </c>
       <c r="E231">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F231" s="1" t="s">
         <v>60</v>
@@ -8441,7 +8441,7 @@
         <v>40029</v>
       </c>
       <c r="E232">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F232" s="1" t="s">
         <v>60</v>
@@ -8473,7 +8473,7 @@
         <v>50029</v>
       </c>
       <c r="E233">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F233" s="1" t="s">
         <v>60</v>
@@ -8505,7 +8505,7 @@
         <v>60029</v>
       </c>
       <c r="E234">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F234" s="1" t="s">
         <v>60</v>
@@ -8537,7 +8537,7 @@
         <v>70029</v>
       </c>
       <c r="E235">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F235" s="1" t="s">
         <v>60</v>
@@ -8569,7 +8569,7 @@
         <v>80029</v>
       </c>
       <c r="E236">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F236" s="1" t="s">
         <v>60</v>
@@ -8601,7 +8601,7 @@
         <v>10030</v>
       </c>
       <c r="E237">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="F237" s="1" t="s">
         <v>61</v>
@@ -8633,7 +8633,7 @@
         <v>20030</v>
       </c>
       <c r="E238">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="F238" s="1" t="s">
         <v>61</v>
@@ -8665,7 +8665,7 @@
         <v>30030</v>
       </c>
       <c r="E239">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="F239" s="1" t="s">
         <v>61</v>
@@ -8697,7 +8697,7 @@
         <v>40030</v>
       </c>
       <c r="E240">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="F240" s="1" t="s">
         <v>61</v>
@@ -8729,7 +8729,7 @@
         <v>50030</v>
       </c>
       <c r="E241">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="F241" s="1" t="s">
         <v>61</v>
@@ -8761,7 +8761,7 @@
         <v>60030</v>
       </c>
       <c r="E242">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="F242" s="1" t="s">
         <v>61</v>
@@ -8793,7 +8793,7 @@
         <v>70030</v>
       </c>
       <c r="E243">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="F243" s="1" t="s">
         <v>61</v>
@@ -8825,7 +8825,7 @@
         <v>80030</v>
       </c>
       <c r="E244">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="F244" s="1" t="s">
         <v>61</v>
@@ -8857,7 +8857,7 @@
         <v>10031</v>
       </c>
       <c r="E245">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F245" s="1" t="s">
         <v>62</v>
@@ -8889,7 +8889,7 @@
         <v>20031</v>
       </c>
       <c r="E246">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F246" s="1" t="s">
         <v>62</v>
@@ -8921,7 +8921,7 @@
         <v>30031</v>
       </c>
       <c r="E247">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F247" s="1" t="s">
         <v>62</v>
@@ -8953,7 +8953,7 @@
         <v>40031</v>
       </c>
       <c r="E248">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F248" s="1" t="s">
         <v>62</v>
@@ -8985,7 +8985,7 @@
         <v>50031</v>
       </c>
       <c r="E249">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F249" s="1" t="s">
         <v>62</v>
@@ -9017,7 +9017,7 @@
         <v>60031</v>
       </c>
       <c r="E250">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F250" s="1" t="s">
         <v>62</v>
@@ -9049,7 +9049,7 @@
         <v>70031</v>
       </c>
       <c r="E251">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F251" s="1" t="s">
         <v>62</v>
@@ -9081,7 +9081,7 @@
         <v>80031</v>
       </c>
       <c r="E252">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F252" s="1" t="s">
         <v>62</v>
@@ -9113,7 +9113,7 @@
         <v>10032</v>
       </c>
       <c r="E253">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F253" s="1" t="s">
         <v>63</v>
@@ -9145,7 +9145,7 @@
         <v>20032</v>
       </c>
       <c r="E254">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F254" s="1" t="s">
         <v>63</v>
@@ -9177,7 +9177,7 @@
         <v>30032</v>
       </c>
       <c r="E255">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F255" s="1" t="s">
         <v>63</v>
@@ -9209,7 +9209,7 @@
         <v>40032</v>
       </c>
       <c r="E256">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F256" s="1" t="s">
         <v>63</v>
@@ -9241,7 +9241,7 @@
         <v>50032</v>
       </c>
       <c r="E257">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F257" s="1" t="s">
         <v>63</v>
@@ -9273,7 +9273,7 @@
         <v>60032</v>
       </c>
       <c r="E258">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F258" s="1" t="s">
         <v>63</v>
@@ -9305,7 +9305,7 @@
         <v>70032</v>
       </c>
       <c r="E259">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F259" s="1" t="s">
         <v>63</v>
@@ -9337,7 +9337,7 @@
         <v>80032</v>
       </c>
       <c r="E260">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F260" s="1" t="s">
         <v>63</v>
@@ -9369,7 +9369,7 @@
         <v>10033</v>
       </c>
       <c r="E261">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F261" s="1" t="s">
         <v>64</v>
@@ -9401,7 +9401,7 @@
         <v>20033</v>
       </c>
       <c r="E262">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F262" s="1" t="s">
         <v>64</v>
@@ -9433,7 +9433,7 @@
         <v>30033</v>
       </c>
       <c r="E263">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F263" s="1" t="s">
         <v>64</v>
@@ -9465,7 +9465,7 @@
         <v>40033</v>
       </c>
       <c r="E264">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F264" s="1" t="s">
         <v>64</v>
@@ -9497,7 +9497,7 @@
         <v>50033</v>
       </c>
       <c r="E265">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F265" s="1" t="s">
         <v>64</v>
@@ -9529,7 +9529,7 @@
         <v>60033</v>
       </c>
       <c r="E266">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F266" s="1" t="s">
         <v>64</v>
@@ -9561,7 +9561,7 @@
         <v>70033</v>
       </c>
       <c r="E267">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F267" s="1" t="s">
         <v>64</v>
@@ -9593,7 +9593,7 @@
         <v>80033</v>
       </c>
       <c r="E268">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F268" s="1" t="s">
         <v>64</v>
@@ -9625,7 +9625,7 @@
         <v>10034</v>
       </c>
       <c r="E269">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F269" s="1" t="s">
         <v>65</v>
@@ -9657,7 +9657,7 @@
         <v>20034</v>
       </c>
       <c r="E270">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F270" s="1" t="s">
         <v>65</v>
@@ -9689,7 +9689,7 @@
         <v>30034</v>
       </c>
       <c r="E271">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F271" s="1" t="s">
         <v>65</v>
@@ -9721,7 +9721,7 @@
         <v>40034</v>
       </c>
       <c r="E272">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F272" s="1" t="s">
         <v>65</v>
@@ -9753,7 +9753,7 @@
         <v>50034</v>
       </c>
       <c r="E273">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>65</v>
@@ -9785,7 +9785,7 @@
         <v>60034</v>
       </c>
       <c r="E274">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>65</v>
@@ -9817,7 +9817,7 @@
         <v>70034</v>
       </c>
       <c r="E275">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F275" s="1" t="s">
         <v>65</v>
@@ -9849,7 +9849,7 @@
         <v>80034</v>
       </c>
       <c r="E276">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F276" s="1" t="s">
         <v>65</v>
@@ -9881,7 +9881,7 @@
         <v>10035</v>
       </c>
       <c r="E277">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="F277" s="1" t="s">
         <v>66</v>
@@ -9913,7 +9913,7 @@
         <v>20035</v>
       </c>
       <c r="E278">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="F278" s="1" t="s">
         <v>66</v>
@@ -9945,7 +9945,7 @@
         <v>30035</v>
       </c>
       <c r="E279">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="F279" s="1" t="s">
         <v>66</v>
@@ -9977,7 +9977,7 @@
         <v>40035</v>
       </c>
       <c r="E280">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="F280" s="1" t="s">
         <v>66</v>
@@ -10009,7 +10009,7 @@
         <v>50035</v>
       </c>
       <c r="E281">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="F281" s="1" t="s">
         <v>66</v>
@@ -10041,7 +10041,7 @@
         <v>60035</v>
       </c>
       <c r="E282">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="F282" s="1" t="s">
         <v>66</v>
@@ -10073,7 +10073,7 @@
         <v>70035</v>
       </c>
       <c r="E283">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="F283" s="1" t="s">
         <v>66</v>
@@ -10105,7 +10105,7 @@
         <v>80035</v>
       </c>
       <c r="E284">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="F284" s="1" t="s">
         <v>66</v>
@@ -10137,7 +10137,7 @@
         <v>10036</v>
       </c>
       <c r="E285">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F285" s="1" t="s">
         <v>67</v>
@@ -10169,7 +10169,7 @@
         <v>20036</v>
       </c>
       <c r="E286">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F286" s="1" t="s">
         <v>67</v>
@@ -10201,7 +10201,7 @@
         <v>30036</v>
       </c>
       <c r="E287">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F287" s="1" t="s">
         <v>67</v>
@@ -10233,7 +10233,7 @@
         <v>40036</v>
       </c>
       <c r="E288">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F288" s="1" t="s">
         <v>67</v>
@@ -10265,7 +10265,7 @@
         <v>50036</v>
       </c>
       <c r="E289">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F289" s="1" t="s">
         <v>67</v>
@@ -10297,7 +10297,7 @@
         <v>60036</v>
       </c>
       <c r="E290">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F290" s="1" t="s">
         <v>67</v>
@@ -10329,7 +10329,7 @@
         <v>70036</v>
       </c>
       <c r="E291">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F291" s="1" t="s">
         <v>67</v>
@@ -10361,7 +10361,7 @@
         <v>80036</v>
       </c>
       <c r="E292">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F292" s="1" t="s">
         <v>67</v>
@@ -10393,7 +10393,7 @@
         <v>10037</v>
       </c>
       <c r="E293">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F293" s="1" t="s">
         <v>68</v>
@@ -10425,7 +10425,7 @@
         <v>20037</v>
       </c>
       <c r="E294">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F294" s="1" t="s">
         <v>68</v>
@@ -10457,7 +10457,7 @@
         <v>30037</v>
       </c>
       <c r="E295">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F295" s="1" t="s">
         <v>68</v>
@@ -10489,7 +10489,7 @@
         <v>40037</v>
       </c>
       <c r="E296">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F296" s="1" t="s">
         <v>68</v>
@@ -10521,7 +10521,7 @@
         <v>50037</v>
       </c>
       <c r="E297">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F297" s="1" t="s">
         <v>68</v>
@@ -10553,7 +10553,7 @@
         <v>60037</v>
       </c>
       <c r="E298">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F298" s="1" t="s">
         <v>68</v>
@@ -10585,7 +10585,7 @@
         <v>70037</v>
       </c>
       <c r="E299">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F299" s="1" t="s">
         <v>68</v>
@@ -10617,7 +10617,7 @@
         <v>80037</v>
       </c>
       <c r="E300">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F300" s="1" t="s">
         <v>68</v>
@@ -10649,7 +10649,7 @@
         <v>10038</v>
       </c>
       <c r="E301">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>69</v>
@@ -10681,7 +10681,7 @@
         <v>20038</v>
       </c>
       <c r="E302">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="F302" s="1" t="s">
         <v>69</v>
@@ -10713,7 +10713,7 @@
         <v>30038</v>
       </c>
       <c r="E303">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="F303" s="1" t="s">
         <v>69</v>
@@ -10745,7 +10745,7 @@
         <v>40038</v>
       </c>
       <c r="E304">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="F304" s="1" t="s">
         <v>69</v>
@@ -10777,7 +10777,7 @@
         <v>50038</v>
       </c>
       <c r="E305">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="F305" s="1" t="s">
         <v>69</v>
@@ -10809,7 +10809,7 @@
         <v>60038</v>
       </c>
       <c r="E306">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="F306" s="1" t="s">
         <v>69</v>
@@ -10841,7 +10841,7 @@
         <v>70038</v>
       </c>
       <c r="E307">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="F307" s="1" t="s">
         <v>69</v>
@@ -10873,7 +10873,7 @@
         <v>80038</v>
       </c>
       <c r="E308">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="F308" s="1" t="s">
         <v>69</v>
@@ -10905,7 +10905,7 @@
         <v>10039</v>
       </c>
       <c r="E309">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="F309" s="1" t="s">
         <v>70</v>
@@ -10937,7 +10937,7 @@
         <v>20039</v>
       </c>
       <c r="E310">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="F310" s="1" t="s">
         <v>70</v>
@@ -10969,7 +10969,7 @@
         <v>30039</v>
       </c>
       <c r="E311">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="F311" s="1" t="s">
         <v>70</v>
@@ -11001,7 +11001,7 @@
         <v>40039</v>
       </c>
       <c r="E312">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="F312" s="1" t="s">
         <v>70</v>
@@ -11033,7 +11033,7 @@
         <v>50039</v>
       </c>
       <c r="E313">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="F313" s="1" t="s">
         <v>70</v>
@@ -11065,7 +11065,7 @@
         <v>60039</v>
       </c>
       <c r="E314">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="F314" s="1" t="s">
         <v>70</v>
@@ -11097,7 +11097,7 @@
         <v>70039</v>
       </c>
       <c r="E315">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="F315" s="1" t="s">
         <v>70</v>
@@ -11129,7 +11129,7 @@
         <v>80039</v>
       </c>
       <c r="E316">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="F316" s="1" t="s">
         <v>70</v>
@@ -11161,7 +11161,7 @@
         <v>10040</v>
       </c>
       <c r="E317">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F317" s="1" t="s">
         <v>71</v>
@@ -11193,7 +11193,7 @@
         <v>20040</v>
       </c>
       <c r="E318">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F318" s="1" t="s">
         <v>71</v>
@@ -11225,7 +11225,7 @@
         <v>30040</v>
       </c>
       <c r="E319">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F319" s="1" t="s">
         <v>71</v>
@@ -11257,7 +11257,7 @@
         <v>40040</v>
       </c>
       <c r="E320">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F320" s="1" t="s">
         <v>71</v>
@@ -11289,7 +11289,7 @@
         <v>50040</v>
       </c>
       <c r="E321">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F321" s="1" t="s">
         <v>71</v>
@@ -11321,7 +11321,7 @@
         <v>60040</v>
       </c>
       <c r="E322">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F322" s="1" t="s">
         <v>71</v>
@@ -11353,7 +11353,7 @@
         <v>70040</v>
       </c>
       <c r="E323">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F323" s="1" t="s">
         <v>71</v>
@@ -11385,7 +11385,7 @@
         <v>80040</v>
       </c>
       <c r="E324">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F324" s="1" t="s">
         <v>71</v>
@@ -11417,7 +11417,7 @@
         <v>10041</v>
       </c>
       <c r="E325">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F325" s="1" t="s">
         <v>72</v>
@@ -11449,7 +11449,7 @@
         <v>20041</v>
       </c>
       <c r="E326">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F326" s="1" t="s">
         <v>72</v>
@@ -11481,7 +11481,7 @@
         <v>30041</v>
       </c>
       <c r="E327">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F327" s="1" t="s">
         <v>72</v>
@@ -11513,7 +11513,7 @@
         <v>40041</v>
       </c>
       <c r="E328">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F328" s="1" t="s">
         <v>72</v>
@@ -11545,7 +11545,7 @@
         <v>50041</v>
       </c>
       <c r="E329">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F329" s="1" t="s">
         <v>72</v>
@@ -11577,7 +11577,7 @@
         <v>60041</v>
       </c>
       <c r="E330">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F330" s="1" t="s">
         <v>72</v>
@@ -11609,7 +11609,7 @@
         <v>70041</v>
       </c>
       <c r="E331">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F331" s="1" t="s">
         <v>72</v>
@@ -11641,7 +11641,7 @@
         <v>80041</v>
       </c>
       <c r="E332">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F332" s="1" t="s">
         <v>72</v>
@@ -11673,7 +11673,7 @@
         <v>10042</v>
       </c>
       <c r="E333">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="F333" s="1" t="s">
         <v>73</v>
@@ -11705,7 +11705,7 @@
         <v>20042</v>
       </c>
       <c r="E334">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="F334" s="1" t="s">
         <v>73</v>
@@ -11737,7 +11737,7 @@
         <v>30042</v>
       </c>
       <c r="E335">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="F335" s="1" t="s">
         <v>73</v>
@@ -11769,7 +11769,7 @@
         <v>40042</v>
       </c>
       <c r="E336">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="F336" s="1" t="s">
         <v>73</v>
@@ -11801,7 +11801,7 @@
         <v>50042</v>
       </c>
       <c r="E337">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="F337" s="1" t="s">
         <v>73</v>
@@ -11833,7 +11833,7 @@
         <v>60042</v>
       </c>
       <c r="E338">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="F338" s="1" t="s">
         <v>73</v>
@@ -11865,7 +11865,7 @@
         <v>70042</v>
       </c>
       <c r="E339">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="F339" s="1" t="s">
         <v>73</v>
@@ -11897,7 +11897,7 @@
         <v>80042</v>
       </c>
       <c r="E340">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="F340" s="1" t="s">
         <v>73</v>
@@ -11929,7 +11929,7 @@
         <v>10043</v>
       </c>
       <c r="E341">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="F341" s="1" t="s">
         <v>74</v>
@@ -11961,7 +11961,7 @@
         <v>20043</v>
       </c>
       <c r="E342">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="F342" s="1" t="s">
         <v>74</v>
@@ -11993,7 +11993,7 @@
         <v>30043</v>
       </c>
       <c r="E343">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="F343" s="1" t="s">
         <v>74</v>
@@ -12025,7 +12025,7 @@
         <v>40043</v>
       </c>
       <c r="E344">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="F344" s="1" t="s">
         <v>74</v>
@@ -12057,7 +12057,7 @@
         <v>50043</v>
       </c>
       <c r="E345">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="F345" s="1" t="s">
         <v>74</v>
@@ -12089,7 +12089,7 @@
         <v>60043</v>
       </c>
       <c r="E346">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="F346" s="1" t="s">
         <v>74</v>
@@ -12121,7 +12121,7 @@
         <v>70043</v>
       </c>
       <c r="E347">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="F347" s="1" t="s">
         <v>74</v>
@@ -12153,7 +12153,7 @@
         <v>80043</v>
       </c>
       <c r="E348">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="F348" s="1" t="s">
         <v>74</v>
@@ -12185,7 +12185,7 @@
         <v>10044</v>
       </c>
       <c r="E349">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="F349" s="1" t="s">
         <v>75</v>
@@ -12217,7 +12217,7 @@
         <v>20044</v>
       </c>
       <c r="E350">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="F350" s="1" t="s">
         <v>75</v>
@@ -12249,7 +12249,7 @@
         <v>30044</v>
       </c>
       <c r="E351">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="F351" s="1" t="s">
         <v>75</v>
@@ -12281,7 +12281,7 @@
         <v>40044</v>
       </c>
       <c r="E352">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="F352" s="1" t="s">
         <v>75</v>
@@ -12313,7 +12313,7 @@
         <v>50044</v>
       </c>
       <c r="E353">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="F353" s="1" t="s">
         <v>75</v>
@@ -12345,7 +12345,7 @@
         <v>60044</v>
       </c>
       <c r="E354">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="F354" s="1" t="s">
         <v>75</v>
@@ -12377,7 +12377,7 @@
         <v>70044</v>
       </c>
       <c r="E355">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="F355" s="1" t="s">
         <v>75</v>
@@ -12409,7 +12409,7 @@
         <v>80044</v>
       </c>
       <c r="E356">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="F356" s="1" t="s">
         <v>75</v>
@@ -12441,7 +12441,7 @@
         <v>10045</v>
       </c>
       <c r="E357">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="F357" s="1" t="s">
         <v>76</v>
@@ -12473,7 +12473,7 @@
         <v>20045</v>
       </c>
       <c r="E358">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="F358" s="1" t="s">
         <v>76</v>
@@ -12505,7 +12505,7 @@
         <v>30045</v>
       </c>
       <c r="E359">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="F359" s="1" t="s">
         <v>76</v>
@@ -12537,7 +12537,7 @@
         <v>40045</v>
       </c>
       <c r="E360">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="F360" s="1" t="s">
         <v>76</v>
@@ -12569,7 +12569,7 @@
         <v>50045</v>
       </c>
       <c r="E361">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="F361" s="1" t="s">
         <v>76</v>
@@ -12601,7 +12601,7 @@
         <v>60045</v>
       </c>
       <c r="E362">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="F362" s="1" t="s">
         <v>76</v>
@@ -12633,7 +12633,7 @@
         <v>70045</v>
       </c>
       <c r="E363">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="F363" s="1" t="s">
         <v>76</v>
@@ -12665,7 +12665,7 @@
         <v>80045</v>
       </c>
       <c r="E364">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="F364" s="1" t="s">
         <v>76</v>
@@ -12697,7 +12697,7 @@
         <v>10046</v>
       </c>
       <c r="E365">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F365" s="1" t="s">
         <v>77</v>
@@ -12729,7 +12729,7 @@
         <v>20046</v>
       </c>
       <c r="E366">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F366" s="1" t="s">
         <v>77</v>
@@ -12761,7 +12761,7 @@
         <v>30046</v>
       </c>
       <c r="E367">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F367" s="1" t="s">
         <v>77</v>
@@ -12793,7 +12793,7 @@
         <v>40046</v>
       </c>
       <c r="E368">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F368" s="1" t="s">
         <v>77</v>
@@ -12825,7 +12825,7 @@
         <v>50046</v>
       </c>
       <c r="E369">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F369" s="1" t="s">
         <v>77</v>
@@ -12857,7 +12857,7 @@
         <v>60046</v>
       </c>
       <c r="E370">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F370" s="1" t="s">
         <v>77</v>
@@ -12889,7 +12889,7 @@
         <v>70046</v>
       </c>
       <c r="E371">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F371" s="1" t="s">
         <v>77</v>
@@ -12921,7 +12921,7 @@
         <v>80046</v>
       </c>
       <c r="E372">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F372" s="1" t="s">
         <v>77</v>
@@ -12953,7 +12953,7 @@
         <v>10047</v>
       </c>
       <c r="E373">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="F373" s="1" t="s">
         <v>78</v>
@@ -12985,7 +12985,7 @@
         <v>20047</v>
       </c>
       <c r="E374">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="F374" s="1" t="s">
         <v>78</v>
@@ -13017,7 +13017,7 @@
         <v>30047</v>
       </c>
       <c r="E375">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="F375" s="1" t="s">
         <v>78</v>
@@ -13049,7 +13049,7 @@
         <v>40047</v>
       </c>
       <c r="E376">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="F376" s="1" t="s">
         <v>78</v>
@@ -13081,7 +13081,7 @@
         <v>50047</v>
       </c>
       <c r="E377">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="F377" s="1" t="s">
         <v>78</v>
@@ -13113,7 +13113,7 @@
         <v>60047</v>
       </c>
       <c r="E378">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="F378" s="1" t="s">
         <v>78</v>
@@ -13145,7 +13145,7 @@
         <v>70047</v>
       </c>
       <c r="E379">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="F379" s="1" t="s">
         <v>78</v>
@@ -13177,7 +13177,7 @@
         <v>80047</v>
       </c>
       <c r="E380">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="F380" s="1" t="s">
         <v>78</v>
@@ -13209,7 +13209,7 @@
         <v>10048</v>
       </c>
       <c r="E381">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="F381" s="1" t="s">
         <v>79</v>
@@ -13241,7 +13241,7 @@
         <v>20048</v>
       </c>
       <c r="E382">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="F382" s="1" t="s">
         <v>79</v>
@@ -13273,7 +13273,7 @@
         <v>30048</v>
       </c>
       <c r="E383">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="F383" s="1" t="s">
         <v>79</v>
@@ -13305,7 +13305,7 @@
         <v>40048</v>
       </c>
       <c r="E384">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="F384" s="1" t="s">
         <v>79</v>
@@ -13337,7 +13337,7 @@
         <v>50048</v>
       </c>
       <c r="E385">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="F385" s="1" t="s">
         <v>79</v>
@@ -13369,7 +13369,7 @@
         <v>60048</v>
       </c>
       <c r="E386">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="F386" s="1" t="s">
         <v>79</v>
@@ -13401,7 +13401,7 @@
         <v>70048</v>
       </c>
       <c r="E387">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="F387" s="1" t="s">
         <v>79</v>
@@ -13433,7 +13433,7 @@
         <v>80048</v>
       </c>
       <c r="E388">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="F388" s="1" t="s">
         <v>79</v>
@@ -13465,7 +13465,7 @@
         <v>10049</v>
       </c>
       <c r="E389">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="F389" s="1" t="s">
         <v>80</v>
@@ -13497,7 +13497,7 @@
         <v>20049</v>
       </c>
       <c r="E390">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="F390" s="1" t="s">
         <v>80</v>
@@ -13529,7 +13529,7 @@
         <v>30049</v>
       </c>
       <c r="E391">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="F391" s="1" t="s">
         <v>80</v>
@@ -13561,7 +13561,7 @@
         <v>40049</v>
       </c>
       <c r="E392">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="F392" s="1" t="s">
         <v>80</v>
@@ -13593,7 +13593,7 @@
         <v>50049</v>
       </c>
       <c r="E393">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="F393" s="1" t="s">
         <v>80</v>
@@ -13625,7 +13625,7 @@
         <v>60049</v>
       </c>
       <c r="E394">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="F394" s="1" t="s">
         <v>80</v>
@@ -13657,7 +13657,7 @@
         <v>70049</v>
       </c>
       <c r="E395">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="F395" s="1" t="s">
         <v>80</v>
@@ -13689,7 +13689,7 @@
         <v>80049</v>
       </c>
       <c r="E396">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="F396" s="1" t="s">
         <v>80</v>
@@ -13721,7 +13721,7 @@
         <v>10050</v>
       </c>
       <c r="E397">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="F397" s="1" t="s">
         <v>81</v>
@@ -13753,7 +13753,7 @@
         <v>20050</v>
       </c>
       <c r="E398">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="F398" s="1" t="s">
         <v>81</v>
@@ -13785,7 +13785,7 @@
         <v>30050</v>
       </c>
       <c r="E399">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="F399" s="1" t="s">
         <v>81</v>
@@ -13817,7 +13817,7 @@
         <v>40050</v>
       </c>
       <c r="E400">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="F400" s="1" t="s">
         <v>81</v>
@@ -13849,7 +13849,7 @@
         <v>50050</v>
       </c>
       <c r="E401">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="F401" s="1" t="s">
         <v>81</v>
@@ -13881,7 +13881,7 @@
         <v>60050</v>
       </c>
       <c r="E402">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="F402" s="1" t="s">
         <v>81</v>
@@ -13913,7 +13913,7 @@
         <v>70050</v>
       </c>
       <c r="E403">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="F403" s="1" t="s">
         <v>81</v>
@@ -13945,7 +13945,7 @@
         <v>80050</v>
       </c>
       <c r="E404">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="F404" s="1" t="s">
         <v>81</v>
@@ -13977,7 +13977,7 @@
         <v>-1</v>
       </c>
       <c r="E405">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F405" s="1" t="s">
         <v>82</v>
@@ -14009,7 +14009,7 @@
         <v>-1</v>
       </c>
       <c r="E406">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F406" s="1" t="s">
         <v>82</v>
@@ -14041,7 +14041,7 @@
         <v>-1</v>
       </c>
       <c r="E407">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F407" s="1" t="s">
         <v>82</v>
@@ -14073,7 +14073,7 @@
         <v>-1</v>
       </c>
       <c r="E408">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F408" s="1" t="s">
         <v>82</v>
@@ -14105,7 +14105,7 @@
         <v>-1</v>
       </c>
       <c r="E409">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F409" s="1" t="s">
         <v>82</v>
@@ -14137,7 +14137,7 @@
         <v>-1</v>
       </c>
       <c r="E410">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F410" s="1" t="s">
         <v>82</v>
@@ -14169,7 +14169,7 @@
         <v>-1</v>
       </c>
       <c r="E411">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F411" s="1" t="s">
         <v>82</v>
@@ -14201,7 +14201,7 @@
         <v>-1</v>
       </c>
       <c r="E412">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F412" s="1" t="s">
         <v>82</v>

--- a/servers/maze_main_server/conf.d/data/maze_equip_pos_lv_v8【迷宫-装备-部位强化等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_equip_pos_lv_v8【迷宫-装备-部位强化等级】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04BF05F0-FB64-423D-BB63-50C9A08DB3F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF594F24-9C74-4601-A876-0C7503EAFD86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3737,7 +3737,7 @@
         <v>10011</v>
       </c>
       <c r="E85">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>42</v>
@@ -3769,7 +3769,7 @@
         <v>20011</v>
       </c>
       <c r="E86">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>42</v>
@@ -3801,7 +3801,7 @@
         <v>30011</v>
       </c>
       <c r="E87">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>42</v>
@@ -3833,7 +3833,7 @@
         <v>40011</v>
       </c>
       <c r="E88">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>42</v>
@@ -3865,7 +3865,7 @@
         <v>50011</v>
       </c>
       <c r="E89">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>42</v>
@@ -3897,7 +3897,7 @@
         <v>60011</v>
       </c>
       <c r="E90">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>42</v>
@@ -3929,7 +3929,7 @@
         <v>70011</v>
       </c>
       <c r="E91">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>42</v>
@@ -3961,7 +3961,7 @@
         <v>80011</v>
       </c>
       <c r="E92">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>42</v>
@@ -3993,7 +3993,7 @@
         <v>10012</v>
       </c>
       <c r="E93">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>43</v>
@@ -4025,7 +4025,7 @@
         <v>20012</v>
       </c>
       <c r="E94">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>43</v>
@@ -4057,7 +4057,7 @@
         <v>30012</v>
       </c>
       <c r="E95">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>43</v>
@@ -4089,7 +4089,7 @@
         <v>40012</v>
       </c>
       <c r="E96">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>43</v>
@@ -4121,7 +4121,7 @@
         <v>50012</v>
       </c>
       <c r="E97">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>43</v>
@@ -4153,7 +4153,7 @@
         <v>60012</v>
       </c>
       <c r="E98">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>43</v>
@@ -4185,7 +4185,7 @@
         <v>70012</v>
       </c>
       <c r="E99">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>43</v>
@@ -4217,7 +4217,7 @@
         <v>80012</v>
       </c>
       <c r="E100">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>43</v>
@@ -4249,7 +4249,7 @@
         <v>10013</v>
       </c>
       <c r="E101">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>44</v>
@@ -4281,7 +4281,7 @@
         <v>20013</v>
       </c>
       <c r="E102">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>44</v>
@@ -4313,7 +4313,7 @@
         <v>30013</v>
       </c>
       <c r="E103">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>44</v>
@@ -4345,7 +4345,7 @@
         <v>40013</v>
       </c>
       <c r="E104">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>44</v>
@@ -4377,7 +4377,7 @@
         <v>50013</v>
       </c>
       <c r="E105">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>44</v>
@@ -4409,7 +4409,7 @@
         <v>60013</v>
       </c>
       <c r="E106">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>44</v>
@@ -4441,7 +4441,7 @@
         <v>70013</v>
       </c>
       <c r="E107">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>44</v>
@@ -4473,7 +4473,7 @@
         <v>80013</v>
       </c>
       <c r="E108">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>44</v>
@@ -4505,7 +4505,7 @@
         <v>10014</v>
       </c>
       <c r="E109">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>45</v>
@@ -4537,7 +4537,7 @@
         <v>20014</v>
       </c>
       <c r="E110">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>45</v>
@@ -4569,7 +4569,7 @@
         <v>30014</v>
       </c>
       <c r="E111">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>45</v>
@@ -4601,7 +4601,7 @@
         <v>40014</v>
       </c>
       <c r="E112">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>45</v>
@@ -4633,7 +4633,7 @@
         <v>50014</v>
       </c>
       <c r="E113">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>45</v>
@@ -4665,7 +4665,7 @@
         <v>60014</v>
       </c>
       <c r="E114">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>45</v>
@@ -4697,7 +4697,7 @@
         <v>70014</v>
       </c>
       <c r="E115">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>45</v>
@@ -4729,7 +4729,7 @@
         <v>80014</v>
       </c>
       <c r="E116">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>45</v>
@@ -4761,7 +4761,7 @@
         <v>10015</v>
       </c>
       <c r="E117">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>46</v>
@@ -4793,7 +4793,7 @@
         <v>20015</v>
       </c>
       <c r="E118">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>46</v>
@@ -4825,7 +4825,7 @@
         <v>30015</v>
       </c>
       <c r="E119">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>46</v>
@@ -4857,7 +4857,7 @@
         <v>40015</v>
       </c>
       <c r="E120">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>46</v>
@@ -4889,7 +4889,7 @@
         <v>50015</v>
       </c>
       <c r="E121">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>46</v>
@@ -4921,7 +4921,7 @@
         <v>60015</v>
       </c>
       <c r="E122">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>46</v>
@@ -4953,7 +4953,7 @@
         <v>70015</v>
       </c>
       <c r="E123">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>46</v>
@@ -4985,7 +4985,7 @@
         <v>80015</v>
       </c>
       <c r="E124">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>46</v>
@@ -5017,7 +5017,7 @@
         <v>10016</v>
       </c>
       <c r="E125">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>47</v>
@@ -5049,7 +5049,7 @@
         <v>20016</v>
       </c>
       <c r="E126">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>47</v>
@@ -5081,7 +5081,7 @@
         <v>30016</v>
       </c>
       <c r="E127">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>47</v>
@@ -5113,7 +5113,7 @@
         <v>40016</v>
       </c>
       <c r="E128">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>47</v>
@@ -5145,7 +5145,7 @@
         <v>50016</v>
       </c>
       <c r="E129">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>47</v>
@@ -5177,7 +5177,7 @@
         <v>60016</v>
       </c>
       <c r="E130">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>47</v>
@@ -5209,7 +5209,7 @@
         <v>70016</v>
       </c>
       <c r="E131">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>47</v>
@@ -5241,7 +5241,7 @@
         <v>80016</v>
       </c>
       <c r="E132">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>47</v>
@@ -5273,7 +5273,7 @@
         <v>10017</v>
       </c>
       <c r="E133">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>48</v>
@@ -5305,7 +5305,7 @@
         <v>20017</v>
       </c>
       <c r="E134">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>48</v>
@@ -5337,7 +5337,7 @@
         <v>30017</v>
       </c>
       <c r="E135">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>48</v>
@@ -5369,7 +5369,7 @@
         <v>40017</v>
       </c>
       <c r="E136">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>48</v>
@@ -5401,7 +5401,7 @@
         <v>50017</v>
       </c>
       <c r="E137">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>48</v>
@@ -5433,7 +5433,7 @@
         <v>60017</v>
       </c>
       <c r="E138">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>48</v>
@@ -5465,7 +5465,7 @@
         <v>70017</v>
       </c>
       <c r="E139">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>48</v>
@@ -5497,7 +5497,7 @@
         <v>80017</v>
       </c>
       <c r="E140">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>48</v>
@@ -5529,7 +5529,7 @@
         <v>10018</v>
       </c>
       <c r="E141">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>49</v>
@@ -5561,7 +5561,7 @@
         <v>20018</v>
       </c>
       <c r="E142">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>49</v>
@@ -5593,7 +5593,7 @@
         <v>30018</v>
       </c>
       <c r="E143">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>49</v>
@@ -5625,7 +5625,7 @@
         <v>40018</v>
       </c>
       <c r="E144">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>49</v>
@@ -5657,7 +5657,7 @@
         <v>50018</v>
       </c>
       <c r="E145">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>49</v>
@@ -5689,7 +5689,7 @@
         <v>60018</v>
       </c>
       <c r="E146">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>49</v>
@@ -5721,7 +5721,7 @@
         <v>70018</v>
       </c>
       <c r="E147">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>49</v>
@@ -5753,7 +5753,7 @@
         <v>80018</v>
       </c>
       <c r="E148">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>49</v>
@@ -5785,7 +5785,7 @@
         <v>10019</v>
       </c>
       <c r="E149">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>50</v>
@@ -5817,7 +5817,7 @@
         <v>20019</v>
       </c>
       <c r="E150">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>50</v>
@@ -5849,7 +5849,7 @@
         <v>30019</v>
       </c>
       <c r="E151">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>50</v>
@@ -5881,7 +5881,7 @@
         <v>40019</v>
       </c>
       <c r="E152">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>50</v>
@@ -5913,7 +5913,7 @@
         <v>50019</v>
       </c>
       <c r="E153">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>50</v>
@@ -5945,7 +5945,7 @@
         <v>60019</v>
       </c>
       <c r="E154">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>50</v>
@@ -5977,7 +5977,7 @@
         <v>70019</v>
       </c>
       <c r="E155">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>50</v>
@@ -6009,7 +6009,7 @@
         <v>80019</v>
       </c>
       <c r="E156">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>50</v>
@@ -6041,7 +6041,7 @@
         <v>10020</v>
       </c>
       <c r="E157">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>51</v>
@@ -6073,7 +6073,7 @@
         <v>20020</v>
       </c>
       <c r="E158">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>51</v>
@@ -6105,7 +6105,7 @@
         <v>30020</v>
       </c>
       <c r="E159">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>51</v>
@@ -6137,7 +6137,7 @@
         <v>40020</v>
       </c>
       <c r="E160">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>51</v>
@@ -6169,7 +6169,7 @@
         <v>50020</v>
       </c>
       <c r="E161">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>51</v>
@@ -6201,7 +6201,7 @@
         <v>60020</v>
       </c>
       <c r="E162">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>51</v>
@@ -6233,7 +6233,7 @@
         <v>70020</v>
       </c>
       <c r="E163">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>51</v>
@@ -6265,7 +6265,7 @@
         <v>80020</v>
       </c>
       <c r="E164">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>51</v>
@@ -6297,7 +6297,7 @@
         <v>10021</v>
       </c>
       <c r="E165">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>52</v>
@@ -6329,7 +6329,7 @@
         <v>20021</v>
       </c>
       <c r="E166">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>52</v>
@@ -6361,7 +6361,7 @@
         <v>30021</v>
       </c>
       <c r="E167">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>52</v>
@@ -6393,7 +6393,7 @@
         <v>40021</v>
       </c>
       <c r="E168">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>52</v>
@@ -6425,7 +6425,7 @@
         <v>50021</v>
       </c>
       <c r="E169">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>52</v>
@@ -6457,7 +6457,7 @@
         <v>60021</v>
       </c>
       <c r="E170">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>52</v>
@@ -6489,7 +6489,7 @@
         <v>70021</v>
       </c>
       <c r="E171">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>52</v>
@@ -6521,7 +6521,7 @@
         <v>80021</v>
       </c>
       <c r="E172">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>52</v>
@@ -6553,7 +6553,7 @@
         <v>10022</v>
       </c>
       <c r="E173">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>53</v>
@@ -6585,7 +6585,7 @@
         <v>20022</v>
       </c>
       <c r="E174">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>53</v>
@@ -6617,7 +6617,7 @@
         <v>30022</v>
       </c>
       <c r="E175">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>53</v>
@@ -6649,7 +6649,7 @@
         <v>40022</v>
       </c>
       <c r="E176">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>53</v>
@@ -6681,7 +6681,7 @@
         <v>50022</v>
       </c>
       <c r="E177">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>53</v>
@@ -6713,7 +6713,7 @@
         <v>60022</v>
       </c>
       <c r="E178">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>53</v>
@@ -6745,7 +6745,7 @@
         <v>70022</v>
       </c>
       <c r="E179">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>53</v>
@@ -6777,7 +6777,7 @@
         <v>80022</v>
       </c>
       <c r="E180">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>53</v>
@@ -6809,7 +6809,7 @@
         <v>10023</v>
       </c>
       <c r="E181">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>54</v>
@@ -6841,7 +6841,7 @@
         <v>20023</v>
       </c>
       <c r="E182">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>54</v>
@@ -6873,7 +6873,7 @@
         <v>30023</v>
       </c>
       <c r="E183">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>54</v>
@@ -6905,7 +6905,7 @@
         <v>40023</v>
       </c>
       <c r="E184">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>54</v>
@@ -6937,7 +6937,7 @@
         <v>50023</v>
       </c>
       <c r="E185">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>54</v>
@@ -6969,7 +6969,7 @@
         <v>60023</v>
       </c>
       <c r="E186">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>54</v>
@@ -7001,7 +7001,7 @@
         <v>70023</v>
       </c>
       <c r="E187">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>54</v>
@@ -7033,7 +7033,7 @@
         <v>80023</v>
       </c>
       <c r="E188">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>54</v>
@@ -7065,7 +7065,7 @@
         <v>10024</v>
       </c>
       <c r="E189">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>55</v>
@@ -7097,7 +7097,7 @@
         <v>20024</v>
       </c>
       <c r="E190">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>55</v>
@@ -7129,7 +7129,7 @@
         <v>30024</v>
       </c>
       <c r="E191">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>55</v>
@@ -7161,7 +7161,7 @@
         <v>40024</v>
       </c>
       <c r="E192">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>55</v>
@@ -7193,7 +7193,7 @@
         <v>50024</v>
       </c>
       <c r="E193">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>55</v>
@@ -7225,7 +7225,7 @@
         <v>60024</v>
       </c>
       <c r="E194">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>55</v>
@@ -7257,7 +7257,7 @@
         <v>70024</v>
       </c>
       <c r="E195">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>55</v>
@@ -7289,7 +7289,7 @@
         <v>80024</v>
       </c>
       <c r="E196">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>55</v>
@@ -7321,7 +7321,7 @@
         <v>10025</v>
       </c>
       <c r="E197">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>56</v>
@@ -7353,7 +7353,7 @@
         <v>20025</v>
       </c>
       <c r="E198">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>56</v>
@@ -7385,7 +7385,7 @@
         <v>30025</v>
       </c>
       <c r="E199">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>56</v>
@@ -7417,7 +7417,7 @@
         <v>40025</v>
       </c>
       <c r="E200">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>56</v>
@@ -7449,7 +7449,7 @@
         <v>50025</v>
       </c>
       <c r="E201">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>56</v>
@@ -7481,7 +7481,7 @@
         <v>60025</v>
       </c>
       <c r="E202">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>56</v>
@@ -7513,7 +7513,7 @@
         <v>70025</v>
       </c>
       <c r="E203">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>56</v>
@@ -7545,7 +7545,7 @@
         <v>80025</v>
       </c>
       <c r="E204">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>56</v>
@@ -7577,7 +7577,7 @@
         <v>10026</v>
       </c>
       <c r="E205">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>57</v>
@@ -7609,7 +7609,7 @@
         <v>20026</v>
       </c>
       <c r="E206">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>57</v>
@@ -7641,7 +7641,7 @@
         <v>30026</v>
       </c>
       <c r="E207">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>57</v>
@@ -7673,7 +7673,7 @@
         <v>40026</v>
       </c>
       <c r="E208">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>57</v>
@@ -7705,7 +7705,7 @@
         <v>50026</v>
       </c>
       <c r="E209">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>57</v>
@@ -7737,7 +7737,7 @@
         <v>60026</v>
       </c>
       <c r="E210">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>57</v>
@@ -7769,7 +7769,7 @@
         <v>70026</v>
       </c>
       <c r="E211">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>57</v>
@@ -7801,7 +7801,7 @@
         <v>80026</v>
       </c>
       <c r="E212">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>57</v>
@@ -7833,7 +7833,7 @@
         <v>10027</v>
       </c>
       <c r="E213">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>58</v>
@@ -7865,7 +7865,7 @@
         <v>20027</v>
       </c>
       <c r="E214">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>58</v>
@@ -7897,7 +7897,7 @@
         <v>30027</v>
       </c>
       <c r="E215">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>58</v>
@@ -7929,7 +7929,7 @@
         <v>40027</v>
       </c>
       <c r="E216">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>58</v>
@@ -7961,7 +7961,7 @@
         <v>50027</v>
       </c>
       <c r="E217">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>58</v>
@@ -7993,7 +7993,7 @@
         <v>60027</v>
       </c>
       <c r="E218">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>58</v>
@@ -8025,7 +8025,7 @@
         <v>70027</v>
       </c>
       <c r="E219">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F219" s="1" t="s">
         <v>58</v>
@@ -8057,7 +8057,7 @@
         <v>80027</v>
       </c>
       <c r="E220">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F220" s="1" t="s">
         <v>58</v>
@@ -8089,7 +8089,7 @@
         <v>10028</v>
       </c>
       <c r="E221">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F221" s="1" t="s">
         <v>59</v>
@@ -8121,7 +8121,7 @@
         <v>20028</v>
       </c>
       <c r="E222">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F222" s="1" t="s">
         <v>59</v>
@@ -8153,7 +8153,7 @@
         <v>30028</v>
       </c>
       <c r="E223">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F223" s="1" t="s">
         <v>59</v>
@@ -8185,7 +8185,7 @@
         <v>40028</v>
       </c>
       <c r="E224">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F224" s="1" t="s">
         <v>59</v>
@@ -8217,7 +8217,7 @@
         <v>50028</v>
       </c>
       <c r="E225">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F225" s="1" t="s">
         <v>59</v>
@@ -8249,7 +8249,7 @@
         <v>60028</v>
       </c>
       <c r="E226">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F226" s="1" t="s">
         <v>59</v>
@@ -8281,7 +8281,7 @@
         <v>70028</v>
       </c>
       <c r="E227">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F227" s="1" t="s">
         <v>59</v>
@@ -8313,7 +8313,7 @@
         <v>80028</v>
       </c>
       <c r="E228">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F228" s="1" t="s">
         <v>59</v>
@@ -8345,7 +8345,7 @@
         <v>10029</v>
       </c>
       <c r="E229">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F229" s="1" t="s">
         <v>60</v>
@@ -8377,7 +8377,7 @@
         <v>20029</v>
       </c>
       <c r="E230">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F230" s="1" t="s">
         <v>60</v>
@@ -8409,7 +8409,7 @@
         <v>30029</v>
       </c>
       <c r="E231">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F231" s="1" t="s">
         <v>60</v>
@@ -8441,7 +8441,7 @@
         <v>40029</v>
       </c>
       <c r="E232">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F232" s="1" t="s">
         <v>60</v>
@@ -8473,7 +8473,7 @@
         <v>50029</v>
       </c>
       <c r="E233">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F233" s="1" t="s">
         <v>60</v>
@@ -8505,7 +8505,7 @@
         <v>60029</v>
       </c>
       <c r="E234">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F234" s="1" t="s">
         <v>60</v>
@@ -8537,7 +8537,7 @@
         <v>70029</v>
       </c>
       <c r="E235">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F235" s="1" t="s">
         <v>60</v>
@@ -8569,7 +8569,7 @@
         <v>80029</v>
       </c>
       <c r="E236">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F236" s="1" t="s">
         <v>60</v>
@@ -8601,7 +8601,7 @@
         <v>10030</v>
       </c>
       <c r="E237">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F237" s="1" t="s">
         <v>61</v>
@@ -8633,7 +8633,7 @@
         <v>20030</v>
       </c>
       <c r="E238">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F238" s="1" t="s">
         <v>61</v>
@@ -8665,7 +8665,7 @@
         <v>30030</v>
       </c>
       <c r="E239">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F239" s="1" t="s">
         <v>61</v>
@@ -8697,7 +8697,7 @@
         <v>40030</v>
       </c>
       <c r="E240">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F240" s="1" t="s">
         <v>61</v>
@@ -8729,7 +8729,7 @@
         <v>50030</v>
       </c>
       <c r="E241">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F241" s="1" t="s">
         <v>61</v>
@@ -8761,7 +8761,7 @@
         <v>60030</v>
       </c>
       <c r="E242">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F242" s="1" t="s">
         <v>61</v>
@@ -8793,7 +8793,7 @@
         <v>70030</v>
       </c>
       <c r="E243">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F243" s="1" t="s">
         <v>61</v>
@@ -8825,7 +8825,7 @@
         <v>80030</v>
       </c>
       <c r="E244">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F244" s="1" t="s">
         <v>61</v>
@@ -8857,7 +8857,7 @@
         <v>10031</v>
       </c>
       <c r="E245">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F245" s="1" t="s">
         <v>62</v>
@@ -8889,7 +8889,7 @@
         <v>20031</v>
       </c>
       <c r="E246">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F246" s="1" t="s">
         <v>62</v>
@@ -8921,7 +8921,7 @@
         <v>30031</v>
       </c>
       <c r="E247">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F247" s="1" t="s">
         <v>62</v>
@@ -8953,7 +8953,7 @@
         <v>40031</v>
       </c>
       <c r="E248">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F248" s="1" t="s">
         <v>62</v>
@@ -8985,7 +8985,7 @@
         <v>50031</v>
       </c>
       <c r="E249">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F249" s="1" t="s">
         <v>62</v>
@@ -9017,7 +9017,7 @@
         <v>60031</v>
       </c>
       <c r="E250">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F250" s="1" t="s">
         <v>62</v>
@@ -9049,7 +9049,7 @@
         <v>70031</v>
       </c>
       <c r="E251">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F251" s="1" t="s">
         <v>62</v>
@@ -9081,7 +9081,7 @@
         <v>80031</v>
       </c>
       <c r="E252">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F252" s="1" t="s">
         <v>62</v>
@@ -9113,7 +9113,7 @@
         <v>10032</v>
       </c>
       <c r="E253">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F253" s="1" t="s">
         <v>63</v>
@@ -9145,7 +9145,7 @@
         <v>20032</v>
       </c>
       <c r="E254">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F254" s="1" t="s">
         <v>63</v>
@@ -9177,7 +9177,7 @@
         <v>30032</v>
       </c>
       <c r="E255">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F255" s="1" t="s">
         <v>63</v>
@@ -9209,7 +9209,7 @@
         <v>40032</v>
       </c>
       <c r="E256">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F256" s="1" t="s">
         <v>63</v>
@@ -9241,7 +9241,7 @@
         <v>50032</v>
       </c>
       <c r="E257">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F257" s="1" t="s">
         <v>63</v>
@@ -9273,7 +9273,7 @@
         <v>60032</v>
       </c>
       <c r="E258">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F258" s="1" t="s">
         <v>63</v>
@@ -9305,7 +9305,7 @@
         <v>70032</v>
       </c>
       <c r="E259">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F259" s="1" t="s">
         <v>63</v>
@@ -9337,7 +9337,7 @@
         <v>80032</v>
       </c>
       <c r="E260">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F260" s="1" t="s">
         <v>63</v>
@@ -9369,7 +9369,7 @@
         <v>10033</v>
       </c>
       <c r="E261">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F261" s="1" t="s">
         <v>64</v>
@@ -9401,7 +9401,7 @@
         <v>20033</v>
       </c>
       <c r="E262">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F262" s="1" t="s">
         <v>64</v>
@@ -9433,7 +9433,7 @@
         <v>30033</v>
       </c>
       <c r="E263">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F263" s="1" t="s">
         <v>64</v>
@@ -9465,7 +9465,7 @@
         <v>40033</v>
       </c>
       <c r="E264">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F264" s="1" t="s">
         <v>64</v>
@@ -9497,7 +9497,7 @@
         <v>50033</v>
       </c>
       <c r="E265">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F265" s="1" t="s">
         <v>64</v>
@@ -9529,7 +9529,7 @@
         <v>60033</v>
       </c>
       <c r="E266">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F266" s="1" t="s">
         <v>64</v>
@@ -9561,7 +9561,7 @@
         <v>70033</v>
       </c>
       <c r="E267">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F267" s="1" t="s">
         <v>64</v>
@@ -9593,7 +9593,7 @@
         <v>80033</v>
       </c>
       <c r="E268">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F268" s="1" t="s">
         <v>64</v>
@@ -9625,7 +9625,7 @@
         <v>10034</v>
       </c>
       <c r="E269">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F269" s="1" t="s">
         <v>65</v>
@@ -9657,7 +9657,7 @@
         <v>20034</v>
       </c>
       <c r="E270">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F270" s="1" t="s">
         <v>65</v>
@@ -9689,7 +9689,7 @@
         <v>30034</v>
       </c>
       <c r="E271">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F271" s="1" t="s">
         <v>65</v>
@@ -9721,7 +9721,7 @@
         <v>40034</v>
       </c>
       <c r="E272">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F272" s="1" t="s">
         <v>65</v>
@@ -9753,7 +9753,7 @@
         <v>50034</v>
       </c>
       <c r="E273">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>65</v>
@@ -9785,7 +9785,7 @@
         <v>60034</v>
       </c>
       <c r="E274">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>65</v>
@@ -9817,7 +9817,7 @@
         <v>70034</v>
       </c>
       <c r="E275">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F275" s="1" t="s">
         <v>65</v>
@@ -9849,7 +9849,7 @@
         <v>80034</v>
       </c>
       <c r="E276">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F276" s="1" t="s">
         <v>65</v>
@@ -9881,7 +9881,7 @@
         <v>10035</v>
       </c>
       <c r="E277">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F277" s="1" t="s">
         <v>66</v>
@@ -9913,7 +9913,7 @@
         <v>20035</v>
       </c>
       <c r="E278">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F278" s="1" t="s">
         <v>66</v>
@@ -9945,7 +9945,7 @@
         <v>30035</v>
       </c>
       <c r="E279">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F279" s="1" t="s">
         <v>66</v>
@@ -9977,7 +9977,7 @@
         <v>40035</v>
       </c>
       <c r="E280">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F280" s="1" t="s">
         <v>66</v>
@@ -10009,7 +10009,7 @@
         <v>50035</v>
       </c>
       <c r="E281">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F281" s="1" t="s">
         <v>66</v>
@@ -10041,7 +10041,7 @@
         <v>60035</v>
       </c>
       <c r="E282">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F282" s="1" t="s">
         <v>66</v>
@@ -10073,7 +10073,7 @@
         <v>70035</v>
       </c>
       <c r="E283">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F283" s="1" t="s">
         <v>66</v>
@@ -10105,7 +10105,7 @@
         <v>80035</v>
       </c>
       <c r="E284">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F284" s="1" t="s">
         <v>66</v>
@@ -10137,7 +10137,7 @@
         <v>10036</v>
       </c>
       <c r="E285">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F285" s="1" t="s">
         <v>67</v>
@@ -10169,7 +10169,7 @@
         <v>20036</v>
       </c>
       <c r="E286">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F286" s="1" t="s">
         <v>67</v>
@@ -10201,7 +10201,7 @@
         <v>30036</v>
       </c>
       <c r="E287">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F287" s="1" t="s">
         <v>67</v>
@@ -10233,7 +10233,7 @@
         <v>40036</v>
       </c>
       <c r="E288">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F288" s="1" t="s">
         <v>67</v>
@@ -10265,7 +10265,7 @@
         <v>50036</v>
       </c>
       <c r="E289">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F289" s="1" t="s">
         <v>67</v>
@@ -10297,7 +10297,7 @@
         <v>60036</v>
       </c>
       <c r="E290">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F290" s="1" t="s">
         <v>67</v>
@@ -10329,7 +10329,7 @@
         <v>70036</v>
       </c>
       <c r="E291">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F291" s="1" t="s">
         <v>67</v>
@@ -10361,7 +10361,7 @@
         <v>80036</v>
       </c>
       <c r="E292">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F292" s="1" t="s">
         <v>67</v>
@@ -10393,7 +10393,7 @@
         <v>10037</v>
       </c>
       <c r="E293">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F293" s="1" t="s">
         <v>68</v>
@@ -10425,7 +10425,7 @@
         <v>20037</v>
       </c>
       <c r="E294">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F294" s="1" t="s">
         <v>68</v>
@@ -10457,7 +10457,7 @@
         <v>30037</v>
       </c>
       <c r="E295">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F295" s="1" t="s">
         <v>68</v>
@@ -10489,7 +10489,7 @@
         <v>40037</v>
       </c>
       <c r="E296">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F296" s="1" t="s">
         <v>68</v>
@@ -10521,7 +10521,7 @@
         <v>50037</v>
       </c>
       <c r="E297">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F297" s="1" t="s">
         <v>68</v>
@@ -10553,7 +10553,7 @@
         <v>60037</v>
       </c>
       <c r="E298">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F298" s="1" t="s">
         <v>68</v>
@@ -10585,7 +10585,7 @@
         <v>70037</v>
       </c>
       <c r="E299">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F299" s="1" t="s">
         <v>68</v>
@@ -10617,7 +10617,7 @@
         <v>80037</v>
       </c>
       <c r="E300">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F300" s="1" t="s">
         <v>68</v>
@@ -10649,7 +10649,7 @@
         <v>10038</v>
       </c>
       <c r="E301">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>69</v>
@@ -10681,7 +10681,7 @@
         <v>20038</v>
       </c>
       <c r="E302">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F302" s="1" t="s">
         <v>69</v>
@@ -10713,7 +10713,7 @@
         <v>30038</v>
       </c>
       <c r="E303">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F303" s="1" t="s">
         <v>69</v>
@@ -10745,7 +10745,7 @@
         <v>40038</v>
       </c>
       <c r="E304">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F304" s="1" t="s">
         <v>69</v>
@@ -10777,7 +10777,7 @@
         <v>50038</v>
       </c>
       <c r="E305">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F305" s="1" t="s">
         <v>69</v>
@@ -10809,7 +10809,7 @@
         <v>60038</v>
       </c>
       <c r="E306">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F306" s="1" t="s">
         <v>69</v>
@@ -10841,7 +10841,7 @@
         <v>70038</v>
       </c>
       <c r="E307">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F307" s="1" t="s">
         <v>69</v>
@@ -10873,7 +10873,7 @@
         <v>80038</v>
       </c>
       <c r="E308">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F308" s="1" t="s">
         <v>69</v>
@@ -10905,7 +10905,7 @@
         <v>10039</v>
       </c>
       <c r="E309">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F309" s="1" t="s">
         <v>70</v>
@@ -10937,7 +10937,7 @@
         <v>20039</v>
       </c>
       <c r="E310">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F310" s="1" t="s">
         <v>70</v>
@@ -10969,7 +10969,7 @@
         <v>30039</v>
       </c>
       <c r="E311">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F311" s="1" t="s">
         <v>70</v>
@@ -11001,7 +11001,7 @@
         <v>40039</v>
       </c>
       <c r="E312">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F312" s="1" t="s">
         <v>70</v>
@@ -11033,7 +11033,7 @@
         <v>50039</v>
       </c>
       <c r="E313">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F313" s="1" t="s">
         <v>70</v>
@@ -11065,7 +11065,7 @@
         <v>60039</v>
       </c>
       <c r="E314">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F314" s="1" t="s">
         <v>70</v>
@@ -11097,7 +11097,7 @@
         <v>70039</v>
       </c>
       <c r="E315">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F315" s="1" t="s">
         <v>70</v>
@@ -11129,7 +11129,7 @@
         <v>80039</v>
       </c>
       <c r="E316">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F316" s="1" t="s">
         <v>70</v>
@@ -11161,7 +11161,7 @@
         <v>10040</v>
       </c>
       <c r="E317">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F317" s="1" t="s">
         <v>71</v>
@@ -11193,7 +11193,7 @@
         <v>20040</v>
       </c>
       <c r="E318">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F318" s="1" t="s">
         <v>71</v>
@@ -11225,7 +11225,7 @@
         <v>30040</v>
       </c>
       <c r="E319">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F319" s="1" t="s">
         <v>71</v>
@@ -11257,7 +11257,7 @@
         <v>40040</v>
       </c>
       <c r="E320">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F320" s="1" t="s">
         <v>71</v>
@@ -11289,7 +11289,7 @@
         <v>50040</v>
       </c>
       <c r="E321">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F321" s="1" t="s">
         <v>71</v>
@@ -11321,7 +11321,7 @@
         <v>60040</v>
       </c>
       <c r="E322">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F322" s="1" t="s">
         <v>71</v>
@@ -11353,7 +11353,7 @@
         <v>70040</v>
       </c>
       <c r="E323">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F323" s="1" t="s">
         <v>71</v>
@@ -11385,7 +11385,7 @@
         <v>80040</v>
       </c>
       <c r="E324">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F324" s="1" t="s">
         <v>71</v>
@@ -11417,7 +11417,7 @@
         <v>10041</v>
       </c>
       <c r="E325">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F325" s="1" t="s">
         <v>72</v>
@@ -11449,7 +11449,7 @@
         <v>20041</v>
       </c>
       <c r="E326">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F326" s="1" t="s">
         <v>72</v>
@@ -11481,7 +11481,7 @@
         <v>30041</v>
       </c>
       <c r="E327">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F327" s="1" t="s">
         <v>72</v>
@@ -11513,7 +11513,7 @@
         <v>40041</v>
       </c>
       <c r="E328">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F328" s="1" t="s">
         <v>72</v>
@@ -11545,7 +11545,7 @@
         <v>50041</v>
       </c>
       <c r="E329">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F329" s="1" t="s">
         <v>72</v>
@@ -11577,7 +11577,7 @@
         <v>60041</v>
       </c>
       <c r="E330">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F330" s="1" t="s">
         <v>72</v>
@@ -11609,7 +11609,7 @@
         <v>70041</v>
       </c>
       <c r="E331">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F331" s="1" t="s">
         <v>72</v>
@@ -11641,7 +11641,7 @@
         <v>80041</v>
       </c>
       <c r="E332">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F332" s="1" t="s">
         <v>72</v>
@@ -11673,7 +11673,7 @@
         <v>10042</v>
       </c>
       <c r="E333">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F333" s="1" t="s">
         <v>73</v>
@@ -11705,7 +11705,7 @@
         <v>20042</v>
       </c>
       <c r="E334">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F334" s="1" t="s">
         <v>73</v>
@@ -11737,7 +11737,7 @@
         <v>30042</v>
       </c>
       <c r="E335">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F335" s="1" t="s">
         <v>73</v>
@@ -11769,7 +11769,7 @@
         <v>40042</v>
       </c>
       <c r="E336">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F336" s="1" t="s">
         <v>73</v>
@@ -11801,7 +11801,7 @@
         <v>50042</v>
       </c>
       <c r="E337">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F337" s="1" t="s">
         <v>73</v>
@@ -11833,7 +11833,7 @@
         <v>60042</v>
       </c>
       <c r="E338">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F338" s="1" t="s">
         <v>73</v>
@@ -11865,7 +11865,7 @@
         <v>70042</v>
       </c>
       <c r="E339">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F339" s="1" t="s">
         <v>73</v>
@@ -11897,7 +11897,7 @@
         <v>80042</v>
       </c>
       <c r="E340">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F340" s="1" t="s">
         <v>73</v>
@@ -11929,7 +11929,7 @@
         <v>10043</v>
       </c>
       <c r="E341">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F341" s="1" t="s">
         <v>74</v>
@@ -11961,7 +11961,7 @@
         <v>20043</v>
       </c>
       <c r="E342">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F342" s="1" t="s">
         <v>74</v>
@@ -11993,7 +11993,7 @@
         <v>30043</v>
       </c>
       <c r="E343">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F343" s="1" t="s">
         <v>74</v>
@@ -12025,7 +12025,7 @@
         <v>40043</v>
       </c>
       <c r="E344">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F344" s="1" t="s">
         <v>74</v>
@@ -12057,7 +12057,7 @@
         <v>50043</v>
       </c>
       <c r="E345">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F345" s="1" t="s">
         <v>74</v>
@@ -12089,7 +12089,7 @@
         <v>60043</v>
       </c>
       <c r="E346">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F346" s="1" t="s">
         <v>74</v>
@@ -12121,7 +12121,7 @@
         <v>70043</v>
       </c>
       <c r="E347">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F347" s="1" t="s">
         <v>74</v>
@@ -12153,7 +12153,7 @@
         <v>80043</v>
       </c>
       <c r="E348">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F348" s="1" t="s">
         <v>74</v>
@@ -12185,7 +12185,7 @@
         <v>10044</v>
       </c>
       <c r="E349">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F349" s="1" t="s">
         <v>75</v>
@@ -12217,7 +12217,7 @@
         <v>20044</v>
       </c>
       <c r="E350">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F350" s="1" t="s">
         <v>75</v>
@@ -12249,7 +12249,7 @@
         <v>30044</v>
       </c>
       <c r="E351">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F351" s="1" t="s">
         <v>75</v>
@@ -12281,7 +12281,7 @@
         <v>40044</v>
       </c>
       <c r="E352">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F352" s="1" t="s">
         <v>75</v>
@@ -12313,7 +12313,7 @@
         <v>50044</v>
       </c>
       <c r="E353">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F353" s="1" t="s">
         <v>75</v>
@@ -12345,7 +12345,7 @@
         <v>60044</v>
       </c>
       <c r="E354">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F354" s="1" t="s">
         <v>75</v>
@@ -12377,7 +12377,7 @@
         <v>70044</v>
       </c>
       <c r="E355">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F355" s="1" t="s">
         <v>75</v>
@@ -12409,7 +12409,7 @@
         <v>80044</v>
       </c>
       <c r="E356">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F356" s="1" t="s">
         <v>75</v>
@@ -12441,7 +12441,7 @@
         <v>10045</v>
       </c>
       <c r="E357">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F357" s="1" t="s">
         <v>76</v>
@@ -12473,7 +12473,7 @@
         <v>20045</v>
       </c>
       <c r="E358">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F358" s="1" t="s">
         <v>76</v>
@@ -12505,7 +12505,7 @@
         <v>30045</v>
       </c>
       <c r="E359">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F359" s="1" t="s">
         <v>76</v>
@@ -12537,7 +12537,7 @@
         <v>40045</v>
       </c>
       <c r="E360">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F360" s="1" t="s">
         <v>76</v>
@@ -12569,7 +12569,7 @@
         <v>50045</v>
       </c>
       <c r="E361">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F361" s="1" t="s">
         <v>76</v>
@@ -12601,7 +12601,7 @@
         <v>60045</v>
       </c>
       <c r="E362">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F362" s="1" t="s">
         <v>76</v>
@@ -12633,7 +12633,7 @@
         <v>70045</v>
       </c>
       <c r="E363">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F363" s="1" t="s">
         <v>76</v>
@@ -12665,7 +12665,7 @@
         <v>80045</v>
       </c>
       <c r="E364">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F364" s="1" t="s">
         <v>76</v>
@@ -12697,7 +12697,7 @@
         <v>10046</v>
       </c>
       <c r="E365">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F365" s="1" t="s">
         <v>77</v>
@@ -12729,7 +12729,7 @@
         <v>20046</v>
       </c>
       <c r="E366">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F366" s="1" t="s">
         <v>77</v>
@@ -12761,7 +12761,7 @@
         <v>30046</v>
       </c>
       <c r="E367">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F367" s="1" t="s">
         <v>77</v>
@@ -12793,7 +12793,7 @@
         <v>40046</v>
       </c>
       <c r="E368">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F368" s="1" t="s">
         <v>77</v>
@@ -12825,7 +12825,7 @@
         <v>50046</v>
       </c>
       <c r="E369">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F369" s="1" t="s">
         <v>77</v>
@@ -12857,7 +12857,7 @@
         <v>60046</v>
       </c>
       <c r="E370">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F370" s="1" t="s">
         <v>77</v>
@@ -12889,7 +12889,7 @@
         <v>70046</v>
       </c>
       <c r="E371">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F371" s="1" t="s">
         <v>77</v>
@@ -12921,7 +12921,7 @@
         <v>80046</v>
       </c>
       <c r="E372">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F372" s="1" t="s">
         <v>77</v>
@@ -12953,7 +12953,7 @@
         <v>10047</v>
       </c>
       <c r="E373">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F373" s="1" t="s">
         <v>78</v>
@@ -12985,7 +12985,7 @@
         <v>20047</v>
       </c>
       <c r="E374">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F374" s="1" t="s">
         <v>78</v>
@@ -13017,7 +13017,7 @@
         <v>30047</v>
       </c>
       <c r="E375">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F375" s="1" t="s">
         <v>78</v>
@@ -13049,7 +13049,7 @@
         <v>40047</v>
       </c>
       <c r="E376">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F376" s="1" t="s">
         <v>78</v>
@@ -13081,7 +13081,7 @@
         <v>50047</v>
       </c>
       <c r="E377">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F377" s="1" t="s">
         <v>78</v>
@@ -13113,7 +13113,7 @@
         <v>60047</v>
       </c>
       <c r="E378">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F378" s="1" t="s">
         <v>78</v>
@@ -13145,7 +13145,7 @@
         <v>70047</v>
       </c>
       <c r="E379">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F379" s="1" t="s">
         <v>78</v>
@@ -13177,7 +13177,7 @@
         <v>80047</v>
       </c>
       <c r="E380">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F380" s="1" t="s">
         <v>78</v>
@@ -13209,7 +13209,7 @@
         <v>10048</v>
       </c>
       <c r="E381">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F381" s="1" t="s">
         <v>79</v>
@@ -13241,7 +13241,7 @@
         <v>20048</v>
       </c>
       <c r="E382">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F382" s="1" t="s">
         <v>79</v>
@@ -13273,7 +13273,7 @@
         <v>30048</v>
       </c>
       <c r="E383">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F383" s="1" t="s">
         <v>79</v>
@@ -13305,7 +13305,7 @@
         <v>40048</v>
       </c>
       <c r="E384">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F384" s="1" t="s">
         <v>79</v>
@@ -13337,7 +13337,7 @@
         <v>50048</v>
       </c>
       <c r="E385">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F385" s="1" t="s">
         <v>79</v>
@@ -13369,7 +13369,7 @@
         <v>60048</v>
       </c>
       <c r="E386">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F386" s="1" t="s">
         <v>79</v>
@@ -13401,7 +13401,7 @@
         <v>70048</v>
       </c>
       <c r="E387">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F387" s="1" t="s">
         <v>79</v>
@@ -13433,7 +13433,7 @@
         <v>80048</v>
       </c>
       <c r="E388">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F388" s="1" t="s">
         <v>79</v>
@@ -13465,7 +13465,7 @@
         <v>10049</v>
       </c>
       <c r="E389">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F389" s="1" t="s">
         <v>80</v>
@@ -13497,7 +13497,7 @@
         <v>20049</v>
       </c>
       <c r="E390">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F390" s="1" t="s">
         <v>80</v>
@@ -13529,7 +13529,7 @@
         <v>30049</v>
       </c>
       <c r="E391">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F391" s="1" t="s">
         <v>80</v>
@@ -13561,7 +13561,7 @@
         <v>40049</v>
       </c>
       <c r="E392">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F392" s="1" t="s">
         <v>80</v>
@@ -13593,7 +13593,7 @@
         <v>50049</v>
       </c>
       <c r="E393">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F393" s="1" t="s">
         <v>80</v>
@@ -13625,7 +13625,7 @@
         <v>60049</v>
       </c>
       <c r="E394">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F394" s="1" t="s">
         <v>80</v>
@@ -13657,7 +13657,7 @@
         <v>70049</v>
       </c>
       <c r="E395">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F395" s="1" t="s">
         <v>80</v>
@@ -13689,7 +13689,7 @@
         <v>80049</v>
       </c>
       <c r="E396">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F396" s="1" t="s">
         <v>80</v>
@@ -13721,7 +13721,7 @@
         <v>10050</v>
       </c>
       <c r="E397">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F397" s="1" t="s">
         <v>81</v>
@@ -13753,7 +13753,7 @@
         <v>20050</v>
       </c>
       <c r="E398">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F398" s="1" t="s">
         <v>81</v>
@@ -13785,7 +13785,7 @@
         <v>30050</v>
       </c>
       <c r="E399">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F399" s="1" t="s">
         <v>81</v>
@@ -13817,7 +13817,7 @@
         <v>40050</v>
       </c>
       <c r="E400">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F400" s="1" t="s">
         <v>81</v>
@@ -13849,7 +13849,7 @@
         <v>50050</v>
       </c>
       <c r="E401">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F401" s="1" t="s">
         <v>81</v>
@@ -13881,7 +13881,7 @@
         <v>60050</v>
       </c>
       <c r="E402">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F402" s="1" t="s">
         <v>81</v>
@@ -13913,7 +13913,7 @@
         <v>70050</v>
       </c>
       <c r="E403">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F403" s="1" t="s">
         <v>81</v>
@@ -13945,7 +13945,7 @@
         <v>80050</v>
       </c>
       <c r="E404">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F404" s="1" t="s">
         <v>81</v>
@@ -13977,7 +13977,7 @@
         <v>-1</v>
       </c>
       <c r="E405">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F405" s="1" t="s">
         <v>82</v>
@@ -14009,7 +14009,7 @@
         <v>-1</v>
       </c>
       <c r="E406">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F406" s="1" t="s">
         <v>82</v>
@@ -14041,7 +14041,7 @@
         <v>-1</v>
       </c>
       <c r="E407">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F407" s="1" t="s">
         <v>82</v>
@@ -14073,7 +14073,7 @@
         <v>-1</v>
       </c>
       <c r="E408">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F408" s="1" t="s">
         <v>82</v>
@@ -14105,7 +14105,7 @@
         <v>-1</v>
       </c>
       <c r="E409">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F409" s="1" t="s">
         <v>82</v>
@@ -14137,7 +14137,7 @@
         <v>-1</v>
       </c>
       <c r="E410">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F410" s="1" t="s">
         <v>82</v>
@@ -14169,7 +14169,7 @@
         <v>-1</v>
       </c>
       <c r="E411">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F411" s="1" t="s">
         <v>82</v>
@@ -14201,7 +14201,7 @@
         <v>-1</v>
       </c>
       <c r="E412">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F412" s="1" t="s">
         <v>82</v>

--- a/servers/maze_main_server/conf.d/data/maze_equip_pos_lv_v8【迷宫-装备-部位强化等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_equip_pos_lv_v8【迷宫-装备-部位强化等级】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF594F24-9C74-4601-A876-0C7503EAFD86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{379AE942-4BD2-4E9B-B974-A304B3E31D9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_equip_pos_lv_v8" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1255" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1255" uniqueCount="225">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -312,87 +312,39 @@
     <t>3010101:4</t>
   </si>
   <si>
-    <t>3030101:130</t>
-  </si>
-  <si>
-    <t>3030101:320</t>
-  </si>
-  <si>
-    <t>3030101:540</t>
-  </si>
-  <si>
     <t>3010101:25</t>
   </si>
   <si>
-    <t>3030101:820</t>
-  </si>
-  <si>
-    <t>3030101:1100</t>
-  </si>
-  <si>
     <t>3010101:47</t>
   </si>
   <si>
-    <t>3030101:1500</t>
-  </si>
-  <si>
     <t>3010101:58</t>
   </si>
   <si>
-    <t>3030101:1800</t>
-  </si>
-  <si>
-    <t>3030101:2200</t>
-  </si>
-  <si>
     <t>3010101:81</t>
   </si>
   <si>
-    <t>3030101:2600</t>
-  </si>
-  <si>
     <t>3010101:92</t>
   </si>
   <si>
-    <t>3030101:2900</t>
-  </si>
-  <si>
     <t>3010101:150</t>
   </si>
   <si>
-    <t>3030101:4800</t>
-  </si>
-  <si>
     <t>3010101:160</t>
   </si>
   <si>
-    <t>3030101:5300</t>
-  </si>
-  <si>
     <t>3010101:180</t>
   </si>
   <si>
-    <t>3030101:5800</t>
-  </si>
-  <si>
     <t>3010101:190</t>
   </si>
   <si>
-    <t>3030101:6300</t>
-  </si>
-  <si>
     <t>3010101:210</t>
   </si>
   <si>
-    <t>3030101:6800</t>
-  </si>
-  <si>
     <t>3010101:230</t>
   </si>
   <si>
-    <t>3030101:7300</t>
-  </si>
-  <si>
     <t>3010101:240</t>
   </si>
   <si>
@@ -402,51 +354,30 @@
     <t>3010101:260</t>
   </si>
   <si>
-    <t>3030101:8300</t>
-  </si>
-  <si>
     <t>3010101:270</t>
   </si>
   <si>
-    <t>3030101:8800</t>
-  </si>
-  <si>
     <t>3010101:290</t>
   </si>
   <si>
-    <t>3030101:9300</t>
-  </si>
-  <si>
     <t>3010101:330</t>
   </si>
   <si>
-    <t>3030101:10000</t>
-  </si>
-  <si>
     <t>3010101:340</t>
   </si>
   <si>
-    <t>3030101:11000</t>
-  </si>
-  <si>
     <t>3010101:360</t>
   </si>
   <si>
     <t>3010101:380</t>
   </si>
   <si>
-    <t>3030101:12000</t>
-  </si>
-  <si>
     <t>3010101:400</t>
   </si>
   <si>
     <t>3010101:410</t>
   </si>
   <si>
-    <t>3030101:13000</t>
-  </si>
-  <si>
     <t>3010101:430</t>
   </si>
   <si>
@@ -459,9 +390,6 @@
     <t>3010101:460</t>
   </si>
   <si>
-    <t>3030101:15000</t>
-  </si>
-  <si>
     <t>3010101:480</t>
   </si>
   <si>
@@ -477,9 +405,6 @@
     <t>3010101:580</t>
   </si>
   <si>
-    <t>3030101:18000</t>
-  </si>
-  <si>
     <t>3010101:600</t>
   </si>
   <si>
@@ -498,9 +423,6 @@
     <t>3010101:670</t>
   </si>
   <si>
-    <t>3030101:21000</t>
-  </si>
-  <si>
     <t>3010101:700</t>
   </si>
   <si>
@@ -516,9 +438,6 @@
     <t>3010101:760</t>
   </si>
   <si>
-    <t>3030101:24000</t>
-  </si>
-  <si>
     <t>3010101:840</t>
   </si>
   <si>
@@ -528,21 +447,12 @@
     <t>3010101:870</t>
   </si>
   <si>
-    <t>3030101:27000</t>
-  </si>
-  <si>
     <t>3010101:900</t>
   </si>
   <si>
-    <t>3030101:29000</t>
-  </si>
-  <si>
     <t>3010101:940</t>
   </si>
   <si>
-    <t>3030101:30000</t>
-  </si>
-  <si>
     <t>3010101:980</t>
   </si>
   <si>
@@ -552,12 +462,6 @@
     <t>3010101:1000</t>
   </si>
   <si>
-    <t>3030101:32000</t>
-  </si>
-  <si>
-    <t>3030101:34000</t>
-  </si>
-  <si>
     <t>3010101:1100</t>
   </si>
   <si>
@@ -718,6 +622,114 @@
   </si>
   <si>
     <t>9101:2392</t>
+  </si>
+  <si>
+    <t>3030101:400</t>
+  </si>
+  <si>
+    <t>3030101:980</t>
+  </si>
+  <si>
+    <t>3030101:1600</t>
+  </si>
+  <si>
+    <t>3030101:2400</t>
+  </si>
+  <si>
+    <t>3030101:3400</t>
+  </si>
+  <si>
+    <t>3030101:4500</t>
+  </si>
+  <si>
+    <t>3030101:5600</t>
+  </si>
+  <si>
+    <t>3030101:6700</t>
+  </si>
+  <si>
+    <t>3030101:8900</t>
+  </si>
+  <si>
+    <t>3030101:16000</t>
+  </si>
+  <si>
+    <t>3030101:25000</t>
+  </si>
+  <si>
+    <t>3030101:28000</t>
+  </si>
+  <si>
+    <t>3030101:33000</t>
+  </si>
+  <si>
+    <t>3030101:40000</t>
+  </si>
+  <si>
+    <t>3030101:41000</t>
+  </si>
+  <si>
+    <t>3030101:43000</t>
+  </si>
+  <si>
+    <t>3030101:45000</t>
+  </si>
+  <si>
+    <t>3030101:46000</t>
+  </si>
+  <si>
+    <t>3030101:51000</t>
+  </si>
+  <si>
+    <t>3030101:53000</t>
+  </si>
+  <si>
+    <t>3030101:55000</t>
+  </si>
+  <si>
+    <t>3030101:58000</t>
+  </si>
+  <si>
+    <t>3030101:60000</t>
+  </si>
+  <si>
+    <t>3030101:62000</t>
+  </si>
+  <si>
+    <t>3030101:65000</t>
+  </si>
+  <si>
+    <t>3030101:67000</t>
+  </si>
+  <si>
+    <t>3030101:70000</t>
+  </si>
+  <si>
+    <t>3030101:73000</t>
+  </si>
+  <si>
+    <t>3030101:80000</t>
+  </si>
+  <si>
+    <t>3030101:83000</t>
+  </si>
+  <si>
+    <t>3030101:87000</t>
+  </si>
+  <si>
+    <t>3030101:90000</t>
+  </si>
+  <si>
+    <t>3030101:94000</t>
+  </si>
+  <si>
+    <t>3030101:98000</t>
+  </si>
+  <si>
+    <t>3030101:100000</t>
+  </si>
+  <si>
+    <t>3030101:110000</t>
   </si>
 </sst>
 </file>
@@ -1442,7 +1454,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="I13" t="s">
         <v>84</v>
@@ -1474,10 +1486,10 @@
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="I14" t="s">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="J14" s="1">
         <v>3030101</v>
@@ -1506,10 +1518,10 @@
         <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="I15" t="s">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="J15" s="1">
         <v>3030101</v>
@@ -1538,10 +1550,10 @@
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="I16" t="s">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="J16" s="1">
         <v>3030101</v>
@@ -1570,7 +1582,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="I17" t="s">
         <v>84</v>
@@ -1602,10 +1614,10 @@
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="I18" t="s">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="J18" s="1">
         <v>3030101</v>
@@ -1634,7 +1646,7 @@
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="I19" t="s">
         <v>84</v>
@@ -1666,7 +1678,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="I20" t="s">
         <v>84</v>
@@ -1698,7 +1710,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I21" t="s">
         <v>26</v>
@@ -1730,10 +1742,10 @@
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I22" t="s">
-        <v>86</v>
+        <v>190</v>
       </c>
       <c r="J22" s="1">
         <v>3030101</v>
@@ -1762,10 +1774,10 @@
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I23" t="s">
-        <v>86</v>
+        <v>190</v>
       </c>
       <c r="J23" s="1">
         <v>3030101</v>
@@ -1794,10 +1806,10 @@
         <v>0</v>
       </c>
       <c r="H24" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I24" t="s">
-        <v>86</v>
+        <v>190</v>
       </c>
       <c r="J24" s="1">
         <v>3030101</v>
@@ -1826,7 +1838,7 @@
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I25" t="s">
         <v>26</v>
@@ -1858,10 +1870,10 @@
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I26" t="s">
-        <v>86</v>
+        <v>190</v>
       </c>
       <c r="J26" s="1">
         <v>3030101</v>
@@ -1890,7 +1902,7 @@
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I27" t="s">
         <v>26</v>
@@ -1922,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I28" t="s">
         <v>26</v>
@@ -1954,7 +1966,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>173</v>
+        <v>141</v>
       </c>
       <c r="I29" t="s">
         <v>27</v>
@@ -1986,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>173</v>
+        <v>141</v>
       </c>
       <c r="I30" t="s">
-        <v>87</v>
+        <v>191</v>
       </c>
       <c r="J30" s="1">
         <v>3030101</v>
@@ -2018,10 +2030,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>173</v>
+        <v>141</v>
       </c>
       <c r="I31" t="s">
-        <v>87</v>
+        <v>191</v>
       </c>
       <c r="J31" s="1">
         <v>3030101</v>
@@ -2050,10 +2062,10 @@
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>173</v>
+        <v>141</v>
       </c>
       <c r="I32" t="s">
-        <v>87</v>
+        <v>191</v>
       </c>
       <c r="J32" s="1">
         <v>3030101</v>
@@ -2082,7 +2094,7 @@
         <v>0</v>
       </c>
       <c r="H33" t="s">
-        <v>173</v>
+        <v>141</v>
       </c>
       <c r="I33" t="s">
         <v>27</v>
@@ -2114,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="H34" t="s">
-        <v>173</v>
+        <v>141</v>
       </c>
       <c r="I34" t="s">
-        <v>87</v>
+        <v>191</v>
       </c>
       <c r="J34" s="1">
         <v>3030101</v>
@@ -2146,7 +2158,7 @@
         <v>0</v>
       </c>
       <c r="H35" t="s">
-        <v>173</v>
+        <v>141</v>
       </c>
       <c r="I35" t="s">
         <v>27</v>
@@ -2178,7 +2190,7 @@
         <v>0</v>
       </c>
       <c r="H36" t="s">
-        <v>173</v>
+        <v>141</v>
       </c>
       <c r="I36" t="s">
         <v>27</v>
@@ -2210,10 +2222,10 @@
         <v>0</v>
       </c>
       <c r="H37" t="s">
-        <v>174</v>
+        <v>142</v>
       </c>
       <c r="I37" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="J37" s="1">
         <v>3010101</v>
@@ -2242,10 +2254,10 @@
         <v>0</v>
       </c>
       <c r="H38" t="s">
-        <v>174</v>
+        <v>142</v>
       </c>
       <c r="I38" t="s">
-        <v>89</v>
+        <v>192</v>
       </c>
       <c r="J38" s="1">
         <v>3030101</v>
@@ -2274,10 +2286,10 @@
         <v>0</v>
       </c>
       <c r="H39" t="s">
-        <v>174</v>
+        <v>142</v>
       </c>
       <c r="I39" t="s">
-        <v>89</v>
+        <v>192</v>
       </c>
       <c r="J39" s="1">
         <v>3030101</v>
@@ -2306,10 +2318,10 @@
         <v>0</v>
       </c>
       <c r="H40" t="s">
-        <v>174</v>
+        <v>142</v>
       </c>
       <c r="I40" t="s">
-        <v>89</v>
+        <v>192</v>
       </c>
       <c r="J40" s="1">
         <v>3030101</v>
@@ -2338,10 +2350,10 @@
         <v>0</v>
       </c>
       <c r="H41" t="s">
-        <v>174</v>
+        <v>142</v>
       </c>
       <c r="I41" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="J41" s="1">
         <v>3010101</v>
@@ -2370,10 +2382,10 @@
         <v>0</v>
       </c>
       <c r="H42" t="s">
-        <v>174</v>
+        <v>142</v>
       </c>
       <c r="I42" t="s">
-        <v>89</v>
+        <v>192</v>
       </c>
       <c r="J42" s="1">
         <v>3030101</v>
@@ -2402,10 +2414,10 @@
         <v>0</v>
       </c>
       <c r="H43" t="s">
-        <v>174</v>
+        <v>142</v>
       </c>
       <c r="I43" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="J43" s="1">
         <v>3010101</v>
@@ -2434,10 +2446,10 @@
         <v>0</v>
       </c>
       <c r="H44" t="s">
-        <v>174</v>
+        <v>142</v>
       </c>
       <c r="I44" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="J44" s="1">
         <v>3010101</v>
@@ -2466,7 +2478,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="s">
-        <v>175</v>
+        <v>143</v>
       </c>
       <c r="I45" t="s">
         <v>28</v>
@@ -2498,10 +2510,10 @@
         <v>0</v>
       </c>
       <c r="H46" t="s">
-        <v>175</v>
+        <v>143</v>
       </c>
       <c r="I46" t="s">
-        <v>90</v>
+        <v>193</v>
       </c>
       <c r="J46" s="1">
         <v>3030101</v>
@@ -2530,10 +2542,10 @@
         <v>0</v>
       </c>
       <c r="H47" t="s">
-        <v>175</v>
+        <v>143</v>
       </c>
       <c r="I47" t="s">
-        <v>90</v>
+        <v>193</v>
       </c>
       <c r="J47" s="1">
         <v>3030101</v>
@@ -2562,10 +2574,10 @@
         <v>0</v>
       </c>
       <c r="H48" t="s">
-        <v>175</v>
+        <v>143</v>
       </c>
       <c r="I48" t="s">
-        <v>90</v>
+        <v>193</v>
       </c>
       <c r="J48" s="1">
         <v>3030101</v>
@@ -2594,7 +2606,7 @@
         <v>0</v>
       </c>
       <c r="H49" t="s">
-        <v>175</v>
+        <v>143</v>
       </c>
       <c r="I49" t="s">
         <v>28</v>
@@ -2626,10 +2638,10 @@
         <v>0</v>
       </c>
       <c r="H50" t="s">
-        <v>175</v>
+        <v>143</v>
       </c>
       <c r="I50" t="s">
-        <v>90</v>
+        <v>193</v>
       </c>
       <c r="J50" s="1">
         <v>3030101</v>
@@ -2658,7 +2670,7 @@
         <v>0</v>
       </c>
       <c r="H51" t="s">
-        <v>175</v>
+        <v>143</v>
       </c>
       <c r="I51" t="s">
         <v>28</v>
@@ -2690,7 +2702,7 @@
         <v>0</v>
       </c>
       <c r="H52" t="s">
-        <v>175</v>
+        <v>143</v>
       </c>
       <c r="I52" t="s">
         <v>28</v>
@@ -2722,10 +2734,10 @@
         <v>0</v>
       </c>
       <c r="H53" t="s">
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="I53" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="J53" s="1">
         <v>3010101</v>
@@ -2754,10 +2766,10 @@
         <v>0</v>
       </c>
       <c r="H54" t="s">
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="I54" t="s">
-        <v>92</v>
+        <v>194</v>
       </c>
       <c r="J54" s="1">
         <v>3030101</v>
@@ -2786,10 +2798,10 @@
         <v>0</v>
       </c>
       <c r="H55" t="s">
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="I55" t="s">
-        <v>92</v>
+        <v>194</v>
       </c>
       <c r="J55" s="1">
         <v>3030101</v>
@@ -2818,10 +2830,10 @@
         <v>0</v>
       </c>
       <c r="H56" t="s">
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="I56" t="s">
-        <v>92</v>
+        <v>194</v>
       </c>
       <c r="J56" s="1">
         <v>3030101</v>
@@ -2850,10 +2862,10 @@
         <v>0</v>
       </c>
       <c r="H57" t="s">
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="I57" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="J57" s="1">
         <v>3010101</v>
@@ -2882,10 +2894,10 @@
         <v>0</v>
       </c>
       <c r="H58" t="s">
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="I58" t="s">
-        <v>92</v>
+        <v>194</v>
       </c>
       <c r="J58" s="1">
         <v>3030101</v>
@@ -2914,10 +2926,10 @@
         <v>0</v>
       </c>
       <c r="H59" t="s">
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="I59" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="J59" s="1">
         <v>3010101</v>
@@ -2946,10 +2958,10 @@
         <v>0</v>
       </c>
       <c r="H60" t="s">
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="I60" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="J60" s="1">
         <v>3010101</v>
@@ -2978,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="H61" t="s">
-        <v>177</v>
+        <v>145</v>
       </c>
       <c r="I61" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="J61" s="1">
         <v>3010101</v>
@@ -3010,10 +3022,10 @@
         <v>0</v>
       </c>
       <c r="H62" t="s">
-        <v>177</v>
+        <v>145</v>
       </c>
       <c r="I62" t="s">
-        <v>94</v>
+        <v>195</v>
       </c>
       <c r="J62" s="1">
         <v>3030101</v>
@@ -3042,10 +3054,10 @@
         <v>0</v>
       </c>
       <c r="H63" t="s">
-        <v>177</v>
+        <v>145</v>
       </c>
       <c r="I63" t="s">
-        <v>94</v>
+        <v>195</v>
       </c>
       <c r="J63" s="1">
         <v>3030101</v>
@@ -3074,10 +3086,10 @@
         <v>0</v>
       </c>
       <c r="H64" t="s">
-        <v>177</v>
+        <v>145</v>
       </c>
       <c r="I64" t="s">
-        <v>94</v>
+        <v>195</v>
       </c>
       <c r="J64" s="1">
         <v>3030101</v>
@@ -3106,10 +3118,10 @@
         <v>0</v>
       </c>
       <c r="H65" t="s">
-        <v>177</v>
+        <v>145</v>
       </c>
       <c r="I65" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="J65" s="1">
         <v>3010101</v>
@@ -3138,10 +3150,10 @@
         <v>0</v>
       </c>
       <c r="H66" t="s">
-        <v>177</v>
+        <v>145</v>
       </c>
       <c r="I66" t="s">
-        <v>94</v>
+        <v>195</v>
       </c>
       <c r="J66" s="1">
         <v>3030101</v>
@@ -3170,10 +3182,10 @@
         <v>0</v>
       </c>
       <c r="H67" t="s">
-        <v>177</v>
+        <v>145</v>
       </c>
       <c r="I67" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="J67" s="1">
         <v>3010101</v>
@@ -3202,10 +3214,10 @@
         <v>0</v>
       </c>
       <c r="H68" t="s">
-        <v>177</v>
+        <v>145</v>
       </c>
       <c r="I68" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="J68" s="1">
         <v>3010101</v>
@@ -3234,7 +3246,7 @@
         <v>0</v>
       </c>
       <c r="H69" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="I69" t="s">
         <v>29</v>
@@ -3266,10 +3278,10 @@
         <v>0</v>
       </c>
       <c r="H70" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="I70" t="s">
-        <v>95</v>
+        <v>196</v>
       </c>
       <c r="J70" s="1">
         <v>3030101</v>
@@ -3298,10 +3310,10 @@
         <v>0</v>
       </c>
       <c r="H71" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="I71" t="s">
-        <v>95</v>
+        <v>196</v>
       </c>
       <c r="J71" s="1">
         <v>3030101</v>
@@ -3330,10 +3342,10 @@
         <v>0</v>
       </c>
       <c r="H72" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="I72" t="s">
-        <v>95</v>
+        <v>196</v>
       </c>
       <c r="J72" s="1">
         <v>3030101</v>
@@ -3362,7 +3374,7 @@
         <v>0</v>
       </c>
       <c r="H73" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="I73" t="s">
         <v>29</v>
@@ -3394,10 +3406,10 @@
         <v>0</v>
       </c>
       <c r="H74" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="I74" t="s">
-        <v>95</v>
+        <v>196</v>
       </c>
       <c r="J74" s="1">
         <v>3030101</v>
@@ -3426,7 +3438,7 @@
         <v>0</v>
       </c>
       <c r="H75" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="I75" t="s">
         <v>29</v>
@@ -3458,7 +3470,7 @@
         <v>0</v>
       </c>
       <c r="H76" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="I76" t="s">
         <v>29</v>
@@ -3490,10 +3502,10 @@
         <v>0</v>
       </c>
       <c r="H77" t="s">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="I77" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="J77" s="1">
         <v>3010101</v>
@@ -3522,7 +3534,7 @@
         <v>0</v>
       </c>
       <c r="H78" t="s">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="I78" t="s">
         <v>97</v>
@@ -3554,7 +3566,7 @@
         <v>0</v>
       </c>
       <c r="H79" t="s">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="I79" t="s">
         <v>97</v>
@@ -3586,7 +3598,7 @@
         <v>0</v>
       </c>
       <c r="H80" t="s">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="I80" t="s">
         <v>97</v>
@@ -3618,10 +3630,10 @@
         <v>0</v>
       </c>
       <c r="H81" t="s">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="I81" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="J81" s="1">
         <v>3010101</v>
@@ -3650,7 +3662,7 @@
         <v>0</v>
       </c>
       <c r="H82" t="s">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="I82" t="s">
         <v>97</v>
@@ -3682,10 +3694,10 @@
         <v>0</v>
       </c>
       <c r="H83" t="s">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="I83" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="J83" s="1">
         <v>3010101</v>
@@ -3714,10 +3726,10 @@
         <v>0</v>
       </c>
       <c r="H84" t="s">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="I84" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="J84" s="1">
         <v>3010101</v>
@@ -3746,10 +3758,10 @@
         <v>10</v>
       </c>
       <c r="H85" t="s">
-        <v>180</v>
+        <v>148</v>
       </c>
       <c r="I85" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="J85" s="1">
         <v>3010101</v>
@@ -3778,10 +3790,10 @@
         <v>10</v>
       </c>
       <c r="H86" t="s">
-        <v>180</v>
+        <v>148</v>
       </c>
       <c r="I86" t="s">
-        <v>99</v>
+        <v>197</v>
       </c>
       <c r="J86" s="1">
         <v>3030101</v>
@@ -3810,10 +3822,10 @@
         <v>10</v>
       </c>
       <c r="H87" t="s">
-        <v>180</v>
+        <v>148</v>
       </c>
       <c r="I87" t="s">
-        <v>99</v>
+        <v>197</v>
       </c>
       <c r="J87" s="1">
         <v>3030101</v>
@@ -3842,10 +3854,10 @@
         <v>10</v>
       </c>
       <c r="H88" t="s">
-        <v>180</v>
+        <v>148</v>
       </c>
       <c r="I88" t="s">
-        <v>99</v>
+        <v>197</v>
       </c>
       <c r="J88" s="1">
         <v>3030101</v>
@@ -3874,10 +3886,10 @@
         <v>10</v>
       </c>
       <c r="H89" t="s">
-        <v>180</v>
+        <v>148</v>
       </c>
       <c r="I89" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="J89" s="1">
         <v>3010101</v>
@@ -3906,10 +3918,10 @@
         <v>10</v>
       </c>
       <c r="H90" t="s">
-        <v>180</v>
+        <v>148</v>
       </c>
       <c r="I90" t="s">
-        <v>99</v>
+        <v>197</v>
       </c>
       <c r="J90" s="1">
         <v>3030101</v>
@@ -3938,10 +3950,10 @@
         <v>10</v>
       </c>
       <c r="H91" t="s">
-        <v>180</v>
+        <v>148</v>
       </c>
       <c r="I91" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="J91" s="1">
         <v>3010101</v>
@@ -3970,10 +3982,10 @@
         <v>10</v>
       </c>
       <c r="H92" t="s">
-        <v>180</v>
+        <v>148</v>
       </c>
       <c r="I92" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="J92" s="1">
         <v>3010101</v>
@@ -4002,10 +4014,10 @@
         <v>10</v>
       </c>
       <c r="H93" t="s">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="I93" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J93" s="1">
         <v>3010101</v>
@@ -4034,10 +4046,10 @@
         <v>10</v>
       </c>
       <c r="H94" t="s">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="I94" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="J94" s="1">
         <v>3030101</v>
@@ -4066,10 +4078,10 @@
         <v>10</v>
       </c>
       <c r="H95" t="s">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="I95" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="J95" s="1">
         <v>3030101</v>
@@ -4098,10 +4110,10 @@
         <v>10</v>
       </c>
       <c r="H96" t="s">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="I96" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="J96" s="1">
         <v>3030101</v>
@@ -4130,10 +4142,10 @@
         <v>10</v>
       </c>
       <c r="H97" t="s">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="I97" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J97" s="1">
         <v>3010101</v>
@@ -4162,10 +4174,10 @@
         <v>10</v>
       </c>
       <c r="H98" t="s">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="I98" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="J98" s="1">
         <v>3030101</v>
@@ -4194,10 +4206,10 @@
         <v>10</v>
       </c>
       <c r="H99" t="s">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="I99" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J99" s="1">
         <v>3010101</v>
@@ -4226,10 +4238,10 @@
         <v>10</v>
       </c>
       <c r="H100" t="s">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="I100" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J100" s="1">
         <v>3010101</v>
@@ -4258,10 +4270,10 @@
         <v>10</v>
       </c>
       <c r="H101" t="s">
-        <v>182</v>
+        <v>150</v>
       </c>
       <c r="I101" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="J101" s="1">
         <v>3010101</v>
@@ -4290,10 +4302,10 @@
         <v>10</v>
       </c>
       <c r="H102" t="s">
-        <v>182</v>
+        <v>150</v>
       </c>
       <c r="I102" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
       <c r="J102" s="1">
         <v>3030101</v>
@@ -4322,10 +4334,10 @@
         <v>10</v>
       </c>
       <c r="H103" t="s">
-        <v>182</v>
+        <v>150</v>
       </c>
       <c r="I103" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
       <c r="J103" s="1">
         <v>3030101</v>
@@ -4354,10 +4366,10 @@
         <v>10</v>
       </c>
       <c r="H104" t="s">
-        <v>182</v>
+        <v>150</v>
       </c>
       <c r="I104" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
       <c r="J104" s="1">
         <v>3030101</v>
@@ -4386,10 +4398,10 @@
         <v>10</v>
       </c>
       <c r="H105" t="s">
-        <v>182</v>
+        <v>150</v>
       </c>
       <c r="I105" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="J105" s="1">
         <v>3010101</v>
@@ -4418,10 +4430,10 @@
         <v>10</v>
       </c>
       <c r="H106" t="s">
-        <v>182</v>
+        <v>150</v>
       </c>
       <c r="I106" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
       <c r="J106" s="1">
         <v>3030101</v>
@@ -4450,10 +4462,10 @@
         <v>10</v>
       </c>
       <c r="H107" t="s">
-        <v>182</v>
+        <v>150</v>
       </c>
       <c r="I107" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="J107" s="1">
         <v>3010101</v>
@@ -4482,10 +4494,10 @@
         <v>10</v>
       </c>
       <c r="H108" t="s">
-        <v>182</v>
+        <v>150</v>
       </c>
       <c r="I108" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="J108" s="1">
         <v>3010101</v>
@@ -4514,10 +4526,10 @@
         <v>10</v>
       </c>
       <c r="H109" t="s">
-        <v>183</v>
+        <v>151</v>
       </c>
       <c r="I109" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="J109" s="1">
         <v>3010101</v>
@@ -4546,10 +4558,10 @@
         <v>10</v>
       </c>
       <c r="H110" t="s">
-        <v>183</v>
+        <v>151</v>
       </c>
       <c r="I110" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="J110" s="1">
         <v>3030101</v>
@@ -4578,10 +4590,10 @@
         <v>10</v>
       </c>
       <c r="H111" t="s">
-        <v>183</v>
+        <v>151</v>
       </c>
       <c r="I111" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="J111" s="1">
         <v>3030101</v>
@@ -4610,10 +4622,10 @@
         <v>10</v>
       </c>
       <c r="H112" t="s">
-        <v>183</v>
+        <v>151</v>
       </c>
       <c r="I112" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="J112" s="1">
         <v>3030101</v>
@@ -4642,10 +4654,10 @@
         <v>10</v>
       </c>
       <c r="H113" t="s">
-        <v>183</v>
+        <v>151</v>
       </c>
       <c r="I113" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="J113" s="1">
         <v>3010101</v>
@@ -4674,10 +4686,10 @@
         <v>10</v>
       </c>
       <c r="H114" t="s">
-        <v>183</v>
+        <v>151</v>
       </c>
       <c r="I114" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="J114" s="1">
         <v>3030101</v>
@@ -4706,10 +4718,10 @@
         <v>10</v>
       </c>
       <c r="H115" t="s">
-        <v>183</v>
+        <v>151</v>
       </c>
       <c r="I115" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="J115" s="1">
         <v>3010101</v>
@@ -4738,10 +4750,10 @@
         <v>10</v>
       </c>
       <c r="H116" t="s">
-        <v>183</v>
+        <v>151</v>
       </c>
       <c r="I116" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="J116" s="1">
         <v>3010101</v>
@@ -4770,10 +4782,10 @@
         <v>10</v>
       </c>
       <c r="H117" t="s">
-        <v>184</v>
+        <v>152</v>
       </c>
       <c r="I117" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="J117" s="1">
         <v>3010101</v>
@@ -4802,10 +4814,10 @@
         <v>10</v>
       </c>
       <c r="H118" t="s">
-        <v>184</v>
+        <v>152</v>
       </c>
       <c r="I118" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="J118" s="1">
         <v>3030101</v>
@@ -4834,10 +4846,10 @@
         <v>10</v>
       </c>
       <c r="H119" t="s">
-        <v>184</v>
+        <v>152</v>
       </c>
       <c r="I119" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="J119" s="1">
         <v>3030101</v>
@@ -4866,10 +4878,10 @@
         <v>10</v>
       </c>
       <c r="H120" t="s">
-        <v>184</v>
+        <v>152</v>
       </c>
       <c r="I120" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="J120" s="1">
         <v>3030101</v>
@@ -4898,10 +4910,10 @@
         <v>10</v>
       </c>
       <c r="H121" t="s">
-        <v>184</v>
+        <v>152</v>
       </c>
       <c r="I121" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="J121" s="1">
         <v>3010101</v>
@@ -4930,10 +4942,10 @@
         <v>10</v>
       </c>
       <c r="H122" t="s">
-        <v>184</v>
+        <v>152</v>
       </c>
       <c r="I122" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="J122" s="1">
         <v>3030101</v>
@@ -4962,10 +4974,10 @@
         <v>10</v>
       </c>
       <c r="H123" t="s">
-        <v>184</v>
+        <v>152</v>
       </c>
       <c r="I123" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="J123" s="1">
         <v>3010101</v>
@@ -4994,10 +5006,10 @@
         <v>10</v>
       </c>
       <c r="H124" t="s">
-        <v>184</v>
+        <v>152</v>
       </c>
       <c r="I124" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="J124" s="1">
         <v>3010101</v>
@@ -5026,10 +5038,10 @@
         <v>10</v>
       </c>
       <c r="H125" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
       <c r="I125" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="J125" s="1">
         <v>3010101</v>
@@ -5058,10 +5070,10 @@
         <v>10</v>
       </c>
       <c r="H126" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
       <c r="I126" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="J126" s="1">
         <v>3030101</v>
@@ -5090,10 +5102,10 @@
         <v>10</v>
       </c>
       <c r="H127" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
       <c r="I127" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="J127" s="1">
         <v>3030101</v>
@@ -5122,10 +5134,10 @@
         <v>10</v>
       </c>
       <c r="H128" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
       <c r="I128" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="J128" s="1">
         <v>3030101</v>
@@ -5154,10 +5166,10 @@
         <v>10</v>
       </c>
       <c r="H129" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
       <c r="I129" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="J129" s="1">
         <v>3010101</v>
@@ -5186,10 +5198,10 @@
         <v>10</v>
       </c>
       <c r="H130" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
       <c r="I130" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="J130" s="1">
         <v>3030101</v>
@@ -5218,10 +5230,10 @@
         <v>10</v>
       </c>
       <c r="H131" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
       <c r="I131" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="J131" s="1">
         <v>3010101</v>
@@ -5250,10 +5262,10 @@
         <v>10</v>
       </c>
       <c r="H132" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
       <c r="I132" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="J132" s="1">
         <v>3010101</v>
@@ -5282,10 +5294,10 @@
         <v>10</v>
       </c>
       <c r="H133" t="s">
-        <v>186</v>
+        <v>154</v>
       </c>
       <c r="I133" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="J133" s="1">
         <v>3010101</v>
@@ -5314,10 +5326,10 @@
         <v>10</v>
       </c>
       <c r="H134" t="s">
-        <v>186</v>
+        <v>154</v>
       </c>
       <c r="I134" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="J134" s="1">
         <v>3030101</v>
@@ -5346,10 +5358,10 @@
         <v>10</v>
       </c>
       <c r="H135" t="s">
-        <v>186</v>
+        <v>154</v>
       </c>
       <c r="I135" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="J135" s="1">
         <v>3030101</v>
@@ -5378,10 +5390,10 @@
         <v>10</v>
       </c>
       <c r="H136" t="s">
-        <v>186</v>
+        <v>154</v>
       </c>
       <c r="I136" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="J136" s="1">
         <v>3030101</v>
@@ -5410,10 +5422,10 @@
         <v>10</v>
       </c>
       <c r="H137" t="s">
-        <v>186</v>
+        <v>154</v>
       </c>
       <c r="I137" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="J137" s="1">
         <v>3010101</v>
@@ -5442,10 +5454,10 @@
         <v>10</v>
       </c>
       <c r="H138" t="s">
-        <v>186</v>
+        <v>154</v>
       </c>
       <c r="I138" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="J138" s="1">
         <v>3030101</v>
@@ -5474,10 +5486,10 @@
         <v>10</v>
       </c>
       <c r="H139" t="s">
-        <v>186</v>
+        <v>154</v>
       </c>
       <c r="I139" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="J139" s="1">
         <v>3010101</v>
@@ -5506,10 +5518,10 @@
         <v>10</v>
       </c>
       <c r="H140" t="s">
-        <v>186</v>
+        <v>154</v>
       </c>
       <c r="I140" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="J140" s="1">
         <v>3010101</v>
@@ -5538,10 +5550,10 @@
         <v>10</v>
       </c>
       <c r="H141" t="s">
-        <v>187</v>
+        <v>155</v>
       </c>
       <c r="I141" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="J141" s="1">
         <v>3010101</v>
@@ -5570,10 +5582,10 @@
         <v>10</v>
       </c>
       <c r="H142" t="s">
-        <v>187</v>
+        <v>155</v>
       </c>
       <c r="I142" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="J142" s="1">
         <v>3030101</v>
@@ -5602,10 +5614,10 @@
         <v>10</v>
       </c>
       <c r="H143" t="s">
-        <v>187</v>
+        <v>155</v>
       </c>
       <c r="I143" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="J143" s="1">
         <v>3030101</v>
@@ -5634,10 +5646,10 @@
         <v>10</v>
       </c>
       <c r="H144" t="s">
-        <v>187</v>
+        <v>155</v>
       </c>
       <c r="I144" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="J144" s="1">
         <v>3030101</v>
@@ -5666,10 +5678,10 @@
         <v>10</v>
       </c>
       <c r="H145" t="s">
-        <v>187</v>
+        <v>155</v>
       </c>
       <c r="I145" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="J145" s="1">
         <v>3010101</v>
@@ -5698,10 +5710,10 @@
         <v>10</v>
       </c>
       <c r="H146" t="s">
-        <v>187</v>
+        <v>155</v>
       </c>
       <c r="I146" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="J146" s="1">
         <v>3030101</v>
@@ -5730,10 +5742,10 @@
         <v>10</v>
       </c>
       <c r="H147" t="s">
-        <v>187</v>
+        <v>155</v>
       </c>
       <c r="I147" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="J147" s="1">
         <v>3010101</v>
@@ -5762,10 +5774,10 @@
         <v>10</v>
       </c>
       <c r="H148" t="s">
-        <v>187</v>
+        <v>155</v>
       </c>
       <c r="I148" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="J148" s="1">
         <v>3010101</v>
@@ -5794,10 +5806,10 @@
         <v>10</v>
       </c>
       <c r="H149" t="s">
-        <v>188</v>
+        <v>156</v>
       </c>
       <c r="I149" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="J149" s="1">
         <v>3010101</v>
@@ -5826,10 +5838,10 @@
         <v>10</v>
       </c>
       <c r="H150" t="s">
-        <v>188</v>
+        <v>156</v>
       </c>
       <c r="I150" t="s">
-        <v>115</v>
+        <v>199</v>
       </c>
       <c r="J150" s="1">
         <v>3030101</v>
@@ -5858,10 +5870,10 @@
         <v>10</v>
       </c>
       <c r="H151" t="s">
-        <v>188</v>
+        <v>156</v>
       </c>
       <c r="I151" t="s">
-        <v>115</v>
+        <v>199</v>
       </c>
       <c r="J151" s="1">
         <v>3030101</v>
@@ -5890,10 +5902,10 @@
         <v>10</v>
       </c>
       <c r="H152" t="s">
-        <v>188</v>
+        <v>156</v>
       </c>
       <c r="I152" t="s">
-        <v>115</v>
+        <v>199</v>
       </c>
       <c r="J152" s="1">
         <v>3030101</v>
@@ -5922,10 +5934,10 @@
         <v>10</v>
       </c>
       <c r="H153" t="s">
-        <v>188</v>
+        <v>156</v>
       </c>
       <c r="I153" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="J153" s="1">
         <v>3010101</v>
@@ -5954,10 +5966,10 @@
         <v>10</v>
       </c>
       <c r="H154" t="s">
-        <v>188</v>
+        <v>156</v>
       </c>
       <c r="I154" t="s">
-        <v>115</v>
+        <v>199</v>
       </c>
       <c r="J154" s="1">
         <v>3030101</v>
@@ -5986,10 +5998,10 @@
         <v>10</v>
       </c>
       <c r="H155" t="s">
-        <v>188</v>
+        <v>156</v>
       </c>
       <c r="I155" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="J155" s="1">
         <v>3010101</v>
@@ -6018,10 +6030,10 @@
         <v>10</v>
       </c>
       <c r="H156" t="s">
-        <v>188</v>
+        <v>156</v>
       </c>
       <c r="I156" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="J156" s="1">
         <v>3010101</v>
@@ -6050,10 +6062,10 @@
         <v>10</v>
       </c>
       <c r="H157" t="s">
-        <v>189</v>
+        <v>157</v>
       </c>
       <c r="I157" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="J157" s="1">
         <v>3010101</v>
@@ -6082,10 +6094,10 @@
         <v>10</v>
       </c>
       <c r="H158" t="s">
-        <v>189</v>
+        <v>157</v>
       </c>
       <c r="I158" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="J158" s="1">
         <v>3030101</v>
@@ -6114,10 +6126,10 @@
         <v>10</v>
       </c>
       <c r="H159" t="s">
-        <v>189</v>
+        <v>157</v>
       </c>
       <c r="I159" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="J159" s="1">
         <v>3030101</v>
@@ -6146,10 +6158,10 @@
         <v>10</v>
       </c>
       <c r="H160" t="s">
-        <v>189</v>
+        <v>157</v>
       </c>
       <c r="I160" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="J160" s="1">
         <v>3030101</v>
@@ -6178,10 +6190,10 @@
         <v>10</v>
       </c>
       <c r="H161" t="s">
-        <v>189</v>
+        <v>157</v>
       </c>
       <c r="I161" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="J161" s="1">
         <v>3010101</v>
@@ -6210,10 +6222,10 @@
         <v>10</v>
       </c>
       <c r="H162" t="s">
-        <v>189</v>
+        <v>157</v>
       </c>
       <c r="I162" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="J162" s="1">
         <v>3030101</v>
@@ -6242,10 +6254,10 @@
         <v>10</v>
       </c>
       <c r="H163" t="s">
-        <v>189</v>
+        <v>157</v>
       </c>
       <c r="I163" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="J163" s="1">
         <v>3010101</v>
@@ -6274,10 +6286,10 @@
         <v>10</v>
       </c>
       <c r="H164" t="s">
-        <v>189</v>
+        <v>157</v>
       </c>
       <c r="I164" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="J164" s="1">
         <v>3010101</v>
@@ -6306,10 +6318,10 @@
         <v>20</v>
       </c>
       <c r="H165" t="s">
-        <v>190</v>
+        <v>158</v>
       </c>
       <c r="I165" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="J165" s="1">
         <v>3010101</v>
@@ -6338,10 +6350,10 @@
         <v>20</v>
       </c>
       <c r="H166" t="s">
-        <v>190</v>
+        <v>158</v>
       </c>
       <c r="I166" t="s">
-        <v>119</v>
+        <v>200</v>
       </c>
       <c r="J166" s="1">
         <v>3030101</v>
@@ -6370,10 +6382,10 @@
         <v>20</v>
       </c>
       <c r="H167" t="s">
-        <v>190</v>
+        <v>158</v>
       </c>
       <c r="I167" t="s">
-        <v>119</v>
+        <v>200</v>
       </c>
       <c r="J167" s="1">
         <v>3030101</v>
@@ -6402,10 +6414,10 @@
         <v>20</v>
       </c>
       <c r="H168" t="s">
-        <v>190</v>
+        <v>158</v>
       </c>
       <c r="I168" t="s">
-        <v>119</v>
+        <v>200</v>
       </c>
       <c r="J168" s="1">
         <v>3030101</v>
@@ -6434,10 +6446,10 @@
         <v>20</v>
       </c>
       <c r="H169" t="s">
-        <v>190</v>
+        <v>158</v>
       </c>
       <c r="I169" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="J169" s="1">
         <v>3010101</v>
@@ -6466,10 +6478,10 @@
         <v>20</v>
       </c>
       <c r="H170" t="s">
-        <v>190</v>
+        <v>158</v>
       </c>
       <c r="I170" t="s">
-        <v>119</v>
+        <v>200</v>
       </c>
       <c r="J170" s="1">
         <v>3030101</v>
@@ -6498,10 +6510,10 @@
         <v>20</v>
       </c>
       <c r="H171" t="s">
-        <v>190</v>
+        <v>158</v>
       </c>
       <c r="I171" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="J171" s="1">
         <v>3010101</v>
@@ -6530,10 +6542,10 @@
         <v>20</v>
       </c>
       <c r="H172" t="s">
-        <v>190</v>
+        <v>158</v>
       </c>
       <c r="I172" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="J172" s="1">
         <v>3010101</v>
@@ -6562,10 +6574,10 @@
         <v>20</v>
       </c>
       <c r="H173" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="I173" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="J173" s="1">
         <v>3010101</v>
@@ -6594,10 +6606,10 @@
         <v>20</v>
       </c>
       <c r="H174" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="I174" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="J174" s="1">
         <v>3030101</v>
@@ -6626,10 +6638,10 @@
         <v>20</v>
       </c>
       <c r="H175" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="I175" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="J175" s="1">
         <v>3030101</v>
@@ -6658,10 +6670,10 @@
         <v>20</v>
       </c>
       <c r="H176" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="I176" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="J176" s="1">
         <v>3030101</v>
@@ -6690,10 +6702,10 @@
         <v>20</v>
       </c>
       <c r="H177" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="I177" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="J177" s="1">
         <v>3010101</v>
@@ -6722,10 +6734,10 @@
         <v>20</v>
       </c>
       <c r="H178" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="I178" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="J178" s="1">
         <v>3030101</v>
@@ -6754,10 +6766,10 @@
         <v>20</v>
       </c>
       <c r="H179" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="I179" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="J179" s="1">
         <v>3010101</v>
@@ -6786,10 +6798,10 @@
         <v>20</v>
       </c>
       <c r="H180" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="I180" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="J180" s="1">
         <v>3010101</v>
@@ -6818,10 +6830,10 @@
         <v>20</v>
       </c>
       <c r="H181" t="s">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="I181" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="J181" s="1">
         <v>3010101</v>
@@ -6850,10 +6862,10 @@
         <v>20</v>
       </c>
       <c r="H182" t="s">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="I182" t="s">
-        <v>123</v>
+        <v>201</v>
       </c>
       <c r="J182" s="1">
         <v>3030101</v>
@@ -6882,10 +6894,10 @@
         <v>20</v>
       </c>
       <c r="H183" t="s">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="I183" t="s">
-        <v>123</v>
+        <v>201</v>
       </c>
       <c r="J183" s="1">
         <v>3030101</v>
@@ -6914,10 +6926,10 @@
         <v>20</v>
       </c>
       <c r="H184" t="s">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="I184" t="s">
-        <v>123</v>
+        <v>201</v>
       </c>
       <c r="J184" s="1">
         <v>3030101</v>
@@ -6946,10 +6958,10 @@
         <v>20</v>
       </c>
       <c r="H185" t="s">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="I185" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="J185" s="1">
         <v>3010101</v>
@@ -6978,10 +6990,10 @@
         <v>20</v>
       </c>
       <c r="H186" t="s">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="I186" t="s">
-        <v>123</v>
+        <v>201</v>
       </c>
       <c r="J186" s="1">
         <v>3030101</v>
@@ -7010,10 +7022,10 @@
         <v>20</v>
       </c>
       <c r="H187" t="s">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="I187" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="J187" s="1">
         <v>3010101</v>
@@ -7042,10 +7054,10 @@
         <v>20</v>
       </c>
       <c r="H188" t="s">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="I188" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="J188" s="1">
         <v>3010101</v>
@@ -7074,10 +7086,10 @@
         <v>20</v>
       </c>
       <c r="H189" t="s">
-        <v>193</v>
+        <v>161</v>
       </c>
       <c r="I189" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="J189" s="1">
         <v>3010101</v>
@@ -7106,10 +7118,10 @@
         <v>20</v>
       </c>
       <c r="H190" t="s">
-        <v>193</v>
+        <v>161</v>
       </c>
       <c r="I190" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="J190" s="1">
         <v>3030101</v>
@@ -7138,10 +7150,10 @@
         <v>20</v>
       </c>
       <c r="H191" t="s">
-        <v>193</v>
+        <v>161</v>
       </c>
       <c r="I191" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="J191" s="1">
         <v>3030101</v>
@@ -7170,10 +7182,10 @@
         <v>20</v>
       </c>
       <c r="H192" t="s">
-        <v>193</v>
+        <v>161</v>
       </c>
       <c r="I192" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="J192" s="1">
         <v>3030101</v>
@@ -7202,10 +7214,10 @@
         <v>20</v>
       </c>
       <c r="H193" t="s">
-        <v>193</v>
+        <v>161</v>
       </c>
       <c r="I193" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="J193" s="1">
         <v>3010101</v>
@@ -7234,10 +7246,10 @@
         <v>20</v>
       </c>
       <c r="H194" t="s">
-        <v>193</v>
+        <v>161</v>
       </c>
       <c r="I194" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="J194" s="1">
         <v>3030101</v>
@@ -7266,10 +7278,10 @@
         <v>20</v>
       </c>
       <c r="H195" t="s">
-        <v>193</v>
+        <v>161</v>
       </c>
       <c r="I195" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="J195" s="1">
         <v>3010101</v>
@@ -7298,10 +7310,10 @@
         <v>20</v>
       </c>
       <c r="H196" t="s">
-        <v>193</v>
+        <v>161</v>
       </c>
       <c r="I196" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="J196" s="1">
         <v>3010101</v>
@@ -7330,10 +7342,10 @@
         <v>20</v>
       </c>
       <c r="H197" t="s">
-        <v>194</v>
+        <v>162</v>
       </c>
       <c r="I197" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="J197" s="1">
         <v>3010101</v>
@@ -7362,10 +7374,10 @@
         <v>20</v>
       </c>
       <c r="H198" t="s">
-        <v>194</v>
+        <v>162</v>
       </c>
       <c r="I198" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="J198" s="1">
         <v>3030101</v>
@@ -7394,10 +7406,10 @@
         <v>20</v>
       </c>
       <c r="H199" t="s">
-        <v>194</v>
+        <v>162</v>
       </c>
       <c r="I199" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="J199" s="1">
         <v>3030101</v>
@@ -7426,10 +7438,10 @@
         <v>20</v>
       </c>
       <c r="H200" t="s">
-        <v>194</v>
+        <v>162</v>
       </c>
       <c r="I200" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="J200" s="1">
         <v>3030101</v>
@@ -7458,10 +7470,10 @@
         <v>20</v>
       </c>
       <c r="H201" t="s">
-        <v>194</v>
+        <v>162</v>
       </c>
       <c r="I201" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="J201" s="1">
         <v>3010101</v>
@@ -7490,10 +7502,10 @@
         <v>20</v>
       </c>
       <c r="H202" t="s">
-        <v>194</v>
+        <v>162</v>
       </c>
       <c r="I202" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="J202" s="1">
         <v>3030101</v>
@@ -7522,10 +7534,10 @@
         <v>20</v>
       </c>
       <c r="H203" t="s">
-        <v>194</v>
+        <v>162</v>
       </c>
       <c r="I203" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="J203" s="1">
         <v>3010101</v>
@@ -7554,10 +7566,10 @@
         <v>20</v>
       </c>
       <c r="H204" t="s">
-        <v>194</v>
+        <v>162</v>
       </c>
       <c r="I204" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="J204" s="1">
         <v>3010101</v>
@@ -7586,10 +7598,10 @@
         <v>20</v>
       </c>
       <c r="H205" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="I205" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="J205" s="1">
         <v>3010101</v>
@@ -7618,10 +7630,10 @@
         <v>20</v>
       </c>
       <c r="H206" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="I206" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="J206" s="1">
         <v>3030101</v>
@@ -7650,10 +7662,10 @@
         <v>20</v>
       </c>
       <c r="H207" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="I207" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="J207" s="1">
         <v>3030101</v>
@@ -7682,10 +7694,10 @@
         <v>20</v>
       </c>
       <c r="H208" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="I208" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="J208" s="1">
         <v>3030101</v>
@@ -7714,10 +7726,10 @@
         <v>20</v>
       </c>
       <c r="H209" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="I209" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="J209" s="1">
         <v>3010101</v>
@@ -7746,10 +7758,10 @@
         <v>20</v>
       </c>
       <c r="H210" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="I210" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="J210" s="1">
         <v>3030101</v>
@@ -7778,10 +7790,10 @@
         <v>20</v>
       </c>
       <c r="H211" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="I211" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="J211" s="1">
         <v>3010101</v>
@@ -7810,10 +7822,10 @@
         <v>20</v>
       </c>
       <c r="H212" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="I212" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="J212" s="1">
         <v>3010101</v>
@@ -7842,10 +7854,10 @@
         <v>20</v>
       </c>
       <c r="H213" t="s">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="I213" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="J213" s="1">
         <v>3010101</v>
@@ -7874,10 +7886,10 @@
         <v>20</v>
       </c>
       <c r="H214" t="s">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="I214" t="s">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="J214" s="1">
         <v>3030101</v>
@@ -7906,10 +7918,10 @@
         <v>20</v>
       </c>
       <c r="H215" t="s">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="I215" t="s">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="J215" s="1">
         <v>3030101</v>
@@ -7938,10 +7950,10 @@
         <v>20</v>
       </c>
       <c r="H216" t="s">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="I216" t="s">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="J216" s="1">
         <v>3030101</v>
@@ -7970,10 +7982,10 @@
         <v>20</v>
       </c>
       <c r="H217" t="s">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="I217" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="J217" s="1">
         <v>3010101</v>
@@ -8002,10 +8014,10 @@
         <v>20</v>
       </c>
       <c r="H218" t="s">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="I218" t="s">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="J218" s="1">
         <v>3030101</v>
@@ -8034,10 +8046,10 @@
         <v>20</v>
       </c>
       <c r="H219" t="s">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="I219" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="J219" s="1">
         <v>3010101</v>
@@ -8066,10 +8078,10 @@
         <v>20</v>
       </c>
       <c r="H220" t="s">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="I220" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="J220" s="1">
         <v>3010101</v>
@@ -8098,10 +8110,10 @@
         <v>20</v>
       </c>
       <c r="H221" t="s">
-        <v>197</v>
+        <v>165</v>
       </c>
       <c r="I221" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="J221" s="1">
         <v>3010101</v>
@@ -8130,10 +8142,10 @@
         <v>20</v>
       </c>
       <c r="H222" t="s">
-        <v>197</v>
+        <v>165</v>
       </c>
       <c r="I222" t="s">
-        <v>129</v>
+        <v>203</v>
       </c>
       <c r="J222" s="1">
         <v>3030101</v>
@@ -8162,10 +8174,10 @@
         <v>20</v>
       </c>
       <c r="H223" t="s">
-        <v>197</v>
+        <v>165</v>
       </c>
       <c r="I223" t="s">
-        <v>129</v>
+        <v>203</v>
       </c>
       <c r="J223" s="1">
         <v>3030101</v>
@@ -8194,10 +8206,10 @@
         <v>20</v>
       </c>
       <c r="H224" t="s">
-        <v>197</v>
+        <v>165</v>
       </c>
       <c r="I224" t="s">
-        <v>129</v>
+        <v>203</v>
       </c>
       <c r="J224" s="1">
         <v>3030101</v>
@@ -8226,10 +8238,10 @@
         <v>20</v>
       </c>
       <c r="H225" t="s">
-        <v>197</v>
+        <v>165</v>
       </c>
       <c r="I225" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="J225" s="1">
         <v>3010101</v>
@@ -8258,10 +8270,10 @@
         <v>20</v>
       </c>
       <c r="H226" t="s">
-        <v>197</v>
+        <v>165</v>
       </c>
       <c r="I226" t="s">
-        <v>129</v>
+        <v>203</v>
       </c>
       <c r="J226" s="1">
         <v>3030101</v>
@@ -8290,10 +8302,10 @@
         <v>20</v>
       </c>
       <c r="H227" t="s">
-        <v>197</v>
+        <v>165</v>
       </c>
       <c r="I227" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="J227" s="1">
         <v>3010101</v>
@@ -8322,10 +8334,10 @@
         <v>20</v>
       </c>
       <c r="H228" t="s">
-        <v>197</v>
+        <v>165</v>
       </c>
       <c r="I228" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="J228" s="1">
         <v>3010101</v>
@@ -8354,10 +8366,10 @@
         <v>20</v>
       </c>
       <c r="H229" t="s">
-        <v>198</v>
+        <v>166</v>
       </c>
       <c r="I229" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="J229" s="1">
         <v>3010101</v>
@@ -8386,10 +8398,10 @@
         <v>20</v>
       </c>
       <c r="H230" t="s">
-        <v>198</v>
+        <v>166</v>
       </c>
       <c r="I230" t="s">
-        <v>132</v>
+        <v>204</v>
       </c>
       <c r="J230" s="1">
         <v>3030101</v>
@@ -8418,10 +8430,10 @@
         <v>20</v>
       </c>
       <c r="H231" t="s">
-        <v>198</v>
+        <v>166</v>
       </c>
       <c r="I231" t="s">
-        <v>132</v>
+        <v>204</v>
       </c>
       <c r="J231" s="1">
         <v>3030101</v>
@@ -8450,10 +8462,10 @@
         <v>20</v>
       </c>
       <c r="H232" t="s">
-        <v>198</v>
+        <v>166</v>
       </c>
       <c r="I232" t="s">
-        <v>132</v>
+        <v>204</v>
       </c>
       <c r="J232" s="1">
         <v>3030101</v>
@@ -8482,10 +8494,10 @@
         <v>20</v>
       </c>
       <c r="H233" t="s">
-        <v>198</v>
+        <v>166</v>
       </c>
       <c r="I233" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="J233" s="1">
         <v>3010101</v>
@@ -8514,10 +8526,10 @@
         <v>20</v>
       </c>
       <c r="H234" t="s">
-        <v>198</v>
+        <v>166</v>
       </c>
       <c r="I234" t="s">
-        <v>132</v>
+        <v>204</v>
       </c>
       <c r="J234" s="1">
         <v>3030101</v>
@@ -8546,10 +8558,10 @@
         <v>20</v>
       </c>
       <c r="H235" t="s">
-        <v>198</v>
+        <v>166</v>
       </c>
       <c r="I235" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="J235" s="1">
         <v>3010101</v>
@@ -8578,10 +8590,10 @@
         <v>20</v>
       </c>
       <c r="H236" t="s">
-        <v>198</v>
+        <v>166</v>
       </c>
       <c r="I236" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="J236" s="1">
         <v>3010101</v>
@@ -8610,10 +8622,10 @@
         <v>20</v>
       </c>
       <c r="H237" t="s">
-        <v>199</v>
+        <v>167</v>
       </c>
       <c r="I237" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="J237" s="1">
         <v>3010101</v>
@@ -8642,10 +8654,10 @@
         <v>20</v>
       </c>
       <c r="H238" t="s">
-        <v>199</v>
+        <v>167</v>
       </c>
       <c r="I238" t="s">
-        <v>134</v>
+        <v>205</v>
       </c>
       <c r="J238" s="1">
         <v>3030101</v>
@@ -8674,10 +8686,10 @@
         <v>20</v>
       </c>
       <c r="H239" t="s">
-        <v>199</v>
+        <v>167</v>
       </c>
       <c r="I239" t="s">
-        <v>134</v>
+        <v>205</v>
       </c>
       <c r="J239" s="1">
         <v>3030101</v>
@@ -8706,10 +8718,10 @@
         <v>20</v>
       </c>
       <c r="H240" t="s">
-        <v>199</v>
+        <v>167</v>
       </c>
       <c r="I240" t="s">
-        <v>134</v>
+        <v>205</v>
       </c>
       <c r="J240" s="1">
         <v>3030101</v>
@@ -8738,10 +8750,10 @@
         <v>20</v>
       </c>
       <c r="H241" t="s">
-        <v>199</v>
+        <v>167</v>
       </c>
       <c r="I241" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="J241" s="1">
         <v>3010101</v>
@@ -8770,10 +8782,10 @@
         <v>20</v>
       </c>
       <c r="H242" t="s">
-        <v>199</v>
+        <v>167</v>
       </c>
       <c r="I242" t="s">
-        <v>134</v>
+        <v>205</v>
       </c>
       <c r="J242" s="1">
         <v>3030101</v>
@@ -8802,10 +8814,10 @@
         <v>20</v>
       </c>
       <c r="H243" t="s">
-        <v>199</v>
+        <v>167</v>
       </c>
       <c r="I243" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="J243" s="1">
         <v>3010101</v>
@@ -8834,10 +8846,10 @@
         <v>20</v>
       </c>
       <c r="H244" t="s">
-        <v>199</v>
+        <v>167</v>
       </c>
       <c r="I244" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="J244" s="1">
         <v>3010101</v>
@@ -8866,10 +8878,10 @@
         <v>30</v>
       </c>
       <c r="H245" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
       <c r="I245" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="J245" s="1">
         <v>3010101</v>
@@ -8898,10 +8910,10 @@
         <v>30</v>
       </c>
       <c r="H246" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
       <c r="I246" t="s">
-        <v>134</v>
+        <v>206</v>
       </c>
       <c r="J246" s="1">
         <v>3030101</v>
@@ -8930,10 +8942,10 @@
         <v>30</v>
       </c>
       <c r="H247" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
       <c r="I247" t="s">
-        <v>134</v>
+        <v>206</v>
       </c>
       <c r="J247" s="1">
         <v>3030101</v>
@@ -8962,10 +8974,10 @@
         <v>30</v>
       </c>
       <c r="H248" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
       <c r="I248" t="s">
-        <v>134</v>
+        <v>206</v>
       </c>
       <c r="J248" s="1">
         <v>3030101</v>
@@ -8994,10 +9006,10 @@
         <v>30</v>
       </c>
       <c r="H249" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
       <c r="I249" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="J249" s="1">
         <v>3010101</v>
@@ -9026,10 +9038,10 @@
         <v>30</v>
       </c>
       <c r="H250" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
       <c r="I250" t="s">
-        <v>134</v>
+        <v>206</v>
       </c>
       <c r="J250" s="1">
         <v>3030101</v>
@@ -9058,10 +9070,10 @@
         <v>30</v>
       </c>
       <c r="H251" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
       <c r="I251" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="J251" s="1">
         <v>3010101</v>
@@ -9090,10 +9102,10 @@
         <v>30</v>
       </c>
       <c r="H252" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
       <c r="I252" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="J252" s="1">
         <v>3010101</v>
@@ -9122,10 +9134,10 @@
         <v>30</v>
       </c>
       <c r="H253" t="s">
-        <v>201</v>
+        <v>169</v>
       </c>
       <c r="I253" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="J253" s="1">
         <v>3010101</v>
@@ -9154,10 +9166,10 @@
         <v>30</v>
       </c>
       <c r="H254" t="s">
-        <v>201</v>
+        <v>169</v>
       </c>
       <c r="I254" t="s">
-        <v>137</v>
+        <v>207</v>
       </c>
       <c r="J254" s="1">
         <v>3030101</v>
@@ -9186,10 +9198,10 @@
         <v>30</v>
       </c>
       <c r="H255" t="s">
-        <v>201</v>
+        <v>169</v>
       </c>
       <c r="I255" t="s">
-        <v>137</v>
+        <v>207</v>
       </c>
       <c r="J255" s="1">
         <v>3030101</v>
@@ -9218,10 +9230,10 @@
         <v>30</v>
       </c>
       <c r="H256" t="s">
-        <v>201</v>
+        <v>169</v>
       </c>
       <c r="I256" t="s">
-        <v>137</v>
+        <v>207</v>
       </c>
       <c r="J256" s="1">
         <v>3030101</v>
@@ -9250,10 +9262,10 @@
         <v>30</v>
       </c>
       <c r="H257" t="s">
-        <v>201</v>
+        <v>169</v>
       </c>
       <c r="I257" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="J257" s="1">
         <v>3010101</v>
@@ -9282,10 +9294,10 @@
         <v>30</v>
       </c>
       <c r="H258" t="s">
-        <v>201</v>
+        <v>169</v>
       </c>
       <c r="I258" t="s">
-        <v>137</v>
+        <v>207</v>
       </c>
       <c r="J258" s="1">
         <v>3030101</v>
@@ -9314,10 +9326,10 @@
         <v>30</v>
       </c>
       <c r="H259" t="s">
-        <v>201</v>
+        <v>169</v>
       </c>
       <c r="I259" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="J259" s="1">
         <v>3010101</v>
@@ -9346,10 +9358,10 @@
         <v>30</v>
       </c>
       <c r="H260" t="s">
-        <v>201</v>
+        <v>169</v>
       </c>
       <c r="I260" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="J260" s="1">
         <v>3010101</v>
@@ -9378,10 +9390,10 @@
         <v>30</v>
       </c>
       <c r="H261" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="I261" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="J261" s="1">
         <v>3010101</v>
@@ -9410,10 +9422,10 @@
         <v>30</v>
       </c>
       <c r="H262" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="I262" t="s">
-        <v>137</v>
+        <v>208</v>
       </c>
       <c r="J262" s="1">
         <v>3030101</v>
@@ -9442,10 +9454,10 @@
         <v>30</v>
       </c>
       <c r="H263" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="I263" t="s">
-        <v>137</v>
+        <v>208</v>
       </c>
       <c r="J263" s="1">
         <v>3030101</v>
@@ -9474,10 +9486,10 @@
         <v>30</v>
       </c>
       <c r="H264" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="I264" t="s">
-        <v>137</v>
+        <v>208</v>
       </c>
       <c r="J264" s="1">
         <v>3030101</v>
@@ -9506,10 +9518,10 @@
         <v>30</v>
       </c>
       <c r="H265" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="I265" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="J265" s="1">
         <v>3010101</v>
@@ -9538,10 +9550,10 @@
         <v>30</v>
       </c>
       <c r="H266" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="I266" t="s">
-        <v>137</v>
+        <v>208</v>
       </c>
       <c r="J266" s="1">
         <v>3030101</v>
@@ -9570,10 +9582,10 @@
         <v>30</v>
       </c>
       <c r="H267" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="I267" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="J267" s="1">
         <v>3010101</v>
@@ -9602,10 +9614,10 @@
         <v>30</v>
       </c>
       <c r="H268" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="I268" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="J268" s="1">
         <v>3010101</v>
@@ -9634,10 +9646,10 @@
         <v>30</v>
       </c>
       <c r="H269" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="I269" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="J269" s="1">
         <v>3010101</v>
@@ -9666,10 +9678,10 @@
         <v>30</v>
       </c>
       <c r="H270" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="I270" t="s">
-        <v>140</v>
+        <v>209</v>
       </c>
       <c r="J270" s="1">
         <v>3030101</v>
@@ -9698,10 +9710,10 @@
         <v>30</v>
       </c>
       <c r="H271" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="I271" t="s">
-        <v>140</v>
+        <v>209</v>
       </c>
       <c r="J271" s="1">
         <v>3030101</v>
@@ -9730,10 +9742,10 @@
         <v>30</v>
       </c>
       <c r="H272" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="I272" t="s">
-        <v>140</v>
+        <v>209</v>
       </c>
       <c r="J272" s="1">
         <v>3030101</v>
@@ -9762,10 +9774,10 @@
         <v>30</v>
       </c>
       <c r="H273" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="I273" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="J273" s="1">
         <v>3010101</v>
@@ -9794,10 +9806,10 @@
         <v>30</v>
       </c>
       <c r="H274" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="I274" t="s">
-        <v>140</v>
+        <v>209</v>
       </c>
       <c r="J274" s="1">
         <v>3030101</v>
@@ -9826,10 +9838,10 @@
         <v>30</v>
       </c>
       <c r="H275" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="I275" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="J275" s="1">
         <v>3010101</v>
@@ -9858,10 +9870,10 @@
         <v>30</v>
       </c>
       <c r="H276" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="I276" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="J276" s="1">
         <v>3010101</v>
@@ -9890,10 +9902,10 @@
         <v>30</v>
       </c>
       <c r="H277" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="I277" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="J277" s="1">
         <v>3010101</v>
@@ -9922,10 +9934,10 @@
         <v>30</v>
       </c>
       <c r="H278" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="I278" t="s">
-        <v>142</v>
+        <v>210</v>
       </c>
       <c r="J278" s="1">
         <v>3030101</v>
@@ -9954,10 +9966,10 @@
         <v>30</v>
       </c>
       <c r="H279" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="I279" t="s">
-        <v>142</v>
+        <v>210</v>
       </c>
       <c r="J279" s="1">
         <v>3030101</v>
@@ -9986,10 +9998,10 @@
         <v>30</v>
       </c>
       <c r="H280" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="I280" t="s">
-        <v>142</v>
+        <v>210</v>
       </c>
       <c r="J280" s="1">
         <v>3030101</v>
@@ -10018,10 +10030,10 @@
         <v>30</v>
       </c>
       <c r="H281" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="I281" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="J281" s="1">
         <v>3010101</v>
@@ -10050,10 +10062,10 @@
         <v>30</v>
       </c>
       <c r="H282" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="I282" t="s">
-        <v>142</v>
+        <v>210</v>
       </c>
       <c r="J282" s="1">
         <v>3030101</v>
@@ -10082,10 +10094,10 @@
         <v>30</v>
       </c>
       <c r="H283" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="I283" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="J283" s="1">
         <v>3010101</v>
@@ -10114,10 +10126,10 @@
         <v>30</v>
       </c>
       <c r="H284" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="I284" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="J284" s="1">
         <v>3010101</v>
@@ -10146,10 +10158,10 @@
         <v>30</v>
       </c>
       <c r="H285" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="I285" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="J285" s="1">
         <v>3010101</v>
@@ -10178,10 +10190,10 @@
         <v>30</v>
       </c>
       <c r="H286" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="I286" t="s">
-        <v>144</v>
+        <v>211</v>
       </c>
       <c r="J286" s="1">
         <v>3030101</v>
@@ -10210,10 +10222,10 @@
         <v>30</v>
       </c>
       <c r="H287" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="I287" t="s">
-        <v>144</v>
+        <v>211</v>
       </c>
       <c r="J287" s="1">
         <v>3030101</v>
@@ -10242,10 +10254,10 @@
         <v>30</v>
       </c>
       <c r="H288" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="I288" t="s">
-        <v>144</v>
+        <v>211</v>
       </c>
       <c r="J288" s="1">
         <v>3030101</v>
@@ -10274,10 +10286,10 @@
         <v>30</v>
       </c>
       <c r="H289" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="I289" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="J289" s="1">
         <v>3010101</v>
@@ -10306,10 +10318,10 @@
         <v>30</v>
       </c>
       <c r="H290" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="I290" t="s">
-        <v>144</v>
+        <v>211</v>
       </c>
       <c r="J290" s="1">
         <v>3030101</v>
@@ -10338,10 +10350,10 @@
         <v>30</v>
       </c>
       <c r="H291" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="I291" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="J291" s="1">
         <v>3010101</v>
@@ -10370,10 +10382,10 @@
         <v>30</v>
       </c>
       <c r="H292" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="I292" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="J292" s="1">
         <v>3010101</v>
@@ -10402,10 +10414,10 @@
         <v>30</v>
       </c>
       <c r="H293" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="I293" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="J293" s="1">
         <v>3010101</v>
@@ -10434,10 +10446,10 @@
         <v>30</v>
       </c>
       <c r="H294" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="I294" t="s">
-        <v>144</v>
+        <v>212</v>
       </c>
       <c r="J294" s="1">
         <v>3030101</v>
@@ -10466,10 +10478,10 @@
         <v>30</v>
       </c>
       <c r="H295" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="I295" t="s">
-        <v>144</v>
+        <v>212</v>
       </c>
       <c r="J295" s="1">
         <v>3030101</v>
@@ -10498,10 +10510,10 @@
         <v>30</v>
       </c>
       <c r="H296" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="I296" t="s">
-        <v>144</v>
+        <v>212</v>
       </c>
       <c r="J296" s="1">
         <v>3030101</v>
@@ -10530,10 +10542,10 @@
         <v>30</v>
       </c>
       <c r="H297" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="I297" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="J297" s="1">
         <v>3010101</v>
@@ -10562,10 +10574,10 @@
         <v>30</v>
       </c>
       <c r="H298" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="I298" t="s">
-        <v>144</v>
+        <v>212</v>
       </c>
       <c r="J298" s="1">
         <v>3030101</v>
@@ -10594,10 +10606,10 @@
         <v>30</v>
       </c>
       <c r="H299" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="I299" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="J299" s="1">
         <v>3010101</v>
@@ -10626,10 +10638,10 @@
         <v>30</v>
       </c>
       <c r="H300" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="I300" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="J300" s="1">
         <v>3010101</v>
@@ -10658,10 +10670,10 @@
         <v>30</v>
       </c>
       <c r="H301" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
       <c r="I301" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="J301" s="1">
         <v>3010101</v>
@@ -10690,10 +10702,10 @@
         <v>30</v>
       </c>
       <c r="H302" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
       <c r="I302" t="s">
-        <v>147</v>
+        <v>213</v>
       </c>
       <c r="J302" s="1">
         <v>3030101</v>
@@ -10722,10 +10734,10 @@
         <v>30</v>
       </c>
       <c r="H303" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
       <c r="I303" t="s">
-        <v>147</v>
+        <v>213</v>
       </c>
       <c r="J303" s="1">
         <v>3030101</v>
@@ -10754,10 +10766,10 @@
         <v>30</v>
       </c>
       <c r="H304" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
       <c r="I304" t="s">
-        <v>147</v>
+        <v>213</v>
       </c>
       <c r="J304" s="1">
         <v>3030101</v>
@@ -10786,10 +10798,10 @@
         <v>30</v>
       </c>
       <c r="H305" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
       <c r="I305" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="J305" s="1">
         <v>3010101</v>
@@ -10818,10 +10830,10 @@
         <v>30</v>
       </c>
       <c r="H306" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
       <c r="I306" t="s">
-        <v>147</v>
+        <v>213</v>
       </c>
       <c r="J306" s="1">
         <v>3030101</v>
@@ -10850,10 +10862,10 @@
         <v>30</v>
       </c>
       <c r="H307" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
       <c r="I307" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="J307" s="1">
         <v>3010101</v>
@@ -10882,10 +10894,10 @@
         <v>30</v>
       </c>
       <c r="H308" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
       <c r="I308" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="J308" s="1">
         <v>3010101</v>
@@ -10914,10 +10926,10 @@
         <v>30</v>
       </c>
       <c r="H309" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="I309" t="s">
-        <v>148</v>
+        <v>122</v>
       </c>
       <c r="J309" s="1">
         <v>3010101</v>
@@ -10946,10 +10958,10 @@
         <v>30</v>
       </c>
       <c r="H310" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="I310" t="s">
-        <v>149</v>
+        <v>214</v>
       </c>
       <c r="J310" s="1">
         <v>3030101</v>
@@ -10978,10 +10990,10 @@
         <v>30</v>
       </c>
       <c r="H311" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="I311" t="s">
-        <v>149</v>
+        <v>214</v>
       </c>
       <c r="J311" s="1">
         <v>3030101</v>
@@ -11010,10 +11022,10 @@
         <v>30</v>
       </c>
       <c r="H312" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="I312" t="s">
-        <v>149</v>
+        <v>214</v>
       </c>
       <c r="J312" s="1">
         <v>3030101</v>
@@ -11042,10 +11054,10 @@
         <v>30</v>
       </c>
       <c r="H313" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="I313" t="s">
-        <v>148</v>
+        <v>122</v>
       </c>
       <c r="J313" s="1">
         <v>3010101</v>
@@ -11074,10 +11086,10 @@
         <v>30</v>
       </c>
       <c r="H314" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="I314" t="s">
-        <v>149</v>
+        <v>214</v>
       </c>
       <c r="J314" s="1">
         <v>3030101</v>
@@ -11106,10 +11118,10 @@
         <v>30</v>
       </c>
       <c r="H315" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="I315" t="s">
-        <v>148</v>
+        <v>122</v>
       </c>
       <c r="J315" s="1">
         <v>3010101</v>
@@ -11138,10 +11150,10 @@
         <v>30</v>
       </c>
       <c r="H316" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="I316" t="s">
-        <v>148</v>
+        <v>122</v>
       </c>
       <c r="J316" s="1">
         <v>3010101</v>
@@ -11170,10 +11182,10 @@
         <v>30</v>
       </c>
       <c r="H317" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="I317" t="s">
-        <v>150</v>
+        <v>124</v>
       </c>
       <c r="J317" s="1">
         <v>3010101</v>
@@ -11202,10 +11214,10 @@
         <v>30</v>
       </c>
       <c r="H318" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="I318" t="s">
-        <v>151</v>
+        <v>215</v>
       </c>
       <c r="J318" s="1">
         <v>3030101</v>
@@ -11234,10 +11246,10 @@
         <v>30</v>
       </c>
       <c r="H319" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="I319" t="s">
-        <v>151</v>
+        <v>215</v>
       </c>
       <c r="J319" s="1">
         <v>3030101</v>
@@ -11266,10 +11278,10 @@
         <v>30</v>
       </c>
       <c r="H320" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="I320" t="s">
-        <v>151</v>
+        <v>215</v>
       </c>
       <c r="J320" s="1">
         <v>3030101</v>
@@ -11298,10 +11310,10 @@
         <v>30</v>
       </c>
       <c r="H321" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="I321" t="s">
-        <v>150</v>
+        <v>124</v>
       </c>
       <c r="J321" s="1">
         <v>3010101</v>
@@ -11330,10 +11342,10 @@
         <v>30</v>
       </c>
       <c r="H322" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="I322" t="s">
-        <v>151</v>
+        <v>215</v>
       </c>
       <c r="J322" s="1">
         <v>3030101</v>
@@ -11362,10 +11374,10 @@
         <v>30</v>
       </c>
       <c r="H323" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="I323" t="s">
-        <v>150</v>
+        <v>124</v>
       </c>
       <c r="J323" s="1">
         <v>3010101</v>
@@ -11394,10 +11406,10 @@
         <v>30</v>
       </c>
       <c r="H324" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="I324" t="s">
-        <v>150</v>
+        <v>124</v>
       </c>
       <c r="J324" s="1">
         <v>3010101</v>
@@ -11426,10 +11438,10 @@
         <v>40</v>
       </c>
       <c r="H325" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="I325" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="J325" s="1">
         <v>3010101</v>
@@ -11458,10 +11470,10 @@
         <v>40</v>
       </c>
       <c r="H326" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="I326" t="s">
-        <v>153</v>
+        <v>216</v>
       </c>
       <c r="J326" s="1">
         <v>3030101</v>
@@ -11490,10 +11502,10 @@
         <v>40</v>
       </c>
       <c r="H327" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="I327" t="s">
-        <v>153</v>
+        <v>216</v>
       </c>
       <c r="J327" s="1">
         <v>3030101</v>
@@ -11522,10 +11534,10 @@
         <v>40</v>
       </c>
       <c r="H328" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="I328" t="s">
-        <v>153</v>
+        <v>216</v>
       </c>
       <c r="J328" s="1">
         <v>3030101</v>
@@ -11554,10 +11566,10 @@
         <v>40</v>
       </c>
       <c r="H329" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="I329" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="J329" s="1">
         <v>3010101</v>
@@ -11586,10 +11598,10 @@
         <v>40</v>
       </c>
       <c r="H330" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="I330" t="s">
-        <v>153</v>
+        <v>216</v>
       </c>
       <c r="J330" s="1">
         <v>3030101</v>
@@ -11618,10 +11630,10 @@
         <v>40</v>
       </c>
       <c r="H331" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="I331" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="J331" s="1">
         <v>3010101</v>
@@ -11650,10 +11662,10 @@
         <v>40</v>
       </c>
       <c r="H332" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="I332" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="J332" s="1">
         <v>3010101</v>
@@ -11682,10 +11694,10 @@
         <v>40</v>
       </c>
       <c r="H333" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="I333" t="s">
-        <v>154</v>
+        <v>127</v>
       </c>
       <c r="J333" s="1">
         <v>3010101</v>
@@ -11714,10 +11726,10 @@
         <v>40</v>
       </c>
       <c r="H334" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="I334" t="s">
-        <v>155</v>
+        <v>217</v>
       </c>
       <c r="J334" s="1">
         <v>3030101</v>
@@ -11746,10 +11758,10 @@
         <v>40</v>
       </c>
       <c r="H335" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="I335" t="s">
-        <v>155</v>
+        <v>217</v>
       </c>
       <c r="J335" s="1">
         <v>3030101</v>
@@ -11778,10 +11790,10 @@
         <v>40</v>
       </c>
       <c r="H336" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="I336" t="s">
-        <v>155</v>
+        <v>217</v>
       </c>
       <c r="J336" s="1">
         <v>3030101</v>
@@ -11810,10 +11822,10 @@
         <v>40</v>
       </c>
       <c r="H337" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="I337" t="s">
-        <v>154</v>
+        <v>127</v>
       </c>
       <c r="J337" s="1">
         <v>3010101</v>
@@ -11842,10 +11854,10 @@
         <v>40</v>
       </c>
       <c r="H338" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="I338" t="s">
-        <v>155</v>
+        <v>217</v>
       </c>
       <c r="J338" s="1">
         <v>3030101</v>
@@ -11874,10 +11886,10 @@
         <v>40</v>
       </c>
       <c r="H339" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="I339" t="s">
-        <v>154</v>
+        <v>127</v>
       </c>
       <c r="J339" s="1">
         <v>3010101</v>
@@ -11906,10 +11918,10 @@
         <v>40</v>
       </c>
       <c r="H340" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="I340" t="s">
-        <v>154</v>
+        <v>127</v>
       </c>
       <c r="J340" s="1">
         <v>3010101</v>
@@ -11938,10 +11950,10 @@
         <v>40</v>
       </c>
       <c r="H341" t="s">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="I341" t="s">
-        <v>156</v>
+        <v>129</v>
       </c>
       <c r="J341" s="1">
         <v>3010101</v>
@@ -11970,10 +11982,10 @@
         <v>40</v>
       </c>
       <c r="H342" t="s">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="I342" t="s">
-        <v>157</v>
+        <v>218</v>
       </c>
       <c r="J342" s="1">
         <v>3030101</v>
@@ -12002,10 +12014,10 @@
         <v>40</v>
       </c>
       <c r="H343" t="s">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="I343" t="s">
-        <v>157</v>
+        <v>218</v>
       </c>
       <c r="J343" s="1">
         <v>3030101</v>
@@ -12034,10 +12046,10 @@
         <v>40</v>
       </c>
       <c r="H344" t="s">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="I344" t="s">
-        <v>157</v>
+        <v>218</v>
       </c>
       <c r="J344" s="1">
         <v>3030101</v>
@@ -12066,10 +12078,10 @@
         <v>40</v>
       </c>
       <c r="H345" t="s">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="I345" t="s">
-        <v>156</v>
+        <v>129</v>
       </c>
       <c r="J345" s="1">
         <v>3010101</v>
@@ -12098,10 +12110,10 @@
         <v>40</v>
       </c>
       <c r="H346" t="s">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="I346" t="s">
-        <v>157</v>
+        <v>218</v>
       </c>
       <c r="J346" s="1">
         <v>3030101</v>
@@ -12130,10 +12142,10 @@
         <v>40</v>
       </c>
       <c r="H347" t="s">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="I347" t="s">
-        <v>156</v>
+        <v>129</v>
       </c>
       <c r="J347" s="1">
         <v>3010101</v>
@@ -12162,10 +12174,10 @@
         <v>40</v>
       </c>
       <c r="H348" t="s">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="I348" t="s">
-        <v>156</v>
+        <v>129</v>
       </c>
       <c r="J348" s="1">
         <v>3010101</v>
@@ -12194,10 +12206,10 @@
         <v>40</v>
       </c>
       <c r="H349" t="s">
-        <v>213</v>
+        <v>181</v>
       </c>
       <c r="I349" t="s">
-        <v>158</v>
+        <v>130</v>
       </c>
       <c r="J349" s="1">
         <v>3010101</v>
@@ -12226,10 +12238,10 @@
         <v>40</v>
       </c>
       <c r="H350" t="s">
-        <v>213</v>
+        <v>181</v>
       </c>
       <c r="I350" t="s">
-        <v>159</v>
+        <v>219</v>
       </c>
       <c r="J350" s="1">
         <v>3030101</v>
@@ -12258,10 +12270,10 @@
         <v>40</v>
       </c>
       <c r="H351" t="s">
-        <v>213</v>
+        <v>181</v>
       </c>
       <c r="I351" t="s">
-        <v>159</v>
+        <v>219</v>
       </c>
       <c r="J351" s="1">
         <v>3030101</v>
@@ -12290,10 +12302,10 @@
         <v>40</v>
       </c>
       <c r="H352" t="s">
-        <v>213</v>
+        <v>181</v>
       </c>
       <c r="I352" t="s">
-        <v>159</v>
+        <v>219</v>
       </c>
       <c r="J352" s="1">
         <v>3030101</v>
@@ -12322,10 +12334,10 @@
         <v>40</v>
       </c>
       <c r="H353" t="s">
-        <v>213</v>
+        <v>181</v>
       </c>
       <c r="I353" t="s">
-        <v>158</v>
+        <v>130</v>
       </c>
       <c r="J353" s="1">
         <v>3010101</v>
@@ -12354,10 +12366,10 @@
         <v>40</v>
       </c>
       <c r="H354" t="s">
-        <v>213</v>
+        <v>181</v>
       </c>
       <c r="I354" t="s">
-        <v>159</v>
+        <v>219</v>
       </c>
       <c r="J354" s="1">
         <v>3030101</v>
@@ -12386,10 +12398,10 @@
         <v>40</v>
       </c>
       <c r="H355" t="s">
-        <v>213</v>
+        <v>181</v>
       </c>
       <c r="I355" t="s">
-        <v>158</v>
+        <v>130</v>
       </c>
       <c r="J355" s="1">
         <v>3010101</v>
@@ -12418,10 +12430,10 @@
         <v>40</v>
       </c>
       <c r="H356" t="s">
-        <v>213</v>
+        <v>181</v>
       </c>
       <c r="I356" t="s">
-        <v>158</v>
+        <v>130</v>
       </c>
       <c r="J356" s="1">
         <v>3010101</v>
@@ -12450,10 +12462,10 @@
         <v>40</v>
       </c>
       <c r="H357" t="s">
-        <v>214</v>
+        <v>182</v>
       </c>
       <c r="I357" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="J357" s="1">
         <v>3010101</v>
@@ -12482,10 +12494,10 @@
         <v>40</v>
       </c>
       <c r="H358" t="s">
-        <v>214</v>
+        <v>182</v>
       </c>
       <c r="I358" t="s">
-        <v>161</v>
+        <v>220</v>
       </c>
       <c r="J358" s="1">
         <v>3030101</v>
@@ -12514,10 +12526,10 @@
         <v>40</v>
       </c>
       <c r="H359" t="s">
-        <v>214</v>
+        <v>182</v>
       </c>
       <c r="I359" t="s">
-        <v>161</v>
+        <v>220</v>
       </c>
       <c r="J359" s="1">
         <v>3030101</v>
@@ -12546,10 +12558,10 @@
         <v>40</v>
       </c>
       <c r="H360" t="s">
-        <v>214</v>
+        <v>182</v>
       </c>
       <c r="I360" t="s">
-        <v>161</v>
+        <v>220</v>
       </c>
       <c r="J360" s="1">
         <v>3030101</v>
@@ -12578,10 +12590,10 @@
         <v>40</v>
       </c>
       <c r="H361" t="s">
-        <v>214</v>
+        <v>182</v>
       </c>
       <c r="I361" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="J361" s="1">
         <v>3010101</v>
@@ -12610,10 +12622,10 @@
         <v>40</v>
       </c>
       <c r="H362" t="s">
-        <v>214</v>
+        <v>182</v>
       </c>
       <c r="I362" t="s">
-        <v>161</v>
+        <v>220</v>
       </c>
       <c r="J362" s="1">
         <v>3030101</v>
@@ -12642,10 +12654,10 @@
         <v>40</v>
       </c>
       <c r="H363" t="s">
-        <v>214</v>
+        <v>182</v>
       </c>
       <c r="I363" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="J363" s="1">
         <v>3010101</v>
@@ -12674,10 +12686,10 @@
         <v>40</v>
       </c>
       <c r="H364" t="s">
-        <v>214</v>
+        <v>182</v>
       </c>
       <c r="I364" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="J364" s="1">
         <v>3010101</v>
@@ -12706,10 +12718,10 @@
         <v>40</v>
       </c>
       <c r="H365" t="s">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="I365" t="s">
-        <v>162</v>
+        <v>132</v>
       </c>
       <c r="J365" s="1">
         <v>3010101</v>
@@ -12738,10 +12750,10 @@
         <v>40</v>
       </c>
       <c r="H366" t="s">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="I366" t="s">
-        <v>163</v>
+        <v>221</v>
       </c>
       <c r="J366" s="1">
         <v>3030101</v>
@@ -12770,10 +12782,10 @@
         <v>40</v>
       </c>
       <c r="H367" t="s">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="I367" t="s">
-        <v>163</v>
+        <v>221</v>
       </c>
       <c r="J367" s="1">
         <v>3030101</v>
@@ -12802,10 +12814,10 @@
         <v>40</v>
       </c>
       <c r="H368" t="s">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="I368" t="s">
-        <v>163</v>
+        <v>221</v>
       </c>
       <c r="J368" s="1">
         <v>3030101</v>
@@ -12834,10 +12846,10 @@
         <v>40</v>
       </c>
       <c r="H369" t="s">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="I369" t="s">
-        <v>162</v>
+        <v>132</v>
       </c>
       <c r="J369" s="1">
         <v>3010101</v>
@@ -12866,10 +12878,10 @@
         <v>40</v>
       </c>
       <c r="H370" t="s">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="I370" t="s">
-        <v>163</v>
+        <v>221</v>
       </c>
       <c r="J370" s="1">
         <v>3030101</v>
@@ -12898,10 +12910,10 @@
         <v>40</v>
       </c>
       <c r="H371" t="s">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="I371" t="s">
-        <v>162</v>
+        <v>132</v>
       </c>
       <c r="J371" s="1">
         <v>3010101</v>
@@ -12930,10 +12942,10 @@
         <v>40</v>
       </c>
       <c r="H372" t="s">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="I372" t="s">
-        <v>162</v>
+        <v>132</v>
       </c>
       <c r="J372" s="1">
         <v>3010101</v>
@@ -12962,10 +12974,10 @@
         <v>40</v>
       </c>
       <c r="H373" t="s">
-        <v>216</v>
+        <v>184</v>
       </c>
       <c r="I373" t="s">
-        <v>164</v>
+        <v>134</v>
       </c>
       <c r="J373" s="1">
         <v>3010101</v>
@@ -12994,10 +13006,10 @@
         <v>40</v>
       </c>
       <c r="H374" t="s">
-        <v>216</v>
+        <v>184</v>
       </c>
       <c r="I374" t="s">
-        <v>165</v>
+        <v>222</v>
       </c>
       <c r="J374" s="1">
         <v>3030101</v>
@@ -13026,10 +13038,10 @@
         <v>40</v>
       </c>
       <c r="H375" t="s">
-        <v>216</v>
+        <v>184</v>
       </c>
       <c r="I375" t="s">
-        <v>165</v>
+        <v>222</v>
       </c>
       <c r="J375" s="1">
         <v>3030101</v>
@@ -13058,10 +13070,10 @@
         <v>40</v>
       </c>
       <c r="H376" t="s">
-        <v>216</v>
+        <v>184</v>
       </c>
       <c r="I376" t="s">
-        <v>165</v>
+        <v>222</v>
       </c>
       <c r="J376" s="1">
         <v>3030101</v>
@@ -13090,10 +13102,10 @@
         <v>40</v>
       </c>
       <c r="H377" t="s">
-        <v>216</v>
+        <v>184</v>
       </c>
       <c r="I377" t="s">
-        <v>164</v>
+        <v>134</v>
       </c>
       <c r="J377" s="1">
         <v>3010101</v>
@@ -13122,10 +13134,10 @@
         <v>40</v>
       </c>
       <c r="H378" t="s">
-        <v>216</v>
+        <v>184</v>
       </c>
       <c r="I378" t="s">
-        <v>165</v>
+        <v>222</v>
       </c>
       <c r="J378" s="1">
         <v>3030101</v>
@@ -13154,10 +13166,10 @@
         <v>40</v>
       </c>
       <c r="H379" t="s">
-        <v>216</v>
+        <v>184</v>
       </c>
       <c r="I379" t="s">
-        <v>164</v>
+        <v>134</v>
       </c>
       <c r="J379" s="1">
         <v>3010101</v>
@@ -13186,10 +13198,10 @@
         <v>40</v>
       </c>
       <c r="H380" t="s">
-        <v>216</v>
+        <v>184</v>
       </c>
       <c r="I380" t="s">
-        <v>164</v>
+        <v>134</v>
       </c>
       <c r="J380" s="1">
         <v>3010101</v>
@@ -13218,10 +13230,10 @@
         <v>40</v>
       </c>
       <c r="H381" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="I381" t="s">
-        <v>164</v>
+        <v>134</v>
       </c>
       <c r="J381" s="1">
         <v>3010101</v>
@@ -13250,10 +13262,10 @@
         <v>40</v>
       </c>
       <c r="H382" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="I382" t="s">
-        <v>166</v>
+        <v>223</v>
       </c>
       <c r="J382" s="1">
         <v>3030101</v>
@@ -13282,10 +13294,10 @@
         <v>40</v>
       </c>
       <c r="H383" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="I383" t="s">
-        <v>166</v>
+        <v>223</v>
       </c>
       <c r="J383" s="1">
         <v>3030101</v>
@@ -13314,10 +13326,10 @@
         <v>40</v>
       </c>
       <c r="H384" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="I384" t="s">
-        <v>166</v>
+        <v>223</v>
       </c>
       <c r="J384" s="1">
         <v>3030101</v>
@@ -13346,10 +13358,10 @@
         <v>40</v>
       </c>
       <c r="H385" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="I385" t="s">
-        <v>164</v>
+        <v>134</v>
       </c>
       <c r="J385" s="1">
         <v>3010101</v>
@@ -13378,10 +13390,10 @@
         <v>40</v>
       </c>
       <c r="H386" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="I386" t="s">
-        <v>166</v>
+        <v>223</v>
       </c>
       <c r="J386" s="1">
         <v>3030101</v>
@@ -13410,10 +13422,10 @@
         <v>40</v>
       </c>
       <c r="H387" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="I387" t="s">
-        <v>164</v>
+        <v>134</v>
       </c>
       <c r="J387" s="1">
         <v>3010101</v>
@@ -13442,10 +13454,10 @@
         <v>40</v>
       </c>
       <c r="H388" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="I388" t="s">
-        <v>164</v>
+        <v>134</v>
       </c>
       <c r="J388" s="1">
         <v>3010101</v>
@@ -13474,10 +13486,10 @@
         <v>40</v>
       </c>
       <c r="H389" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="I389" t="s">
-        <v>167</v>
+        <v>135</v>
       </c>
       <c r="J389" s="1">
         <v>3010101</v>
@@ -13506,10 +13518,10 @@
         <v>40</v>
       </c>
       <c r="H390" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="I390" t="s">
-        <v>168</v>
+        <v>223</v>
       </c>
       <c r="J390" s="1">
         <v>3030101</v>
@@ -13538,10 +13550,10 @@
         <v>40</v>
       </c>
       <c r="H391" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="I391" t="s">
-        <v>168</v>
+        <v>223</v>
       </c>
       <c r="J391" s="1">
         <v>3030101</v>
@@ -13570,10 +13582,10 @@
         <v>40</v>
       </c>
       <c r="H392" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="I392" t="s">
-        <v>168</v>
+        <v>223</v>
       </c>
       <c r="J392" s="1">
         <v>3030101</v>
@@ -13602,10 +13614,10 @@
         <v>40</v>
       </c>
       <c r="H393" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="I393" t="s">
-        <v>167</v>
+        <v>135</v>
       </c>
       <c r="J393" s="1">
         <v>3010101</v>
@@ -13634,10 +13646,10 @@
         <v>40</v>
       </c>
       <c r="H394" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="I394" t="s">
-        <v>168</v>
+        <v>223</v>
       </c>
       <c r="J394" s="1">
         <v>3030101</v>
@@ -13666,10 +13678,10 @@
         <v>40</v>
       </c>
       <c r="H395" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="I395" t="s">
-        <v>167</v>
+        <v>135</v>
       </c>
       <c r="J395" s="1">
         <v>3010101</v>
@@ -13698,10 +13710,10 @@
         <v>40</v>
       </c>
       <c r="H396" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="I396" t="s">
-        <v>167</v>
+        <v>135</v>
       </c>
       <c r="J396" s="1">
         <v>3010101</v>
@@ -13730,10 +13742,10 @@
         <v>40</v>
       </c>
       <c r="H397" t="s">
-        <v>219</v>
+        <v>187</v>
       </c>
       <c r="I397" t="s">
-        <v>167</v>
+        <v>135</v>
       </c>
       <c r="J397" s="1">
         <v>3010101</v>
@@ -13762,10 +13774,10 @@
         <v>40</v>
       </c>
       <c r="H398" t="s">
-        <v>219</v>
+        <v>187</v>
       </c>
       <c r="I398" t="s">
-        <v>169</v>
+        <v>224</v>
       </c>
       <c r="J398" s="1">
         <v>3030101</v>
@@ -13794,10 +13806,10 @@
         <v>40</v>
       </c>
       <c r="H399" t="s">
-        <v>219</v>
+        <v>187</v>
       </c>
       <c r="I399" t="s">
-        <v>169</v>
+        <v>224</v>
       </c>
       <c r="J399" s="1">
         <v>3030101</v>
@@ -13826,10 +13838,10 @@
         <v>40</v>
       </c>
       <c r="H400" t="s">
-        <v>219</v>
+        <v>187</v>
       </c>
       <c r="I400" t="s">
-        <v>169</v>
+        <v>224</v>
       </c>
       <c r="J400" s="1">
         <v>3030101</v>
@@ -13858,10 +13870,10 @@
         <v>40</v>
       </c>
       <c r="H401" t="s">
-        <v>219</v>
+        <v>187</v>
       </c>
       <c r="I401" t="s">
-        <v>167</v>
+        <v>135</v>
       </c>
       <c r="J401" s="1">
         <v>3010101</v>
@@ -13890,10 +13902,10 @@
         <v>40</v>
       </c>
       <c r="H402" t="s">
-        <v>219</v>
+        <v>187</v>
       </c>
       <c r="I402" t="s">
-        <v>169</v>
+        <v>224</v>
       </c>
       <c r="J402" s="1">
         <v>3030101</v>
@@ -13922,10 +13934,10 @@
         <v>40</v>
       </c>
       <c r="H403" t="s">
-        <v>219</v>
+        <v>187</v>
       </c>
       <c r="I403" t="s">
-        <v>167</v>
+        <v>135</v>
       </c>
       <c r="J403" s="1">
         <v>3010101</v>
@@ -13954,10 +13966,10 @@
         <v>40</v>
       </c>
       <c r="H404" t="s">
-        <v>219</v>
+        <v>187</v>
       </c>
       <c r="I404" t="s">
-        <v>167</v>
+        <v>135</v>
       </c>
       <c r="J404" s="1">
         <v>3010101</v>
@@ -13986,10 +13998,10 @@
         <v>50</v>
       </c>
       <c r="H405" t="s">
-        <v>220</v>
+        <v>188</v>
       </c>
       <c r="I405" t="s">
-        <v>167</v>
+        <v>135</v>
       </c>
       <c r="J405" s="1">
         <v>3010101</v>
@@ -14018,10 +14030,10 @@
         <v>50</v>
       </c>
       <c r="H406" t="s">
-        <v>220</v>
+        <v>188</v>
       </c>
       <c r="I406" t="s">
-        <v>170</v>
+        <v>224</v>
       </c>
       <c r="J406" s="1">
         <v>3030101</v>
@@ -14050,10 +14062,10 @@
         <v>50</v>
       </c>
       <c r="H407" t="s">
-        <v>220</v>
+        <v>188</v>
       </c>
       <c r="I407" t="s">
-        <v>170</v>
+        <v>224</v>
       </c>
       <c r="J407" s="1">
         <v>3030101</v>
@@ -14082,10 +14094,10 @@
         <v>50</v>
       </c>
       <c r="H408" t="s">
-        <v>220</v>
+        <v>188</v>
       </c>
       <c r="I408" t="s">
-        <v>170</v>
+        <v>224</v>
       </c>
       <c r="J408" s="1">
         <v>3030101</v>
@@ -14114,10 +14126,10 @@
         <v>50</v>
       </c>
       <c r="H409" t="s">
-        <v>220</v>
+        <v>188</v>
       </c>
       <c r="I409" t="s">
-        <v>167</v>
+        <v>135</v>
       </c>
       <c r="J409" s="1">
         <v>3010101</v>
@@ -14146,10 +14158,10 @@
         <v>50</v>
       </c>
       <c r="H410" t="s">
-        <v>220</v>
+        <v>188</v>
       </c>
       <c r="I410" t="s">
-        <v>170</v>
+        <v>224</v>
       </c>
       <c r="J410" s="1">
         <v>3030101</v>
@@ -14178,10 +14190,10 @@
         <v>50</v>
       </c>
       <c r="H411" t="s">
-        <v>220</v>
+        <v>188</v>
       </c>
       <c r="I411" t="s">
-        <v>167</v>
+        <v>135</v>
       </c>
       <c r="J411" s="1">
         <v>3010101</v>
@@ -14210,10 +14222,10 @@
         <v>50</v>
       </c>
       <c r="H412" t="s">
-        <v>220</v>
+        <v>188</v>
       </c>
       <c r="I412" t="s">
-        <v>167</v>
+        <v>135</v>
       </c>
       <c r="J412" s="1">
         <v>3010101</v>

--- a/servers/maze_main_server/conf.d/data/maze_equip_pos_lv_v8【迷宫-装备-部位强化等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_equip_pos_lv_v8【迷宫-装备-部位强化等级】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{379AE942-4BD2-4E9B-B974-A304B3E31D9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7112F16E-635C-46FE-8B4C-0EBF573B3D49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1255" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1255" uniqueCount="275">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -141,9 +141,6 @@
     <t>3010101:17</t>
   </si>
   <si>
-    <t>3010101:35</t>
-  </si>
-  <si>
     <t>3010101:70</t>
   </si>
   <si>
@@ -312,379 +309,484 @@
     <t>3010101:4</t>
   </si>
   <si>
-    <t>3010101:25</t>
-  </si>
-  <si>
     <t>3010101:47</t>
   </si>
   <si>
-    <t>3010101:58</t>
-  </si>
-  <si>
-    <t>3010101:81</t>
-  </si>
-  <si>
-    <t>3010101:92</t>
-  </si>
-  <si>
     <t>3010101:150</t>
   </si>
   <si>
-    <t>3010101:160</t>
-  </si>
-  <si>
     <t>3010101:180</t>
   </si>
   <si>
-    <t>3010101:190</t>
-  </si>
-  <si>
     <t>3010101:210</t>
   </si>
   <si>
     <t>3010101:230</t>
   </si>
   <si>
-    <t>3010101:240</t>
+    <t>3010101:260</t>
+  </si>
+  <si>
+    <t>3010101:290</t>
+  </si>
+  <si>
+    <t>3010101:330</t>
+  </si>
+  <si>
+    <t>3010101:380</t>
+  </si>
+  <si>
+    <t>3010101:400</t>
+  </si>
+  <si>
+    <t>3010101:430</t>
+  </si>
+  <si>
+    <t>3010101:450</t>
+  </si>
+  <si>
+    <t>3010101:580</t>
+  </si>
+  <si>
+    <t>3010101:600</t>
+  </si>
+  <si>
+    <t>3030101:19000</t>
+  </si>
+  <si>
+    <t>3010101:650</t>
+  </si>
+  <si>
+    <t>3030101:22000</t>
+  </si>
+  <si>
+    <t>3010101:760</t>
+  </si>
+  <si>
+    <t>3010101:840</t>
+  </si>
+  <si>
+    <t>3010101:870</t>
+  </si>
+  <si>
+    <t>3010101:980</t>
+  </si>
+  <si>
+    <t>3010101:1000</t>
+  </si>
+  <si>
+    <t>3010101:1100</t>
+  </si>
+  <si>
+    <t>3030101:35000</t>
+  </si>
+  <si>
+    <t>9101:8</t>
+  </si>
+  <si>
+    <t>9101:20</t>
+  </si>
+  <si>
+    <t>9101:34</t>
+  </si>
+  <si>
+    <t>9101:51</t>
+  </si>
+  <si>
+    <t>9101:71</t>
+  </si>
+  <si>
+    <t>9101:94</t>
+  </si>
+  <si>
+    <t>9101:117</t>
+  </si>
+  <si>
+    <t>9101:140</t>
+  </si>
+  <si>
+    <t>9101:163</t>
+  </si>
+  <si>
+    <t>9101:185</t>
+  </si>
+  <si>
+    <t>9101:303</t>
+  </si>
+  <si>
+    <t>9101:334</t>
+  </si>
+  <si>
+    <t>9101:366</t>
+  </si>
+  <si>
+    <t>9101:397</t>
+  </si>
+  <si>
+    <t>9101:428</t>
+  </si>
+  <si>
+    <t>9101:460</t>
+  </si>
+  <si>
+    <t>9101:491</t>
+  </si>
+  <si>
+    <t>9101:523</t>
+  </si>
+  <si>
+    <t>9101:554</t>
+  </si>
+  <si>
+    <t>9101:585</t>
+  </si>
+  <si>
+    <t>9101:664</t>
+  </si>
+  <si>
+    <t>9101:698</t>
+  </si>
+  <si>
+    <t>9101:732</t>
+  </si>
+  <si>
+    <t>9101:766</t>
+  </si>
+  <si>
+    <t>9101:800</t>
+  </si>
+  <si>
+    <t>9101:835</t>
+  </si>
+  <si>
+    <t>9101:869</t>
+  </si>
+  <si>
+    <t>9101:903</t>
+  </si>
+  <si>
+    <t>9101:939</t>
+  </si>
+  <si>
+    <t>9101:976</t>
+  </si>
+  <si>
+    <t>9101:1074</t>
+  </si>
+  <si>
+    <t>9101:1117</t>
+  </si>
+  <si>
+    <t>9101:1161</t>
+  </si>
+  <si>
+    <t>9101:1208</t>
+  </si>
+  <si>
+    <t>9101:1256</t>
+  </si>
+  <si>
+    <t>9101:1306</t>
+  </si>
+  <si>
+    <t>9101:1359</t>
+  </si>
+  <si>
+    <t>9101:1413</t>
+  </si>
+  <si>
+    <t>9101:1470</t>
+  </si>
+  <si>
+    <t>9101:1529</t>
+  </si>
+  <si>
+    <t>9101:1681</t>
+  </si>
+  <si>
+    <t>9101:1748</t>
+  </si>
+  <si>
+    <t>9101:1818</t>
+  </si>
+  <si>
+    <t>9101:1891</t>
+  </si>
+  <si>
+    <t>9101:1966</t>
+  </si>
+  <si>
+    <t>9101:2044</t>
+  </si>
+  <si>
+    <t>9101:2126</t>
+  </si>
+  <si>
+    <t>9101:2211</t>
+  </si>
+  <si>
+    <t>9101:2299</t>
+  </si>
+  <si>
+    <t>9101:2392</t>
+  </si>
+  <si>
+    <t>3030101:3400</t>
+  </si>
+  <si>
+    <t>3030101:4500</t>
+  </si>
+  <si>
+    <t>3030101:16000</t>
+  </si>
+  <si>
+    <t>3030101:28000</t>
+  </si>
+  <si>
+    <t>3030101:40000</t>
+  </si>
+  <si>
+    <t>3030101:45000</t>
+  </si>
+  <si>
+    <t>3020101:0</t>
+  </si>
+  <si>
+    <t>3020101:2</t>
+  </si>
+  <si>
+    <t>3010101:26</t>
+  </si>
+  <si>
+    <t>3010101:36</t>
+  </si>
+  <si>
+    <t>3020101:7</t>
+  </si>
+  <si>
+    <t>3010101:59</t>
+  </si>
+  <si>
+    <t>3020101:14</t>
+  </si>
+  <si>
+    <t>3010101:82</t>
+  </si>
+  <si>
+    <t>3010101:93</t>
+  </si>
+  <si>
+    <t>3020101:19</t>
+  </si>
+  <si>
+    <t>3010101:170</t>
+  </si>
+  <si>
+    <t>3020101:33</t>
+  </si>
+  <si>
+    <t>3020101:37</t>
+  </si>
+  <si>
+    <t>3010101:200</t>
+  </si>
+  <si>
+    <t>3010101:250</t>
+  </si>
+  <si>
+    <t>3010101:280</t>
+  </si>
+  <si>
+    <t>3010101:350</t>
+  </si>
+  <si>
+    <t>3010101:370</t>
+  </si>
+  <si>
+    <t>3030101:18000</t>
+  </si>
+  <si>
+    <t>3020101:73</t>
+  </si>
+  <si>
+    <t>3020101:80</t>
+  </si>
+  <si>
+    <t>3010101:420</t>
+  </si>
+  <si>
+    <t>3030101:21000</t>
+  </si>
+  <si>
+    <t>3010101:470</t>
+  </si>
+  <si>
+    <t>3010101:490</t>
+  </si>
+  <si>
+    <t>3020101:98</t>
+  </si>
+  <si>
+    <t>3010101:540</t>
+  </si>
+  <si>
+    <t>3020101:110</t>
+  </si>
+  <si>
+    <t>3010101:560</t>
+  </si>
+  <si>
+    <t>3030101:27000</t>
+  </si>
+  <si>
+    <t>3020101:120</t>
+  </si>
+  <si>
+    <t>3010101:630</t>
+  </si>
+  <si>
+    <t>3020101:130</t>
+  </si>
+  <si>
+    <t>3010101:680</t>
+  </si>
+  <si>
+    <t>3020101:140</t>
+  </si>
+  <si>
+    <t>3010101:710</t>
+  </si>
+  <si>
+    <t>3030101:34000</t>
+  </si>
+  <si>
+    <t>3010101:740</t>
+  </si>
+  <si>
+    <t>3020101:150</t>
+  </si>
+  <si>
+    <t>3030101:37000</t>
+  </si>
+  <si>
+    <t>3020101:170</t>
+  </si>
+  <si>
+    <t>3030101:42000</t>
+  </si>
+  <si>
+    <t>3010101:910</t>
+  </si>
+  <si>
+    <t>3020101:180</t>
+  </si>
+  <si>
+    <t>3010101:950</t>
+  </si>
+  <si>
+    <t>3020101:190</t>
+  </si>
+  <si>
+    <t>3030101:47000</t>
+  </si>
+  <si>
+    <t>3020101:200</t>
+  </si>
+  <si>
+    <t>3020101:210</t>
+  </si>
+  <si>
+    <t>3020101:220</t>
+  </si>
+  <si>
+    <t>3020101:230</t>
+  </si>
+  <si>
+    <t>3010101:1200</t>
+  </si>
+  <si>
+    <t>3020101:240</t>
+  </si>
+  <si>
+    <t>3030101:400</t>
+  </si>
+  <si>
+    <t>3030101:980</t>
+  </si>
+  <si>
+    <t>3020101:4</t>
+  </si>
+  <si>
+    <t>3030101:1600</t>
+  </si>
+  <si>
+    <t>3030101:2500</t>
+  </si>
+  <si>
+    <t>3020101:10</t>
+  </si>
+  <si>
+    <t>3030101:5600</t>
+  </si>
+  <si>
+    <t>3020101:23</t>
+  </si>
+  <si>
+    <t>3030101:6700</t>
+  </si>
+  <si>
+    <t>3020101:28</t>
   </si>
   <si>
     <t>3030101:7800</t>
   </si>
   <si>
-    <t>3010101:260</t>
-  </si>
-  <si>
-    <t>3010101:270</t>
-  </si>
-  <si>
-    <t>3010101:290</t>
-  </si>
-  <si>
-    <t>3010101:330</t>
-  </si>
-  <si>
-    <t>3010101:340</t>
-  </si>
-  <si>
-    <t>3010101:360</t>
-  </si>
-  <si>
-    <t>3010101:380</t>
-  </si>
-  <si>
-    <t>3010101:400</t>
-  </si>
-  <si>
-    <t>3010101:410</t>
-  </si>
-  <si>
-    <t>3010101:430</t>
-  </si>
-  <si>
-    <t>3010101:450</t>
-  </si>
-  <si>
-    <t>3030101:14000</t>
-  </si>
-  <si>
-    <t>3010101:460</t>
-  </si>
-  <si>
-    <t>3010101:480</t>
-  </si>
-  <si>
-    <t>3010101:530</t>
-  </si>
-  <si>
-    <t>3030101:17000</t>
-  </si>
-  <si>
-    <t>3010101:550</t>
-  </si>
-  <si>
-    <t>3010101:580</t>
-  </si>
-  <si>
-    <t>3010101:600</t>
-  </si>
-  <si>
-    <t>3030101:19000</t>
-  </si>
-  <si>
-    <t>3010101:620</t>
-  </si>
-  <si>
-    <t>3030101:20000</t>
-  </si>
-  <si>
-    <t>3010101:650</t>
-  </si>
-  <si>
-    <t>3010101:670</t>
-  </si>
-  <si>
-    <t>3010101:700</t>
-  </si>
-  <si>
-    <t>3030101:22000</t>
-  </si>
-  <si>
-    <t>3010101:730</t>
-  </si>
-  <si>
-    <t>3030101:23000</t>
-  </si>
-  <si>
-    <t>3010101:760</t>
-  </si>
-  <si>
-    <t>3010101:840</t>
-  </si>
-  <si>
-    <t>3030101:26000</t>
-  </si>
-  <si>
-    <t>3010101:870</t>
-  </si>
-  <si>
-    <t>3010101:900</t>
-  </si>
-  <si>
-    <t>3010101:940</t>
-  </si>
-  <si>
-    <t>3010101:980</t>
-  </si>
-  <si>
-    <t>3030101:31000</t>
-  </si>
-  <si>
-    <t>3010101:1000</t>
-  </si>
-  <si>
-    <t>3010101:1100</t>
-  </si>
-  <si>
-    <t>3030101:35000</t>
-  </si>
-  <si>
-    <t>3030101:36000</t>
+    <t>3030101:8900</t>
+  </si>
+  <si>
+    <t>3030101:15000</t>
+  </si>
+  <si>
+    <t>3020101:61</t>
+  </si>
+  <si>
+    <t>3020101:67</t>
+  </si>
+  <si>
+    <t>3020101:86</t>
+  </si>
+  <si>
+    <t>3020101:92</t>
+  </si>
+  <si>
+    <t>3030101:24000</t>
+  </si>
+  <si>
+    <t>3030101:25000</t>
+  </si>
+  <si>
+    <t>3020101:100</t>
+  </si>
+  <si>
+    <t>3030101:32000</t>
   </si>
   <si>
     <t>3030101:38000</t>
   </si>
   <si>
-    <t>9101:8</t>
-  </si>
-  <si>
-    <t>9101:20</t>
-  </si>
-  <si>
-    <t>9101:34</t>
-  </si>
-  <si>
-    <t>9101:51</t>
-  </si>
-  <si>
-    <t>9101:71</t>
-  </si>
-  <si>
-    <t>9101:94</t>
-  </si>
-  <si>
-    <t>9101:117</t>
-  </si>
-  <si>
-    <t>9101:140</t>
-  </si>
-  <si>
-    <t>9101:163</t>
-  </si>
-  <si>
-    <t>9101:185</t>
-  </si>
-  <si>
-    <t>9101:303</t>
-  </si>
-  <si>
-    <t>9101:334</t>
-  </si>
-  <si>
-    <t>9101:366</t>
-  </si>
-  <si>
-    <t>9101:397</t>
-  </si>
-  <si>
-    <t>9101:428</t>
-  </si>
-  <si>
-    <t>9101:460</t>
-  </si>
-  <si>
-    <t>9101:491</t>
-  </si>
-  <si>
-    <t>9101:523</t>
-  </si>
-  <si>
-    <t>9101:554</t>
-  </si>
-  <si>
-    <t>9101:585</t>
-  </si>
-  <si>
-    <t>9101:664</t>
-  </si>
-  <si>
-    <t>9101:698</t>
-  </si>
-  <si>
-    <t>9101:732</t>
-  </si>
-  <si>
-    <t>9101:766</t>
-  </si>
-  <si>
-    <t>9101:800</t>
-  </si>
-  <si>
-    <t>9101:835</t>
-  </si>
-  <si>
-    <t>9101:869</t>
-  </si>
-  <si>
-    <t>9101:903</t>
-  </si>
-  <si>
-    <t>9101:939</t>
-  </si>
-  <si>
-    <t>9101:976</t>
-  </si>
-  <si>
-    <t>9101:1074</t>
-  </si>
-  <si>
-    <t>9101:1117</t>
-  </si>
-  <si>
-    <t>9101:1161</t>
-  </si>
-  <si>
-    <t>9101:1208</t>
-  </si>
-  <si>
-    <t>9101:1256</t>
-  </si>
-  <si>
-    <t>9101:1306</t>
-  </si>
-  <si>
-    <t>9101:1359</t>
-  </si>
-  <si>
-    <t>9101:1413</t>
-  </si>
-  <si>
-    <t>9101:1470</t>
-  </si>
-  <si>
-    <t>9101:1529</t>
-  </si>
-  <si>
-    <t>9101:1681</t>
-  </si>
-  <si>
-    <t>9101:1748</t>
-  </si>
-  <si>
-    <t>9101:1818</t>
-  </si>
-  <si>
-    <t>9101:1891</t>
-  </si>
-  <si>
-    <t>9101:1966</t>
-  </si>
-  <si>
-    <t>9101:2044</t>
-  </si>
-  <si>
-    <t>9101:2126</t>
-  </si>
-  <si>
-    <t>9101:2211</t>
-  </si>
-  <si>
-    <t>9101:2299</t>
-  </si>
-  <si>
-    <t>9101:2392</t>
-  </si>
-  <si>
-    <t>3030101:400</t>
-  </si>
-  <si>
-    <t>3030101:980</t>
-  </si>
-  <si>
-    <t>3030101:1600</t>
-  </si>
-  <si>
-    <t>3030101:2400</t>
-  </si>
-  <si>
-    <t>3030101:3400</t>
-  </si>
-  <si>
-    <t>3030101:4500</t>
-  </si>
-  <si>
-    <t>3030101:5600</t>
-  </si>
-  <si>
-    <t>3030101:6700</t>
-  </si>
-  <si>
-    <t>3030101:8900</t>
-  </si>
-  <si>
-    <t>3030101:16000</t>
-  </si>
-  <si>
-    <t>3030101:25000</t>
-  </si>
-  <si>
-    <t>3030101:28000</t>
-  </si>
-  <si>
-    <t>3030101:33000</t>
-  </si>
-  <si>
-    <t>3030101:40000</t>
-  </si>
-  <si>
-    <t>3030101:41000</t>
+    <t>3020101:160</t>
   </si>
   <si>
     <t>3030101:43000</t>
   </si>
   <si>
-    <t>3030101:45000</t>
-  </si>
-  <si>
-    <t>3030101:46000</t>
-  </si>
-  <si>
-    <t>3030101:51000</t>
-  </si>
-  <si>
-    <t>3030101:53000</t>
-  </si>
-  <si>
-    <t>3030101:55000</t>
+    <t>3030101:52000</t>
+  </si>
+  <si>
+    <t>3030101:54000</t>
+  </si>
+  <si>
+    <t>3030101:56000</t>
   </si>
   <si>
     <t>3030101:58000</t>
@@ -693,43 +795,91 @@
     <t>3030101:60000</t>
   </si>
   <si>
-    <t>3030101:62000</t>
+    <t>3020101:250</t>
+  </si>
+  <si>
+    <t>3030101:63000</t>
+  </si>
+  <si>
+    <t>3020101:260</t>
   </si>
   <si>
     <t>3030101:65000</t>
   </si>
   <si>
-    <t>3030101:67000</t>
-  </si>
-  <si>
-    <t>3030101:70000</t>
+    <t>3020101:270</t>
+  </si>
+  <si>
+    <t>3030101:68000</t>
+  </si>
+  <si>
+    <t>3020101:280</t>
+  </si>
+  <si>
+    <t>3030101:71000</t>
+  </si>
+  <si>
+    <t>3020101:290</t>
   </si>
   <si>
     <t>3030101:73000</t>
   </si>
   <si>
-    <t>3030101:80000</t>
-  </si>
-  <si>
-    <t>3030101:83000</t>
+    <t>3020101:310</t>
+  </si>
+  <si>
+    <t>3030101:81000</t>
+  </si>
+  <si>
+    <t>3020101:340</t>
+  </si>
+  <si>
+    <t>3030101:84000</t>
+  </si>
+  <si>
+    <t>3020101:350</t>
   </si>
   <si>
     <t>3030101:87000</t>
   </si>
   <si>
-    <t>3030101:90000</t>
+    <t>3020101:360</t>
+  </si>
+  <si>
+    <t>3030101:91000</t>
+  </si>
+  <si>
+    <t>3020101:380</t>
   </si>
   <si>
     <t>3030101:94000</t>
   </si>
   <si>
+    <t>3020101:390</t>
+  </si>
+  <si>
     <t>3030101:98000</t>
   </si>
   <si>
+    <t>3020101:410</t>
+  </si>
+  <si>
     <t>3030101:100000</t>
   </si>
   <si>
+    <t>3020101:430</t>
+  </si>
+  <si>
     <t>3030101:110000</t>
+  </si>
+  <si>
+    <t>3020101:440</t>
+  </si>
+  <si>
+    <t>3020101:460</t>
+  </si>
+  <si>
+    <t>3020101:480</t>
   </si>
 </sst>
 </file>
@@ -1192,16 +1342,16 @@
         <v>0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J5">
         <v>3010101</v>
@@ -1224,16 +1374,16 @@
         <v>0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J6">
         <v>3030101</v>
@@ -1256,19 +1406,19 @@
         <v>0</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I7" t="s">
-        <v>31</v>
+        <v>164</v>
       </c>
       <c r="J7">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -1288,16 +1438,16 @@
         <v>0</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J8">
         <v>3030101</v>
@@ -1320,16 +1470,16 @@
         <v>0</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J9">
         <v>3010101</v>
@@ -1352,19 +1502,19 @@
         <v>0</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I10" t="s">
-        <v>31</v>
+        <v>164</v>
       </c>
       <c r="J10">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
@@ -1384,16 +1534,16 @@
         <v>0</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J11">
         <v>3010101</v>
@@ -1416,16 +1566,16 @@
         <v>0</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J12">
         <v>3010101</v>
@@ -1448,16 +1598,16 @@
         <v>0</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>139</v>
+        <v>108</v>
       </c>
       <c r="I13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J13" s="1">
         <v>3010101</v>
@@ -1480,16 +1630,16 @@
         <v>0</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>139</v>
+        <v>108</v>
       </c>
       <c r="I14" t="s">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="J14" s="1">
         <v>3030101</v>
@@ -1512,19 +1662,19 @@
         <v>0</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>139</v>
+        <v>108</v>
       </c>
       <c r="I15" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="J15" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
@@ -1544,16 +1694,16 @@
         <v>0</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>139</v>
+        <v>108</v>
       </c>
       <c r="I16" t="s">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="J16" s="1">
         <v>3030101</v>
@@ -1576,16 +1726,16 @@
         <v>0</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G17">
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>139</v>
+        <v>108</v>
       </c>
       <c r="I17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J17" s="1">
         <v>3010101</v>
@@ -1608,19 +1758,19 @@
         <v>0</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>139</v>
+        <v>108</v>
       </c>
       <c r="I18" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="J18" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
@@ -1640,16 +1790,16 @@
         <v>0</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>139</v>
+        <v>108</v>
       </c>
       <c r="I19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J19" s="1">
         <v>3010101</v>
@@ -1672,16 +1822,16 @@
         <v>0</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>139</v>
+        <v>108</v>
       </c>
       <c r="I20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J20" s="1">
         <v>3010101</v>
@@ -1704,13 +1854,13 @@
         <v>0</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G21">
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>140</v>
+        <v>109</v>
       </c>
       <c r="I21" t="s">
         <v>26</v>
@@ -1736,16 +1886,16 @@
         <v>0</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G22">
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>140</v>
+        <v>109</v>
       </c>
       <c r="I22" t="s">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="J22" s="1">
         <v>3030101</v>
@@ -1768,19 +1918,19 @@
         <v>0</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G23">
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>140</v>
+        <v>109</v>
       </c>
       <c r="I23" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
       <c r="J23" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
@@ -1800,16 +1950,16 @@
         <v>0</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G24">
         <v>0</v>
       </c>
       <c r="H24" t="s">
-        <v>140</v>
+        <v>109</v>
       </c>
       <c r="I24" t="s">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="J24" s="1">
         <v>3030101</v>
@@ -1832,13 +1982,13 @@
         <v>0</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G25">
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>140</v>
+        <v>109</v>
       </c>
       <c r="I25" t="s">
         <v>26</v>
@@ -1864,19 +2014,19 @@
         <v>0</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G26">
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>140</v>
+        <v>109</v>
       </c>
       <c r="I26" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
       <c r="J26" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
@@ -1896,13 +2046,13 @@
         <v>0</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G27">
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>140</v>
+        <v>109</v>
       </c>
       <c r="I27" t="s">
         <v>26</v>
@@ -1928,13 +2078,13 @@
         <v>0</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G28">
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>140</v>
+        <v>109</v>
       </c>
       <c r="I28" t="s">
         <v>26</v>
@@ -1960,13 +2110,13 @@
         <v>0</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G29">
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="I29" t="s">
         <v>27</v>
@@ -1992,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G30">
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="I30" t="s">
-        <v>191</v>
+        <v>220</v>
       </c>
       <c r="J30" s="1">
         <v>3030101</v>
@@ -2024,19 +2174,19 @@
         <v>0</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G31">
         <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="I31" t="s">
-        <v>191</v>
+        <v>168</v>
       </c>
       <c r="J31" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
@@ -2056,16 +2206,16 @@
         <v>0</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G32">
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="I32" t="s">
-        <v>191</v>
+        <v>220</v>
       </c>
       <c r="J32" s="1">
         <v>3030101</v>
@@ -2088,13 +2238,13 @@
         <v>0</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G33">
         <v>0</v>
       </c>
       <c r="H33" t="s">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="I33" t="s">
         <v>27</v>
@@ -2120,19 +2270,19 @@
         <v>0</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G34">
         <v>0</v>
       </c>
       <c r="H34" t="s">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="I34" t="s">
-        <v>191</v>
+        <v>168</v>
       </c>
       <c r="J34" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
@@ -2152,13 +2302,13 @@
         <v>0</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G35">
         <v>0</v>
       </c>
       <c r="H35" t="s">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="I35" t="s">
         <v>27</v>
@@ -2184,13 +2334,13 @@
         <v>0</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G36">
         <v>0</v>
       </c>
       <c r="H36" t="s">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="I36" t="s">
         <v>27</v>
@@ -2216,16 +2366,16 @@
         <v>0</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G37">
         <v>0</v>
       </c>
       <c r="H37" t="s">
-        <v>142</v>
+        <v>111</v>
       </c>
       <c r="I37" t="s">
-        <v>85</v>
+        <v>166</v>
       </c>
       <c r="J37" s="1">
         <v>3010101</v>
@@ -2248,16 +2398,16 @@
         <v>0</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G38">
         <v>0</v>
       </c>
       <c r="H38" t="s">
-        <v>142</v>
+        <v>111</v>
       </c>
       <c r="I38" t="s">
-        <v>192</v>
+        <v>221</v>
       </c>
       <c r="J38" s="1">
         <v>3030101</v>
@@ -2280,19 +2430,19 @@
         <v>0</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G39">
         <v>0</v>
       </c>
       <c r="H39" t="s">
-        <v>142</v>
+        <v>111</v>
       </c>
       <c r="I39" t="s">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="J39" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
@@ -2312,16 +2462,16 @@
         <v>0</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G40">
         <v>0</v>
       </c>
       <c r="H40" t="s">
-        <v>142</v>
+        <v>111</v>
       </c>
       <c r="I40" t="s">
-        <v>192</v>
+        <v>221</v>
       </c>
       <c r="J40" s="1">
         <v>3030101</v>
@@ -2344,16 +2494,16 @@
         <v>0</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G41">
         <v>0</v>
       </c>
       <c r="H41" t="s">
-        <v>142</v>
+        <v>111</v>
       </c>
       <c r="I41" t="s">
-        <v>85</v>
+        <v>166</v>
       </c>
       <c r="J41" s="1">
         <v>3010101</v>
@@ -2376,19 +2526,19 @@
         <v>0</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G42">
         <v>0</v>
       </c>
       <c r="H42" t="s">
-        <v>142</v>
+        <v>111</v>
       </c>
       <c r="I42" t="s">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="J42" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
@@ -2408,16 +2558,16 @@
         <v>0</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G43">
         <v>0</v>
       </c>
       <c r="H43" t="s">
-        <v>142</v>
+        <v>111</v>
       </c>
       <c r="I43" t="s">
-        <v>85</v>
+        <v>166</v>
       </c>
       <c r="J43" s="1">
         <v>3010101</v>
@@ -2440,16 +2590,16 @@
         <v>0</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G44">
         <v>0</v>
       </c>
       <c r="H44" t="s">
-        <v>142</v>
+        <v>111</v>
       </c>
       <c r="I44" t="s">
-        <v>85</v>
+        <v>166</v>
       </c>
       <c r="J44" s="1">
         <v>3010101</v>
@@ -2472,16 +2622,16 @@
         <v>0</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G45">
         <v>0</v>
       </c>
       <c r="H45" t="s">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="I45" t="s">
-        <v>28</v>
+        <v>167</v>
       </c>
       <c r="J45" s="1">
         <v>3010101</v>
@@ -2504,16 +2654,16 @@
         <v>0</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G46">
         <v>0</v>
       </c>
       <c r="H46" t="s">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="I46" t="s">
-        <v>193</v>
+        <v>158</v>
       </c>
       <c r="J46" s="1">
         <v>3030101</v>
@@ -2536,19 +2686,19 @@
         <v>0</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G47">
         <v>0</v>
       </c>
       <c r="H47" t="s">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="I47" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="J47" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
@@ -2568,16 +2718,16 @@
         <v>0</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G48">
         <v>0</v>
       </c>
       <c r="H48" t="s">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="I48" t="s">
-        <v>193</v>
+        <v>158</v>
       </c>
       <c r="J48" s="1">
         <v>3030101</v>
@@ -2600,16 +2750,16 @@
         <v>0</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G49">
         <v>0</v>
       </c>
       <c r="H49" t="s">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="I49" t="s">
-        <v>28</v>
+        <v>167</v>
       </c>
       <c r="J49" s="1">
         <v>3010101</v>
@@ -2632,19 +2782,19 @@
         <v>0</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G50">
         <v>0</v>
       </c>
       <c r="H50" t="s">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="I50" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="J50" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.2">
@@ -2664,16 +2814,16 @@
         <v>0</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G51">
         <v>0</v>
       </c>
       <c r="H51" t="s">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="I51" t="s">
-        <v>28</v>
+        <v>167</v>
       </c>
       <c r="J51" s="1">
         <v>3010101</v>
@@ -2696,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G52">
         <v>0</v>
       </c>
       <c r="H52" t="s">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="I52" t="s">
-        <v>28</v>
+        <v>167</v>
       </c>
       <c r="J52" s="1">
         <v>3010101</v>
@@ -2728,16 +2878,16 @@
         <v>0</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G53">
         <v>0</v>
       </c>
       <c r="H53" t="s">
-        <v>144</v>
+        <v>113</v>
       </c>
       <c r="I53" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J53" s="1">
         <v>3010101</v>
@@ -2760,16 +2910,16 @@
         <v>0</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G54">
         <v>0</v>
       </c>
       <c r="H54" t="s">
-        <v>144</v>
+        <v>113</v>
       </c>
       <c r="I54" t="s">
-        <v>194</v>
+        <v>159</v>
       </c>
       <c r="J54" s="1">
         <v>3030101</v>
@@ -2792,19 +2942,19 @@
         <v>0</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G55">
         <v>0</v>
       </c>
       <c r="H55" t="s">
-        <v>144</v>
+        <v>113</v>
       </c>
       <c r="I55" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="J55" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.2">
@@ -2824,16 +2974,16 @@
         <v>0</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G56">
         <v>0</v>
       </c>
       <c r="H56" t="s">
-        <v>144</v>
+        <v>113</v>
       </c>
       <c r="I56" t="s">
-        <v>194</v>
+        <v>159</v>
       </c>
       <c r="J56" s="1">
         <v>3030101</v>
@@ -2856,16 +3006,16 @@
         <v>0</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G57">
         <v>0</v>
       </c>
       <c r="H57" t="s">
-        <v>144</v>
+        <v>113</v>
       </c>
       <c r="I57" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J57" s="1">
         <v>3010101</v>
@@ -2888,19 +3038,19 @@
         <v>0</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G58">
         <v>0</v>
       </c>
       <c r="H58" t="s">
-        <v>144</v>
+        <v>113</v>
       </c>
       <c r="I58" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="J58" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.2">
@@ -2920,16 +3070,16 @@
         <v>0</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G59">
         <v>0</v>
       </c>
       <c r="H59" t="s">
-        <v>144</v>
+        <v>113</v>
       </c>
       <c r="I59" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J59" s="1">
         <v>3010101</v>
@@ -2952,16 +3102,16 @@
         <v>0</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G60">
         <v>0</v>
       </c>
       <c r="H60" t="s">
-        <v>144</v>
+        <v>113</v>
       </c>
       <c r="I60" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J60" s="1">
         <v>3010101</v>
@@ -2984,16 +3134,16 @@
         <v>0</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G61">
         <v>0</v>
       </c>
       <c r="H61" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="I61" t="s">
-        <v>87</v>
+        <v>169</v>
       </c>
       <c r="J61" s="1">
         <v>3010101</v>
@@ -3016,16 +3166,16 @@
         <v>0</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G62">
         <v>0</v>
       </c>
       <c r="H62" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="I62" t="s">
-        <v>195</v>
+        <v>223</v>
       </c>
       <c r="J62" s="1">
         <v>3030101</v>
@@ -3048,19 +3198,19 @@
         <v>0</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G63">
         <v>0</v>
       </c>
       <c r="H63" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="I63" t="s">
-        <v>195</v>
+        <v>224</v>
       </c>
       <c r="J63" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.2">
@@ -3080,16 +3230,16 @@
         <v>0</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G64">
         <v>0</v>
       </c>
       <c r="H64" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="I64" t="s">
-        <v>195</v>
+        <v>223</v>
       </c>
       <c r="J64" s="1">
         <v>3030101</v>
@@ -3112,16 +3262,16 @@
         <v>0</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G65">
         <v>0</v>
       </c>
       <c r="H65" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="I65" t="s">
-        <v>87</v>
+        <v>169</v>
       </c>
       <c r="J65" s="1">
         <v>3010101</v>
@@ -3144,19 +3294,19 @@
         <v>0</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G66">
         <v>0</v>
       </c>
       <c r="H66" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="I66" t="s">
-        <v>195</v>
+        <v>224</v>
       </c>
       <c r="J66" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.2">
@@ -3176,16 +3326,16 @@
         <v>0</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G67">
         <v>0</v>
       </c>
       <c r="H67" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="I67" t="s">
-        <v>87</v>
+        <v>169</v>
       </c>
       <c r="J67" s="1">
         <v>3010101</v>
@@ -3208,16 +3358,16 @@
         <v>0</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G68">
         <v>0</v>
       </c>
       <c r="H68" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="I68" t="s">
-        <v>87</v>
+        <v>169</v>
       </c>
       <c r="J68" s="1">
         <v>3010101</v>
@@ -3240,16 +3390,16 @@
         <v>0</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G69">
         <v>0</v>
       </c>
       <c r="H69" t="s">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="I69" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J69" s="1">
         <v>3010101</v>
@@ -3272,16 +3422,16 @@
         <v>0</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G70">
         <v>0</v>
       </c>
       <c r="H70" t="s">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="I70" t="s">
-        <v>196</v>
+        <v>225</v>
       </c>
       <c r="J70" s="1">
         <v>3030101</v>
@@ -3304,19 +3454,19 @@
         <v>0</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G71">
         <v>0</v>
       </c>
       <c r="H71" t="s">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="I71" t="s">
-        <v>196</v>
+        <v>226</v>
       </c>
       <c r="J71" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.2">
@@ -3336,16 +3486,16 @@
         <v>0</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G72">
         <v>0</v>
       </c>
       <c r="H72" t="s">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="I72" t="s">
-        <v>196</v>
+        <v>225</v>
       </c>
       <c r="J72" s="1">
         <v>3030101</v>
@@ -3368,16 +3518,16 @@
         <v>0</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G73">
         <v>0</v>
       </c>
       <c r="H73" t="s">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="I73" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J73" s="1">
         <v>3010101</v>
@@ -3400,19 +3550,19 @@
         <v>0</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G74">
         <v>0</v>
       </c>
       <c r="H74" t="s">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="I74" t="s">
-        <v>196</v>
+        <v>226</v>
       </c>
       <c r="J74" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.2">
@@ -3432,16 +3582,16 @@
         <v>0</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G75">
         <v>0</v>
       </c>
       <c r="H75" t="s">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="I75" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J75" s="1">
         <v>3010101</v>
@@ -3464,16 +3614,16 @@
         <v>0</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G76">
         <v>0</v>
       </c>
       <c r="H76" t="s">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="I76" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J76" s="1">
         <v>3010101</v>
@@ -3496,16 +3646,16 @@
         <v>0</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G77">
         <v>0</v>
       </c>
       <c r="H77" t="s">
-        <v>147</v>
+        <v>116</v>
       </c>
       <c r="I77" t="s">
-        <v>88</v>
+        <v>171</v>
       </c>
       <c r="J77" s="1">
         <v>3010101</v>
@@ -3528,16 +3678,16 @@
         <v>0</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G78">
         <v>0</v>
       </c>
       <c r="H78" t="s">
-        <v>147</v>
+        <v>116</v>
       </c>
       <c r="I78" t="s">
-        <v>97</v>
+        <v>227</v>
       </c>
       <c r="J78" s="1">
         <v>3030101</v>
@@ -3560,19 +3710,19 @@
         <v>0</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G79">
         <v>0</v>
       </c>
       <c r="H79" t="s">
-        <v>147</v>
+        <v>116</v>
       </c>
       <c r="I79" t="s">
-        <v>97</v>
+        <v>175</v>
       </c>
       <c r="J79" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.2">
@@ -3592,16 +3742,16 @@
         <v>0</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G80">
         <v>0</v>
       </c>
       <c r="H80" t="s">
-        <v>147</v>
+        <v>116</v>
       </c>
       <c r="I80" t="s">
-        <v>97</v>
+        <v>227</v>
       </c>
       <c r="J80" s="1">
         <v>3030101</v>
@@ -3624,16 +3774,16 @@
         <v>0</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G81">
         <v>0</v>
       </c>
       <c r="H81" t="s">
-        <v>147</v>
+        <v>116</v>
       </c>
       <c r="I81" t="s">
-        <v>88</v>
+        <v>171</v>
       </c>
       <c r="J81" s="1">
         <v>3010101</v>
@@ -3656,19 +3806,19 @@
         <v>0</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G82">
         <v>0</v>
       </c>
       <c r="H82" t="s">
-        <v>147</v>
+        <v>116</v>
       </c>
       <c r="I82" t="s">
-        <v>97</v>
+        <v>175</v>
       </c>
       <c r="J82" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.2">
@@ -3688,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G83">
         <v>0</v>
       </c>
       <c r="H83" t="s">
-        <v>147</v>
+        <v>116</v>
       </c>
       <c r="I83" t="s">
-        <v>88</v>
+        <v>171</v>
       </c>
       <c r="J83" s="1">
         <v>3010101</v>
@@ -3720,16 +3870,16 @@
         <v>0</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G84">
         <v>0</v>
       </c>
       <c r="H84" t="s">
-        <v>147</v>
+        <v>116</v>
       </c>
       <c r="I84" t="s">
-        <v>88</v>
+        <v>171</v>
       </c>
       <c r="J84" s="1">
         <v>3010101</v>
@@ -3752,16 +3902,16 @@
         <v>10</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G85">
         <v>10</v>
       </c>
       <c r="H85" t="s">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="I85" t="s">
-        <v>89</v>
+        <v>172</v>
       </c>
       <c r="J85" s="1">
         <v>3010101</v>
@@ -3784,16 +3934,16 @@
         <v>10</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G86">
         <v>10</v>
       </c>
       <c r="H86" t="s">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="I86" t="s">
-        <v>197</v>
+        <v>228</v>
       </c>
       <c r="J86" s="1">
         <v>3030101</v>
@@ -3816,19 +3966,19 @@
         <v>10</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G87">
         <v>10</v>
       </c>
       <c r="H87" t="s">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="I87" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="J87" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.2">
@@ -3848,16 +3998,16 @@
         <v>10</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G88">
         <v>10</v>
       </c>
       <c r="H88" t="s">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="I88" t="s">
-        <v>197</v>
+        <v>228</v>
       </c>
       <c r="J88" s="1">
         <v>3030101</v>
@@ -3880,16 +4030,16 @@
         <v>10</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G89">
         <v>10</v>
       </c>
       <c r="H89" t="s">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="I89" t="s">
-        <v>89</v>
+        <v>172</v>
       </c>
       <c r="J89" s="1">
         <v>3010101</v>
@@ -3912,19 +4062,19 @@
         <v>10</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G90">
         <v>10</v>
       </c>
       <c r="H90" t="s">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="I90" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="J90" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.2">
@@ -3944,16 +4094,16 @@
         <v>10</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G91">
         <v>10</v>
       </c>
       <c r="H91" t="s">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="I91" t="s">
-        <v>89</v>
+        <v>172</v>
       </c>
       <c r="J91" s="1">
         <v>3010101</v>
@@ -3976,16 +4126,16 @@
         <v>10</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G92">
         <v>10</v>
       </c>
       <c r="H92" t="s">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="I92" t="s">
-        <v>89</v>
+        <v>172</v>
       </c>
       <c r="J92" s="1">
         <v>3010101</v>
@@ -4008,16 +4158,16 @@
         <v>10</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G93">
         <v>10</v>
       </c>
       <c r="H93" t="s">
-        <v>149</v>
+        <v>118</v>
       </c>
       <c r="I93" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="J93" s="1">
         <v>3010101</v>
@@ -4040,16 +4190,16 @@
         <v>10</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G94">
         <v>10</v>
       </c>
       <c r="H94" t="s">
-        <v>149</v>
+        <v>118</v>
       </c>
       <c r="I94" t="s">
-        <v>109</v>
+        <v>229</v>
       </c>
       <c r="J94" s="1">
         <v>3030101</v>
@@ -4072,19 +4222,19 @@
         <v>10</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G95">
         <v>10</v>
       </c>
       <c r="H95" t="s">
-        <v>149</v>
+        <v>118</v>
       </c>
       <c r="I95" t="s">
-        <v>109</v>
+        <v>230</v>
       </c>
       <c r="J95" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.2">
@@ -4104,16 +4254,16 @@
         <v>10</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G96">
         <v>10</v>
       </c>
       <c r="H96" t="s">
-        <v>149</v>
+        <v>118</v>
       </c>
       <c r="I96" t="s">
-        <v>109</v>
+        <v>229</v>
       </c>
       <c r="J96" s="1">
         <v>3030101</v>
@@ -4136,16 +4286,16 @@
         <v>10</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G97">
         <v>10</v>
       </c>
       <c r="H97" t="s">
-        <v>149</v>
+        <v>118</v>
       </c>
       <c r="I97" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="J97" s="1">
         <v>3010101</v>
@@ -4168,19 +4318,19 @@
         <v>10</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G98">
         <v>10</v>
       </c>
       <c r="H98" t="s">
-        <v>149</v>
+        <v>118</v>
       </c>
       <c r="I98" t="s">
-        <v>109</v>
+        <v>230</v>
       </c>
       <c r="J98" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.2">
@@ -4200,16 +4350,16 @@
         <v>10</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G99">
         <v>10</v>
       </c>
       <c r="H99" t="s">
-        <v>149</v>
+        <v>118</v>
       </c>
       <c r="I99" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="J99" s="1">
         <v>3010101</v>
@@ -4232,16 +4382,16 @@
         <v>10</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G100">
         <v>10</v>
       </c>
       <c r="H100" t="s">
-        <v>149</v>
+        <v>118</v>
       </c>
       <c r="I100" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="J100" s="1">
         <v>3010101</v>
@@ -4264,16 +4414,16 @@
         <v>10</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G101">
         <v>10</v>
       </c>
       <c r="H101" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="I101" t="s">
-        <v>91</v>
+        <v>174</v>
       </c>
       <c r="J101" s="1">
         <v>3010101</v>
@@ -4296,16 +4446,16 @@
         <v>10</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G102">
         <v>10</v>
       </c>
       <c r="H102" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="I102" t="s">
-        <v>198</v>
+        <v>160</v>
       </c>
       <c r="J102" s="1">
         <v>3030101</v>
@@ -4328,19 +4478,19 @@
         <v>10</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G103">
         <v>10</v>
       </c>
       <c r="H103" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="I103" t="s">
-        <v>198</v>
+        <v>231</v>
       </c>
       <c r="J103" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.2">
@@ -4360,16 +4510,16 @@
         <v>10</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G104">
         <v>10</v>
       </c>
       <c r="H104" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="I104" t="s">
-        <v>198</v>
+        <v>160</v>
       </c>
       <c r="J104" s="1">
         <v>3030101</v>
@@ -4392,16 +4542,16 @@
         <v>10</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G105">
         <v>10</v>
       </c>
       <c r="H105" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="I105" t="s">
-        <v>91</v>
+        <v>174</v>
       </c>
       <c r="J105" s="1">
         <v>3010101</v>
@@ -4424,19 +4574,19 @@
         <v>10</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G106">
         <v>10</v>
       </c>
       <c r="H106" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="I106" t="s">
-        <v>198</v>
+        <v>231</v>
       </c>
       <c r="J106" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.2">
@@ -4456,16 +4606,16 @@
         <v>10</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G107">
         <v>10</v>
       </c>
       <c r="H107" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="I107" t="s">
-        <v>91</v>
+        <v>174</v>
       </c>
       <c r="J107" s="1">
         <v>3010101</v>
@@ -4488,16 +4638,16 @@
         <v>10</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G108">
         <v>10</v>
       </c>
       <c r="H108" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="I108" t="s">
-        <v>91</v>
+        <v>174</v>
       </c>
       <c r="J108" s="1">
         <v>3010101</v>
@@ -4520,16 +4670,16 @@
         <v>10</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G109">
         <v>10</v>
       </c>
       <c r="H109" t="s">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="I109" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="J109" s="1">
         <v>3010101</v>
@@ -4552,16 +4702,16 @@
         <v>10</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G110">
         <v>10</v>
       </c>
       <c r="H110" t="s">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="I110" t="s">
-        <v>113</v>
+        <v>182</v>
       </c>
       <c r="J110" s="1">
         <v>3030101</v>
@@ -4584,19 +4734,19 @@
         <v>10</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G111">
         <v>10</v>
       </c>
       <c r="H111" t="s">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="I111" t="s">
-        <v>113</v>
+        <v>183</v>
       </c>
       <c r="J111" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.2">
@@ -4616,16 +4766,16 @@
         <v>10</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G112">
         <v>10</v>
       </c>
       <c r="H112" t="s">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="I112" t="s">
-        <v>113</v>
+        <v>182</v>
       </c>
       <c r="J112" s="1">
         <v>3030101</v>
@@ -4648,16 +4798,16 @@
         <v>10</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G113">
         <v>10</v>
       </c>
       <c r="H113" t="s">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="I113" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="J113" s="1">
         <v>3010101</v>
@@ -4680,19 +4830,19 @@
         <v>10</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G114">
         <v>10</v>
       </c>
       <c r="H114" t="s">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="I114" t="s">
-        <v>113</v>
+        <v>183</v>
       </c>
       <c r="J114" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.2">
@@ -4712,16 +4862,16 @@
         <v>10</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G115">
         <v>10</v>
       </c>
       <c r="H115" t="s">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="I115" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="J115" s="1">
         <v>3010101</v>
@@ -4744,16 +4894,16 @@
         <v>10</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G116">
         <v>10</v>
       </c>
       <c r="H116" t="s">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="I116" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="J116" s="1">
         <v>3010101</v>
@@ -4776,16 +4926,16 @@
         <v>10</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G117">
         <v>10</v>
       </c>
       <c r="H117" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
       <c r="I117" t="s">
-        <v>93</v>
+        <v>177</v>
       </c>
       <c r="J117" s="1">
         <v>3010101</v>
@@ -4808,16 +4958,16 @@
         <v>10</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G118">
         <v>10</v>
       </c>
       <c r="H118" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
       <c r="I118" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="J118" s="1">
         <v>3030101</v>
@@ -4840,19 +4990,19 @@
         <v>10</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G119">
         <v>10</v>
       </c>
       <c r="H119" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
       <c r="I119" t="s">
-        <v>117</v>
+        <v>184</v>
       </c>
       <c r="J119" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.2">
@@ -4872,16 +5022,16 @@
         <v>10</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G120">
         <v>10</v>
       </c>
       <c r="H120" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
       <c r="I120" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="J120" s="1">
         <v>3030101</v>
@@ -4904,16 +5054,16 @@
         <v>10</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G121">
         <v>10</v>
       </c>
       <c r="H121" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
       <c r="I121" t="s">
-        <v>93</v>
+        <v>177</v>
       </c>
       <c r="J121" s="1">
         <v>3010101</v>
@@ -4936,19 +5086,19 @@
         <v>10</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G122">
         <v>10</v>
       </c>
       <c r="H122" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
       <c r="I122" t="s">
-        <v>117</v>
+        <v>184</v>
       </c>
       <c r="J122" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.2">
@@ -4968,16 +5118,16 @@
         <v>10</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G123">
         <v>10</v>
       </c>
       <c r="H123" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
       <c r="I123" t="s">
-        <v>93</v>
+        <v>177</v>
       </c>
       <c r="J123" s="1">
         <v>3010101</v>
@@ -5000,16 +5150,16 @@
         <v>10</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G124">
         <v>10</v>
       </c>
       <c r="H124" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
       <c r="I124" t="s">
-        <v>93</v>
+        <v>177</v>
       </c>
       <c r="J124" s="1">
         <v>3010101</v>
@@ -5032,16 +5182,16 @@
         <v>10</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G125">
         <v>10</v>
       </c>
       <c r="H125" t="s">
-        <v>153</v>
+        <v>122</v>
       </c>
       <c r="I125" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="J125" s="1">
         <v>3010101</v>
@@ -5064,16 +5214,16 @@
         <v>10</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G126">
         <v>10</v>
       </c>
       <c r="H126" t="s">
-        <v>153</v>
+        <v>122</v>
       </c>
       <c r="I126" t="s">
-        <v>119</v>
+        <v>186</v>
       </c>
       <c r="J126" s="1">
         <v>3030101</v>
@@ -5096,19 +5246,19 @@
         <v>10</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G127">
         <v>10</v>
       </c>
       <c r="H127" t="s">
-        <v>153</v>
+        <v>122</v>
       </c>
       <c r="I127" t="s">
-        <v>119</v>
+        <v>232</v>
       </c>
       <c r="J127" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.2">
@@ -5128,16 +5278,16 @@
         <v>10</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G128">
         <v>10</v>
       </c>
       <c r="H128" t="s">
-        <v>153</v>
+        <v>122</v>
       </c>
       <c r="I128" t="s">
-        <v>119</v>
+        <v>186</v>
       </c>
       <c r="J128" s="1">
         <v>3030101</v>
@@ -5160,16 +5310,16 @@
         <v>10</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G129">
         <v>10</v>
       </c>
       <c r="H129" t="s">
-        <v>153</v>
+        <v>122</v>
       </c>
       <c r="I129" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="J129" s="1">
         <v>3010101</v>
@@ -5192,19 +5342,19 @@
         <v>10</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G130">
         <v>10</v>
       </c>
       <c r="H130" t="s">
-        <v>153</v>
+        <v>122</v>
       </c>
       <c r="I130" t="s">
-        <v>119</v>
+        <v>232</v>
       </c>
       <c r="J130" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.2">
@@ -5224,16 +5374,16 @@
         <v>10</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G131">
         <v>10</v>
       </c>
       <c r="H131" t="s">
-        <v>153</v>
+        <v>122</v>
       </c>
       <c r="I131" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="J131" s="1">
         <v>3010101</v>
@@ -5256,16 +5406,16 @@
         <v>10</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G132">
         <v>10</v>
       </c>
       <c r="H132" t="s">
-        <v>153</v>
+        <v>122</v>
       </c>
       <c r="I132" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="J132" s="1">
         <v>3010101</v>
@@ -5288,16 +5438,16 @@
         <v>10</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G133">
         <v>10</v>
       </c>
       <c r="H133" t="s">
-        <v>154</v>
+        <v>123</v>
       </c>
       <c r="I133" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="J133" s="1">
         <v>3010101</v>
@@ -5320,16 +5470,16 @@
         <v>10</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G134">
         <v>10</v>
       </c>
       <c r="H134" t="s">
-        <v>154</v>
+        <v>123</v>
       </c>
       <c r="I134" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="J134" s="1">
         <v>3030101</v>
@@ -5352,19 +5502,19 @@
         <v>10</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G135">
         <v>10</v>
       </c>
       <c r="H135" t="s">
-        <v>154</v>
+        <v>123</v>
       </c>
       <c r="I135" t="s">
-        <v>123</v>
+        <v>233</v>
       </c>
       <c r="J135" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.2">
@@ -5384,16 +5534,16 @@
         <v>10</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G136">
         <v>10</v>
       </c>
       <c r="H136" t="s">
-        <v>154</v>
+        <v>123</v>
       </c>
       <c r="I136" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="J136" s="1">
         <v>3030101</v>
@@ -5416,16 +5566,16 @@
         <v>10</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G137">
         <v>10</v>
       </c>
       <c r="H137" t="s">
-        <v>154</v>
+        <v>123</v>
       </c>
       <c r="I137" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="J137" s="1">
         <v>3010101</v>
@@ -5448,19 +5598,19 @@
         <v>10</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G138">
         <v>10</v>
       </c>
       <c r="H138" t="s">
-        <v>154</v>
+        <v>123</v>
       </c>
       <c r="I138" t="s">
-        <v>123</v>
+        <v>233</v>
       </c>
       <c r="J138" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.2">
@@ -5480,16 +5630,16 @@
         <v>10</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G139">
         <v>10</v>
       </c>
       <c r="H139" t="s">
-        <v>154</v>
+        <v>123</v>
       </c>
       <c r="I139" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="J139" s="1">
         <v>3010101</v>
@@ -5512,16 +5662,16 @@
         <v>10</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G140">
         <v>10</v>
       </c>
       <c r="H140" t="s">
-        <v>154</v>
+        <v>123</v>
       </c>
       <c r="I140" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="J140" s="1">
         <v>3010101</v>
@@ -5544,16 +5694,16 @@
         <v>10</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G141">
         <v>10</v>
       </c>
       <c r="H141" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="I141" t="s">
-        <v>96</v>
+        <v>178</v>
       </c>
       <c r="J141" s="1">
         <v>3010101</v>
@@ -5576,16 +5726,16 @@
         <v>10</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G142">
         <v>10</v>
       </c>
       <c r="H142" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="I142" t="s">
-        <v>125</v>
+        <v>234</v>
       </c>
       <c r="J142" s="1">
         <v>3030101</v>
@@ -5608,19 +5758,19 @@
         <v>10</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G143">
         <v>10</v>
       </c>
       <c r="H143" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="I143" t="s">
-        <v>125</v>
+        <v>189</v>
       </c>
       <c r="J143" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.2">
@@ -5640,16 +5790,16 @@
         <v>10</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G144">
         <v>10</v>
       </c>
       <c r="H144" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="I144" t="s">
-        <v>125</v>
+        <v>234</v>
       </c>
       <c r="J144" s="1">
         <v>3030101</v>
@@ -5672,16 +5822,16 @@
         <v>10</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G145">
         <v>10</v>
       </c>
       <c r="H145" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="I145" t="s">
-        <v>96</v>
+        <v>178</v>
       </c>
       <c r="J145" s="1">
         <v>3010101</v>
@@ -5704,19 +5854,19 @@
         <v>10</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G146">
         <v>10</v>
       </c>
       <c r="H146" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="I146" t="s">
-        <v>125</v>
+        <v>189</v>
       </c>
       <c r="J146" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.2">
@@ -5736,16 +5886,16 @@
         <v>10</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G147">
         <v>10</v>
       </c>
       <c r="H147" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="I147" t="s">
-        <v>96</v>
+        <v>178</v>
       </c>
       <c r="J147" s="1">
         <v>3010101</v>
@@ -5768,16 +5918,16 @@
         <v>10</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G148">
         <v>10</v>
       </c>
       <c r="H148" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="I148" t="s">
-        <v>96</v>
+        <v>178</v>
       </c>
       <c r="J148" s="1">
         <v>3010101</v>
@@ -5800,16 +5950,16 @@
         <v>10</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G149">
         <v>10</v>
       </c>
       <c r="H149" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="I149" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="J149" s="1">
         <v>3010101</v>
@@ -5832,16 +5982,16 @@
         <v>10</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G150">
         <v>10</v>
       </c>
       <c r="H150" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="I150" t="s">
-        <v>199</v>
+        <v>235</v>
       </c>
       <c r="J150" s="1">
         <v>3030101</v>
@@ -5864,19 +6014,19 @@
         <v>10</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G151">
         <v>10</v>
       </c>
       <c r="H151" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="I151" t="s">
-        <v>199</v>
+        <v>236</v>
       </c>
       <c r="J151" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.2">
@@ -5896,16 +6046,16 @@
         <v>10</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G152">
         <v>10</v>
       </c>
       <c r="H152" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="I152" t="s">
-        <v>199</v>
+        <v>235</v>
       </c>
       <c r="J152" s="1">
         <v>3030101</v>
@@ -5928,16 +6078,16 @@
         <v>10</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G153">
         <v>10</v>
       </c>
       <c r="H153" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="I153" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="J153" s="1">
         <v>3010101</v>
@@ -5960,19 +6110,19 @@
         <v>10</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G154">
         <v>10</v>
       </c>
       <c r="H154" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="I154" t="s">
-        <v>199</v>
+        <v>236</v>
       </c>
       <c r="J154" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.2">
@@ -5992,16 +6142,16 @@
         <v>10</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G155">
         <v>10</v>
       </c>
       <c r="H155" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="I155" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="J155" s="1">
         <v>3010101</v>
@@ -6024,16 +6174,16 @@
         <v>10</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G156">
         <v>10</v>
       </c>
       <c r="H156" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="I156" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="J156" s="1">
         <v>3010101</v>
@@ -6056,16 +6206,16 @@
         <v>10</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G157">
         <v>10</v>
       </c>
       <c r="H157" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
       <c r="I157" t="s">
-        <v>99</v>
+        <v>179</v>
       </c>
       <c r="J157" s="1">
         <v>3010101</v>
@@ -6088,16 +6238,16 @@
         <v>10</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G158">
         <v>10</v>
       </c>
       <c r="H158" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
       <c r="I158" t="s">
-        <v>128</v>
+        <v>193</v>
       </c>
       <c r="J158" s="1">
         <v>3030101</v>
@@ -6120,19 +6270,19 @@
         <v>10</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G159">
         <v>10</v>
       </c>
       <c r="H159" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
       <c r="I159" t="s">
-        <v>128</v>
+        <v>191</v>
       </c>
       <c r="J159" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.2">
@@ -6152,16 +6302,16 @@
         <v>10</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G160">
         <v>10</v>
       </c>
       <c r="H160" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
       <c r="I160" t="s">
-        <v>128</v>
+        <v>193</v>
       </c>
       <c r="J160" s="1">
         <v>3030101</v>
@@ -6184,16 +6334,16 @@
         <v>10</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G161">
         <v>10</v>
       </c>
       <c r="H161" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
       <c r="I161" t="s">
-        <v>99</v>
+        <v>179</v>
       </c>
       <c r="J161" s="1">
         <v>3010101</v>
@@ -6216,19 +6366,19 @@
         <v>10</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G162">
         <v>10</v>
       </c>
       <c r="H162" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
       <c r="I162" t="s">
-        <v>128</v>
+        <v>191</v>
       </c>
       <c r="J162" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.2">
@@ -6248,16 +6398,16 @@
         <v>10</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G163">
         <v>10</v>
       </c>
       <c r="H163" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
       <c r="I163" t="s">
-        <v>99</v>
+        <v>179</v>
       </c>
       <c r="J163" s="1">
         <v>3010101</v>
@@ -6280,16 +6430,16 @@
         <v>10</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G164">
         <v>10</v>
       </c>
       <c r="H164" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
       <c r="I164" t="s">
-        <v>99</v>
+        <v>179</v>
       </c>
       <c r="J164" s="1">
         <v>3010101</v>
@@ -6312,16 +6462,16 @@
         <v>20</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G165">
         <v>20</v>
       </c>
       <c r="H165" t="s">
-        <v>158</v>
+        <v>127</v>
       </c>
       <c r="I165" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J165" s="1">
         <v>3010101</v>
@@ -6344,16 +6494,16 @@
         <v>20</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G166">
         <v>20</v>
       </c>
       <c r="H166" t="s">
-        <v>158</v>
+        <v>127</v>
       </c>
       <c r="I166" t="s">
-        <v>200</v>
+        <v>161</v>
       </c>
       <c r="J166" s="1">
         <v>3030101</v>
@@ -6376,19 +6526,19 @@
         <v>20</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G167">
         <v>20</v>
       </c>
       <c r="H167" t="s">
-        <v>158</v>
+        <v>127</v>
       </c>
       <c r="I167" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="J167" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.2">
@@ -6408,16 +6558,16 @@
         <v>20</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G168">
         <v>20</v>
       </c>
       <c r="H168" t="s">
-        <v>158</v>
+        <v>127</v>
       </c>
       <c r="I168" t="s">
-        <v>200</v>
+        <v>161</v>
       </c>
       <c r="J168" s="1">
         <v>3030101</v>
@@ -6440,16 +6590,16 @@
         <v>20</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G169">
         <v>20</v>
       </c>
       <c r="H169" t="s">
-        <v>158</v>
+        <v>127</v>
       </c>
       <c r="I169" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J169" s="1">
         <v>3010101</v>
@@ -6472,19 +6622,19 @@
         <v>20</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G170">
         <v>20</v>
       </c>
       <c r="H170" t="s">
-        <v>158</v>
+        <v>127</v>
       </c>
       <c r="I170" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="J170" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.2">
@@ -6504,16 +6654,16 @@
         <v>20</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G171">
         <v>20</v>
       </c>
       <c r="H171" t="s">
-        <v>158</v>
+        <v>127</v>
       </c>
       <c r="I171" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J171" s="1">
         <v>3010101</v>
@@ -6536,16 +6686,16 @@
         <v>20</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G172">
         <v>20</v>
       </c>
       <c r="H172" t="s">
-        <v>158</v>
+        <v>127</v>
       </c>
       <c r="I172" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J172" s="1">
         <v>3010101</v>
@@ -6568,16 +6718,16 @@
         <v>20</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G173">
         <v>20</v>
       </c>
       <c r="H173" t="s">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="I173" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J173" s="1">
         <v>3010101</v>
@@ -6600,16 +6750,16 @@
         <v>20</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G174">
         <v>20</v>
       </c>
       <c r="H174" t="s">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="I174" t="s">
-        <v>133</v>
+        <v>237</v>
       </c>
       <c r="J174" s="1">
         <v>3030101</v>
@@ -6632,19 +6782,19 @@
         <v>20</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G175">
         <v>20</v>
       </c>
       <c r="H175" t="s">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="I175" t="s">
-        <v>133</v>
+        <v>196</v>
       </c>
       <c r="J175" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.2">
@@ -6664,16 +6814,16 @@
         <v>20</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G176">
         <v>20</v>
       </c>
       <c r="H176" t="s">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="I176" t="s">
-        <v>133</v>
+        <v>237</v>
       </c>
       <c r="J176" s="1">
         <v>3030101</v>
@@ -6696,16 +6846,16 @@
         <v>20</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G177">
         <v>20</v>
       </c>
       <c r="H177" t="s">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="I177" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J177" s="1">
         <v>3010101</v>
@@ -6728,19 +6878,19 @@
         <v>20</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G178">
         <v>20</v>
       </c>
       <c r="H178" t="s">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="I178" t="s">
-        <v>133</v>
+        <v>196</v>
       </c>
       <c r="J178" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.2">
@@ -6760,16 +6910,16 @@
         <v>20</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G179">
         <v>20</v>
       </c>
       <c r="H179" t="s">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="I179" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J179" s="1">
         <v>3010101</v>
@@ -6792,16 +6942,16 @@
         <v>20</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G180">
         <v>20</v>
       </c>
       <c r="H180" t="s">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="I180" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J180" s="1">
         <v>3010101</v>
@@ -6824,16 +6974,16 @@
         <v>20</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G181">
         <v>20</v>
       </c>
       <c r="H181" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="I181" t="s">
-        <v>102</v>
+        <v>180</v>
       </c>
       <c r="J181" s="1">
         <v>3010101</v>
@@ -6856,16 +7006,16 @@
         <v>20</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G182">
         <v>20</v>
       </c>
       <c r="H182" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="I182" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J182" s="1">
         <v>3030101</v>
@@ -6888,19 +7038,19 @@
         <v>20</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G183">
         <v>20</v>
       </c>
       <c r="H183" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="I183" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="J183" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.2">
@@ -6920,16 +7070,16 @@
         <v>20</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G184">
         <v>20</v>
       </c>
       <c r="H184" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="I184" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J184" s="1">
         <v>3030101</v>
@@ -6952,16 +7102,16 @@
         <v>20</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G185">
         <v>20</v>
       </c>
       <c r="H185" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="I185" t="s">
-        <v>102</v>
+        <v>180</v>
       </c>
       <c r="J185" s="1">
         <v>3010101</v>
@@ -6984,19 +7134,19 @@
         <v>20</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G186">
         <v>20</v>
       </c>
       <c r="H186" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="I186" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="J186" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.2">
@@ -7016,16 +7166,16 @@
         <v>20</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G187">
         <v>20</v>
       </c>
       <c r="H187" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="I187" t="s">
-        <v>102</v>
+        <v>180</v>
       </c>
       <c r="J187" s="1">
         <v>3010101</v>
@@ -7048,16 +7198,16 @@
         <v>20</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G188">
         <v>20</v>
       </c>
       <c r="H188" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="I188" t="s">
-        <v>102</v>
+        <v>180</v>
       </c>
       <c r="J188" s="1">
         <v>3010101</v>
@@ -7080,16 +7230,16 @@
         <v>20</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G189">
         <v>20</v>
       </c>
       <c r="H189" t="s">
-        <v>161</v>
+        <v>130</v>
       </c>
       <c r="I189" t="s">
-        <v>103</v>
+        <v>181</v>
       </c>
       <c r="J189" s="1">
         <v>3010101</v>
@@ -7112,16 +7262,16 @@
         <v>20</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G190">
         <v>20</v>
       </c>
       <c r="H190" t="s">
-        <v>161</v>
+        <v>130</v>
       </c>
       <c r="I190" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="J190" s="1">
         <v>3030101</v>
@@ -7144,19 +7294,19 @@
         <v>20</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G191">
         <v>20</v>
       </c>
       <c r="H191" t="s">
-        <v>161</v>
+        <v>130</v>
       </c>
       <c r="I191" t="s">
-        <v>136</v>
+        <v>202</v>
       </c>
       <c r="J191" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.2">
@@ -7176,16 +7326,16 @@
         <v>20</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G192">
         <v>20</v>
       </c>
       <c r="H192" t="s">
-        <v>161</v>
+        <v>130</v>
       </c>
       <c r="I192" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="J192" s="1">
         <v>3030101</v>
@@ -7208,16 +7358,16 @@
         <v>20</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G193">
         <v>20</v>
       </c>
       <c r="H193" t="s">
-        <v>161</v>
+        <v>130</v>
       </c>
       <c r="I193" t="s">
-        <v>103</v>
+        <v>181</v>
       </c>
       <c r="J193" s="1">
         <v>3010101</v>
@@ -7240,19 +7390,19 @@
         <v>20</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G194">
         <v>20</v>
       </c>
       <c r="H194" t="s">
-        <v>161</v>
+        <v>130</v>
       </c>
       <c r="I194" t="s">
-        <v>136</v>
+        <v>202</v>
       </c>
       <c r="J194" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.2">
@@ -7272,16 +7422,16 @@
         <v>20</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G195">
         <v>20</v>
       </c>
       <c r="H195" t="s">
-        <v>161</v>
+        <v>130</v>
       </c>
       <c r="I195" t="s">
-        <v>103</v>
+        <v>181</v>
       </c>
       <c r="J195" s="1">
         <v>3010101</v>
@@ -7304,16 +7454,16 @@
         <v>20</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G196">
         <v>20</v>
       </c>
       <c r="H196" t="s">
-        <v>161</v>
+        <v>130</v>
       </c>
       <c r="I196" t="s">
-        <v>103</v>
+        <v>181</v>
       </c>
       <c r="J196" s="1">
         <v>3010101</v>
@@ -7336,16 +7486,16 @@
         <v>20</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G197">
         <v>20</v>
       </c>
       <c r="H197" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="I197" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="J197" s="1">
         <v>3010101</v>
@@ -7368,16 +7518,16 @@
         <v>20</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G198">
         <v>20</v>
       </c>
       <c r="H198" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="I198" t="s">
-        <v>137</v>
+        <v>203</v>
       </c>
       <c r="J198" s="1">
         <v>3030101</v>
@@ -7400,19 +7550,19 @@
         <v>20</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G199">
         <v>20</v>
       </c>
       <c r="H199" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="I199" t="s">
-        <v>137</v>
+        <v>202</v>
       </c>
       <c r="J199" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.2">
@@ -7432,16 +7582,16 @@
         <v>20</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G200">
         <v>20</v>
       </c>
       <c r="H200" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="I200" t="s">
-        <v>137</v>
+        <v>203</v>
       </c>
       <c r="J200" s="1">
         <v>3030101</v>
@@ -7464,16 +7614,16 @@
         <v>20</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G201">
         <v>20</v>
       </c>
       <c r="H201" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="I201" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="J201" s="1">
         <v>3010101</v>
@@ -7496,19 +7646,19 @@
         <v>20</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G202">
         <v>20</v>
       </c>
       <c r="H202" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="I202" t="s">
-        <v>137</v>
+        <v>202</v>
       </c>
       <c r="J202" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.2">
@@ -7528,16 +7678,16 @@
         <v>20</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G203">
         <v>20</v>
       </c>
       <c r="H203" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="I203" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="J203" s="1">
         <v>3010101</v>
@@ -7560,16 +7710,16 @@
         <v>20</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G204">
         <v>20</v>
       </c>
       <c r="H204" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="I204" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="J204" s="1">
         <v>3010101</v>
@@ -7592,16 +7742,16 @@
         <v>20</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G205">
         <v>20</v>
       </c>
       <c r="H205" t="s">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="I205" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="J205" s="1">
         <v>3010101</v>
@@ -7624,16 +7774,16 @@
         <v>20</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G206">
         <v>20</v>
       </c>
       <c r="H206" t="s">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="I206" t="s">
-        <v>138</v>
+        <v>238</v>
       </c>
       <c r="J206" s="1">
         <v>3030101</v>
@@ -7656,19 +7806,19 @@
         <v>20</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G207">
         <v>20</v>
       </c>
       <c r="H207" t="s">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="I207" t="s">
-        <v>138</v>
+        <v>239</v>
       </c>
       <c r="J207" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.2">
@@ -7688,16 +7838,16 @@
         <v>20</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G208">
         <v>20</v>
       </c>
       <c r="H208" t="s">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="I208" t="s">
-        <v>138</v>
+        <v>238</v>
       </c>
       <c r="J208" s="1">
         <v>3030101</v>
@@ -7720,16 +7870,16 @@
         <v>20</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G209">
         <v>20</v>
       </c>
       <c r="H209" t="s">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="I209" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="J209" s="1">
         <v>3010101</v>
@@ -7752,19 +7902,19 @@
         <v>20</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G210">
         <v>20</v>
       </c>
       <c r="H210" t="s">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="I210" t="s">
-        <v>138</v>
+        <v>239</v>
       </c>
       <c r="J210" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.2">
@@ -7784,16 +7934,16 @@
         <v>20</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G211">
         <v>20</v>
       </c>
       <c r="H211" t="s">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="I211" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="J211" s="1">
         <v>3010101</v>
@@ -7816,16 +7966,16 @@
         <v>20</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G212">
         <v>20</v>
       </c>
       <c r="H212" t="s">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="I212" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="J212" s="1">
         <v>3010101</v>
@@ -7848,16 +7998,16 @@
         <v>20</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G213">
         <v>20</v>
       </c>
       <c r="H213" t="s">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="I213" t="s">
-        <v>106</v>
+        <v>185</v>
       </c>
       <c r="J213" s="1">
         <v>3010101</v>
@@ -7880,16 +8030,16 @@
         <v>20</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G214">
         <v>20</v>
       </c>
       <c r="H214" t="s">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="I214" t="s">
-        <v>202</v>
+        <v>162</v>
       </c>
       <c r="J214" s="1">
         <v>3030101</v>
@@ -7912,19 +8062,19 @@
         <v>20</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G215">
         <v>20</v>
       </c>
       <c r="H215" t="s">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="I215" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J215" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.2">
@@ -7944,16 +8094,16 @@
         <v>20</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G216">
         <v>20</v>
       </c>
       <c r="H216" t="s">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="I216" t="s">
-        <v>202</v>
+        <v>162</v>
       </c>
       <c r="J216" s="1">
         <v>3030101</v>
@@ -7976,16 +8126,16 @@
         <v>20</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G217">
         <v>20</v>
       </c>
       <c r="H217" t="s">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="I217" t="s">
-        <v>106</v>
+        <v>185</v>
       </c>
       <c r="J217" s="1">
         <v>3010101</v>
@@ -8008,19 +8158,19 @@
         <v>20</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G218">
         <v>20</v>
       </c>
       <c r="H218" t="s">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="I218" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J218" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.2">
@@ -8040,16 +8190,16 @@
         <v>20</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G219">
         <v>20</v>
       </c>
       <c r="H219" t="s">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="I219" t="s">
-        <v>106</v>
+        <v>185</v>
       </c>
       <c r="J219" s="1">
         <v>3010101</v>
@@ -8072,16 +8222,16 @@
         <v>20</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G220">
         <v>20</v>
       </c>
       <c r="H220" t="s">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="I220" t="s">
-        <v>106</v>
+        <v>185</v>
       </c>
       <c r="J220" s="1">
         <v>3010101</v>
@@ -8104,16 +8254,16 @@
         <v>20</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G221">
         <v>20</v>
       </c>
       <c r="H221" t="s">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="I221" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="J221" s="1">
         <v>3010101</v>
@@ -8136,16 +8286,16 @@
         <v>20</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G222">
         <v>20</v>
       </c>
       <c r="H222" t="s">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="I222" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="J222" s="1">
         <v>3030101</v>
@@ -8168,19 +8318,19 @@
         <v>20</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G223">
         <v>20</v>
       </c>
       <c r="H223" t="s">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="I223" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J223" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.2">
@@ -8200,16 +8350,16 @@
         <v>20</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G224">
         <v>20</v>
       </c>
       <c r="H224" t="s">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="I224" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="J224" s="1">
         <v>3030101</v>
@@ -8232,16 +8382,16 @@
         <v>20</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G225">
         <v>20</v>
       </c>
       <c r="H225" t="s">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="I225" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="J225" s="1">
         <v>3010101</v>
@@ -8264,19 +8414,19 @@
         <v>20</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G226">
         <v>20</v>
       </c>
       <c r="H226" t="s">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="I226" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J226" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.2">
@@ -8296,16 +8446,16 @@
         <v>20</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G227">
         <v>20</v>
       </c>
       <c r="H227" t="s">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="I227" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="J227" s="1">
         <v>3010101</v>
@@ -8328,16 +8478,16 @@
         <v>20</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G228">
         <v>20</v>
       </c>
       <c r="H228" t="s">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="I228" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="J228" s="1">
         <v>3010101</v>
@@ -8360,16 +8510,16 @@
         <v>20</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G229">
         <v>20</v>
       </c>
       <c r="H229" t="s">
-        <v>166</v>
+        <v>135</v>
       </c>
       <c r="I229" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="J229" s="1">
         <v>3010101</v>
@@ -8392,16 +8542,16 @@
         <v>20</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G230">
         <v>20</v>
       </c>
       <c r="H230" t="s">
-        <v>166</v>
+        <v>135</v>
       </c>
       <c r="I230" t="s">
-        <v>204</v>
+        <v>240</v>
       </c>
       <c r="J230" s="1">
         <v>3030101</v>
@@ -8424,19 +8574,19 @@
         <v>20</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G231">
         <v>20</v>
       </c>
       <c r="H231" t="s">
-        <v>166</v>
+        <v>135</v>
       </c>
       <c r="I231" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="J231" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.2">
@@ -8456,16 +8606,16 @@
         <v>20</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G232">
         <v>20</v>
       </c>
       <c r="H232" t="s">
-        <v>166</v>
+        <v>135</v>
       </c>
       <c r="I232" t="s">
-        <v>204</v>
+        <v>240</v>
       </c>
       <c r="J232" s="1">
         <v>3030101</v>
@@ -8488,16 +8638,16 @@
         <v>20</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G233">
         <v>20</v>
       </c>
       <c r="H233" t="s">
-        <v>166</v>
+        <v>135</v>
       </c>
       <c r="I233" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="J233" s="1">
         <v>3010101</v>
@@ -8520,19 +8670,19 @@
         <v>20</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G234">
         <v>20</v>
       </c>
       <c r="H234" t="s">
-        <v>166</v>
+        <v>135</v>
       </c>
       <c r="I234" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="J234" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.2">
@@ -8552,16 +8702,16 @@
         <v>20</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G235">
         <v>20</v>
       </c>
       <c r="H235" t="s">
-        <v>166</v>
+        <v>135</v>
       </c>
       <c r="I235" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="J235" s="1">
         <v>3010101</v>
@@ -8584,16 +8734,16 @@
         <v>20</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G236">
         <v>20</v>
       </c>
       <c r="H236" t="s">
-        <v>166</v>
+        <v>135</v>
       </c>
       <c r="I236" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="J236" s="1">
         <v>3010101</v>
@@ -8616,16 +8766,16 @@
         <v>20</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G237">
         <v>20</v>
       </c>
       <c r="H237" t="s">
-        <v>167</v>
+        <v>136</v>
       </c>
       <c r="I237" t="s">
-        <v>110</v>
+        <v>187</v>
       </c>
       <c r="J237" s="1">
         <v>3010101</v>
@@ -8648,16 +8798,16 @@
         <v>20</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G238">
         <v>20</v>
       </c>
       <c r="H238" t="s">
-        <v>167</v>
+        <v>136</v>
       </c>
       <c r="I238" t="s">
-        <v>205</v>
+        <v>163</v>
       </c>
       <c r="J238" s="1">
         <v>3030101</v>
@@ -8680,19 +8830,19 @@
         <v>20</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G239">
         <v>20</v>
       </c>
       <c r="H239" t="s">
-        <v>167</v>
+        <v>136</v>
       </c>
       <c r="I239" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="J239" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.2">
@@ -8712,16 +8862,16 @@
         <v>20</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G240">
         <v>20</v>
       </c>
       <c r="H240" t="s">
-        <v>167</v>
+        <v>136</v>
       </c>
       <c r="I240" t="s">
-        <v>205</v>
+        <v>163</v>
       </c>
       <c r="J240" s="1">
         <v>3030101</v>
@@ -8744,16 +8894,16 @@
         <v>20</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G241">
         <v>20</v>
       </c>
       <c r="H241" t="s">
-        <v>167</v>
+        <v>136</v>
       </c>
       <c r="I241" t="s">
-        <v>110</v>
+        <v>187</v>
       </c>
       <c r="J241" s="1">
         <v>3010101</v>
@@ -8776,19 +8926,19 @@
         <v>20</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G242">
         <v>20</v>
       </c>
       <c r="H242" t="s">
-        <v>167</v>
+        <v>136</v>
       </c>
       <c r="I242" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="J242" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.2">
@@ -8808,16 +8958,16 @@
         <v>20</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G243">
         <v>20</v>
       </c>
       <c r="H243" t="s">
-        <v>167</v>
+        <v>136</v>
       </c>
       <c r="I243" t="s">
-        <v>110</v>
+        <v>187</v>
       </c>
       <c r="J243" s="1">
         <v>3010101</v>
@@ -8840,16 +8990,16 @@
         <v>20</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G244">
         <v>20</v>
       </c>
       <c r="H244" t="s">
-        <v>167</v>
+        <v>136</v>
       </c>
       <c r="I244" t="s">
-        <v>110</v>
+        <v>187</v>
       </c>
       <c r="J244" s="1">
         <v>3010101</v>
@@ -8872,16 +9022,16 @@
         <v>30</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G245">
         <v>30</v>
       </c>
       <c r="H245" t="s">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="I245" t="s">
-        <v>111</v>
+        <v>188</v>
       </c>
       <c r="J245" s="1">
         <v>3010101</v>
@@ -8904,16 +9054,16 @@
         <v>30</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G246">
         <v>30</v>
       </c>
       <c r="H246" t="s">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="I246" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="J246" s="1">
         <v>3030101</v>
@@ -8936,19 +9086,19 @@
         <v>30</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G247">
         <v>30</v>
       </c>
       <c r="H247" t="s">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="I247" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="J247" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.2">
@@ -8968,16 +9118,16 @@
         <v>30</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G248">
         <v>30</v>
       </c>
       <c r="H248" t="s">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="I248" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="J248" s="1">
         <v>3030101</v>
@@ -9000,16 +9150,16 @@
         <v>30</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G249">
         <v>30</v>
       </c>
       <c r="H249" t="s">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="I249" t="s">
-        <v>111</v>
+        <v>188</v>
       </c>
       <c r="J249" s="1">
         <v>3010101</v>
@@ -9032,19 +9182,19 @@
         <v>30</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G250">
         <v>30</v>
       </c>
       <c r="H250" t="s">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="I250" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="J250" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.2">
@@ -9064,16 +9214,16 @@
         <v>30</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G251">
         <v>30</v>
       </c>
       <c r="H251" t="s">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="I251" t="s">
-        <v>111</v>
+        <v>188</v>
       </c>
       <c r="J251" s="1">
         <v>3010101</v>
@@ -9096,16 +9246,16 @@
         <v>30</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G252">
         <v>30</v>
       </c>
       <c r="H252" t="s">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="I252" t="s">
-        <v>111</v>
+        <v>188</v>
       </c>
       <c r="J252" s="1">
         <v>3010101</v>
@@ -9128,16 +9278,16 @@
         <v>30</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G253">
         <v>30</v>
       </c>
       <c r="H253" t="s">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="I253" t="s">
-        <v>112</v>
+        <v>190</v>
       </c>
       <c r="J253" s="1">
         <v>3010101</v>
@@ -9160,16 +9310,16 @@
         <v>30</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G254">
         <v>30</v>
       </c>
       <c r="H254" t="s">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="I254" t="s">
-        <v>207</v>
+        <v>241</v>
       </c>
       <c r="J254" s="1">
         <v>3030101</v>
@@ -9192,19 +9342,19 @@
         <v>30</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G255">
         <v>30</v>
       </c>
       <c r="H255" t="s">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="I255" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="J255" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.2">
@@ -9224,16 +9374,16 @@
         <v>30</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G256">
         <v>30</v>
       </c>
       <c r="H256" t="s">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="I256" t="s">
-        <v>207</v>
+        <v>241</v>
       </c>
       <c r="J256" s="1">
         <v>3030101</v>
@@ -9256,16 +9406,16 @@
         <v>30</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G257">
         <v>30</v>
       </c>
       <c r="H257" t="s">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="I257" t="s">
-        <v>112</v>
+        <v>190</v>
       </c>
       <c r="J257" s="1">
         <v>3010101</v>
@@ -9288,19 +9438,19 @@
         <v>30</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G258">
         <v>30</v>
       </c>
       <c r="H258" t="s">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="I258" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="J258" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.2">
@@ -9320,16 +9470,16 @@
         <v>30</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G259">
         <v>30</v>
       </c>
       <c r="H259" t="s">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="I259" t="s">
-        <v>112</v>
+        <v>190</v>
       </c>
       <c r="J259" s="1">
         <v>3010101</v>
@@ -9352,16 +9502,16 @@
         <v>30</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G260">
         <v>30</v>
       </c>
       <c r="H260" t="s">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="I260" t="s">
-        <v>112</v>
+        <v>190</v>
       </c>
       <c r="J260" s="1">
         <v>3010101</v>
@@ -9384,16 +9534,16 @@
         <v>30</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G261">
         <v>30</v>
       </c>
       <c r="H261" t="s">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="I261" t="s">
-        <v>114</v>
+        <v>192</v>
       </c>
       <c r="J261" s="1">
         <v>3010101</v>
@@ -9416,16 +9566,16 @@
         <v>30</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G262">
         <v>30</v>
       </c>
       <c r="H262" t="s">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="I262" t="s">
-        <v>208</v>
+        <v>242</v>
       </c>
       <c r="J262" s="1">
         <v>3030101</v>
@@ -9448,19 +9598,19 @@
         <v>30</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G263">
         <v>30</v>
       </c>
       <c r="H263" t="s">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="I263" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="J263" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.2">
@@ -9480,16 +9630,16 @@
         <v>30</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G264">
         <v>30</v>
       </c>
       <c r="H264" t="s">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="I264" t="s">
-        <v>208</v>
+        <v>242</v>
       </c>
       <c r="J264" s="1">
         <v>3030101</v>
@@ -9512,16 +9662,16 @@
         <v>30</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G265">
         <v>30</v>
       </c>
       <c r="H265" t="s">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="I265" t="s">
-        <v>114</v>
+        <v>192</v>
       </c>
       <c r="J265" s="1">
         <v>3010101</v>
@@ -9544,19 +9694,19 @@
         <v>30</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G266">
         <v>30</v>
       </c>
       <c r="H266" t="s">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="I266" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="J266" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.2">
@@ -9576,16 +9726,16 @@
         <v>30</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G267">
         <v>30</v>
       </c>
       <c r="H267" t="s">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="I267" t="s">
-        <v>114</v>
+        <v>192</v>
       </c>
       <c r="J267" s="1">
         <v>3010101</v>
@@ -9608,16 +9758,16 @@
         <v>30</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G268">
         <v>30</v>
       </c>
       <c r="H268" t="s">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="I268" t="s">
-        <v>114</v>
+        <v>192</v>
       </c>
       <c r="J268" s="1">
         <v>3010101</v>
@@ -9640,16 +9790,16 @@
         <v>30</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G269">
         <v>30</v>
       </c>
       <c r="H269" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="I269" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="J269" s="1">
         <v>3010101</v>
@@ -9672,16 +9822,16 @@
         <v>30</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G270">
         <v>30</v>
       </c>
       <c r="H270" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="I270" t="s">
-        <v>209</v>
+        <v>243</v>
       </c>
       <c r="J270" s="1">
         <v>3030101</v>
@@ -9704,19 +9854,19 @@
         <v>30</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G271">
         <v>30</v>
       </c>
       <c r="H271" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="I271" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="J271" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.2">
@@ -9736,16 +9886,16 @@
         <v>30</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G272">
         <v>30</v>
       </c>
       <c r="H272" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="I272" t="s">
-        <v>209</v>
+        <v>243</v>
       </c>
       <c r="J272" s="1">
         <v>3030101</v>
@@ -9768,16 +9918,16 @@
         <v>30</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G273">
         <v>30</v>
       </c>
       <c r="H273" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="I273" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="J273" s="1">
         <v>3010101</v>
@@ -9800,19 +9950,19 @@
         <v>30</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G274">
         <v>30</v>
       </c>
       <c r="H274" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="I274" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="J274" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.2">
@@ -9832,16 +9982,16 @@
         <v>30</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G275">
         <v>30</v>
       </c>
       <c r="H275" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="I275" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="J275" s="1">
         <v>3010101</v>
@@ -9864,16 +10014,16 @@
         <v>30</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G276">
         <v>30</v>
       </c>
       <c r="H276" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="I276" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="J276" s="1">
         <v>3010101</v>
@@ -9896,16 +10046,16 @@
         <v>30</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G277">
         <v>30</v>
       </c>
       <c r="H277" t="s">
-        <v>172</v>
+        <v>141</v>
       </c>
       <c r="I277" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="J277" s="1">
         <v>3010101</v>
@@ -9928,16 +10078,16 @@
         <v>30</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G278">
         <v>30</v>
       </c>
       <c r="H278" t="s">
-        <v>172</v>
+        <v>141</v>
       </c>
       <c r="I278" t="s">
-        <v>210</v>
+        <v>244</v>
       </c>
       <c r="J278" s="1">
         <v>3030101</v>
@@ -9960,19 +10110,19 @@
         <v>30</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G279">
         <v>30</v>
       </c>
       <c r="H279" t="s">
-        <v>172</v>
+        <v>141</v>
       </c>
       <c r="I279" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="J279" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.2">
@@ -9992,16 +10142,16 @@
         <v>30</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G280">
         <v>30</v>
       </c>
       <c r="H280" t="s">
-        <v>172</v>
+        <v>141</v>
       </c>
       <c r="I280" t="s">
-        <v>210</v>
+        <v>244</v>
       </c>
       <c r="J280" s="1">
         <v>3030101</v>
@@ -10024,16 +10174,16 @@
         <v>30</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G281">
         <v>30</v>
       </c>
       <c r="H281" t="s">
-        <v>172</v>
+        <v>141</v>
       </c>
       <c r="I281" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="J281" s="1">
         <v>3010101</v>
@@ -10056,19 +10206,19 @@
         <v>30</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G282">
         <v>30</v>
       </c>
       <c r="H282" t="s">
-        <v>172</v>
+        <v>141</v>
       </c>
       <c r="I282" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="J282" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.2">
@@ -10088,16 +10238,16 @@
         <v>30</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G283">
         <v>30</v>
       </c>
       <c r="H283" t="s">
-        <v>172</v>
+        <v>141</v>
       </c>
       <c r="I283" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="J283" s="1">
         <v>3010101</v>
@@ -10120,16 +10270,16 @@
         <v>30</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G284">
         <v>30</v>
       </c>
       <c r="H284" t="s">
-        <v>172</v>
+        <v>141</v>
       </c>
       <c r="I284" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="J284" s="1">
         <v>3010101</v>
@@ -10152,16 +10302,16 @@
         <v>30</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G285">
         <v>30</v>
       </c>
       <c r="H285" t="s">
-        <v>173</v>
+        <v>142</v>
       </c>
       <c r="I285" t="s">
-        <v>118</v>
+        <v>195</v>
       </c>
       <c r="J285" s="1">
         <v>3010101</v>
@@ -10184,16 +10334,16 @@
         <v>30</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G286">
         <v>30</v>
       </c>
       <c r="H286" t="s">
-        <v>173</v>
+        <v>142</v>
       </c>
       <c r="I286" t="s">
-        <v>211</v>
+        <v>245</v>
       </c>
       <c r="J286" s="1">
         <v>3030101</v>
@@ -10216,19 +10366,19 @@
         <v>30</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G287">
         <v>30</v>
       </c>
       <c r="H287" t="s">
-        <v>173</v>
+        <v>142</v>
       </c>
       <c r="I287" t="s">
-        <v>211</v>
+        <v>246</v>
       </c>
       <c r="J287" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.2">
@@ -10248,16 +10398,16 @@
         <v>30</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G288">
         <v>30</v>
       </c>
       <c r="H288" t="s">
-        <v>173</v>
+        <v>142</v>
       </c>
       <c r="I288" t="s">
-        <v>211</v>
+        <v>245</v>
       </c>
       <c r="J288" s="1">
         <v>3030101</v>
@@ -10280,16 +10430,16 @@
         <v>30</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G289">
         <v>30</v>
       </c>
       <c r="H289" t="s">
-        <v>173</v>
+        <v>142</v>
       </c>
       <c r="I289" t="s">
-        <v>118</v>
+        <v>195</v>
       </c>
       <c r="J289" s="1">
         <v>3010101</v>
@@ -10312,19 +10462,19 @@
         <v>30</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G290">
         <v>30</v>
       </c>
       <c r="H290" t="s">
-        <v>173</v>
+        <v>142</v>
       </c>
       <c r="I290" t="s">
-        <v>211</v>
+        <v>246</v>
       </c>
       <c r="J290" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.2">
@@ -10344,16 +10494,16 @@
         <v>30</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G291">
         <v>30</v>
       </c>
       <c r="H291" t="s">
-        <v>173</v>
+        <v>142</v>
       </c>
       <c r="I291" t="s">
-        <v>118</v>
+        <v>195</v>
       </c>
       <c r="J291" s="1">
         <v>3010101</v>
@@ -10376,16 +10526,16 @@
         <v>30</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G292">
         <v>30</v>
       </c>
       <c r="H292" t="s">
-        <v>173</v>
+        <v>142</v>
       </c>
       <c r="I292" t="s">
-        <v>118</v>
+        <v>195</v>
       </c>
       <c r="J292" s="1">
         <v>3010101</v>
@@ -10408,16 +10558,16 @@
         <v>30</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G293">
         <v>30</v>
       </c>
       <c r="H293" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="I293" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="J293" s="1">
         <v>3010101</v>
@@ -10440,16 +10590,16 @@
         <v>30</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G294">
         <v>30</v>
       </c>
       <c r="H294" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="I294" t="s">
-        <v>212</v>
+        <v>247</v>
       </c>
       <c r="J294" s="1">
         <v>3030101</v>
@@ -10472,19 +10622,19 @@
         <v>30</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G295">
         <v>30</v>
       </c>
       <c r="H295" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="I295" t="s">
-        <v>212</v>
+        <v>248</v>
       </c>
       <c r="J295" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.2">
@@ -10504,16 +10654,16 @@
         <v>30</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G296">
         <v>30</v>
       </c>
       <c r="H296" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="I296" t="s">
-        <v>212</v>
+        <v>247</v>
       </c>
       <c r="J296" s="1">
         <v>3030101</v>
@@ -10536,16 +10686,16 @@
         <v>30</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G297">
         <v>30</v>
       </c>
       <c r="H297" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="I297" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="J297" s="1">
         <v>3010101</v>
@@ -10568,19 +10718,19 @@
         <v>30</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G298">
         <v>30</v>
       </c>
       <c r="H298" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="I298" t="s">
-        <v>212</v>
+        <v>248</v>
       </c>
       <c r="J298" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.2">
@@ -10600,16 +10750,16 @@
         <v>30</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G299">
         <v>30</v>
       </c>
       <c r="H299" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="I299" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="J299" s="1">
         <v>3010101</v>
@@ -10632,16 +10782,16 @@
         <v>30</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G300">
         <v>30</v>
       </c>
       <c r="H300" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="I300" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="J300" s="1">
         <v>3010101</v>
@@ -10664,16 +10814,16 @@
         <v>30</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G301">
         <v>30</v>
       </c>
       <c r="H301" t="s">
-        <v>175</v>
+        <v>144</v>
       </c>
       <c r="I301" t="s">
-        <v>121</v>
+        <v>197</v>
       </c>
       <c r="J301" s="1">
         <v>3010101</v>
@@ -10696,16 +10846,16 @@
         <v>30</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G302">
         <v>30</v>
       </c>
       <c r="H302" t="s">
-        <v>175</v>
+        <v>144</v>
       </c>
       <c r="I302" t="s">
-        <v>213</v>
+        <v>249</v>
       </c>
       <c r="J302" s="1">
         <v>3030101</v>
@@ -10728,19 +10878,19 @@
         <v>30</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G303">
         <v>30</v>
       </c>
       <c r="H303" t="s">
-        <v>175</v>
+        <v>144</v>
       </c>
       <c r="I303" t="s">
-        <v>213</v>
+        <v>250</v>
       </c>
       <c r="J303" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.2">
@@ -10760,16 +10910,16 @@
         <v>30</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G304">
         <v>30</v>
       </c>
       <c r="H304" t="s">
-        <v>175</v>
+        <v>144</v>
       </c>
       <c r="I304" t="s">
-        <v>213</v>
+        <v>249</v>
       </c>
       <c r="J304" s="1">
         <v>3030101</v>
@@ -10792,16 +10942,16 @@
         <v>30</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G305">
         <v>30</v>
       </c>
       <c r="H305" t="s">
-        <v>175</v>
+        <v>144</v>
       </c>
       <c r="I305" t="s">
-        <v>121</v>
+        <v>197</v>
       </c>
       <c r="J305" s="1">
         <v>3010101</v>
@@ -10824,19 +10974,19 @@
         <v>30</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G306">
         <v>30</v>
       </c>
       <c r="H306" t="s">
-        <v>175</v>
+        <v>144</v>
       </c>
       <c r="I306" t="s">
-        <v>213</v>
+        <v>250</v>
       </c>
       <c r="J306" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="307" spans="1:10" x14ac:dyDescent="0.2">
@@ -10856,16 +11006,16 @@
         <v>30</v>
       </c>
       <c r="F307" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G307">
         <v>30</v>
       </c>
       <c r="H307" t="s">
-        <v>175</v>
+        <v>144</v>
       </c>
       <c r="I307" t="s">
-        <v>121</v>
+        <v>197</v>
       </c>
       <c r="J307" s="1">
         <v>3010101</v>
@@ -10888,16 +11038,16 @@
         <v>30</v>
       </c>
       <c r="F308" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G308">
         <v>30</v>
       </c>
       <c r="H308" t="s">
-        <v>175</v>
+        <v>144</v>
       </c>
       <c r="I308" t="s">
-        <v>121</v>
+        <v>197</v>
       </c>
       <c r="J308" s="1">
         <v>3010101</v>
@@ -10920,16 +11070,16 @@
         <v>30</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G309">
         <v>30</v>
       </c>
       <c r="H309" t="s">
-        <v>176</v>
+        <v>145</v>
       </c>
       <c r="I309" t="s">
-        <v>122</v>
+        <v>199</v>
       </c>
       <c r="J309" s="1">
         <v>3010101</v>
@@ -10952,16 +11102,16 @@
         <v>30</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G310">
         <v>30</v>
       </c>
       <c r="H310" t="s">
-        <v>176</v>
+        <v>145</v>
       </c>
       <c r="I310" t="s">
-        <v>214</v>
+        <v>251</v>
       </c>
       <c r="J310" s="1">
         <v>3030101</v>
@@ -10984,19 +11134,19 @@
         <v>30</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G311">
         <v>30</v>
       </c>
       <c r="H311" t="s">
-        <v>176</v>
+        <v>145</v>
       </c>
       <c r="I311" t="s">
-        <v>214</v>
+        <v>252</v>
       </c>
       <c r="J311" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="312" spans="1:10" x14ac:dyDescent="0.2">
@@ -11016,16 +11166,16 @@
         <v>30</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G312">
         <v>30</v>
       </c>
       <c r="H312" t="s">
-        <v>176</v>
+        <v>145</v>
       </c>
       <c r="I312" t="s">
-        <v>214</v>
+        <v>251</v>
       </c>
       <c r="J312" s="1">
         <v>3030101</v>
@@ -11048,16 +11198,16 @@
         <v>30</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G313">
         <v>30</v>
       </c>
       <c r="H313" t="s">
-        <v>176</v>
+        <v>145</v>
       </c>
       <c r="I313" t="s">
-        <v>122</v>
+        <v>199</v>
       </c>
       <c r="J313" s="1">
         <v>3010101</v>
@@ -11080,19 +11230,19 @@
         <v>30</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G314">
         <v>30</v>
       </c>
       <c r="H314" t="s">
-        <v>176</v>
+        <v>145</v>
       </c>
       <c r="I314" t="s">
-        <v>214</v>
+        <v>252</v>
       </c>
       <c r="J314" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="315" spans="1:10" x14ac:dyDescent="0.2">
@@ -11112,16 +11262,16 @@
         <v>30</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G315">
         <v>30</v>
       </c>
       <c r="H315" t="s">
-        <v>176</v>
+        <v>145</v>
       </c>
       <c r="I315" t="s">
-        <v>122</v>
+        <v>199</v>
       </c>
       <c r="J315" s="1">
         <v>3010101</v>
@@ -11144,16 +11294,16 @@
         <v>30</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G316">
         <v>30</v>
       </c>
       <c r="H316" t="s">
-        <v>176</v>
+        <v>145</v>
       </c>
       <c r="I316" t="s">
-        <v>122</v>
+        <v>199</v>
       </c>
       <c r="J316" s="1">
         <v>3010101</v>
@@ -11176,16 +11326,16 @@
         <v>30</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G317">
         <v>30</v>
       </c>
       <c r="H317" t="s">
-        <v>177</v>
+        <v>146</v>
       </c>
       <c r="I317" t="s">
-        <v>124</v>
+        <v>201</v>
       </c>
       <c r="J317" s="1">
         <v>3010101</v>
@@ -11208,16 +11358,16 @@
         <v>30</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G318">
         <v>30</v>
       </c>
       <c r="H318" t="s">
-        <v>177</v>
+        <v>146</v>
       </c>
       <c r="I318" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="J318" s="1">
         <v>3030101</v>
@@ -11240,19 +11390,19 @@
         <v>30</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G319">
         <v>30</v>
       </c>
       <c r="H319" t="s">
-        <v>177</v>
+        <v>146</v>
       </c>
       <c r="I319" t="s">
-        <v>215</v>
+        <v>254</v>
       </c>
       <c r="J319" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="320" spans="1:10" x14ac:dyDescent="0.2">
@@ -11272,16 +11422,16 @@
         <v>30</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G320">
         <v>30</v>
       </c>
       <c r="H320" t="s">
-        <v>177</v>
+        <v>146</v>
       </c>
       <c r="I320" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="J320" s="1">
         <v>3030101</v>
@@ -11304,16 +11454,16 @@
         <v>30</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G321">
         <v>30</v>
       </c>
       <c r="H321" t="s">
-        <v>177</v>
+        <v>146</v>
       </c>
       <c r="I321" t="s">
-        <v>124</v>
+        <v>201</v>
       </c>
       <c r="J321" s="1">
         <v>3010101</v>
@@ -11336,19 +11486,19 @@
         <v>30</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G322">
         <v>30</v>
       </c>
       <c r="H322" t="s">
-        <v>177</v>
+        <v>146</v>
       </c>
       <c r="I322" t="s">
-        <v>215</v>
+        <v>254</v>
       </c>
       <c r="J322" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="323" spans="1:10" x14ac:dyDescent="0.2">
@@ -11368,16 +11518,16 @@
         <v>30</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G323">
         <v>30</v>
       </c>
       <c r="H323" t="s">
-        <v>177</v>
+        <v>146</v>
       </c>
       <c r="I323" t="s">
-        <v>124</v>
+        <v>201</v>
       </c>
       <c r="J323" s="1">
         <v>3010101</v>
@@ -11400,16 +11550,16 @@
         <v>30</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G324">
         <v>30</v>
       </c>
       <c r="H324" t="s">
-        <v>177</v>
+        <v>146</v>
       </c>
       <c r="I324" t="s">
-        <v>124</v>
+        <v>201</v>
       </c>
       <c r="J324" s="1">
         <v>3010101</v>
@@ -11432,16 +11582,16 @@
         <v>40</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G325">
         <v>40</v>
       </c>
       <c r="H325" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
       <c r="I325" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="J325" s="1">
         <v>3010101</v>
@@ -11464,16 +11614,16 @@
         <v>40</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G326">
         <v>40</v>
       </c>
       <c r="H326" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
       <c r="I326" t="s">
-        <v>216</v>
+        <v>255</v>
       </c>
       <c r="J326" s="1">
         <v>3030101</v>
@@ -11496,19 +11646,19 @@
         <v>40</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G327">
         <v>40</v>
       </c>
       <c r="H327" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
       <c r="I327" t="s">
-        <v>216</v>
+        <v>256</v>
       </c>
       <c r="J327" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="328" spans="1:10" x14ac:dyDescent="0.2">
@@ -11528,16 +11678,16 @@
         <v>40</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G328">
         <v>40</v>
       </c>
       <c r="H328" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
       <c r="I328" t="s">
-        <v>216</v>
+        <v>255</v>
       </c>
       <c r="J328" s="1">
         <v>3030101</v>
@@ -11560,16 +11710,16 @@
         <v>40</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G329">
         <v>40</v>
       </c>
       <c r="H329" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
       <c r="I329" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="J329" s="1">
         <v>3010101</v>
@@ -11592,19 +11742,19 @@
         <v>40</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G330">
         <v>40</v>
       </c>
       <c r="H330" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
       <c r="I330" t="s">
-        <v>216</v>
+        <v>256</v>
       </c>
       <c r="J330" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.2">
@@ -11624,16 +11774,16 @@
         <v>40</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G331">
         <v>40</v>
       </c>
       <c r="H331" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
       <c r="I331" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="J331" s="1">
         <v>3010101</v>
@@ -11656,16 +11806,16 @@
         <v>40</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G332">
         <v>40</v>
       </c>
       <c r="H332" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
       <c r="I332" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="J332" s="1">
         <v>3010101</v>
@@ -11688,16 +11838,16 @@
         <v>40</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G333">
         <v>40</v>
       </c>
       <c r="H333" t="s">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="I333" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="J333" s="1">
         <v>3010101</v>
@@ -11720,16 +11870,16 @@
         <v>40</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G334">
         <v>40</v>
       </c>
       <c r="H334" t="s">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="I334" t="s">
-        <v>217</v>
+        <v>257</v>
       </c>
       <c r="J334" s="1">
         <v>3030101</v>
@@ -11752,19 +11902,19 @@
         <v>40</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G335">
         <v>40</v>
       </c>
       <c r="H335" t="s">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="I335" t="s">
-        <v>217</v>
+        <v>258</v>
       </c>
       <c r="J335" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.2">
@@ -11784,16 +11934,16 @@
         <v>40</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G336">
         <v>40</v>
       </c>
       <c r="H336" t="s">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="I336" t="s">
-        <v>217</v>
+        <v>257</v>
       </c>
       <c r="J336" s="1">
         <v>3030101</v>
@@ -11816,16 +11966,16 @@
         <v>40</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G337">
         <v>40</v>
       </c>
       <c r="H337" t="s">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="I337" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="J337" s="1">
         <v>3010101</v>
@@ -11848,19 +11998,19 @@
         <v>40</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G338">
         <v>40</v>
       </c>
       <c r="H338" t="s">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="I338" t="s">
-        <v>217</v>
+        <v>258</v>
       </c>
       <c r="J338" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.2">
@@ -11880,16 +12030,16 @@
         <v>40</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G339">
         <v>40</v>
       </c>
       <c r="H339" t="s">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="I339" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="J339" s="1">
         <v>3010101</v>
@@ -11912,16 +12062,16 @@
         <v>40</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G340">
         <v>40</v>
       </c>
       <c r="H340" t="s">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="I340" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="J340" s="1">
         <v>3010101</v>
@@ -11944,16 +12094,16 @@
         <v>40</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G341">
         <v>40</v>
       </c>
       <c r="H341" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="I341" t="s">
-        <v>129</v>
+        <v>103</v>
       </c>
       <c r="J341" s="1">
         <v>3010101</v>
@@ -11976,16 +12126,16 @@
         <v>40</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G342">
         <v>40</v>
       </c>
       <c r="H342" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="I342" t="s">
-        <v>218</v>
+        <v>259</v>
       </c>
       <c r="J342" s="1">
         <v>3030101</v>
@@ -12008,19 +12158,19 @@
         <v>40</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G343">
         <v>40</v>
       </c>
       <c r="H343" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="I343" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="J343" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.2">
@@ -12040,16 +12190,16 @@
         <v>40</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G344">
         <v>40</v>
       </c>
       <c r="H344" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="I344" t="s">
-        <v>218</v>
+        <v>259</v>
       </c>
       <c r="J344" s="1">
         <v>3030101</v>
@@ -12072,16 +12222,16 @@
         <v>40</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G345">
         <v>40</v>
       </c>
       <c r="H345" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="I345" t="s">
-        <v>129</v>
+        <v>103</v>
       </c>
       <c r="J345" s="1">
         <v>3010101</v>
@@ -12104,19 +12254,19 @@
         <v>40</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G346">
         <v>40</v>
       </c>
       <c r="H346" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="I346" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="J346" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.2">
@@ -12136,16 +12286,16 @@
         <v>40</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G347">
         <v>40</v>
       </c>
       <c r="H347" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="I347" t="s">
-        <v>129</v>
+        <v>103</v>
       </c>
       <c r="J347" s="1">
         <v>3010101</v>
@@ -12168,16 +12318,16 @@
         <v>40</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G348">
         <v>40</v>
       </c>
       <c r="H348" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="I348" t="s">
-        <v>129</v>
+        <v>103</v>
       </c>
       <c r="J348" s="1">
         <v>3010101</v>
@@ -12200,16 +12350,16 @@
         <v>40</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G349">
         <v>40</v>
       </c>
       <c r="H349" t="s">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="I349" t="s">
-        <v>130</v>
+        <v>206</v>
       </c>
       <c r="J349" s="1">
         <v>3010101</v>
@@ -12232,16 +12382,16 @@
         <v>40</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G350">
         <v>40</v>
       </c>
       <c r="H350" t="s">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="I350" t="s">
-        <v>219</v>
+        <v>261</v>
       </c>
       <c r="J350" s="1">
         <v>3030101</v>
@@ -12264,19 +12414,19 @@
         <v>40</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G351">
         <v>40</v>
       </c>
       <c r="H351" t="s">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="I351" t="s">
-        <v>219</v>
+        <v>262</v>
       </c>
       <c r="J351" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.2">
@@ -12296,16 +12446,16 @@
         <v>40</v>
       </c>
       <c r="F352" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G352">
         <v>40</v>
       </c>
       <c r="H352" t="s">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="I352" t="s">
-        <v>219</v>
+        <v>261</v>
       </c>
       <c r="J352" s="1">
         <v>3030101</v>
@@ -12328,16 +12478,16 @@
         <v>40</v>
       </c>
       <c r="F353" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G353">
         <v>40</v>
       </c>
       <c r="H353" t="s">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="I353" t="s">
-        <v>130</v>
+        <v>206</v>
       </c>
       <c r="J353" s="1">
         <v>3010101</v>
@@ -12360,19 +12510,19 @@
         <v>40</v>
       </c>
       <c r="F354" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G354">
         <v>40</v>
       </c>
       <c r="H354" t="s">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="I354" t="s">
-        <v>219</v>
+        <v>262</v>
       </c>
       <c r="J354" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="355" spans="1:10" x14ac:dyDescent="0.2">
@@ -12392,16 +12542,16 @@
         <v>40</v>
       </c>
       <c r="F355" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G355">
         <v>40</v>
       </c>
       <c r="H355" t="s">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="I355" t="s">
-        <v>130</v>
+        <v>206</v>
       </c>
       <c r="J355" s="1">
         <v>3010101</v>
@@ -12424,16 +12574,16 @@
         <v>40</v>
       </c>
       <c r="F356" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G356">
         <v>40</v>
       </c>
       <c r="H356" t="s">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="I356" t="s">
-        <v>130</v>
+        <v>206</v>
       </c>
       <c r="J356" s="1">
         <v>3010101</v>
@@ -12456,16 +12606,16 @@
         <v>40</v>
       </c>
       <c r="F357" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G357">
         <v>40</v>
       </c>
       <c r="H357" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="I357" t="s">
-        <v>131</v>
+        <v>208</v>
       </c>
       <c r="J357" s="1">
         <v>3010101</v>
@@ -12488,16 +12638,16 @@
         <v>40</v>
       </c>
       <c r="F358" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G358">
         <v>40</v>
       </c>
       <c r="H358" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="I358" t="s">
-        <v>220</v>
+        <v>263</v>
       </c>
       <c r="J358" s="1">
         <v>3030101</v>
@@ -12520,19 +12670,19 @@
         <v>40</v>
       </c>
       <c r="F359" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G359">
         <v>40</v>
       </c>
       <c r="H359" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="I359" t="s">
-        <v>220</v>
+        <v>264</v>
       </c>
       <c r="J359" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="360" spans="1:10" x14ac:dyDescent="0.2">
@@ -12552,16 +12702,16 @@
         <v>40</v>
       </c>
       <c r="F360" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G360">
         <v>40</v>
       </c>
       <c r="H360" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="I360" t="s">
-        <v>220</v>
+        <v>263</v>
       </c>
       <c r="J360" s="1">
         <v>3030101</v>
@@ -12584,16 +12734,16 @@
         <v>40</v>
       </c>
       <c r="F361" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G361">
         <v>40</v>
       </c>
       <c r="H361" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="I361" t="s">
-        <v>131</v>
+        <v>208</v>
       </c>
       <c r="J361" s="1">
         <v>3010101</v>
@@ -12616,19 +12766,19 @@
         <v>40</v>
       </c>
       <c r="F362" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G362">
         <v>40</v>
       </c>
       <c r="H362" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="I362" t="s">
-        <v>220</v>
+        <v>264</v>
       </c>
       <c r="J362" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="363" spans="1:10" x14ac:dyDescent="0.2">
@@ -12648,16 +12798,16 @@
         <v>40</v>
       </c>
       <c r="F363" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G363">
         <v>40</v>
       </c>
       <c r="H363" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="I363" t="s">
-        <v>131</v>
+        <v>208</v>
       </c>
       <c r="J363" s="1">
         <v>3010101</v>
@@ -12680,16 +12830,16 @@
         <v>40</v>
       </c>
       <c r="F364" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G364">
         <v>40</v>
       </c>
       <c r="H364" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="I364" t="s">
-        <v>131</v>
+        <v>208</v>
       </c>
       <c r="J364" s="1">
         <v>3010101</v>
@@ -12712,16 +12862,16 @@
         <v>40</v>
       </c>
       <c r="F365" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G365">
         <v>40</v>
       </c>
       <c r="H365" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="I365" t="s">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="J365" s="1">
         <v>3010101</v>
@@ -12744,16 +12894,16 @@
         <v>40</v>
       </c>
       <c r="F366" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G366">
         <v>40</v>
       </c>
       <c r="H366" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="I366" t="s">
-        <v>221</v>
+        <v>265</v>
       </c>
       <c r="J366" s="1">
         <v>3030101</v>
@@ -12776,19 +12926,19 @@
         <v>40</v>
       </c>
       <c r="F367" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G367">
         <v>40</v>
       </c>
       <c r="H367" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="I367" t="s">
-        <v>221</v>
+        <v>266</v>
       </c>
       <c r="J367" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="368" spans="1:10" x14ac:dyDescent="0.2">
@@ -12808,16 +12958,16 @@
         <v>40</v>
       </c>
       <c r="F368" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G368">
         <v>40</v>
       </c>
       <c r="H368" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="I368" t="s">
-        <v>221</v>
+        <v>265</v>
       </c>
       <c r="J368" s="1">
         <v>3030101</v>
@@ -12840,16 +12990,16 @@
         <v>40</v>
       </c>
       <c r="F369" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G369">
         <v>40</v>
       </c>
       <c r="H369" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="I369" t="s">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="J369" s="1">
         <v>3010101</v>
@@ -12872,19 +13022,19 @@
         <v>40</v>
       </c>
       <c r="F370" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G370">
         <v>40</v>
       </c>
       <c r="H370" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="I370" t="s">
-        <v>221</v>
+        <v>266</v>
       </c>
       <c r="J370" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="371" spans="1:10" x14ac:dyDescent="0.2">
@@ -12904,16 +13054,16 @@
         <v>40</v>
       </c>
       <c r="F371" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G371">
         <v>40</v>
       </c>
       <c r="H371" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="I371" t="s">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="J371" s="1">
         <v>3010101</v>
@@ -12936,16 +13086,16 @@
         <v>40</v>
       </c>
       <c r="F372" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G372">
         <v>40</v>
       </c>
       <c r="H372" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="I372" t="s">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="J372" s="1">
         <v>3010101</v>
@@ -12968,16 +13118,16 @@
         <v>40</v>
       </c>
       <c r="F373" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G373">
         <v>40</v>
       </c>
       <c r="H373" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="I373" t="s">
-        <v>134</v>
+        <v>105</v>
       </c>
       <c r="J373" s="1">
         <v>3010101</v>
@@ -13000,16 +13150,16 @@
         <v>40</v>
       </c>
       <c r="F374" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G374">
         <v>40</v>
       </c>
       <c r="H374" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="I374" t="s">
-        <v>222</v>
+        <v>267</v>
       </c>
       <c r="J374" s="1">
         <v>3030101</v>
@@ -13032,19 +13182,19 @@
         <v>40</v>
       </c>
       <c r="F375" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G375">
         <v>40</v>
       </c>
       <c r="H375" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="I375" t="s">
-        <v>222</v>
+        <v>268</v>
       </c>
       <c r="J375" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="376" spans="1:10" x14ac:dyDescent="0.2">
@@ -13064,16 +13214,16 @@
         <v>40</v>
       </c>
       <c r="F376" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G376">
         <v>40</v>
       </c>
       <c r="H376" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="I376" t="s">
-        <v>222</v>
+        <v>267</v>
       </c>
       <c r="J376" s="1">
         <v>3030101</v>
@@ -13096,16 +13246,16 @@
         <v>40</v>
       </c>
       <c r="F377" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G377">
         <v>40</v>
       </c>
       <c r="H377" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="I377" t="s">
-        <v>134</v>
+        <v>105</v>
       </c>
       <c r="J377" s="1">
         <v>3010101</v>
@@ -13128,19 +13278,19 @@
         <v>40</v>
       </c>
       <c r="F378" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G378">
         <v>40</v>
       </c>
       <c r="H378" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="I378" t="s">
-        <v>222</v>
+        <v>268</v>
       </c>
       <c r="J378" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="379" spans="1:10" x14ac:dyDescent="0.2">
@@ -13160,16 +13310,16 @@
         <v>40</v>
       </c>
       <c r="F379" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G379">
         <v>40</v>
       </c>
       <c r="H379" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="I379" t="s">
-        <v>134</v>
+        <v>105</v>
       </c>
       <c r="J379" s="1">
         <v>3010101</v>
@@ -13192,16 +13342,16 @@
         <v>40</v>
       </c>
       <c r="F380" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G380">
         <v>40</v>
       </c>
       <c r="H380" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="I380" t="s">
-        <v>134</v>
+        <v>105</v>
       </c>
       <c r="J380" s="1">
         <v>3010101</v>
@@ -13224,16 +13374,16 @@
         <v>40</v>
       </c>
       <c r="F381" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G381">
         <v>40</v>
       </c>
       <c r="H381" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="I381" t="s">
-        <v>134</v>
+        <v>106</v>
       </c>
       <c r="J381" s="1">
         <v>3010101</v>
@@ -13256,16 +13406,16 @@
         <v>40</v>
       </c>
       <c r="F382" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G382">
         <v>40</v>
       </c>
       <c r="H382" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="I382" t="s">
-        <v>223</v>
+        <v>269</v>
       </c>
       <c r="J382" s="1">
         <v>3030101</v>
@@ -13288,19 +13438,19 @@
         <v>40</v>
       </c>
       <c r="F383" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G383">
         <v>40</v>
       </c>
       <c r="H383" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="I383" t="s">
-        <v>223</v>
+        <v>270</v>
       </c>
       <c r="J383" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="384" spans="1:10" x14ac:dyDescent="0.2">
@@ -13320,16 +13470,16 @@
         <v>40</v>
       </c>
       <c r="F384" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G384">
         <v>40</v>
       </c>
       <c r="H384" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="I384" t="s">
-        <v>223</v>
+        <v>269</v>
       </c>
       <c r="J384" s="1">
         <v>3030101</v>
@@ -13352,16 +13502,16 @@
         <v>40</v>
       </c>
       <c r="F385" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G385">
         <v>40</v>
       </c>
       <c r="H385" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="I385" t="s">
-        <v>134</v>
+        <v>106</v>
       </c>
       <c r="J385" s="1">
         <v>3010101</v>
@@ -13384,19 +13534,19 @@
         <v>40</v>
       </c>
       <c r="F386" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G386">
         <v>40</v>
       </c>
       <c r="H386" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="I386" t="s">
-        <v>223</v>
+        <v>270</v>
       </c>
       <c r="J386" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="387" spans="1:10" x14ac:dyDescent="0.2">
@@ -13416,16 +13566,16 @@
         <v>40</v>
       </c>
       <c r="F387" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G387">
         <v>40</v>
       </c>
       <c r="H387" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="I387" t="s">
-        <v>134</v>
+        <v>106</v>
       </c>
       <c r="J387" s="1">
         <v>3010101</v>
@@ -13448,16 +13598,16 @@
         <v>40</v>
       </c>
       <c r="F388" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G388">
         <v>40</v>
       </c>
       <c r="H388" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="I388" t="s">
-        <v>134</v>
+        <v>106</v>
       </c>
       <c r="J388" s="1">
         <v>3010101</v>
@@ -13480,16 +13630,16 @@
         <v>40</v>
       </c>
       <c r="F389" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G389">
         <v>40</v>
       </c>
       <c r="H389" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="I389" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="J389" s="1">
         <v>3010101</v>
@@ -13512,16 +13662,16 @@
         <v>40</v>
       </c>
       <c r="F390" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G390">
         <v>40</v>
       </c>
       <c r="H390" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="I390" t="s">
-        <v>223</v>
+        <v>271</v>
       </c>
       <c r="J390" s="1">
         <v>3030101</v>
@@ -13544,19 +13694,19 @@
         <v>40</v>
       </c>
       <c r="F391" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G391">
         <v>40</v>
       </c>
       <c r="H391" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="I391" t="s">
-        <v>223</v>
+        <v>272</v>
       </c>
       <c r="J391" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="392" spans="1:10" x14ac:dyDescent="0.2">
@@ -13576,16 +13726,16 @@
         <v>40</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G392">
         <v>40</v>
       </c>
       <c r="H392" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="I392" t="s">
-        <v>223</v>
+        <v>271</v>
       </c>
       <c r="J392" s="1">
         <v>3030101</v>
@@ -13608,16 +13758,16 @@
         <v>40</v>
       </c>
       <c r="F393" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G393">
         <v>40</v>
       </c>
       <c r="H393" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="I393" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="J393" s="1">
         <v>3010101</v>
@@ -13640,19 +13790,19 @@
         <v>40</v>
       </c>
       <c r="F394" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G394">
         <v>40</v>
       </c>
       <c r="H394" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="I394" t="s">
-        <v>223</v>
+        <v>272</v>
       </c>
       <c r="J394" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="395" spans="1:10" x14ac:dyDescent="0.2">
@@ -13672,16 +13822,16 @@
         <v>40</v>
       </c>
       <c r="F395" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G395">
         <v>40</v>
       </c>
       <c r="H395" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="I395" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="J395" s="1">
         <v>3010101</v>
@@ -13704,16 +13854,16 @@
         <v>40</v>
       </c>
       <c r="F396" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G396">
         <v>40</v>
       </c>
       <c r="H396" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="I396" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="J396" s="1">
         <v>3010101</v>
@@ -13736,16 +13886,16 @@
         <v>40</v>
       </c>
       <c r="F397" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G397">
         <v>40</v>
       </c>
       <c r="H397" t="s">
-        <v>187</v>
+        <v>156</v>
       </c>
       <c r="I397" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="J397" s="1">
         <v>3010101</v>
@@ -13768,16 +13918,16 @@
         <v>40</v>
       </c>
       <c r="F398" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G398">
         <v>40</v>
       </c>
       <c r="H398" t="s">
-        <v>187</v>
+        <v>156</v>
       </c>
       <c r="I398" t="s">
-        <v>224</v>
+        <v>271</v>
       </c>
       <c r="J398" s="1">
         <v>3030101</v>
@@ -13800,19 +13950,19 @@
         <v>40</v>
       </c>
       <c r="F399" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G399">
         <v>40</v>
       </c>
       <c r="H399" t="s">
-        <v>187</v>
+        <v>156</v>
       </c>
       <c r="I399" t="s">
-        <v>224</v>
+        <v>273</v>
       </c>
       <c r="J399" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="400" spans="1:10" x14ac:dyDescent="0.2">
@@ -13832,16 +13982,16 @@
         <v>40</v>
       </c>
       <c r="F400" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G400">
         <v>40</v>
       </c>
       <c r="H400" t="s">
-        <v>187</v>
+        <v>156</v>
       </c>
       <c r="I400" t="s">
-        <v>224</v>
+        <v>271</v>
       </c>
       <c r="J400" s="1">
         <v>3030101</v>
@@ -13864,16 +14014,16 @@
         <v>40</v>
       </c>
       <c r="F401" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G401">
         <v>40</v>
       </c>
       <c r="H401" t="s">
-        <v>187</v>
+        <v>156</v>
       </c>
       <c r="I401" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="J401" s="1">
         <v>3010101</v>
@@ -13896,19 +14046,19 @@
         <v>40</v>
       </c>
       <c r="F402" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G402">
         <v>40</v>
       </c>
       <c r="H402" t="s">
-        <v>187</v>
+        <v>156</v>
       </c>
       <c r="I402" t="s">
-        <v>224</v>
+        <v>273</v>
       </c>
       <c r="J402" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="403" spans="1:10" x14ac:dyDescent="0.2">
@@ -13928,16 +14078,16 @@
         <v>40</v>
       </c>
       <c r="F403" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G403">
         <v>40</v>
       </c>
       <c r="H403" t="s">
-        <v>187</v>
+        <v>156</v>
       </c>
       <c r="I403" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="J403" s="1">
         <v>3010101</v>
@@ -13960,16 +14110,16 @@
         <v>40</v>
       </c>
       <c r="F404" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G404">
         <v>40</v>
       </c>
       <c r="H404" t="s">
-        <v>187</v>
+        <v>156</v>
       </c>
       <c r="I404" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="J404" s="1">
         <v>3010101</v>
@@ -13992,16 +14142,16 @@
         <v>50</v>
       </c>
       <c r="F405" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G405">
         <v>50</v>
       </c>
       <c r="H405" t="s">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="I405" t="s">
-        <v>135</v>
+        <v>215</v>
       </c>
       <c r="J405" s="1">
         <v>3010101</v>
@@ -14024,16 +14174,16 @@
         <v>50</v>
       </c>
       <c r="F406" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G406">
         <v>50</v>
       </c>
       <c r="H406" t="s">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="I406" t="s">
-        <v>224</v>
+        <v>271</v>
       </c>
       <c r="J406" s="1">
         <v>3030101</v>
@@ -14056,19 +14206,19 @@
         <v>50</v>
       </c>
       <c r="F407" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G407">
         <v>50</v>
       </c>
       <c r="H407" t="s">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="I407" t="s">
-        <v>224</v>
+        <v>274</v>
       </c>
       <c r="J407" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="408" spans="1:10" x14ac:dyDescent="0.2">
@@ -14088,16 +14238,16 @@
         <v>50</v>
       </c>
       <c r="F408" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G408">
         <v>50</v>
       </c>
       <c r="H408" t="s">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="I408" t="s">
-        <v>224</v>
+        <v>271</v>
       </c>
       <c r="J408" s="1">
         <v>3030101</v>
@@ -14120,16 +14270,16 @@
         <v>50</v>
       </c>
       <c r="F409" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G409">
         <v>50</v>
       </c>
       <c r="H409" t="s">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="I409" t="s">
-        <v>135</v>
+        <v>215</v>
       </c>
       <c r="J409" s="1">
         <v>3010101</v>
@@ -14152,19 +14302,19 @@
         <v>50</v>
       </c>
       <c r="F410" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G410">
         <v>50</v>
       </c>
       <c r="H410" t="s">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="I410" t="s">
-        <v>224</v>
+        <v>274</v>
       </c>
       <c r="J410" s="1">
-        <v>3030101</v>
+        <v>3020101</v>
       </c>
     </row>
     <row r="411" spans="1:10" x14ac:dyDescent="0.2">
@@ -14184,16 +14334,16 @@
         <v>50</v>
       </c>
       <c r="F411" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G411">
         <v>50</v>
       </c>
       <c r="H411" t="s">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="I411" t="s">
-        <v>135</v>
+        <v>215</v>
       </c>
       <c r="J411" s="1">
         <v>3010101</v>
@@ -14216,16 +14366,16 @@
         <v>50</v>
       </c>
       <c r="F412" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G412">
         <v>50</v>
       </c>
       <c r="H412" t="s">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="I412" t="s">
-        <v>135</v>
+        <v>215</v>
       </c>
       <c r="J412" s="1">
         <v>3010101</v>
